--- a/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
+++ b/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
@@ -14,8 +14,7 @@
     <sheet name="Acerca de" sheetId="12" state="hidden" r:id="rId4"/>
     <sheet name="Tablero" sheetId="15" r:id="rId12"/>
     <sheet name="Entregas Próximas" sheetId="16" r:id="rId13"/>
-    <sheet name="Guía" sheetId="17" r:id="rId14"/>
-    <sheet name="_Datos" sheetId="18" state="hidden" r:id="rId15"/>
+    <sheet name="_Datos" sheetId="18" state="hidden" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="hoy" localSheetId="2">TODAY()</definedName>
@@ -15922,13 +15921,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="11" max="11" width="9" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -16206,7 +16206,7 @@
       </c>
       <c r="D20" s="173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Completadas</t>
+          <t xml:space="preserve">Pendientes</t>
         </is>
       </c>
       <c r="E20" s="173" t="inlineStr">
@@ -16216,177 +16216,348 @@
       </c>
       <c r="F20" s="173" t="inlineStr">
         <is>
+          <t xml:space="preserve">Próx. a vencer</t>
+        </is>
+      </c>
+      <c r="G20" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Próxima entrega</t>
+        </is>
+      </c>
+      <c r="H20" s="173" t="inlineStr">
+        <is>
           <t xml:space="preserve">% Avance</t>
         </is>
       </c>
-      <c r="G20" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Avance</t>
-        </is>
-      </c>
-      <c r="H20" s="173"/>
-      <c r="I20" s="173"/>
     </row>
     <row r="21">
       <c r="B21" s="202">
-        <v>1</v>
+        <f>IF($K21="","",IF($K21=9999,"(Sin sprint)",$K21))</f>
       </c>
       <c r="C21" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B21)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B21))</f>
+        <f>IF($K21="","",COUNTIF('_Datos'!$N$7:$N$200,$K21))</f>
       </c>
       <c r="D21" s="202">
-        <f>IF($C21="","",COUNTIFS('_Datos'!$M$7:$M$200,$B21,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K21="","",COUNTIFS('_Datos'!$N$7:$N$200,$K21,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E21" s="202">
-        <f>IF($C21="","",COUNTIFS('_Datos'!$M$7:$M$200,$B21,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F21" s="205">
-        <f>IF($C21="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B21,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G21" s="205">
-        <f>IF($C21="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B21,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H21" s="202"/>
+        <f>IF($K21="","",COUNTIFS('_Datos'!$N$7:$N$200,$K21,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F21" s="202">
+        <f>IF($K21="","",COUNTIFS('_Datos'!$N$7:$N$200,$K21,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G21" s="204">
+        <f>IF($K21="","",IF($D21=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K21,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H21" s="205">
+        <f>IF($K21="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K21,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I21" s="202"/>
+      <c r="K21" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="22">
       <c r="B22" s="202">
-        <v>2</v>
+        <f>IF($K22="","",IF($K22=9999,"(Sin sprint)",$K22))</f>
       </c>
       <c r="C22" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B22)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B22))</f>
+        <f>IF($K22="","",COUNTIF('_Datos'!$N$7:$N$200,$K22))</f>
       </c>
       <c r="D22" s="202">
-        <f>IF($C22="","",COUNTIFS('_Datos'!$M$7:$M$200,$B22,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K22="","",COUNTIFS('_Datos'!$N$7:$N$200,$K22,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E22" s="202">
-        <f>IF($C22="","",COUNTIFS('_Datos'!$M$7:$M$200,$B22,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F22" s="205">
-        <f>IF($C22="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B22,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G22" s="205">
-        <f>IF($C22="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B22,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H22" s="202"/>
+        <f>IF($K22="","",COUNTIFS('_Datos'!$N$7:$N$200,$K22,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F22" s="202">
+        <f>IF($K22="","",COUNTIFS('_Datos'!$N$7:$N$200,$K22,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G22" s="204">
+        <f>IF($K22="","",IF($D22=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K22,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H22" s="205">
+        <f>IF($K22="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K22,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I22" s="202"/>
+      <c r="K22" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="23">
       <c r="B23" s="202">
-        <v>3</v>
+        <f>IF($K23="","",IF($K23=9999,"(Sin sprint)",$K23))</f>
       </c>
       <c r="C23" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B23)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B23))</f>
+        <f>IF($K23="","",COUNTIF('_Datos'!$N$7:$N$200,$K23))</f>
       </c>
       <c r="D23" s="202">
-        <f>IF($C23="","",COUNTIFS('_Datos'!$M$7:$M$200,$B23,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K23="","",COUNTIFS('_Datos'!$N$7:$N$200,$K23,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E23" s="202">
-        <f>IF($C23="","",COUNTIFS('_Datos'!$M$7:$M$200,$B23,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F23" s="205">
-        <f>IF($C23="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B23,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G23" s="205">
-        <f>IF($C23="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B23,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H23" s="202"/>
+        <f>IF($K23="","",COUNTIFS('_Datos'!$N$7:$N$200,$K23,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F23" s="202">
+        <f>IF($K23="","",COUNTIFS('_Datos'!$N$7:$N$200,$K23,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G23" s="204">
+        <f>IF($K23="","",IF($D23=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K23,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H23" s="205">
+        <f>IF($K23="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K23,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I23" s="202"/>
+      <c r="K23" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="24">
       <c r="B24" s="202">
-        <v>4</v>
+        <f>IF($K24="","",IF($K24=9999,"(Sin sprint)",$K24))</f>
       </c>
       <c r="C24" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B24)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B24))</f>
+        <f>IF($K24="","",COUNTIF('_Datos'!$N$7:$N$200,$K24))</f>
       </c>
       <c r="D24" s="202">
-        <f>IF($C24="","",COUNTIFS('_Datos'!$M$7:$M$200,$B24,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K24="","",COUNTIFS('_Datos'!$N$7:$N$200,$K24,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E24" s="202">
-        <f>IF($C24="","",COUNTIFS('_Datos'!$M$7:$M$200,$B24,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F24" s="205">
-        <f>IF($C24="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B24,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G24" s="205">
-        <f>IF($C24="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B24,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H24" s="202"/>
+        <f>IF($K24="","",COUNTIFS('_Datos'!$N$7:$N$200,$K24,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F24" s="202">
+        <f>IF($K24="","",COUNTIFS('_Datos'!$N$7:$N$200,$K24,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G24" s="204">
+        <f>IF($K24="","",IF($D24=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K24,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H24" s="205">
+        <f>IF($K24="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K24,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I24" s="202"/>
+      <c r="K24" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="202">
-        <v>5</v>
+        <f>IF($K25="","",IF($K25=9999,"(Sin sprint)",$K25))</f>
       </c>
       <c r="C25" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B25)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B25))</f>
+        <f>IF($K25="","",COUNTIF('_Datos'!$N$7:$N$200,$K25))</f>
       </c>
       <c r="D25" s="202">
-        <f>IF($C25="","",COUNTIFS('_Datos'!$M$7:$M$200,$B25,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K25="","",COUNTIFS('_Datos'!$N$7:$N$200,$K25,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E25" s="202">
-        <f>IF($C25="","",COUNTIFS('_Datos'!$M$7:$M$200,$B25,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F25" s="205">
-        <f>IF($C25="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B25,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G25" s="205">
-        <f>IF($C25="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B25,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H25" s="202"/>
+        <f>IF($K25="","",COUNTIFS('_Datos'!$N$7:$N$200,$K25,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F25" s="202">
+        <f>IF($K25="","",COUNTIFS('_Datos'!$N$7:$N$200,$K25,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G25" s="204">
+        <f>IF($K25="","",IF($D25=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K25,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H25" s="205">
+        <f>IF($K25="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K25,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I25" s="202"/>
+      <c r="K25" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="26">
       <c r="B26" s="202">
-        <v>6</v>
+        <f>IF($K26="","",IF($K26=9999,"(Sin sprint)",$K26))</f>
       </c>
       <c r="C26" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B26)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B26))</f>
+        <f>IF($K26="","",COUNTIF('_Datos'!$N$7:$N$200,$K26))</f>
       </c>
       <c r="D26" s="202">
-        <f>IF($C26="","",COUNTIFS('_Datos'!$M$7:$M$200,$B26,'_Datos'!$J$7:$J$200,"Completado"))</f>
+        <f>IF($K26="","",COUNTIFS('_Datos'!$N$7:$N$200,$K26,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
       </c>
       <c r="E26" s="202">
-        <f>IF($C26="","",COUNTIFS('_Datos'!$M$7:$M$200,$B26,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F26" s="205">
-        <f>IF($C26="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B26,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G26" s="205">
-        <f>IF($C26="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B26,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H26" s="202"/>
+        <f>IF($K26="","",COUNTIFS('_Datos'!$N$7:$N$200,$K26,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F26" s="202">
+        <f>IF($K26="","",COUNTIFS('_Datos'!$N$7:$N$200,$K26,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G26" s="204">
+        <f>IF($K26="","",IF($D26=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K26,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H26" s="205">
+        <f>IF($K26="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K26,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
       <c r="I26" s="202"/>
+      <c r="K26" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
     </row>
     <row r="27">
-      <c r="B27" s="202" t="inlineStr">
+      <c r="B27" s="202">
+        <f>IF($K27="","",IF($K27=9999,"(Sin sprint)",$K27))</f>
+      </c>
+      <c r="C27" s="202">
+        <f>IF($K27="","",COUNTIF('_Datos'!$N$7:$N$200,$K27))</f>
+      </c>
+      <c r="D27" s="202">
+        <f>IF($K27="","",COUNTIFS('_Datos'!$N$7:$N$200,$K27,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E27" s="202">
+        <f>IF($K27="","",COUNTIFS('_Datos'!$N$7:$N$200,$K27,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F27" s="202">
+        <f>IF($K27="","",COUNTIFS('_Datos'!$N$7:$N$200,$K27,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G27" s="204">
+        <f>IF($K27="","",IF($D27=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K27,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H27" s="205">
+        <f>IF($K27="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K27,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I27" s="202"/>
+      <c r="K27" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="202">
+        <f>IF($K28="","",IF($K28=9999,"(Sin sprint)",$K28))</f>
+      </c>
+      <c r="C28" s="202">
+        <f>IF($K28="","",COUNTIF('_Datos'!$N$7:$N$200,$K28))</f>
+      </c>
+      <c r="D28" s="202">
+        <f>IF($K28="","",COUNTIFS('_Datos'!$N$7:$N$200,$K28,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E28" s="202">
+        <f>IF($K28="","",COUNTIFS('_Datos'!$N$7:$N$200,$K28,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F28" s="202">
+        <f>IF($K28="","",COUNTIFS('_Datos'!$N$7:$N$200,$K28,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G28" s="204">
+        <f>IF($K28="","",IF($D28=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K28,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H28" s="205">
+        <f>IF($K28="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K28,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I28" s="202"/>
+      <c r="K28" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="202">
+        <f>IF($K29="","",IF($K29=9999,"(Sin sprint)",$K29))</f>
+      </c>
+      <c r="C29" s="202">
+        <f>IF($K29="","",COUNTIF('_Datos'!$N$7:$N$200,$K29))</f>
+      </c>
+      <c r="D29" s="202">
+        <f>IF($K29="","",COUNTIFS('_Datos'!$N$7:$N$200,$K29,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E29" s="202">
+        <f>IF($K29="","",COUNTIFS('_Datos'!$N$7:$N$200,$K29,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F29" s="202">
+        <f>IF($K29="","",COUNTIFS('_Datos'!$N$7:$N$200,$K29,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G29" s="204">
+        <f>IF($K29="","",IF($D29=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K29,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H29" s="205">
+        <f>IF($K29="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K29,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I29" s="202"/>
+      <c r="K29" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="202">
+        <f>IF($K30="","",IF($K30=9999,"(Sin sprint)",$K30))</f>
+      </c>
+      <c r="C30" s="202">
+        <f>IF($K30="","",COUNTIF('_Datos'!$N$7:$N$200,$K30))</f>
+      </c>
+      <c r="D30" s="202">
+        <f>IF($K30="","",COUNTIFS('_Datos'!$N$7:$N$200,$K30,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E30" s="202">
+        <f>IF($K30="","",COUNTIFS('_Datos'!$N$7:$N$200,$K30,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F30" s="202">
+        <f>IF($K30="","",COUNTIFS('_Datos'!$N$7:$N$200,$K30,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G30" s="204">
+        <f>IF($K30="","",IF($D30=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K30,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H30" s="205">
+        <f>IF($K30="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K30,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I30" s="202"/>
+      <c r="K30" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="202">
+        <f>IF($K31="","",IF($K31=9999,"(Sin sprint)",$K31))</f>
+      </c>
+      <c r="C31" s="202">
+        <f>IF($K31="","",COUNTIF('_Datos'!$N$7:$N$200,$K31))</f>
+      </c>
+      <c r="D31" s="202">
+        <f>IF($K31="","",COUNTIFS('_Datos'!$N$7:$N$200,$K31,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E31" s="202">
+        <f>IF($K31="","",COUNTIFS('_Datos'!$N$7:$N$200,$K31,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F31" s="202">
+        <f>IF($K31="","",COUNTIFS('_Datos'!$N$7:$N$200,$K31,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G31" s="204">
+        <f>IF($K31="","",IF($D31=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K31,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H31" s="205">
+        <f>IF($K31="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K31,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I31" s="202"/>
+      <c r="K31" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="202">
+        <f>IF($K32="","",IF($K32=9999,"(Sin sprint)",$K32))</f>
+      </c>
+      <c r="C32" s="202">
+        <f>IF($K32="","",COUNTIF('_Datos'!$N$7:$N$200,$K32))</f>
+      </c>
+      <c r="D32" s="202">
+        <f>IF($K32="","",COUNTIFS('_Datos'!$N$7:$N$200,$K32,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
+      </c>
+      <c r="E32" s="202">
+        <f>IF($K32="","",COUNTIFS('_Datos'!$N$7:$N$200,$K32,'_Datos'!$J$7:$J$200,"Vencido"))</f>
+      </c>
+      <c r="F32" s="202">
+        <f>IF($K32="","",COUNTIFS('_Datos'!$N$7:$N$200,$K32,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
+      </c>
+      <c r="G32" s="204">
+        <f>IF($K32="","",IF($D32=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$N$7:$N$200,$K32,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
+      </c>
+      <c r="H32" s="205">
+        <f>IF($K32="","",IFERROR(AVERAGEIF('_Datos'!$N$7:$N$200,$K32,'_Datos'!$I$7:$I$200),""))</f>
+      </c>
+      <c r="I32" s="202"/>
+      <c r="K32" s="200">
+        <f>IFERROR(SMALL('_Datos'!$Q$7:$Q$37,ROW()-21+1),"")</f>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="176" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Sin sprint)</t>
-        </is>
-      </c>
-      <c r="C27" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B27)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B27))</f>
-      </c>
-      <c r="D27" s="202">
-        <f>IF($C27="","",COUNTIFS('_Datos'!$M$7:$M$200,$B27,'_Datos'!$J$7:$J$200,"Completado"))</f>
-      </c>
-      <c r="E27" s="202">
-        <f>IF($C27="","",COUNTIFS('_Datos'!$M$7:$M$200,$B27,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F27" s="205">
-        <f>IF($C27="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B27,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="G27" s="205">
-        <f>IF($C27="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B27,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="H27" s="202"/>
-      <c r="I27" s="202"/>
-    </row>
-    <row r="29">
-      <c r="B29" s="176" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Las métricas se recalculan automáticamente a partir de la hoja Gantt. El % de avance por módulo se recalcula de forma independiente (no usa las celdas de promedio de las filas de fase).</t>
+          <t xml:space="preserve">Las métricas se recalculan solas desde la hoja Gantt. Los sprints aparecen automáticamente al usarse (el histórico se conserva). El % por módulo se recalcula de forma independiente (no usa las celdas de promedio de las filas de fase).</t>
         </is>
       </c>
     </row>
@@ -16406,7 +16577,7 @@
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B29:I29"/>
+    <mergeCell ref="B34:I34"/>
   </mergeCells>
   <conditionalFormatting sqref="H10:H16">
     <cfRule type="dataBar" priority="10">
@@ -16426,7 +16597,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G21:G27">
+  <conditionalFormatting sqref="H21:H32">
     <cfRule type="dataBar" priority="12">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -16440,9 +16611,9 @@
       <formula>$B10&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B21:G27">
+  <conditionalFormatting sqref="B21:H32">
     <cfRule type="expression" dxfId="21" priority="14">
-      <formula>$C21&lt;&gt;""</formula>
+      <formula>$B21&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -16451,13 +16622,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K156"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
-    <col min="4" max="4" width="50" customWidth="1"/>
+    <col min="4" max="4" width="52" customWidth="1"/>
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
@@ -16482,7 +16653,7 @@
     </row>
     <row r="2" ht="16" customHeight="1">
       <c r="B2" s="170">
-        <f>"Proyecto Datos Op. Complejas · IHSA S.A. · Seguimiento de entregas · Actualizado al "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
+        <f>"Proyecto Datos Op. Complejas · IHSA S.A. · Hoy "&amp;TEXT(TODAY(),"dd/mm/yyyy")&amp;"   |   Entregas: "&amp;COUNT('_Datos'!$H$7:$H$200)&amp;"   |   Vencidas: "&amp;COUNTIF('_Datos'!$J$7:$J$200,"Vencido")&amp;"   |   Próximas: "&amp;COUNTIF('_Datos'!$J$7:$J$200,"Próximo a vencer")&amp;"   |   Avance: "&amp;TEXT(IFERROR(AVERAGE('_Datos'!$I$7:$I$200),0),"0%")&amp;"   |   Próxima entrega: "&amp;IFERROR(TEXT(_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"),"dd/mm/yyyy"),"-")&amp;"   |   Resumen por sprint → hoja Tablero"</f>
       </c>
       <c r="C2" s="170"/>
       <c r="D2" s="170"/>
@@ -16492,346 +16663,446 @@
       <c r="H2" s="170"/>
       <c r="I2" s="170"/>
     </row>
-    <row r="4">
-      <c r="B4" s="175" t="inlineStr">
+    <row r="3">
+      <c r="B3" s="175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Referencia de estados:</t>
+          <t xml:space="preserve">Estados:</t>
         </is>
       </c>
-      <c r="C4" s="192" t="inlineStr">
+      <c r="C3" s="192" t="inlineStr">
         <is>
           <t xml:space="preserve">Vencido</t>
         </is>
       </c>
-      <c r="D4" s="193" t="inlineStr">
+      <c r="D3" s="193" t="inlineStr">
         <is>
           <t xml:space="preserve">Próximo a vencer</t>
         </is>
       </c>
-      <c r="E4" s="194" t="inlineStr">
+      <c r="E3" s="194" t="inlineStr">
         <is>
           <t xml:space="preserve">En curso (en plazo)</t>
         </is>
       </c>
-      <c r="F4" s="195" t="inlineStr">
+      <c r="F3" s="195" t="inlineStr">
         <is>
           <t xml:space="preserve">Completado</t>
         </is>
       </c>
-      <c r="G4" s="175" t="inlineStr">
+      <c r="G3" s="175" t="inlineStr">
         <is>
           <t xml:space="preserve">Umbral 'Próximo' (días):</t>
         </is>
       </c>
-      <c r="H4" s="175"/>
-      <c r="I4" s="191">
+      <c r="H3" s="175"/>
+      <c r="I3" s="191">
         <v>7</v>
       </c>
     </row>
+    <row r="5">
+      <c r="B5" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DETALLE DE ENTREGAS  (ordenado por Sprint y luego por Fecha de entrega)</t>
+        </is>
+      </c>
+      <c r="C5" s="172"/>
+      <c r="D5" s="172"/>
+      <c r="E5" s="172"/>
+      <c r="F5" s="172"/>
+      <c r="G5" s="172"/>
+      <c r="H5" s="172"/>
+      <c r="I5" s="172"/>
+    </row>
     <row r="6">
-      <c r="B6" s="172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">RESUMEN POR SPRINT</t>
-        </is>
-      </c>
-      <c r="C6" s="172"/>
-      <c r="D6" s="172"/>
-      <c r="E6" s="172"/>
-      <c r="F6" s="172"/>
-      <c r="G6" s="172"/>
-      <c r="H6" s="172"/>
-      <c r="I6" s="172"/>
-    </row>
-    <row r="7">
-      <c r="B7" s="173" t="inlineStr">
+      <c r="B6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Sprint</t>
         </is>
       </c>
-      <c r="C7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tareas</t>
-        </is>
-      </c>
-      <c r="D7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Pendientes</t>
-        </is>
-      </c>
-      <c r="E7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vencidas</t>
-        </is>
-      </c>
-      <c r="F7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Próx. a vencer</t>
-        </is>
-      </c>
-      <c r="G7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Próxima entrega</t>
-        </is>
-      </c>
-      <c r="H7" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">% Avance</t>
-        </is>
-      </c>
-      <c r="I7" s="173"/>
-    </row>
-    <row r="8">
-      <c r="B8" s="202">
-        <v>1</v>
-      </c>
-      <c r="C8" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B8)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B8))</f>
-      </c>
-      <c r="D8" s="202">
-        <f>IF($C8="","",COUNTIFS('_Datos'!$M$7:$M$200,$B8,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E8" s="202">
-        <f>IF($C8="","",COUNTIFS('_Datos'!$M$7:$M$200,$B8,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F8" s="202">
-        <f>IF($C8="","",COUNTIFS('_Datos'!$M$7:$M$200,$B8,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G8" s="204">
-        <f>IF($C8="","",IF($D8=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B8,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H8" s="205">
-        <f>IF($C8="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B8,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I8" s="202"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="202">
-        <v>2</v>
-      </c>
-      <c r="C9" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B9)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B9))</f>
-      </c>
-      <c r="D9" s="202">
-        <f>IF($C9="","",COUNTIFS('_Datos'!$M$7:$M$200,$B9,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E9" s="202">
-        <f>IF($C9="","",COUNTIFS('_Datos'!$M$7:$M$200,$B9,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F9" s="202">
-        <f>IF($C9="","",COUNTIFS('_Datos'!$M$7:$M$200,$B9,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G9" s="204">
-        <f>IF($C9="","",IF($D9=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B9,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H9" s="205">
-        <f>IF($C9="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B9,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I9" s="202"/>
-    </row>
-    <row r="10">
-      <c r="B10" s="202">
-        <v>3</v>
-      </c>
-      <c r="C10" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B10)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B10))</f>
-      </c>
-      <c r="D10" s="202">
-        <f>IF($C10="","",COUNTIFS('_Datos'!$M$7:$M$200,$B10,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E10" s="202">
-        <f>IF($C10="","",COUNTIFS('_Datos'!$M$7:$M$200,$B10,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F10" s="202">
-        <f>IF($C10="","",COUNTIFS('_Datos'!$M$7:$M$200,$B10,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G10" s="204">
-        <f>IF($C10="","",IF($D10=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B10,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H10" s="205">
-        <f>IF($C10="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B10,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I10" s="202"/>
-    </row>
-    <row r="11">
-      <c r="B11" s="202">
-        <v>4</v>
-      </c>
-      <c r="C11" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B11)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B11))</f>
-      </c>
-      <c r="D11" s="202">
-        <f>IF($C11="","",COUNTIFS('_Datos'!$M$7:$M$200,$B11,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E11" s="202">
-        <f>IF($C11="","",COUNTIFS('_Datos'!$M$7:$M$200,$B11,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F11" s="202">
-        <f>IF($C11="","",COUNTIFS('_Datos'!$M$7:$M$200,$B11,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G11" s="204">
-        <f>IF($C11="","",IF($D11=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B11,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H11" s="205">
-        <f>IF($C11="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B11,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I11" s="202"/>
-    </row>
-    <row r="12">
-      <c r="B12" s="202">
-        <v>5</v>
-      </c>
-      <c r="C12" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B12)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B12))</f>
-      </c>
-      <c r="D12" s="202">
-        <f>IF($C12="","",COUNTIFS('_Datos'!$M$7:$M$200,$B12,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E12" s="202">
-        <f>IF($C12="","",COUNTIFS('_Datos'!$M$7:$M$200,$B12,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F12" s="202">
-        <f>IF($C12="","",COUNTIFS('_Datos'!$M$7:$M$200,$B12,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G12" s="204">
-        <f>IF($C12="","",IF($D12=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B12,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H12" s="205">
-        <f>IF($C12="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B12,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I12" s="202"/>
-    </row>
-    <row r="13">
-      <c r="B13" s="202">
-        <v>6</v>
-      </c>
-      <c r="C13" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B13)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B13))</f>
-      </c>
-      <c r="D13" s="202">
-        <f>IF($C13="","",COUNTIFS('_Datos'!$M$7:$M$200,$B13,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E13" s="202">
-        <f>IF($C13="","",COUNTIFS('_Datos'!$M$7:$M$200,$B13,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F13" s="202">
-        <f>IF($C13="","",COUNTIFS('_Datos'!$M$7:$M$200,$B13,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G13" s="204">
-        <f>IF($C13="","",IF($D13=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B13,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H13" s="205">
-        <f>IF($C13="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B13,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I13" s="202"/>
-    </row>
-    <row r="14">
-      <c r="B14" s="202" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Sin sprint)</t>
-        </is>
-      </c>
-      <c r="C14" s="202">
-        <f>IF(COUNTIF('_Datos'!$M$7:$M$200,$B14)=0,"",COUNTIF('_Datos'!$M$7:$M$200,$B14))</f>
-      </c>
-      <c r="D14" s="202">
-        <f>IF($C14="","",COUNTIFS('_Datos'!$M$7:$M$200,$B14,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="E14" s="202">
-        <f>IF($C14="","",COUNTIFS('_Datos'!$M$7:$M$200,$B14,'_Datos'!$J$7:$J$200,"Vencido"))</f>
-      </c>
-      <c r="F14" s="202">
-        <f>IF($C14="","",COUNTIFS('_Datos'!$M$7:$M$200,$B14,'_Datos'!$J$7:$J$200,"Próximo a vencer"))</f>
-      </c>
-      <c r="G14" s="204">
-        <f>IF($C14="","",IF($D14=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$M$7:$M$200,$B14,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado")))</f>
-      </c>
-      <c r="H14" s="205">
-        <f>IF($C14="","",IFERROR(AVERAGEIF('_Datos'!$M$7:$M$200,$B14,'_Datos'!$I$7:$I$200),""))</f>
-      </c>
-      <c r="I14" s="202"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="188" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
-      </c>
-      <c r="C15" s="187">
-        <f>COUNT('_Datos'!$H$7:$H$200)</f>
-      </c>
-      <c r="D15" s="187">
-        <f>COUNTIF('_Datos'!$J$7:$J$200,"Vencido")+COUNTIF('_Datos'!$J$7:$J$200,"Próximo a vencer")+COUNTIF('_Datos'!$J$7:$J$200,"En curso")</f>
-      </c>
-      <c r="E15" s="187">
-        <f>COUNTIF('_Datos'!$J$7:$J$200,"Vencido")</f>
-      </c>
-      <c r="F15" s="187">
-        <f>COUNTIF('_Datos'!$J$7:$J$200,"Próximo a vencer")</f>
-      </c>
-      <c r="G15" s="190">
-        <f>IF($D15=0,"—",_xlfn.MINIFS('_Datos'!$H$7:$H$200,'_Datos'!$J$7:$J$200,"&lt;&gt;Completado"))</f>
-      </c>
-      <c r="H15" s="189">
-        <f>IFERROR(AVERAGE('_Datos'!$I$7:$I$200),"")</f>
-      </c>
-      <c r="I15" s="187"/>
-    </row>
-    <row r="17">
-      <c r="B17" s="172" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DETALLE DE ENTREGAS  (ordenado por Sprint y luego por Fecha de entrega)</t>
-        </is>
-      </c>
-      <c r="C17" s="172"/>
-      <c r="D17" s="172"/>
-      <c r="E17" s="172"/>
-      <c r="F17" s="172"/>
-      <c r="G17" s="172"/>
-      <c r="H17" s="172"/>
-      <c r="I17" s="172"/>
-    </row>
-    <row r="18">
-      <c r="B18" s="173" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sprint</t>
-        </is>
-      </c>
-      <c r="C18" s="173" t="inlineStr">
+      <c r="C6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Entregable (Módulo)</t>
         </is>
       </c>
-      <c r="D18" s="173" t="inlineStr">
+      <c r="D6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Tarea</t>
         </is>
       </c>
-      <c r="E18" s="173" t="inlineStr">
+      <c r="E6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Responsable</t>
         </is>
       </c>
-      <c r="F18" s="173" t="inlineStr">
+      <c r="F6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Fecha entrega</t>
         </is>
       </c>
-      <c r="G18" s="173" t="inlineStr">
+      <c r="G6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Estado</t>
         </is>
       </c>
-      <c r="H18" s="173" t="inlineStr">
+      <c r="H6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Días rest.</t>
         </is>
       </c>
-      <c r="I18" s="173" t="inlineStr">
+      <c r="I6" s="173" t="inlineStr">
         <is>
           <t xml:space="preserve">Progreso</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="B7" s="202">
+        <f>IF($K7="","",INDEX('_Datos'!$M$7:$M$200,$K7))</f>
+      </c>
+      <c r="C7" s="203">
+        <f>IF($K7="","",INDEX('_Datos'!$D$7:$D$200,$K7))</f>
+      </c>
+      <c r="D7" s="203">
+        <f>IF($K7="","",INDEX('_Datos'!$F$7:$F$200,$K7))</f>
+      </c>
+      <c r="E7" s="203">
+        <f>IF($K7="","",INDEX('_Datos'!$G$7:$G$200,$K7))</f>
+      </c>
+      <c r="F7" s="204">
+        <f>IF($K7="","",INDEX('_Datos'!$H$7:$H$200,$K7))</f>
+      </c>
+      <c r="G7" s="202">
+        <f>IF($K7="","",INDEX('_Datos'!$J$7:$J$200,$K7))</f>
+      </c>
+      <c r="H7" s="206">
+        <f>IF($K7="","",INDEX('_Datos'!$K$7:$K$200,$K7))</f>
+      </c>
+      <c r="I7" s="205">
+        <f>IF($K7="","",INDEX('_Datos'!$I$7:$I$200,$K7))</f>
+      </c>
+      <c r="K7" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="202">
+        <f>IF($K8="","",INDEX('_Datos'!$M$7:$M$200,$K8))</f>
+      </c>
+      <c r="C8" s="203">
+        <f>IF($K8="","",INDEX('_Datos'!$D$7:$D$200,$K8))</f>
+      </c>
+      <c r="D8" s="203">
+        <f>IF($K8="","",INDEX('_Datos'!$F$7:$F$200,$K8))</f>
+      </c>
+      <c r="E8" s="203">
+        <f>IF($K8="","",INDEX('_Datos'!$G$7:$G$200,$K8))</f>
+      </c>
+      <c r="F8" s="204">
+        <f>IF($K8="","",INDEX('_Datos'!$H$7:$H$200,$K8))</f>
+      </c>
+      <c r="G8" s="202">
+        <f>IF($K8="","",INDEX('_Datos'!$J$7:$J$200,$K8))</f>
+      </c>
+      <c r="H8" s="206">
+        <f>IF($K8="","",INDEX('_Datos'!$K$7:$K$200,$K8))</f>
+      </c>
+      <c r="I8" s="205">
+        <f>IF($K8="","",INDEX('_Datos'!$I$7:$I$200,$K8))</f>
+      </c>
+      <c r="K8" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="202">
+        <f>IF($K9="","",INDEX('_Datos'!$M$7:$M$200,$K9))</f>
+      </c>
+      <c r="C9" s="203">
+        <f>IF($K9="","",INDEX('_Datos'!$D$7:$D$200,$K9))</f>
+      </c>
+      <c r="D9" s="203">
+        <f>IF($K9="","",INDEX('_Datos'!$F$7:$F$200,$K9))</f>
+      </c>
+      <c r="E9" s="203">
+        <f>IF($K9="","",INDEX('_Datos'!$G$7:$G$200,$K9))</f>
+      </c>
+      <c r="F9" s="204">
+        <f>IF($K9="","",INDEX('_Datos'!$H$7:$H$200,$K9))</f>
+      </c>
+      <c r="G9" s="202">
+        <f>IF($K9="","",INDEX('_Datos'!$J$7:$J$200,$K9))</f>
+      </c>
+      <c r="H9" s="206">
+        <f>IF($K9="","",INDEX('_Datos'!$K$7:$K$200,$K9))</f>
+      </c>
+      <c r="I9" s="205">
+        <f>IF($K9="","",INDEX('_Datos'!$I$7:$I$200,$K9))</f>
+      </c>
+      <c r="K9" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="202">
+        <f>IF($K10="","",INDEX('_Datos'!$M$7:$M$200,$K10))</f>
+      </c>
+      <c r="C10" s="203">
+        <f>IF($K10="","",INDEX('_Datos'!$D$7:$D$200,$K10))</f>
+      </c>
+      <c r="D10" s="203">
+        <f>IF($K10="","",INDEX('_Datos'!$F$7:$F$200,$K10))</f>
+      </c>
+      <c r="E10" s="203">
+        <f>IF($K10="","",INDEX('_Datos'!$G$7:$G$200,$K10))</f>
+      </c>
+      <c r="F10" s="204">
+        <f>IF($K10="","",INDEX('_Datos'!$H$7:$H$200,$K10))</f>
+      </c>
+      <c r="G10" s="202">
+        <f>IF($K10="","",INDEX('_Datos'!$J$7:$J$200,$K10))</f>
+      </c>
+      <c r="H10" s="206">
+        <f>IF($K10="","",INDEX('_Datos'!$K$7:$K$200,$K10))</f>
+      </c>
+      <c r="I10" s="205">
+        <f>IF($K10="","",INDEX('_Datos'!$I$7:$I$200,$K10))</f>
+      </c>
+      <c r="K10" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="202">
+        <f>IF($K11="","",INDEX('_Datos'!$M$7:$M$200,$K11))</f>
+      </c>
+      <c r="C11" s="203">
+        <f>IF($K11="","",INDEX('_Datos'!$D$7:$D$200,$K11))</f>
+      </c>
+      <c r="D11" s="203">
+        <f>IF($K11="","",INDEX('_Datos'!$F$7:$F$200,$K11))</f>
+      </c>
+      <c r="E11" s="203">
+        <f>IF($K11="","",INDEX('_Datos'!$G$7:$G$200,$K11))</f>
+      </c>
+      <c r="F11" s="204">
+        <f>IF($K11="","",INDEX('_Datos'!$H$7:$H$200,$K11))</f>
+      </c>
+      <c r="G11" s="202">
+        <f>IF($K11="","",INDEX('_Datos'!$J$7:$J$200,$K11))</f>
+      </c>
+      <c r="H11" s="206">
+        <f>IF($K11="","",INDEX('_Datos'!$K$7:$K$200,$K11))</f>
+      </c>
+      <c r="I11" s="205">
+        <f>IF($K11="","",INDEX('_Datos'!$I$7:$I$200,$K11))</f>
+      </c>
+      <c r="K11" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="202">
+        <f>IF($K12="","",INDEX('_Datos'!$M$7:$M$200,$K12))</f>
+      </c>
+      <c r="C12" s="203">
+        <f>IF($K12="","",INDEX('_Datos'!$D$7:$D$200,$K12))</f>
+      </c>
+      <c r="D12" s="203">
+        <f>IF($K12="","",INDEX('_Datos'!$F$7:$F$200,$K12))</f>
+      </c>
+      <c r="E12" s="203">
+        <f>IF($K12="","",INDEX('_Datos'!$G$7:$G$200,$K12))</f>
+      </c>
+      <c r="F12" s="204">
+        <f>IF($K12="","",INDEX('_Datos'!$H$7:$H$200,$K12))</f>
+      </c>
+      <c r="G12" s="202">
+        <f>IF($K12="","",INDEX('_Datos'!$J$7:$J$200,$K12))</f>
+      </c>
+      <c r="H12" s="206">
+        <f>IF($K12="","",INDEX('_Datos'!$K$7:$K$200,$K12))</f>
+      </c>
+      <c r="I12" s="205">
+        <f>IF($K12="","",INDEX('_Datos'!$I$7:$I$200,$K12))</f>
+      </c>
+      <c r="K12" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="202">
+        <f>IF($K13="","",INDEX('_Datos'!$M$7:$M$200,$K13))</f>
+      </c>
+      <c r="C13" s="203">
+        <f>IF($K13="","",INDEX('_Datos'!$D$7:$D$200,$K13))</f>
+      </c>
+      <c r="D13" s="203">
+        <f>IF($K13="","",INDEX('_Datos'!$F$7:$F$200,$K13))</f>
+      </c>
+      <c r="E13" s="203">
+        <f>IF($K13="","",INDEX('_Datos'!$G$7:$G$200,$K13))</f>
+      </c>
+      <c r="F13" s="204">
+        <f>IF($K13="","",INDEX('_Datos'!$H$7:$H$200,$K13))</f>
+      </c>
+      <c r="G13" s="202">
+        <f>IF($K13="","",INDEX('_Datos'!$J$7:$J$200,$K13))</f>
+      </c>
+      <c r="H13" s="206">
+        <f>IF($K13="","",INDEX('_Datos'!$K$7:$K$200,$K13))</f>
+      </c>
+      <c r="I13" s="205">
+        <f>IF($K13="","",INDEX('_Datos'!$I$7:$I$200,$K13))</f>
+      </c>
+      <c r="K13" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="202">
+        <f>IF($K14="","",INDEX('_Datos'!$M$7:$M$200,$K14))</f>
+      </c>
+      <c r="C14" s="203">
+        <f>IF($K14="","",INDEX('_Datos'!$D$7:$D$200,$K14))</f>
+      </c>
+      <c r="D14" s="203">
+        <f>IF($K14="","",INDEX('_Datos'!$F$7:$F$200,$K14))</f>
+      </c>
+      <c r="E14" s="203">
+        <f>IF($K14="","",INDEX('_Datos'!$G$7:$G$200,$K14))</f>
+      </c>
+      <c r="F14" s="204">
+        <f>IF($K14="","",INDEX('_Datos'!$H$7:$H$200,$K14))</f>
+      </c>
+      <c r="G14" s="202">
+        <f>IF($K14="","",INDEX('_Datos'!$J$7:$J$200,$K14))</f>
+      </c>
+      <c r="H14" s="206">
+        <f>IF($K14="","",INDEX('_Datos'!$K$7:$K$200,$K14))</f>
+      </c>
+      <c r="I14" s="205">
+        <f>IF($K14="","",INDEX('_Datos'!$I$7:$I$200,$K14))</f>
+      </c>
+      <c r="K14" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="202">
+        <f>IF($K15="","",INDEX('_Datos'!$M$7:$M$200,$K15))</f>
+      </c>
+      <c r="C15" s="203">
+        <f>IF($K15="","",INDEX('_Datos'!$D$7:$D$200,$K15))</f>
+      </c>
+      <c r="D15" s="203">
+        <f>IF($K15="","",INDEX('_Datos'!$F$7:$F$200,$K15))</f>
+      </c>
+      <c r="E15" s="203">
+        <f>IF($K15="","",INDEX('_Datos'!$G$7:$G$200,$K15))</f>
+      </c>
+      <c r="F15" s="204">
+        <f>IF($K15="","",INDEX('_Datos'!$H$7:$H$200,$K15))</f>
+      </c>
+      <c r="G15" s="202">
+        <f>IF($K15="","",INDEX('_Datos'!$J$7:$J$200,$K15))</f>
+      </c>
+      <c r="H15" s="206">
+        <f>IF($K15="","",INDEX('_Datos'!$K$7:$K$200,$K15))</f>
+      </c>
+      <c r="I15" s="205">
+        <f>IF($K15="","",INDEX('_Datos'!$I$7:$I$200,$K15))</f>
+      </c>
+      <c r="K15" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="202">
+        <f>IF($K16="","",INDEX('_Datos'!$M$7:$M$200,$K16))</f>
+      </c>
+      <c r="C16" s="203">
+        <f>IF($K16="","",INDEX('_Datos'!$D$7:$D$200,$K16))</f>
+      </c>
+      <c r="D16" s="203">
+        <f>IF($K16="","",INDEX('_Datos'!$F$7:$F$200,$K16))</f>
+      </c>
+      <c r="E16" s="203">
+        <f>IF($K16="","",INDEX('_Datos'!$G$7:$G$200,$K16))</f>
+      </c>
+      <c r="F16" s="204">
+        <f>IF($K16="","",INDEX('_Datos'!$H$7:$H$200,$K16))</f>
+      </c>
+      <c r="G16" s="202">
+        <f>IF($K16="","",INDEX('_Datos'!$J$7:$J$200,$K16))</f>
+      </c>
+      <c r="H16" s="206">
+        <f>IF($K16="","",INDEX('_Datos'!$K$7:$K$200,$K16))</f>
+      </c>
+      <c r="I16" s="205">
+        <f>IF($K16="","",INDEX('_Datos'!$I$7:$I$200,$K16))</f>
+      </c>
+      <c r="K16" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="202">
+        <f>IF($K17="","",INDEX('_Datos'!$M$7:$M$200,$K17))</f>
+      </c>
+      <c r="C17" s="203">
+        <f>IF($K17="","",INDEX('_Datos'!$D$7:$D$200,$K17))</f>
+      </c>
+      <c r="D17" s="203">
+        <f>IF($K17="","",INDEX('_Datos'!$F$7:$F$200,$K17))</f>
+      </c>
+      <c r="E17" s="203">
+        <f>IF($K17="","",INDEX('_Datos'!$G$7:$G$200,$K17))</f>
+      </c>
+      <c r="F17" s="204">
+        <f>IF($K17="","",INDEX('_Datos'!$H$7:$H$200,$K17))</f>
+      </c>
+      <c r="G17" s="202">
+        <f>IF($K17="","",INDEX('_Datos'!$J$7:$J$200,$K17))</f>
+      </c>
+      <c r="H17" s="206">
+        <f>IF($K17="","",INDEX('_Datos'!$K$7:$K$200,$K17))</f>
+      </c>
+      <c r="I17" s="205">
+        <f>IF($K17="","",INDEX('_Datos'!$I$7:$I$200,$K17))</f>
+      </c>
+      <c r="K17" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="202">
+        <f>IF($K18="","",INDEX('_Datos'!$M$7:$M$200,$K18))</f>
+      </c>
+      <c r="C18" s="203">
+        <f>IF($K18="","",INDEX('_Datos'!$D$7:$D$200,$K18))</f>
+      </c>
+      <c r="D18" s="203">
+        <f>IF($K18="","",INDEX('_Datos'!$F$7:$F$200,$K18))</f>
+      </c>
+      <c r="E18" s="203">
+        <f>IF($K18="","",INDEX('_Datos'!$G$7:$G$200,$K18))</f>
+      </c>
+      <c r="F18" s="204">
+        <f>IF($K18="","",INDEX('_Datos'!$H$7:$H$200,$K18))</f>
+      </c>
+      <c r="G18" s="202">
+        <f>IF($K18="","",INDEX('_Datos'!$J$7:$J$200,$K18))</f>
+      </c>
+      <c r="H18" s="206">
+        <f>IF($K18="","",INDEX('_Datos'!$K$7:$K$200,$K18))</f>
+      </c>
+      <c r="I18" s="205">
+        <f>IF($K18="","",INDEX('_Datos'!$I$7:$I$200,$K18))</f>
+      </c>
+      <c r="K18" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
     <row r="19">
       <c r="B19" s="202">
         <f>IF($K19="","",INDEX('_Datos'!$M$7:$M$200,$K19))</f>
@@ -16858,7 +17129,7 @@
         <f>IF($K19="","",INDEX('_Datos'!$I$7:$I$200,$K19))</f>
       </c>
       <c r="K19" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="20">
@@ -16887,7 +17158,7 @@
         <f>IF($K20="","",INDEX('_Datos'!$I$7:$I$200,$K20))</f>
       </c>
       <c r="K20" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="21">
@@ -16916,7 +17187,7 @@
         <f>IF($K21="","",INDEX('_Datos'!$I$7:$I$200,$K21))</f>
       </c>
       <c r="K21" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="22">
@@ -16945,7 +17216,7 @@
         <f>IF($K22="","",INDEX('_Datos'!$I$7:$I$200,$K22))</f>
       </c>
       <c r="K22" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="23">
@@ -16974,7 +17245,7 @@
         <f>IF($K23="","",INDEX('_Datos'!$I$7:$I$200,$K23))</f>
       </c>
       <c r="K23" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="24">
@@ -17003,7 +17274,7 @@
         <f>IF($K24="","",INDEX('_Datos'!$I$7:$I$200,$K24))</f>
       </c>
       <c r="K24" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="25">
@@ -17032,7 +17303,7 @@
         <f>IF($K25="","",INDEX('_Datos'!$I$7:$I$200,$K25))</f>
       </c>
       <c r="K25" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="26">
@@ -17061,7 +17332,7 @@
         <f>IF($K26="","",INDEX('_Datos'!$I$7:$I$200,$K26))</f>
       </c>
       <c r="K26" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="27">
@@ -17090,7 +17361,7 @@
         <f>IF($K27="","",INDEX('_Datos'!$I$7:$I$200,$K27))</f>
       </c>
       <c r="K27" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="28">
@@ -17119,7 +17390,7 @@
         <f>IF($K28="","",INDEX('_Datos'!$I$7:$I$200,$K28))</f>
       </c>
       <c r="K28" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="29">
@@ -17148,7 +17419,7 @@
         <f>IF($K29="","",INDEX('_Datos'!$I$7:$I$200,$K29))</f>
       </c>
       <c r="K29" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="30">
@@ -17177,7 +17448,7 @@
         <f>IF($K30="","",INDEX('_Datos'!$I$7:$I$200,$K30))</f>
       </c>
       <c r="K30" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="31">
@@ -17206,7 +17477,7 @@
         <f>IF($K31="","",INDEX('_Datos'!$I$7:$I$200,$K31))</f>
       </c>
       <c r="K31" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="32">
@@ -17235,7 +17506,7 @@
         <f>IF($K32="","",INDEX('_Datos'!$I$7:$I$200,$K32))</f>
       </c>
       <c r="K32" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="33">
@@ -17264,7 +17535,7 @@
         <f>IF($K33="","",INDEX('_Datos'!$I$7:$I$200,$K33))</f>
       </c>
       <c r="K33" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="34">
@@ -17293,7 +17564,7 @@
         <f>IF($K34="","",INDEX('_Datos'!$I$7:$I$200,$K34))</f>
       </c>
       <c r="K34" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="35">
@@ -17322,7 +17593,7 @@
         <f>IF($K35="","",INDEX('_Datos'!$I$7:$I$200,$K35))</f>
       </c>
       <c r="K35" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="36">
@@ -17351,7 +17622,7 @@
         <f>IF($K36="","",INDEX('_Datos'!$I$7:$I$200,$K36))</f>
       </c>
       <c r="K36" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="37">
@@ -17380,7 +17651,7 @@
         <f>IF($K37="","",INDEX('_Datos'!$I$7:$I$200,$K37))</f>
       </c>
       <c r="K37" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="38">
@@ -17409,7 +17680,7 @@
         <f>IF($K38="","",INDEX('_Datos'!$I$7:$I$200,$K38))</f>
       </c>
       <c r="K38" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="39">
@@ -17438,7 +17709,7 @@
         <f>IF($K39="","",INDEX('_Datos'!$I$7:$I$200,$K39))</f>
       </c>
       <c r="K39" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="40">
@@ -17467,7 +17738,7 @@
         <f>IF($K40="","",INDEX('_Datos'!$I$7:$I$200,$K40))</f>
       </c>
       <c r="K40" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="41">
@@ -17496,7 +17767,7 @@
         <f>IF($K41="","",INDEX('_Datos'!$I$7:$I$200,$K41))</f>
       </c>
       <c r="K41" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="42">
@@ -17525,7 +17796,7 @@
         <f>IF($K42="","",INDEX('_Datos'!$I$7:$I$200,$K42))</f>
       </c>
       <c r="K42" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="43">
@@ -17554,7 +17825,7 @@
         <f>IF($K43="","",INDEX('_Datos'!$I$7:$I$200,$K43))</f>
       </c>
       <c r="K43" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="44">
@@ -17583,7 +17854,7 @@
         <f>IF($K44="","",INDEX('_Datos'!$I$7:$I$200,$K44))</f>
       </c>
       <c r="K44" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="45">
@@ -17612,7 +17883,7 @@
         <f>IF($K45="","",INDEX('_Datos'!$I$7:$I$200,$K45))</f>
       </c>
       <c r="K45" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="46">
@@ -17641,7 +17912,7 @@
         <f>IF($K46="","",INDEX('_Datos'!$I$7:$I$200,$K46))</f>
       </c>
       <c r="K46" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="47">
@@ -17670,7 +17941,7 @@
         <f>IF($K47="","",INDEX('_Datos'!$I$7:$I$200,$K47))</f>
       </c>
       <c r="K47" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="48">
@@ -17699,7 +17970,7 @@
         <f>IF($K48="","",INDEX('_Datos'!$I$7:$I$200,$K48))</f>
       </c>
       <c r="K48" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="49">
@@ -17728,7 +17999,7 @@
         <f>IF($K49="","",INDEX('_Datos'!$I$7:$I$200,$K49))</f>
       </c>
       <c r="K49" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="50">
@@ -17757,7 +18028,7 @@
         <f>IF($K50="","",INDEX('_Datos'!$I$7:$I$200,$K50))</f>
       </c>
       <c r="K50" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="51">
@@ -17786,7 +18057,7 @@
         <f>IF($K51="","",INDEX('_Datos'!$I$7:$I$200,$K51))</f>
       </c>
       <c r="K51" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="52">
@@ -17815,7 +18086,7 @@
         <f>IF($K52="","",INDEX('_Datos'!$I$7:$I$200,$K52))</f>
       </c>
       <c r="K52" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="53">
@@ -17844,7 +18115,7 @@
         <f>IF($K53="","",INDEX('_Datos'!$I$7:$I$200,$K53))</f>
       </c>
       <c r="K53" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="54">
@@ -17873,7 +18144,7 @@
         <f>IF($K54="","",INDEX('_Datos'!$I$7:$I$200,$K54))</f>
       </c>
       <c r="K54" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="55">
@@ -17902,7 +18173,7 @@
         <f>IF($K55="","",INDEX('_Datos'!$I$7:$I$200,$K55))</f>
       </c>
       <c r="K55" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="56">
@@ -17931,7 +18202,7 @@
         <f>IF($K56="","",INDEX('_Datos'!$I$7:$I$200,$K56))</f>
       </c>
       <c r="K56" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="57">
@@ -17960,7 +18231,7 @@
         <f>IF($K57="","",INDEX('_Datos'!$I$7:$I$200,$K57))</f>
       </c>
       <c r="K57" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="58">
@@ -17989,7 +18260,7 @@
         <f>IF($K58="","",INDEX('_Datos'!$I$7:$I$200,$K58))</f>
       </c>
       <c r="K58" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="59">
@@ -18018,7 +18289,7 @@
         <f>IF($K59="","",INDEX('_Datos'!$I$7:$I$200,$K59))</f>
       </c>
       <c r="K59" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="60">
@@ -18047,7 +18318,7 @@
         <f>IF($K60="","",INDEX('_Datos'!$I$7:$I$200,$K60))</f>
       </c>
       <c r="K60" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="61">
@@ -18076,7 +18347,7 @@
         <f>IF($K61="","",INDEX('_Datos'!$I$7:$I$200,$K61))</f>
       </c>
       <c r="K61" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="62">
@@ -18105,7 +18376,7 @@
         <f>IF($K62="","",INDEX('_Datos'!$I$7:$I$200,$K62))</f>
       </c>
       <c r="K62" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="63">
@@ -18134,7 +18405,7 @@
         <f>IF($K63="","",INDEX('_Datos'!$I$7:$I$200,$K63))</f>
       </c>
       <c r="K63" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="64">
@@ -18163,7 +18434,7 @@
         <f>IF($K64="","",INDEX('_Datos'!$I$7:$I$200,$K64))</f>
       </c>
       <c r="K64" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="65">
@@ -18192,7 +18463,7 @@
         <f>IF($K65="","",INDEX('_Datos'!$I$7:$I$200,$K65))</f>
       </c>
       <c r="K65" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="66">
@@ -18221,7 +18492,7 @@
         <f>IF($K66="","",INDEX('_Datos'!$I$7:$I$200,$K66))</f>
       </c>
       <c r="K66" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="67">
@@ -18250,7 +18521,7 @@
         <f>IF($K67="","",INDEX('_Datos'!$I$7:$I$200,$K67))</f>
       </c>
       <c r="K67" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="68">
@@ -18279,7 +18550,7 @@
         <f>IF($K68="","",INDEX('_Datos'!$I$7:$I$200,$K68))</f>
       </c>
       <c r="K68" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="69">
@@ -18308,7 +18579,7 @@
         <f>IF($K69="","",INDEX('_Datos'!$I$7:$I$200,$K69))</f>
       </c>
       <c r="K69" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="70">
@@ -18337,7 +18608,7 @@
         <f>IF($K70="","",INDEX('_Datos'!$I$7:$I$200,$K70))</f>
       </c>
       <c r="K70" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="71">
@@ -18366,7 +18637,7 @@
         <f>IF($K71="","",INDEX('_Datos'!$I$7:$I$200,$K71))</f>
       </c>
       <c r="K71" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="72">
@@ -18395,7 +18666,7 @@
         <f>IF($K72="","",INDEX('_Datos'!$I$7:$I$200,$K72))</f>
       </c>
       <c r="K72" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="73">
@@ -18424,7 +18695,7 @@
         <f>IF($K73="","",INDEX('_Datos'!$I$7:$I$200,$K73))</f>
       </c>
       <c r="K73" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="74">
@@ -18453,7 +18724,7 @@
         <f>IF($K74="","",INDEX('_Datos'!$I$7:$I$200,$K74))</f>
       </c>
       <c r="K74" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="75">
@@ -18482,7 +18753,7 @@
         <f>IF($K75="","",INDEX('_Datos'!$I$7:$I$200,$K75))</f>
       </c>
       <c r="K75" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="76">
@@ -18511,7 +18782,7 @@
         <f>IF($K76="","",INDEX('_Datos'!$I$7:$I$200,$K76))</f>
       </c>
       <c r="K76" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="77">
@@ -18540,7 +18811,7 @@
         <f>IF($K77="","",INDEX('_Datos'!$I$7:$I$200,$K77))</f>
       </c>
       <c r="K77" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="78">
@@ -18569,7 +18840,7 @@
         <f>IF($K78="","",INDEX('_Datos'!$I$7:$I$200,$K78))</f>
       </c>
       <c r="K78" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="79">
@@ -18598,7 +18869,7 @@
         <f>IF($K79="","",INDEX('_Datos'!$I$7:$I$200,$K79))</f>
       </c>
       <c r="K79" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="80">
@@ -18627,7 +18898,7 @@
         <f>IF($K80="","",INDEX('_Datos'!$I$7:$I$200,$K80))</f>
       </c>
       <c r="K80" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="81">
@@ -18656,7 +18927,7 @@
         <f>IF($K81="","",INDEX('_Datos'!$I$7:$I$200,$K81))</f>
       </c>
       <c r="K81" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="82">
@@ -18685,7 +18956,7 @@
         <f>IF($K82="","",INDEX('_Datos'!$I$7:$I$200,$K82))</f>
       </c>
       <c r="K82" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="83">
@@ -18714,7 +18985,7 @@
         <f>IF($K83="","",INDEX('_Datos'!$I$7:$I$200,$K83))</f>
       </c>
       <c r="K83" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="84">
@@ -18743,7 +19014,7 @@
         <f>IF($K84="","",INDEX('_Datos'!$I$7:$I$200,$K84))</f>
       </c>
       <c r="K84" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="85">
@@ -18772,7 +19043,7 @@
         <f>IF($K85="","",INDEX('_Datos'!$I$7:$I$200,$K85))</f>
       </c>
       <c r="K85" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="86">
@@ -18801,7 +19072,7 @@
         <f>IF($K86="","",INDEX('_Datos'!$I$7:$I$200,$K86))</f>
       </c>
       <c r="K86" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="87">
@@ -18830,7 +19101,7 @@
         <f>IF($K87="","",INDEX('_Datos'!$I$7:$I$200,$K87))</f>
       </c>
       <c r="K87" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="88">
@@ -18859,7 +19130,7 @@
         <f>IF($K88="","",INDEX('_Datos'!$I$7:$I$200,$K88))</f>
       </c>
       <c r="K88" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="89">
@@ -18888,7 +19159,7 @@
         <f>IF($K89="","",INDEX('_Datos'!$I$7:$I$200,$K89))</f>
       </c>
       <c r="K89" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="90">
@@ -18917,7 +19188,7 @@
         <f>IF($K90="","",INDEX('_Datos'!$I$7:$I$200,$K90))</f>
       </c>
       <c r="K90" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="91">
@@ -18946,7 +19217,7 @@
         <f>IF($K91="","",INDEX('_Datos'!$I$7:$I$200,$K91))</f>
       </c>
       <c r="K91" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="92">
@@ -18975,7 +19246,7 @@
         <f>IF($K92="","",INDEX('_Datos'!$I$7:$I$200,$K92))</f>
       </c>
       <c r="K92" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="93">
@@ -19004,7 +19275,7 @@
         <f>IF($K93="","",INDEX('_Datos'!$I$7:$I$200,$K93))</f>
       </c>
       <c r="K93" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="94">
@@ -19033,7 +19304,7 @@
         <f>IF($K94="","",INDEX('_Datos'!$I$7:$I$200,$K94))</f>
       </c>
       <c r="K94" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="95">
@@ -19062,7 +19333,7 @@
         <f>IF($K95="","",INDEX('_Datos'!$I$7:$I$200,$K95))</f>
       </c>
       <c r="K95" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="96">
@@ -19091,7 +19362,7 @@
         <f>IF($K96="","",INDEX('_Datos'!$I$7:$I$200,$K96))</f>
       </c>
       <c r="K96" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="97">
@@ -19120,7 +19391,7 @@
         <f>IF($K97="","",INDEX('_Datos'!$I$7:$I$200,$K97))</f>
       </c>
       <c r="K97" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
     <row r="98">
@@ -19149,42 +19420,1718 @@
         <f>IF($K98="","",INDEX('_Datos'!$I$7:$I$200,$K98))</f>
       </c>
       <c r="K98" s="200">
-        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-19+1),'_Datos'!$L$7:$L$200,0),"")</f>
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" s="202">
+        <f>IF($K99="","",INDEX('_Datos'!$M$7:$M$200,$K99))</f>
+      </c>
+      <c r="C99" s="203">
+        <f>IF($K99="","",INDEX('_Datos'!$D$7:$D$200,$K99))</f>
+      </c>
+      <c r="D99" s="203">
+        <f>IF($K99="","",INDEX('_Datos'!$F$7:$F$200,$K99))</f>
+      </c>
+      <c r="E99" s="203">
+        <f>IF($K99="","",INDEX('_Datos'!$G$7:$G$200,$K99))</f>
+      </c>
+      <c r="F99" s="204">
+        <f>IF($K99="","",INDEX('_Datos'!$H$7:$H$200,$K99))</f>
+      </c>
+      <c r="G99" s="202">
+        <f>IF($K99="","",INDEX('_Datos'!$J$7:$J$200,$K99))</f>
+      </c>
+      <c r="H99" s="206">
+        <f>IF($K99="","",INDEX('_Datos'!$K$7:$K$200,$K99))</f>
+      </c>
+      <c r="I99" s="205">
+        <f>IF($K99="","",INDEX('_Datos'!$I$7:$I$200,$K99))</f>
+      </c>
+      <c r="K99" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="202">
+        <f>IF($K100="","",INDEX('_Datos'!$M$7:$M$200,$K100))</f>
+      </c>
+      <c r="C100" s="203">
+        <f>IF($K100="","",INDEX('_Datos'!$D$7:$D$200,$K100))</f>
+      </c>
+      <c r="D100" s="203">
+        <f>IF($K100="","",INDEX('_Datos'!$F$7:$F$200,$K100))</f>
+      </c>
+      <c r="E100" s="203">
+        <f>IF($K100="","",INDEX('_Datos'!$G$7:$G$200,$K100))</f>
+      </c>
+      <c r="F100" s="204">
+        <f>IF($K100="","",INDEX('_Datos'!$H$7:$H$200,$K100))</f>
+      </c>
+      <c r="G100" s="202">
+        <f>IF($K100="","",INDEX('_Datos'!$J$7:$J$200,$K100))</f>
+      </c>
+      <c r="H100" s="206">
+        <f>IF($K100="","",INDEX('_Datos'!$K$7:$K$200,$K100))</f>
+      </c>
+      <c r="I100" s="205">
+        <f>IF($K100="","",INDEX('_Datos'!$I$7:$I$200,$K100))</f>
+      </c>
+      <c r="K100" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" s="202">
+        <f>IF($K101="","",INDEX('_Datos'!$M$7:$M$200,$K101))</f>
+      </c>
+      <c r="C101" s="203">
+        <f>IF($K101="","",INDEX('_Datos'!$D$7:$D$200,$K101))</f>
+      </c>
+      <c r="D101" s="203">
+        <f>IF($K101="","",INDEX('_Datos'!$F$7:$F$200,$K101))</f>
+      </c>
+      <c r="E101" s="203">
+        <f>IF($K101="","",INDEX('_Datos'!$G$7:$G$200,$K101))</f>
+      </c>
+      <c r="F101" s="204">
+        <f>IF($K101="","",INDEX('_Datos'!$H$7:$H$200,$K101))</f>
+      </c>
+      <c r="G101" s="202">
+        <f>IF($K101="","",INDEX('_Datos'!$J$7:$J$200,$K101))</f>
+      </c>
+      <c r="H101" s="206">
+        <f>IF($K101="","",INDEX('_Datos'!$K$7:$K$200,$K101))</f>
+      </c>
+      <c r="I101" s="205">
+        <f>IF($K101="","",INDEX('_Datos'!$I$7:$I$200,$K101))</f>
+      </c>
+      <c r="K101" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" s="202">
+        <f>IF($K102="","",INDEX('_Datos'!$M$7:$M$200,$K102))</f>
+      </c>
+      <c r="C102" s="203">
+        <f>IF($K102="","",INDEX('_Datos'!$D$7:$D$200,$K102))</f>
+      </c>
+      <c r="D102" s="203">
+        <f>IF($K102="","",INDEX('_Datos'!$F$7:$F$200,$K102))</f>
+      </c>
+      <c r="E102" s="203">
+        <f>IF($K102="","",INDEX('_Datos'!$G$7:$G$200,$K102))</f>
+      </c>
+      <c r="F102" s="204">
+        <f>IF($K102="","",INDEX('_Datos'!$H$7:$H$200,$K102))</f>
+      </c>
+      <c r="G102" s="202">
+        <f>IF($K102="","",INDEX('_Datos'!$J$7:$J$200,$K102))</f>
+      </c>
+      <c r="H102" s="206">
+        <f>IF($K102="","",INDEX('_Datos'!$K$7:$K$200,$K102))</f>
+      </c>
+      <c r="I102" s="205">
+        <f>IF($K102="","",INDEX('_Datos'!$I$7:$I$200,$K102))</f>
+      </c>
+      <c r="K102" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" s="202">
+        <f>IF($K103="","",INDEX('_Datos'!$M$7:$M$200,$K103))</f>
+      </c>
+      <c r="C103" s="203">
+        <f>IF($K103="","",INDEX('_Datos'!$D$7:$D$200,$K103))</f>
+      </c>
+      <c r="D103" s="203">
+        <f>IF($K103="","",INDEX('_Datos'!$F$7:$F$200,$K103))</f>
+      </c>
+      <c r="E103" s="203">
+        <f>IF($K103="","",INDEX('_Datos'!$G$7:$G$200,$K103))</f>
+      </c>
+      <c r="F103" s="204">
+        <f>IF($K103="","",INDEX('_Datos'!$H$7:$H$200,$K103))</f>
+      </c>
+      <c r="G103" s="202">
+        <f>IF($K103="","",INDEX('_Datos'!$J$7:$J$200,$K103))</f>
+      </c>
+      <c r="H103" s="206">
+        <f>IF($K103="","",INDEX('_Datos'!$K$7:$K$200,$K103))</f>
+      </c>
+      <c r="I103" s="205">
+        <f>IF($K103="","",INDEX('_Datos'!$I$7:$I$200,$K103))</f>
+      </c>
+      <c r="K103" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="202">
+        <f>IF($K104="","",INDEX('_Datos'!$M$7:$M$200,$K104))</f>
+      </c>
+      <c r="C104" s="203">
+        <f>IF($K104="","",INDEX('_Datos'!$D$7:$D$200,$K104))</f>
+      </c>
+      <c r="D104" s="203">
+        <f>IF($K104="","",INDEX('_Datos'!$F$7:$F$200,$K104))</f>
+      </c>
+      <c r="E104" s="203">
+        <f>IF($K104="","",INDEX('_Datos'!$G$7:$G$200,$K104))</f>
+      </c>
+      <c r="F104" s="204">
+        <f>IF($K104="","",INDEX('_Datos'!$H$7:$H$200,$K104))</f>
+      </c>
+      <c r="G104" s="202">
+        <f>IF($K104="","",INDEX('_Datos'!$J$7:$J$200,$K104))</f>
+      </c>
+      <c r="H104" s="206">
+        <f>IF($K104="","",INDEX('_Datos'!$K$7:$K$200,$K104))</f>
+      </c>
+      <c r="I104" s="205">
+        <f>IF($K104="","",INDEX('_Datos'!$I$7:$I$200,$K104))</f>
+      </c>
+      <c r="K104" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="202">
+        <f>IF($K105="","",INDEX('_Datos'!$M$7:$M$200,$K105))</f>
+      </c>
+      <c r="C105" s="203">
+        <f>IF($K105="","",INDEX('_Datos'!$D$7:$D$200,$K105))</f>
+      </c>
+      <c r="D105" s="203">
+        <f>IF($K105="","",INDEX('_Datos'!$F$7:$F$200,$K105))</f>
+      </c>
+      <c r="E105" s="203">
+        <f>IF($K105="","",INDEX('_Datos'!$G$7:$G$200,$K105))</f>
+      </c>
+      <c r="F105" s="204">
+        <f>IF($K105="","",INDEX('_Datos'!$H$7:$H$200,$K105))</f>
+      </c>
+      <c r="G105" s="202">
+        <f>IF($K105="","",INDEX('_Datos'!$J$7:$J$200,$K105))</f>
+      </c>
+      <c r="H105" s="206">
+        <f>IF($K105="","",INDEX('_Datos'!$K$7:$K$200,$K105))</f>
+      </c>
+      <c r="I105" s="205">
+        <f>IF($K105="","",INDEX('_Datos'!$I$7:$I$200,$K105))</f>
+      </c>
+      <c r="K105" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" s="202">
+        <f>IF($K106="","",INDEX('_Datos'!$M$7:$M$200,$K106))</f>
+      </c>
+      <c r="C106" s="203">
+        <f>IF($K106="","",INDEX('_Datos'!$D$7:$D$200,$K106))</f>
+      </c>
+      <c r="D106" s="203">
+        <f>IF($K106="","",INDEX('_Datos'!$F$7:$F$200,$K106))</f>
+      </c>
+      <c r="E106" s="203">
+        <f>IF($K106="","",INDEX('_Datos'!$G$7:$G$200,$K106))</f>
+      </c>
+      <c r="F106" s="204">
+        <f>IF($K106="","",INDEX('_Datos'!$H$7:$H$200,$K106))</f>
+      </c>
+      <c r="G106" s="202">
+        <f>IF($K106="","",INDEX('_Datos'!$J$7:$J$200,$K106))</f>
+      </c>
+      <c r="H106" s="206">
+        <f>IF($K106="","",INDEX('_Datos'!$K$7:$K$200,$K106))</f>
+      </c>
+      <c r="I106" s="205">
+        <f>IF($K106="","",INDEX('_Datos'!$I$7:$I$200,$K106))</f>
+      </c>
+      <c r="K106" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" s="202">
+        <f>IF($K107="","",INDEX('_Datos'!$M$7:$M$200,$K107))</f>
+      </c>
+      <c r="C107" s="203">
+        <f>IF($K107="","",INDEX('_Datos'!$D$7:$D$200,$K107))</f>
+      </c>
+      <c r="D107" s="203">
+        <f>IF($K107="","",INDEX('_Datos'!$F$7:$F$200,$K107))</f>
+      </c>
+      <c r="E107" s="203">
+        <f>IF($K107="","",INDEX('_Datos'!$G$7:$G$200,$K107))</f>
+      </c>
+      <c r="F107" s="204">
+        <f>IF($K107="","",INDEX('_Datos'!$H$7:$H$200,$K107))</f>
+      </c>
+      <c r="G107" s="202">
+        <f>IF($K107="","",INDEX('_Datos'!$J$7:$J$200,$K107))</f>
+      </c>
+      <c r="H107" s="206">
+        <f>IF($K107="","",INDEX('_Datos'!$K$7:$K$200,$K107))</f>
+      </c>
+      <c r="I107" s="205">
+        <f>IF($K107="","",INDEX('_Datos'!$I$7:$I$200,$K107))</f>
+      </c>
+      <c r="K107" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="202">
+        <f>IF($K108="","",INDEX('_Datos'!$M$7:$M$200,$K108))</f>
+      </c>
+      <c r="C108" s="203">
+        <f>IF($K108="","",INDEX('_Datos'!$D$7:$D$200,$K108))</f>
+      </c>
+      <c r="D108" s="203">
+        <f>IF($K108="","",INDEX('_Datos'!$F$7:$F$200,$K108))</f>
+      </c>
+      <c r="E108" s="203">
+        <f>IF($K108="","",INDEX('_Datos'!$G$7:$G$200,$K108))</f>
+      </c>
+      <c r="F108" s="204">
+        <f>IF($K108="","",INDEX('_Datos'!$H$7:$H$200,$K108))</f>
+      </c>
+      <c r="G108" s="202">
+        <f>IF($K108="","",INDEX('_Datos'!$J$7:$J$200,$K108))</f>
+      </c>
+      <c r="H108" s="206">
+        <f>IF($K108="","",INDEX('_Datos'!$K$7:$K$200,$K108))</f>
+      </c>
+      <c r="I108" s="205">
+        <f>IF($K108="","",INDEX('_Datos'!$I$7:$I$200,$K108))</f>
+      </c>
+      <c r="K108" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="202">
+        <f>IF($K109="","",INDEX('_Datos'!$M$7:$M$200,$K109))</f>
+      </c>
+      <c r="C109" s="203">
+        <f>IF($K109="","",INDEX('_Datos'!$D$7:$D$200,$K109))</f>
+      </c>
+      <c r="D109" s="203">
+        <f>IF($K109="","",INDEX('_Datos'!$F$7:$F$200,$K109))</f>
+      </c>
+      <c r="E109" s="203">
+        <f>IF($K109="","",INDEX('_Datos'!$G$7:$G$200,$K109))</f>
+      </c>
+      <c r="F109" s="204">
+        <f>IF($K109="","",INDEX('_Datos'!$H$7:$H$200,$K109))</f>
+      </c>
+      <c r="G109" s="202">
+        <f>IF($K109="","",INDEX('_Datos'!$J$7:$J$200,$K109))</f>
+      </c>
+      <c r="H109" s="206">
+        <f>IF($K109="","",INDEX('_Datos'!$K$7:$K$200,$K109))</f>
+      </c>
+      <c r="I109" s="205">
+        <f>IF($K109="","",INDEX('_Datos'!$I$7:$I$200,$K109))</f>
+      </c>
+      <c r="K109" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="202">
+        <f>IF($K110="","",INDEX('_Datos'!$M$7:$M$200,$K110))</f>
+      </c>
+      <c r="C110" s="203">
+        <f>IF($K110="","",INDEX('_Datos'!$D$7:$D$200,$K110))</f>
+      </c>
+      <c r="D110" s="203">
+        <f>IF($K110="","",INDEX('_Datos'!$F$7:$F$200,$K110))</f>
+      </c>
+      <c r="E110" s="203">
+        <f>IF($K110="","",INDEX('_Datos'!$G$7:$G$200,$K110))</f>
+      </c>
+      <c r="F110" s="204">
+        <f>IF($K110="","",INDEX('_Datos'!$H$7:$H$200,$K110))</f>
+      </c>
+      <c r="G110" s="202">
+        <f>IF($K110="","",INDEX('_Datos'!$J$7:$J$200,$K110))</f>
+      </c>
+      <c r="H110" s="206">
+        <f>IF($K110="","",INDEX('_Datos'!$K$7:$K$200,$K110))</f>
+      </c>
+      <c r="I110" s="205">
+        <f>IF($K110="","",INDEX('_Datos'!$I$7:$I$200,$K110))</f>
+      </c>
+      <c r="K110" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="202">
+        <f>IF($K111="","",INDEX('_Datos'!$M$7:$M$200,$K111))</f>
+      </c>
+      <c r="C111" s="203">
+        <f>IF($K111="","",INDEX('_Datos'!$D$7:$D$200,$K111))</f>
+      </c>
+      <c r="D111" s="203">
+        <f>IF($K111="","",INDEX('_Datos'!$F$7:$F$200,$K111))</f>
+      </c>
+      <c r="E111" s="203">
+        <f>IF($K111="","",INDEX('_Datos'!$G$7:$G$200,$K111))</f>
+      </c>
+      <c r="F111" s="204">
+        <f>IF($K111="","",INDEX('_Datos'!$H$7:$H$200,$K111))</f>
+      </c>
+      <c r="G111" s="202">
+        <f>IF($K111="","",INDEX('_Datos'!$J$7:$J$200,$K111))</f>
+      </c>
+      <c r="H111" s="206">
+        <f>IF($K111="","",INDEX('_Datos'!$K$7:$K$200,$K111))</f>
+      </c>
+      <c r="I111" s="205">
+        <f>IF($K111="","",INDEX('_Datos'!$I$7:$I$200,$K111))</f>
+      </c>
+      <c r="K111" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="202">
+        <f>IF($K112="","",INDEX('_Datos'!$M$7:$M$200,$K112))</f>
+      </c>
+      <c r="C112" s="203">
+        <f>IF($K112="","",INDEX('_Datos'!$D$7:$D$200,$K112))</f>
+      </c>
+      <c r="D112" s="203">
+        <f>IF($K112="","",INDEX('_Datos'!$F$7:$F$200,$K112))</f>
+      </c>
+      <c r="E112" s="203">
+        <f>IF($K112="","",INDEX('_Datos'!$G$7:$G$200,$K112))</f>
+      </c>
+      <c r="F112" s="204">
+        <f>IF($K112="","",INDEX('_Datos'!$H$7:$H$200,$K112))</f>
+      </c>
+      <c r="G112" s="202">
+        <f>IF($K112="","",INDEX('_Datos'!$J$7:$J$200,$K112))</f>
+      </c>
+      <c r="H112" s="206">
+        <f>IF($K112="","",INDEX('_Datos'!$K$7:$K$200,$K112))</f>
+      </c>
+      <c r="I112" s="205">
+        <f>IF($K112="","",INDEX('_Datos'!$I$7:$I$200,$K112))</f>
+      </c>
+      <c r="K112" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="202">
+        <f>IF($K113="","",INDEX('_Datos'!$M$7:$M$200,$K113))</f>
+      </c>
+      <c r="C113" s="203">
+        <f>IF($K113="","",INDEX('_Datos'!$D$7:$D$200,$K113))</f>
+      </c>
+      <c r="D113" s="203">
+        <f>IF($K113="","",INDEX('_Datos'!$F$7:$F$200,$K113))</f>
+      </c>
+      <c r="E113" s="203">
+        <f>IF($K113="","",INDEX('_Datos'!$G$7:$G$200,$K113))</f>
+      </c>
+      <c r="F113" s="204">
+        <f>IF($K113="","",INDEX('_Datos'!$H$7:$H$200,$K113))</f>
+      </c>
+      <c r="G113" s="202">
+        <f>IF($K113="","",INDEX('_Datos'!$J$7:$J$200,$K113))</f>
+      </c>
+      <c r="H113" s="206">
+        <f>IF($K113="","",INDEX('_Datos'!$K$7:$K$200,$K113))</f>
+      </c>
+      <c r="I113" s="205">
+        <f>IF($K113="","",INDEX('_Datos'!$I$7:$I$200,$K113))</f>
+      </c>
+      <c r="K113" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="202">
+        <f>IF($K114="","",INDEX('_Datos'!$M$7:$M$200,$K114))</f>
+      </c>
+      <c r="C114" s="203">
+        <f>IF($K114="","",INDEX('_Datos'!$D$7:$D$200,$K114))</f>
+      </c>
+      <c r="D114" s="203">
+        <f>IF($K114="","",INDEX('_Datos'!$F$7:$F$200,$K114))</f>
+      </c>
+      <c r="E114" s="203">
+        <f>IF($K114="","",INDEX('_Datos'!$G$7:$G$200,$K114))</f>
+      </c>
+      <c r="F114" s="204">
+        <f>IF($K114="","",INDEX('_Datos'!$H$7:$H$200,$K114))</f>
+      </c>
+      <c r="G114" s="202">
+        <f>IF($K114="","",INDEX('_Datos'!$J$7:$J$200,$K114))</f>
+      </c>
+      <c r="H114" s="206">
+        <f>IF($K114="","",INDEX('_Datos'!$K$7:$K$200,$K114))</f>
+      </c>
+      <c r="I114" s="205">
+        <f>IF($K114="","",INDEX('_Datos'!$I$7:$I$200,$K114))</f>
+      </c>
+      <c r="K114" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="202">
+        <f>IF($K115="","",INDEX('_Datos'!$M$7:$M$200,$K115))</f>
+      </c>
+      <c r="C115" s="203">
+        <f>IF($K115="","",INDEX('_Datos'!$D$7:$D$200,$K115))</f>
+      </c>
+      <c r="D115" s="203">
+        <f>IF($K115="","",INDEX('_Datos'!$F$7:$F$200,$K115))</f>
+      </c>
+      <c r="E115" s="203">
+        <f>IF($K115="","",INDEX('_Datos'!$G$7:$G$200,$K115))</f>
+      </c>
+      <c r="F115" s="204">
+        <f>IF($K115="","",INDEX('_Datos'!$H$7:$H$200,$K115))</f>
+      </c>
+      <c r="G115" s="202">
+        <f>IF($K115="","",INDEX('_Datos'!$J$7:$J$200,$K115))</f>
+      </c>
+      <c r="H115" s="206">
+        <f>IF($K115="","",INDEX('_Datos'!$K$7:$K$200,$K115))</f>
+      </c>
+      <c r="I115" s="205">
+        <f>IF($K115="","",INDEX('_Datos'!$I$7:$I$200,$K115))</f>
+      </c>
+      <c r="K115" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="202">
+        <f>IF($K116="","",INDEX('_Datos'!$M$7:$M$200,$K116))</f>
+      </c>
+      <c r="C116" s="203">
+        <f>IF($K116="","",INDEX('_Datos'!$D$7:$D$200,$K116))</f>
+      </c>
+      <c r="D116" s="203">
+        <f>IF($K116="","",INDEX('_Datos'!$F$7:$F$200,$K116))</f>
+      </c>
+      <c r="E116" s="203">
+        <f>IF($K116="","",INDEX('_Datos'!$G$7:$G$200,$K116))</f>
+      </c>
+      <c r="F116" s="204">
+        <f>IF($K116="","",INDEX('_Datos'!$H$7:$H$200,$K116))</f>
+      </c>
+      <c r="G116" s="202">
+        <f>IF($K116="","",INDEX('_Datos'!$J$7:$J$200,$K116))</f>
+      </c>
+      <c r="H116" s="206">
+        <f>IF($K116="","",INDEX('_Datos'!$K$7:$K$200,$K116))</f>
+      </c>
+      <c r="I116" s="205">
+        <f>IF($K116="","",INDEX('_Datos'!$I$7:$I$200,$K116))</f>
+      </c>
+      <c r="K116" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="202">
+        <f>IF($K117="","",INDEX('_Datos'!$M$7:$M$200,$K117))</f>
+      </c>
+      <c r="C117" s="203">
+        <f>IF($K117="","",INDEX('_Datos'!$D$7:$D$200,$K117))</f>
+      </c>
+      <c r="D117" s="203">
+        <f>IF($K117="","",INDEX('_Datos'!$F$7:$F$200,$K117))</f>
+      </c>
+      <c r="E117" s="203">
+        <f>IF($K117="","",INDEX('_Datos'!$G$7:$G$200,$K117))</f>
+      </c>
+      <c r="F117" s="204">
+        <f>IF($K117="","",INDEX('_Datos'!$H$7:$H$200,$K117))</f>
+      </c>
+      <c r="G117" s="202">
+        <f>IF($K117="","",INDEX('_Datos'!$J$7:$J$200,$K117))</f>
+      </c>
+      <c r="H117" s="206">
+        <f>IF($K117="","",INDEX('_Datos'!$K$7:$K$200,$K117))</f>
+      </c>
+      <c r="I117" s="205">
+        <f>IF($K117="","",INDEX('_Datos'!$I$7:$I$200,$K117))</f>
+      </c>
+      <c r="K117" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="202">
+        <f>IF($K118="","",INDEX('_Datos'!$M$7:$M$200,$K118))</f>
+      </c>
+      <c r="C118" s="203">
+        <f>IF($K118="","",INDEX('_Datos'!$D$7:$D$200,$K118))</f>
+      </c>
+      <c r="D118" s="203">
+        <f>IF($K118="","",INDEX('_Datos'!$F$7:$F$200,$K118))</f>
+      </c>
+      <c r="E118" s="203">
+        <f>IF($K118="","",INDEX('_Datos'!$G$7:$G$200,$K118))</f>
+      </c>
+      <c r="F118" s="204">
+        <f>IF($K118="","",INDEX('_Datos'!$H$7:$H$200,$K118))</f>
+      </c>
+      <c r="G118" s="202">
+        <f>IF($K118="","",INDEX('_Datos'!$J$7:$J$200,$K118))</f>
+      </c>
+      <c r="H118" s="206">
+        <f>IF($K118="","",INDEX('_Datos'!$K$7:$K$200,$K118))</f>
+      </c>
+      <c r="I118" s="205">
+        <f>IF($K118="","",INDEX('_Datos'!$I$7:$I$200,$K118))</f>
+      </c>
+      <c r="K118" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="202">
+        <f>IF($K119="","",INDEX('_Datos'!$M$7:$M$200,$K119))</f>
+      </c>
+      <c r="C119" s="203">
+        <f>IF($K119="","",INDEX('_Datos'!$D$7:$D$200,$K119))</f>
+      </c>
+      <c r="D119" s="203">
+        <f>IF($K119="","",INDEX('_Datos'!$F$7:$F$200,$K119))</f>
+      </c>
+      <c r="E119" s="203">
+        <f>IF($K119="","",INDEX('_Datos'!$G$7:$G$200,$K119))</f>
+      </c>
+      <c r="F119" s="204">
+        <f>IF($K119="","",INDEX('_Datos'!$H$7:$H$200,$K119))</f>
+      </c>
+      <c r="G119" s="202">
+        <f>IF($K119="","",INDEX('_Datos'!$J$7:$J$200,$K119))</f>
+      </c>
+      <c r="H119" s="206">
+        <f>IF($K119="","",INDEX('_Datos'!$K$7:$K$200,$K119))</f>
+      </c>
+      <c r="I119" s="205">
+        <f>IF($K119="","",INDEX('_Datos'!$I$7:$I$200,$K119))</f>
+      </c>
+      <c r="K119" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="120">
+      <c r="B120" s="202">
+        <f>IF($K120="","",INDEX('_Datos'!$M$7:$M$200,$K120))</f>
+      </c>
+      <c r="C120" s="203">
+        <f>IF($K120="","",INDEX('_Datos'!$D$7:$D$200,$K120))</f>
+      </c>
+      <c r="D120" s="203">
+        <f>IF($K120="","",INDEX('_Datos'!$F$7:$F$200,$K120))</f>
+      </c>
+      <c r="E120" s="203">
+        <f>IF($K120="","",INDEX('_Datos'!$G$7:$G$200,$K120))</f>
+      </c>
+      <c r="F120" s="204">
+        <f>IF($K120="","",INDEX('_Datos'!$H$7:$H$200,$K120))</f>
+      </c>
+      <c r="G120" s="202">
+        <f>IF($K120="","",INDEX('_Datos'!$J$7:$J$200,$K120))</f>
+      </c>
+      <c r="H120" s="206">
+        <f>IF($K120="","",INDEX('_Datos'!$K$7:$K$200,$K120))</f>
+      </c>
+      <c r="I120" s="205">
+        <f>IF($K120="","",INDEX('_Datos'!$I$7:$I$200,$K120))</f>
+      </c>
+      <c r="K120" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="121">
+      <c r="B121" s="202">
+        <f>IF($K121="","",INDEX('_Datos'!$M$7:$M$200,$K121))</f>
+      </c>
+      <c r="C121" s="203">
+        <f>IF($K121="","",INDEX('_Datos'!$D$7:$D$200,$K121))</f>
+      </c>
+      <c r="D121" s="203">
+        <f>IF($K121="","",INDEX('_Datos'!$F$7:$F$200,$K121))</f>
+      </c>
+      <c r="E121" s="203">
+        <f>IF($K121="","",INDEX('_Datos'!$G$7:$G$200,$K121))</f>
+      </c>
+      <c r="F121" s="204">
+        <f>IF($K121="","",INDEX('_Datos'!$H$7:$H$200,$K121))</f>
+      </c>
+      <c r="G121" s="202">
+        <f>IF($K121="","",INDEX('_Datos'!$J$7:$J$200,$K121))</f>
+      </c>
+      <c r="H121" s="206">
+        <f>IF($K121="","",INDEX('_Datos'!$K$7:$K$200,$K121))</f>
+      </c>
+      <c r="I121" s="205">
+        <f>IF($K121="","",INDEX('_Datos'!$I$7:$I$200,$K121))</f>
+      </c>
+      <c r="K121" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="122">
+      <c r="B122" s="202">
+        <f>IF($K122="","",INDEX('_Datos'!$M$7:$M$200,$K122))</f>
+      </c>
+      <c r="C122" s="203">
+        <f>IF($K122="","",INDEX('_Datos'!$D$7:$D$200,$K122))</f>
+      </c>
+      <c r="D122" s="203">
+        <f>IF($K122="","",INDEX('_Datos'!$F$7:$F$200,$K122))</f>
+      </c>
+      <c r="E122" s="203">
+        <f>IF($K122="","",INDEX('_Datos'!$G$7:$G$200,$K122))</f>
+      </c>
+      <c r="F122" s="204">
+        <f>IF($K122="","",INDEX('_Datos'!$H$7:$H$200,$K122))</f>
+      </c>
+      <c r="G122" s="202">
+        <f>IF($K122="","",INDEX('_Datos'!$J$7:$J$200,$K122))</f>
+      </c>
+      <c r="H122" s="206">
+        <f>IF($K122="","",INDEX('_Datos'!$K$7:$K$200,$K122))</f>
+      </c>
+      <c r="I122" s="205">
+        <f>IF($K122="","",INDEX('_Datos'!$I$7:$I$200,$K122))</f>
+      </c>
+      <c r="K122" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="123">
+      <c r="B123" s="202">
+        <f>IF($K123="","",INDEX('_Datos'!$M$7:$M$200,$K123))</f>
+      </c>
+      <c r="C123" s="203">
+        <f>IF($K123="","",INDEX('_Datos'!$D$7:$D$200,$K123))</f>
+      </c>
+      <c r="D123" s="203">
+        <f>IF($K123="","",INDEX('_Datos'!$F$7:$F$200,$K123))</f>
+      </c>
+      <c r="E123" s="203">
+        <f>IF($K123="","",INDEX('_Datos'!$G$7:$G$200,$K123))</f>
+      </c>
+      <c r="F123" s="204">
+        <f>IF($K123="","",INDEX('_Datos'!$H$7:$H$200,$K123))</f>
+      </c>
+      <c r="G123" s="202">
+        <f>IF($K123="","",INDEX('_Datos'!$J$7:$J$200,$K123))</f>
+      </c>
+      <c r="H123" s="206">
+        <f>IF($K123="","",INDEX('_Datos'!$K$7:$K$200,$K123))</f>
+      </c>
+      <c r="I123" s="205">
+        <f>IF($K123="","",INDEX('_Datos'!$I$7:$I$200,$K123))</f>
+      </c>
+      <c r="K123" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="124">
+      <c r="B124" s="202">
+        <f>IF($K124="","",INDEX('_Datos'!$M$7:$M$200,$K124))</f>
+      </c>
+      <c r="C124" s="203">
+        <f>IF($K124="","",INDEX('_Datos'!$D$7:$D$200,$K124))</f>
+      </c>
+      <c r="D124" s="203">
+        <f>IF($K124="","",INDEX('_Datos'!$F$7:$F$200,$K124))</f>
+      </c>
+      <c r="E124" s="203">
+        <f>IF($K124="","",INDEX('_Datos'!$G$7:$G$200,$K124))</f>
+      </c>
+      <c r="F124" s="204">
+        <f>IF($K124="","",INDEX('_Datos'!$H$7:$H$200,$K124))</f>
+      </c>
+      <c r="G124" s="202">
+        <f>IF($K124="","",INDEX('_Datos'!$J$7:$J$200,$K124))</f>
+      </c>
+      <c r="H124" s="206">
+        <f>IF($K124="","",INDEX('_Datos'!$K$7:$K$200,$K124))</f>
+      </c>
+      <c r="I124" s="205">
+        <f>IF($K124="","",INDEX('_Datos'!$I$7:$I$200,$K124))</f>
+      </c>
+      <c r="K124" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="125">
+      <c r="B125" s="202">
+        <f>IF($K125="","",INDEX('_Datos'!$M$7:$M$200,$K125))</f>
+      </c>
+      <c r="C125" s="203">
+        <f>IF($K125="","",INDEX('_Datos'!$D$7:$D$200,$K125))</f>
+      </c>
+      <c r="D125" s="203">
+        <f>IF($K125="","",INDEX('_Datos'!$F$7:$F$200,$K125))</f>
+      </c>
+      <c r="E125" s="203">
+        <f>IF($K125="","",INDEX('_Datos'!$G$7:$G$200,$K125))</f>
+      </c>
+      <c r="F125" s="204">
+        <f>IF($K125="","",INDEX('_Datos'!$H$7:$H$200,$K125))</f>
+      </c>
+      <c r="G125" s="202">
+        <f>IF($K125="","",INDEX('_Datos'!$J$7:$J$200,$K125))</f>
+      </c>
+      <c r="H125" s="206">
+        <f>IF($K125="","",INDEX('_Datos'!$K$7:$K$200,$K125))</f>
+      </c>
+      <c r="I125" s="205">
+        <f>IF($K125="","",INDEX('_Datos'!$I$7:$I$200,$K125))</f>
+      </c>
+      <c r="K125" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="202">
+        <f>IF($K126="","",INDEX('_Datos'!$M$7:$M$200,$K126))</f>
+      </c>
+      <c r="C126" s="203">
+        <f>IF($K126="","",INDEX('_Datos'!$D$7:$D$200,$K126))</f>
+      </c>
+      <c r="D126" s="203">
+        <f>IF($K126="","",INDEX('_Datos'!$F$7:$F$200,$K126))</f>
+      </c>
+      <c r="E126" s="203">
+        <f>IF($K126="","",INDEX('_Datos'!$G$7:$G$200,$K126))</f>
+      </c>
+      <c r="F126" s="204">
+        <f>IF($K126="","",INDEX('_Datos'!$H$7:$H$200,$K126))</f>
+      </c>
+      <c r="G126" s="202">
+        <f>IF($K126="","",INDEX('_Datos'!$J$7:$J$200,$K126))</f>
+      </c>
+      <c r="H126" s="206">
+        <f>IF($K126="","",INDEX('_Datos'!$K$7:$K$200,$K126))</f>
+      </c>
+      <c r="I126" s="205">
+        <f>IF($K126="","",INDEX('_Datos'!$I$7:$I$200,$K126))</f>
+      </c>
+      <c r="K126" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="202">
+        <f>IF($K127="","",INDEX('_Datos'!$M$7:$M$200,$K127))</f>
+      </c>
+      <c r="C127" s="203">
+        <f>IF($K127="","",INDEX('_Datos'!$D$7:$D$200,$K127))</f>
+      </c>
+      <c r="D127" s="203">
+        <f>IF($K127="","",INDEX('_Datos'!$F$7:$F$200,$K127))</f>
+      </c>
+      <c r="E127" s="203">
+        <f>IF($K127="","",INDEX('_Datos'!$G$7:$G$200,$K127))</f>
+      </c>
+      <c r="F127" s="204">
+        <f>IF($K127="","",INDEX('_Datos'!$H$7:$H$200,$K127))</f>
+      </c>
+      <c r="G127" s="202">
+        <f>IF($K127="","",INDEX('_Datos'!$J$7:$J$200,$K127))</f>
+      </c>
+      <c r="H127" s="206">
+        <f>IF($K127="","",INDEX('_Datos'!$K$7:$K$200,$K127))</f>
+      </c>
+      <c r="I127" s="205">
+        <f>IF($K127="","",INDEX('_Datos'!$I$7:$I$200,$K127))</f>
+      </c>
+      <c r="K127" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" s="202">
+        <f>IF($K128="","",INDEX('_Datos'!$M$7:$M$200,$K128))</f>
+      </c>
+      <c r="C128" s="203">
+        <f>IF($K128="","",INDEX('_Datos'!$D$7:$D$200,$K128))</f>
+      </c>
+      <c r="D128" s="203">
+        <f>IF($K128="","",INDEX('_Datos'!$F$7:$F$200,$K128))</f>
+      </c>
+      <c r="E128" s="203">
+        <f>IF($K128="","",INDEX('_Datos'!$G$7:$G$200,$K128))</f>
+      </c>
+      <c r="F128" s="204">
+        <f>IF($K128="","",INDEX('_Datos'!$H$7:$H$200,$K128))</f>
+      </c>
+      <c r="G128" s="202">
+        <f>IF($K128="","",INDEX('_Datos'!$J$7:$J$200,$K128))</f>
+      </c>
+      <c r="H128" s="206">
+        <f>IF($K128="","",INDEX('_Datos'!$K$7:$K$200,$K128))</f>
+      </c>
+      <c r="I128" s="205">
+        <f>IF($K128="","",INDEX('_Datos'!$I$7:$I$200,$K128))</f>
+      </c>
+      <c r="K128" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" s="202">
+        <f>IF($K129="","",INDEX('_Datos'!$M$7:$M$200,$K129))</f>
+      </c>
+      <c r="C129" s="203">
+        <f>IF($K129="","",INDEX('_Datos'!$D$7:$D$200,$K129))</f>
+      </c>
+      <c r="D129" s="203">
+        <f>IF($K129="","",INDEX('_Datos'!$F$7:$F$200,$K129))</f>
+      </c>
+      <c r="E129" s="203">
+        <f>IF($K129="","",INDEX('_Datos'!$G$7:$G$200,$K129))</f>
+      </c>
+      <c r="F129" s="204">
+        <f>IF($K129="","",INDEX('_Datos'!$H$7:$H$200,$K129))</f>
+      </c>
+      <c r="G129" s="202">
+        <f>IF($K129="","",INDEX('_Datos'!$J$7:$J$200,$K129))</f>
+      </c>
+      <c r="H129" s="206">
+        <f>IF($K129="","",INDEX('_Datos'!$K$7:$K$200,$K129))</f>
+      </c>
+      <c r="I129" s="205">
+        <f>IF($K129="","",INDEX('_Datos'!$I$7:$I$200,$K129))</f>
+      </c>
+      <c r="K129" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" s="202">
+        <f>IF($K130="","",INDEX('_Datos'!$M$7:$M$200,$K130))</f>
+      </c>
+      <c r="C130" s="203">
+        <f>IF($K130="","",INDEX('_Datos'!$D$7:$D$200,$K130))</f>
+      </c>
+      <c r="D130" s="203">
+        <f>IF($K130="","",INDEX('_Datos'!$F$7:$F$200,$K130))</f>
+      </c>
+      <c r="E130" s="203">
+        <f>IF($K130="","",INDEX('_Datos'!$G$7:$G$200,$K130))</f>
+      </c>
+      <c r="F130" s="204">
+        <f>IF($K130="","",INDEX('_Datos'!$H$7:$H$200,$K130))</f>
+      </c>
+      <c r="G130" s="202">
+        <f>IF($K130="","",INDEX('_Datos'!$J$7:$J$200,$K130))</f>
+      </c>
+      <c r="H130" s="206">
+        <f>IF($K130="","",INDEX('_Datos'!$K$7:$K$200,$K130))</f>
+      </c>
+      <c r="I130" s="205">
+        <f>IF($K130="","",INDEX('_Datos'!$I$7:$I$200,$K130))</f>
+      </c>
+      <c r="K130" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" s="202">
+        <f>IF($K131="","",INDEX('_Datos'!$M$7:$M$200,$K131))</f>
+      </c>
+      <c r="C131" s="203">
+        <f>IF($K131="","",INDEX('_Datos'!$D$7:$D$200,$K131))</f>
+      </c>
+      <c r="D131" s="203">
+        <f>IF($K131="","",INDEX('_Datos'!$F$7:$F$200,$K131))</f>
+      </c>
+      <c r="E131" s="203">
+        <f>IF($K131="","",INDEX('_Datos'!$G$7:$G$200,$K131))</f>
+      </c>
+      <c r="F131" s="204">
+        <f>IF($K131="","",INDEX('_Datos'!$H$7:$H$200,$K131))</f>
+      </c>
+      <c r="G131" s="202">
+        <f>IF($K131="","",INDEX('_Datos'!$J$7:$J$200,$K131))</f>
+      </c>
+      <c r="H131" s="206">
+        <f>IF($K131="","",INDEX('_Datos'!$K$7:$K$200,$K131))</f>
+      </c>
+      <c r="I131" s="205">
+        <f>IF($K131="","",INDEX('_Datos'!$I$7:$I$200,$K131))</f>
+      </c>
+      <c r="K131" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" s="202">
+        <f>IF($K132="","",INDEX('_Datos'!$M$7:$M$200,$K132))</f>
+      </c>
+      <c r="C132" s="203">
+        <f>IF($K132="","",INDEX('_Datos'!$D$7:$D$200,$K132))</f>
+      </c>
+      <c r="D132" s="203">
+        <f>IF($K132="","",INDEX('_Datos'!$F$7:$F$200,$K132))</f>
+      </c>
+      <c r="E132" s="203">
+        <f>IF($K132="","",INDEX('_Datos'!$G$7:$G$200,$K132))</f>
+      </c>
+      <c r="F132" s="204">
+        <f>IF($K132="","",INDEX('_Datos'!$H$7:$H$200,$K132))</f>
+      </c>
+      <c r="G132" s="202">
+        <f>IF($K132="","",INDEX('_Datos'!$J$7:$J$200,$K132))</f>
+      </c>
+      <c r="H132" s="206">
+        <f>IF($K132="","",INDEX('_Datos'!$K$7:$K$200,$K132))</f>
+      </c>
+      <c r="I132" s="205">
+        <f>IF($K132="","",INDEX('_Datos'!$I$7:$I$200,$K132))</f>
+      </c>
+      <c r="K132" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" s="202">
+        <f>IF($K133="","",INDEX('_Datos'!$M$7:$M$200,$K133))</f>
+      </c>
+      <c r="C133" s="203">
+        <f>IF($K133="","",INDEX('_Datos'!$D$7:$D$200,$K133))</f>
+      </c>
+      <c r="D133" s="203">
+        <f>IF($K133="","",INDEX('_Datos'!$F$7:$F$200,$K133))</f>
+      </c>
+      <c r="E133" s="203">
+        <f>IF($K133="","",INDEX('_Datos'!$G$7:$G$200,$K133))</f>
+      </c>
+      <c r="F133" s="204">
+        <f>IF($K133="","",INDEX('_Datos'!$H$7:$H$200,$K133))</f>
+      </c>
+      <c r="G133" s="202">
+        <f>IF($K133="","",INDEX('_Datos'!$J$7:$J$200,$K133))</f>
+      </c>
+      <c r="H133" s="206">
+        <f>IF($K133="","",INDEX('_Datos'!$K$7:$K$200,$K133))</f>
+      </c>
+      <c r="I133" s="205">
+        <f>IF($K133="","",INDEX('_Datos'!$I$7:$I$200,$K133))</f>
+      </c>
+      <c r="K133" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" s="202">
+        <f>IF($K134="","",INDEX('_Datos'!$M$7:$M$200,$K134))</f>
+      </c>
+      <c r="C134" s="203">
+        <f>IF($K134="","",INDEX('_Datos'!$D$7:$D$200,$K134))</f>
+      </c>
+      <c r="D134" s="203">
+        <f>IF($K134="","",INDEX('_Datos'!$F$7:$F$200,$K134))</f>
+      </c>
+      <c r="E134" s="203">
+        <f>IF($K134="","",INDEX('_Datos'!$G$7:$G$200,$K134))</f>
+      </c>
+      <c r="F134" s="204">
+        <f>IF($K134="","",INDEX('_Datos'!$H$7:$H$200,$K134))</f>
+      </c>
+      <c r="G134" s="202">
+        <f>IF($K134="","",INDEX('_Datos'!$J$7:$J$200,$K134))</f>
+      </c>
+      <c r="H134" s="206">
+        <f>IF($K134="","",INDEX('_Datos'!$K$7:$K$200,$K134))</f>
+      </c>
+      <c r="I134" s="205">
+        <f>IF($K134="","",INDEX('_Datos'!$I$7:$I$200,$K134))</f>
+      </c>
+      <c r="K134" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" s="202">
+        <f>IF($K135="","",INDEX('_Datos'!$M$7:$M$200,$K135))</f>
+      </c>
+      <c r="C135" s="203">
+        <f>IF($K135="","",INDEX('_Datos'!$D$7:$D$200,$K135))</f>
+      </c>
+      <c r="D135" s="203">
+        <f>IF($K135="","",INDEX('_Datos'!$F$7:$F$200,$K135))</f>
+      </c>
+      <c r="E135" s="203">
+        <f>IF($K135="","",INDEX('_Datos'!$G$7:$G$200,$K135))</f>
+      </c>
+      <c r="F135" s="204">
+        <f>IF($K135="","",INDEX('_Datos'!$H$7:$H$200,$K135))</f>
+      </c>
+      <c r="G135" s="202">
+        <f>IF($K135="","",INDEX('_Datos'!$J$7:$J$200,$K135))</f>
+      </c>
+      <c r="H135" s="206">
+        <f>IF($K135="","",INDEX('_Datos'!$K$7:$K$200,$K135))</f>
+      </c>
+      <c r="I135" s="205">
+        <f>IF($K135="","",INDEX('_Datos'!$I$7:$I$200,$K135))</f>
+      </c>
+      <c r="K135" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="202">
+        <f>IF($K136="","",INDEX('_Datos'!$M$7:$M$200,$K136))</f>
+      </c>
+      <c r="C136" s="203">
+        <f>IF($K136="","",INDEX('_Datos'!$D$7:$D$200,$K136))</f>
+      </c>
+      <c r="D136" s="203">
+        <f>IF($K136="","",INDEX('_Datos'!$F$7:$F$200,$K136))</f>
+      </c>
+      <c r="E136" s="203">
+        <f>IF($K136="","",INDEX('_Datos'!$G$7:$G$200,$K136))</f>
+      </c>
+      <c r="F136" s="204">
+        <f>IF($K136="","",INDEX('_Datos'!$H$7:$H$200,$K136))</f>
+      </c>
+      <c r="G136" s="202">
+        <f>IF($K136="","",INDEX('_Datos'!$J$7:$J$200,$K136))</f>
+      </c>
+      <c r="H136" s="206">
+        <f>IF($K136="","",INDEX('_Datos'!$K$7:$K$200,$K136))</f>
+      </c>
+      <c r="I136" s="205">
+        <f>IF($K136="","",INDEX('_Datos'!$I$7:$I$200,$K136))</f>
+      </c>
+      <c r="K136" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="202">
+        <f>IF($K137="","",INDEX('_Datos'!$M$7:$M$200,$K137))</f>
+      </c>
+      <c r="C137" s="203">
+        <f>IF($K137="","",INDEX('_Datos'!$D$7:$D$200,$K137))</f>
+      </c>
+      <c r="D137" s="203">
+        <f>IF($K137="","",INDEX('_Datos'!$F$7:$F$200,$K137))</f>
+      </c>
+      <c r="E137" s="203">
+        <f>IF($K137="","",INDEX('_Datos'!$G$7:$G$200,$K137))</f>
+      </c>
+      <c r="F137" s="204">
+        <f>IF($K137="","",INDEX('_Datos'!$H$7:$H$200,$K137))</f>
+      </c>
+      <c r="G137" s="202">
+        <f>IF($K137="","",INDEX('_Datos'!$J$7:$J$200,$K137))</f>
+      </c>
+      <c r="H137" s="206">
+        <f>IF($K137="","",INDEX('_Datos'!$K$7:$K$200,$K137))</f>
+      </c>
+      <c r="I137" s="205">
+        <f>IF($K137="","",INDEX('_Datos'!$I$7:$I$200,$K137))</f>
+      </c>
+      <c r="K137" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="202">
+        <f>IF($K138="","",INDEX('_Datos'!$M$7:$M$200,$K138))</f>
+      </c>
+      <c r="C138" s="203">
+        <f>IF($K138="","",INDEX('_Datos'!$D$7:$D$200,$K138))</f>
+      </c>
+      <c r="D138" s="203">
+        <f>IF($K138="","",INDEX('_Datos'!$F$7:$F$200,$K138))</f>
+      </c>
+      <c r="E138" s="203">
+        <f>IF($K138="","",INDEX('_Datos'!$G$7:$G$200,$K138))</f>
+      </c>
+      <c r="F138" s="204">
+        <f>IF($K138="","",INDEX('_Datos'!$H$7:$H$200,$K138))</f>
+      </c>
+      <c r="G138" s="202">
+        <f>IF($K138="","",INDEX('_Datos'!$J$7:$J$200,$K138))</f>
+      </c>
+      <c r="H138" s="206">
+        <f>IF($K138="","",INDEX('_Datos'!$K$7:$K$200,$K138))</f>
+      </c>
+      <c r="I138" s="205">
+        <f>IF($K138="","",INDEX('_Datos'!$I$7:$I$200,$K138))</f>
+      </c>
+      <c r="K138" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="202">
+        <f>IF($K139="","",INDEX('_Datos'!$M$7:$M$200,$K139))</f>
+      </c>
+      <c r="C139" s="203">
+        <f>IF($K139="","",INDEX('_Datos'!$D$7:$D$200,$K139))</f>
+      </c>
+      <c r="D139" s="203">
+        <f>IF($K139="","",INDEX('_Datos'!$F$7:$F$200,$K139))</f>
+      </c>
+      <c r="E139" s="203">
+        <f>IF($K139="","",INDEX('_Datos'!$G$7:$G$200,$K139))</f>
+      </c>
+      <c r="F139" s="204">
+        <f>IF($K139="","",INDEX('_Datos'!$H$7:$H$200,$K139))</f>
+      </c>
+      <c r="G139" s="202">
+        <f>IF($K139="","",INDEX('_Datos'!$J$7:$J$200,$K139))</f>
+      </c>
+      <c r="H139" s="206">
+        <f>IF($K139="","",INDEX('_Datos'!$K$7:$K$200,$K139))</f>
+      </c>
+      <c r="I139" s="205">
+        <f>IF($K139="","",INDEX('_Datos'!$I$7:$I$200,$K139))</f>
+      </c>
+      <c r="K139" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="202">
+        <f>IF($K140="","",INDEX('_Datos'!$M$7:$M$200,$K140))</f>
+      </c>
+      <c r="C140" s="203">
+        <f>IF($K140="","",INDEX('_Datos'!$D$7:$D$200,$K140))</f>
+      </c>
+      <c r="D140" s="203">
+        <f>IF($K140="","",INDEX('_Datos'!$F$7:$F$200,$K140))</f>
+      </c>
+      <c r="E140" s="203">
+        <f>IF($K140="","",INDEX('_Datos'!$G$7:$G$200,$K140))</f>
+      </c>
+      <c r="F140" s="204">
+        <f>IF($K140="","",INDEX('_Datos'!$H$7:$H$200,$K140))</f>
+      </c>
+      <c r="G140" s="202">
+        <f>IF($K140="","",INDEX('_Datos'!$J$7:$J$200,$K140))</f>
+      </c>
+      <c r="H140" s="206">
+        <f>IF($K140="","",INDEX('_Datos'!$K$7:$K$200,$K140))</f>
+      </c>
+      <c r="I140" s="205">
+        <f>IF($K140="","",INDEX('_Datos'!$I$7:$I$200,$K140))</f>
+      </c>
+      <c r="K140" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="141">
+      <c r="B141" s="202">
+        <f>IF($K141="","",INDEX('_Datos'!$M$7:$M$200,$K141))</f>
+      </c>
+      <c r="C141" s="203">
+        <f>IF($K141="","",INDEX('_Datos'!$D$7:$D$200,$K141))</f>
+      </c>
+      <c r="D141" s="203">
+        <f>IF($K141="","",INDEX('_Datos'!$F$7:$F$200,$K141))</f>
+      </c>
+      <c r="E141" s="203">
+        <f>IF($K141="","",INDEX('_Datos'!$G$7:$G$200,$K141))</f>
+      </c>
+      <c r="F141" s="204">
+        <f>IF($K141="","",INDEX('_Datos'!$H$7:$H$200,$K141))</f>
+      </c>
+      <c r="G141" s="202">
+        <f>IF($K141="","",INDEX('_Datos'!$J$7:$J$200,$K141))</f>
+      </c>
+      <c r="H141" s="206">
+        <f>IF($K141="","",INDEX('_Datos'!$K$7:$K$200,$K141))</f>
+      </c>
+      <c r="I141" s="205">
+        <f>IF($K141="","",INDEX('_Datos'!$I$7:$I$200,$K141))</f>
+      </c>
+      <c r="K141" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="142">
+      <c r="B142" s="202">
+        <f>IF($K142="","",INDEX('_Datos'!$M$7:$M$200,$K142))</f>
+      </c>
+      <c r="C142" s="203">
+        <f>IF($K142="","",INDEX('_Datos'!$D$7:$D$200,$K142))</f>
+      </c>
+      <c r="D142" s="203">
+        <f>IF($K142="","",INDEX('_Datos'!$F$7:$F$200,$K142))</f>
+      </c>
+      <c r="E142" s="203">
+        <f>IF($K142="","",INDEX('_Datos'!$G$7:$G$200,$K142))</f>
+      </c>
+      <c r="F142" s="204">
+        <f>IF($K142="","",INDEX('_Datos'!$H$7:$H$200,$K142))</f>
+      </c>
+      <c r="G142" s="202">
+        <f>IF($K142="","",INDEX('_Datos'!$J$7:$J$200,$K142))</f>
+      </c>
+      <c r="H142" s="206">
+        <f>IF($K142="","",INDEX('_Datos'!$K$7:$K$200,$K142))</f>
+      </c>
+      <c r="I142" s="205">
+        <f>IF($K142="","",INDEX('_Datos'!$I$7:$I$200,$K142))</f>
+      </c>
+      <c r="K142" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" s="202">
+        <f>IF($K143="","",INDEX('_Datos'!$M$7:$M$200,$K143))</f>
+      </c>
+      <c r="C143" s="203">
+        <f>IF($K143="","",INDEX('_Datos'!$D$7:$D$200,$K143))</f>
+      </c>
+      <c r="D143" s="203">
+        <f>IF($K143="","",INDEX('_Datos'!$F$7:$F$200,$K143))</f>
+      </c>
+      <c r="E143" s="203">
+        <f>IF($K143="","",INDEX('_Datos'!$G$7:$G$200,$K143))</f>
+      </c>
+      <c r="F143" s="204">
+        <f>IF($K143="","",INDEX('_Datos'!$H$7:$H$200,$K143))</f>
+      </c>
+      <c r="G143" s="202">
+        <f>IF($K143="","",INDEX('_Datos'!$J$7:$J$200,$K143))</f>
+      </c>
+      <c r="H143" s="206">
+        <f>IF($K143="","",INDEX('_Datos'!$K$7:$K$200,$K143))</f>
+      </c>
+      <c r="I143" s="205">
+        <f>IF($K143="","",INDEX('_Datos'!$I$7:$I$200,$K143))</f>
+      </c>
+      <c r="K143" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="144">
+      <c r="B144" s="202">
+        <f>IF($K144="","",INDEX('_Datos'!$M$7:$M$200,$K144))</f>
+      </c>
+      <c r="C144" s="203">
+        <f>IF($K144="","",INDEX('_Datos'!$D$7:$D$200,$K144))</f>
+      </c>
+      <c r="D144" s="203">
+        <f>IF($K144="","",INDEX('_Datos'!$F$7:$F$200,$K144))</f>
+      </c>
+      <c r="E144" s="203">
+        <f>IF($K144="","",INDEX('_Datos'!$G$7:$G$200,$K144))</f>
+      </c>
+      <c r="F144" s="204">
+        <f>IF($K144="","",INDEX('_Datos'!$H$7:$H$200,$K144))</f>
+      </c>
+      <c r="G144" s="202">
+        <f>IF($K144="","",INDEX('_Datos'!$J$7:$J$200,$K144))</f>
+      </c>
+      <c r="H144" s="206">
+        <f>IF($K144="","",INDEX('_Datos'!$K$7:$K$200,$K144))</f>
+      </c>
+      <c r="I144" s="205">
+        <f>IF($K144="","",INDEX('_Datos'!$I$7:$I$200,$K144))</f>
+      </c>
+      <c r="K144" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="145">
+      <c r="B145" s="202">
+        <f>IF($K145="","",INDEX('_Datos'!$M$7:$M$200,$K145))</f>
+      </c>
+      <c r="C145" s="203">
+        <f>IF($K145="","",INDEX('_Datos'!$D$7:$D$200,$K145))</f>
+      </c>
+      <c r="D145" s="203">
+        <f>IF($K145="","",INDEX('_Datos'!$F$7:$F$200,$K145))</f>
+      </c>
+      <c r="E145" s="203">
+        <f>IF($K145="","",INDEX('_Datos'!$G$7:$G$200,$K145))</f>
+      </c>
+      <c r="F145" s="204">
+        <f>IF($K145="","",INDEX('_Datos'!$H$7:$H$200,$K145))</f>
+      </c>
+      <c r="G145" s="202">
+        <f>IF($K145="","",INDEX('_Datos'!$J$7:$J$200,$K145))</f>
+      </c>
+      <c r="H145" s="206">
+        <f>IF($K145="","",INDEX('_Datos'!$K$7:$K$200,$K145))</f>
+      </c>
+      <c r="I145" s="205">
+        <f>IF($K145="","",INDEX('_Datos'!$I$7:$I$200,$K145))</f>
+      </c>
+      <c r="K145" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="146">
+      <c r="B146" s="202">
+        <f>IF($K146="","",INDEX('_Datos'!$M$7:$M$200,$K146))</f>
+      </c>
+      <c r="C146" s="203">
+        <f>IF($K146="","",INDEX('_Datos'!$D$7:$D$200,$K146))</f>
+      </c>
+      <c r="D146" s="203">
+        <f>IF($K146="","",INDEX('_Datos'!$F$7:$F$200,$K146))</f>
+      </c>
+      <c r="E146" s="203">
+        <f>IF($K146="","",INDEX('_Datos'!$G$7:$G$200,$K146))</f>
+      </c>
+      <c r="F146" s="204">
+        <f>IF($K146="","",INDEX('_Datos'!$H$7:$H$200,$K146))</f>
+      </c>
+      <c r="G146" s="202">
+        <f>IF($K146="","",INDEX('_Datos'!$J$7:$J$200,$K146))</f>
+      </c>
+      <c r="H146" s="206">
+        <f>IF($K146="","",INDEX('_Datos'!$K$7:$K$200,$K146))</f>
+      </c>
+      <c r="I146" s="205">
+        <f>IF($K146="","",INDEX('_Datos'!$I$7:$I$200,$K146))</f>
+      </c>
+      <c r="K146" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="147">
+      <c r="B147" s="202">
+        <f>IF($K147="","",INDEX('_Datos'!$M$7:$M$200,$K147))</f>
+      </c>
+      <c r="C147" s="203">
+        <f>IF($K147="","",INDEX('_Datos'!$D$7:$D$200,$K147))</f>
+      </c>
+      <c r="D147" s="203">
+        <f>IF($K147="","",INDEX('_Datos'!$F$7:$F$200,$K147))</f>
+      </c>
+      <c r="E147" s="203">
+        <f>IF($K147="","",INDEX('_Datos'!$G$7:$G$200,$K147))</f>
+      </c>
+      <c r="F147" s="204">
+        <f>IF($K147="","",INDEX('_Datos'!$H$7:$H$200,$K147))</f>
+      </c>
+      <c r="G147" s="202">
+        <f>IF($K147="","",INDEX('_Datos'!$J$7:$J$200,$K147))</f>
+      </c>
+      <c r="H147" s="206">
+        <f>IF($K147="","",INDEX('_Datos'!$K$7:$K$200,$K147))</f>
+      </c>
+      <c r="I147" s="205">
+        <f>IF($K147="","",INDEX('_Datos'!$I$7:$I$200,$K147))</f>
+      </c>
+      <c r="K147" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="B148" s="202">
+        <f>IF($K148="","",INDEX('_Datos'!$M$7:$M$200,$K148))</f>
+      </c>
+      <c r="C148" s="203">
+        <f>IF($K148="","",INDEX('_Datos'!$D$7:$D$200,$K148))</f>
+      </c>
+      <c r="D148" s="203">
+        <f>IF($K148="","",INDEX('_Datos'!$F$7:$F$200,$K148))</f>
+      </c>
+      <c r="E148" s="203">
+        <f>IF($K148="","",INDEX('_Datos'!$G$7:$G$200,$K148))</f>
+      </c>
+      <c r="F148" s="204">
+        <f>IF($K148="","",INDEX('_Datos'!$H$7:$H$200,$K148))</f>
+      </c>
+      <c r="G148" s="202">
+        <f>IF($K148="","",INDEX('_Datos'!$J$7:$J$200,$K148))</f>
+      </c>
+      <c r="H148" s="206">
+        <f>IF($K148="","",INDEX('_Datos'!$K$7:$K$200,$K148))</f>
+      </c>
+      <c r="I148" s="205">
+        <f>IF($K148="","",INDEX('_Datos'!$I$7:$I$200,$K148))</f>
+      </c>
+      <c r="K148" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="149">
+      <c r="B149" s="202">
+        <f>IF($K149="","",INDEX('_Datos'!$M$7:$M$200,$K149))</f>
+      </c>
+      <c r="C149" s="203">
+        <f>IF($K149="","",INDEX('_Datos'!$D$7:$D$200,$K149))</f>
+      </c>
+      <c r="D149" s="203">
+        <f>IF($K149="","",INDEX('_Datos'!$F$7:$F$200,$K149))</f>
+      </c>
+      <c r="E149" s="203">
+        <f>IF($K149="","",INDEX('_Datos'!$G$7:$G$200,$K149))</f>
+      </c>
+      <c r="F149" s="204">
+        <f>IF($K149="","",INDEX('_Datos'!$H$7:$H$200,$K149))</f>
+      </c>
+      <c r="G149" s="202">
+        <f>IF($K149="","",INDEX('_Datos'!$J$7:$J$200,$K149))</f>
+      </c>
+      <c r="H149" s="206">
+        <f>IF($K149="","",INDEX('_Datos'!$K$7:$K$200,$K149))</f>
+      </c>
+      <c r="I149" s="205">
+        <f>IF($K149="","",INDEX('_Datos'!$I$7:$I$200,$K149))</f>
+      </c>
+      <c r="K149" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="150">
+      <c r="B150" s="202">
+        <f>IF($K150="","",INDEX('_Datos'!$M$7:$M$200,$K150))</f>
+      </c>
+      <c r="C150" s="203">
+        <f>IF($K150="","",INDEX('_Datos'!$D$7:$D$200,$K150))</f>
+      </c>
+      <c r="D150" s="203">
+        <f>IF($K150="","",INDEX('_Datos'!$F$7:$F$200,$K150))</f>
+      </c>
+      <c r="E150" s="203">
+        <f>IF($K150="","",INDEX('_Datos'!$G$7:$G$200,$K150))</f>
+      </c>
+      <c r="F150" s="204">
+        <f>IF($K150="","",INDEX('_Datos'!$H$7:$H$200,$K150))</f>
+      </c>
+      <c r="G150" s="202">
+        <f>IF($K150="","",INDEX('_Datos'!$J$7:$J$200,$K150))</f>
+      </c>
+      <c r="H150" s="206">
+        <f>IF($K150="","",INDEX('_Datos'!$K$7:$K$200,$K150))</f>
+      </c>
+      <c r="I150" s="205">
+        <f>IF($K150="","",INDEX('_Datos'!$I$7:$I$200,$K150))</f>
+      </c>
+      <c r="K150" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="151">
+      <c r="B151" s="202">
+        <f>IF($K151="","",INDEX('_Datos'!$M$7:$M$200,$K151))</f>
+      </c>
+      <c r="C151" s="203">
+        <f>IF($K151="","",INDEX('_Datos'!$D$7:$D$200,$K151))</f>
+      </c>
+      <c r="D151" s="203">
+        <f>IF($K151="","",INDEX('_Datos'!$F$7:$F$200,$K151))</f>
+      </c>
+      <c r="E151" s="203">
+        <f>IF($K151="","",INDEX('_Datos'!$G$7:$G$200,$K151))</f>
+      </c>
+      <c r="F151" s="204">
+        <f>IF($K151="","",INDEX('_Datos'!$H$7:$H$200,$K151))</f>
+      </c>
+      <c r="G151" s="202">
+        <f>IF($K151="","",INDEX('_Datos'!$J$7:$J$200,$K151))</f>
+      </c>
+      <c r="H151" s="206">
+        <f>IF($K151="","",INDEX('_Datos'!$K$7:$K$200,$K151))</f>
+      </c>
+      <c r="I151" s="205">
+        <f>IF($K151="","",INDEX('_Datos'!$I$7:$I$200,$K151))</f>
+      </c>
+      <c r="K151" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="152">
+      <c r="B152" s="202">
+        <f>IF($K152="","",INDEX('_Datos'!$M$7:$M$200,$K152))</f>
+      </c>
+      <c r="C152" s="203">
+        <f>IF($K152="","",INDEX('_Datos'!$D$7:$D$200,$K152))</f>
+      </c>
+      <c r="D152" s="203">
+        <f>IF($K152="","",INDEX('_Datos'!$F$7:$F$200,$K152))</f>
+      </c>
+      <c r="E152" s="203">
+        <f>IF($K152="","",INDEX('_Datos'!$G$7:$G$200,$K152))</f>
+      </c>
+      <c r="F152" s="204">
+        <f>IF($K152="","",INDEX('_Datos'!$H$7:$H$200,$K152))</f>
+      </c>
+      <c r="G152" s="202">
+        <f>IF($K152="","",INDEX('_Datos'!$J$7:$J$200,$K152))</f>
+      </c>
+      <c r="H152" s="206">
+        <f>IF($K152="","",INDEX('_Datos'!$K$7:$K$200,$K152))</f>
+      </c>
+      <c r="I152" s="205">
+        <f>IF($K152="","",INDEX('_Datos'!$I$7:$I$200,$K152))</f>
+      </c>
+      <c r="K152" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="153">
+      <c r="B153" s="202">
+        <f>IF($K153="","",INDEX('_Datos'!$M$7:$M$200,$K153))</f>
+      </c>
+      <c r="C153" s="203">
+        <f>IF($K153="","",INDEX('_Datos'!$D$7:$D$200,$K153))</f>
+      </c>
+      <c r="D153" s="203">
+        <f>IF($K153="","",INDEX('_Datos'!$F$7:$F$200,$K153))</f>
+      </c>
+      <c r="E153" s="203">
+        <f>IF($K153="","",INDEX('_Datos'!$G$7:$G$200,$K153))</f>
+      </c>
+      <c r="F153" s="204">
+        <f>IF($K153="","",INDEX('_Datos'!$H$7:$H$200,$K153))</f>
+      </c>
+      <c r="G153" s="202">
+        <f>IF($K153="","",INDEX('_Datos'!$J$7:$J$200,$K153))</f>
+      </c>
+      <c r="H153" s="206">
+        <f>IF($K153="","",INDEX('_Datos'!$K$7:$K$200,$K153))</f>
+      </c>
+      <c r="I153" s="205">
+        <f>IF($K153="","",INDEX('_Datos'!$I$7:$I$200,$K153))</f>
+      </c>
+      <c r="K153" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="154">
+      <c r="B154" s="202">
+        <f>IF($K154="","",INDEX('_Datos'!$M$7:$M$200,$K154))</f>
+      </c>
+      <c r="C154" s="203">
+        <f>IF($K154="","",INDEX('_Datos'!$D$7:$D$200,$K154))</f>
+      </c>
+      <c r="D154" s="203">
+        <f>IF($K154="","",INDEX('_Datos'!$F$7:$F$200,$K154))</f>
+      </c>
+      <c r="E154" s="203">
+        <f>IF($K154="","",INDEX('_Datos'!$G$7:$G$200,$K154))</f>
+      </c>
+      <c r="F154" s="204">
+        <f>IF($K154="","",INDEX('_Datos'!$H$7:$H$200,$K154))</f>
+      </c>
+      <c r="G154" s="202">
+        <f>IF($K154="","",INDEX('_Datos'!$J$7:$J$200,$K154))</f>
+      </c>
+      <c r="H154" s="206">
+        <f>IF($K154="","",INDEX('_Datos'!$K$7:$K$200,$K154))</f>
+      </c>
+      <c r="I154" s="205">
+        <f>IF($K154="","",INDEX('_Datos'!$I$7:$I$200,$K154))</f>
+      </c>
+      <c r="K154" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="B155" s="202">
+        <f>IF($K155="","",INDEX('_Datos'!$M$7:$M$200,$K155))</f>
+      </c>
+      <c r="C155" s="203">
+        <f>IF($K155="","",INDEX('_Datos'!$D$7:$D$200,$K155))</f>
+      </c>
+      <c r="D155" s="203">
+        <f>IF($K155="","",INDEX('_Datos'!$F$7:$F$200,$K155))</f>
+      </c>
+      <c r="E155" s="203">
+        <f>IF($K155="","",INDEX('_Datos'!$G$7:$G$200,$K155))</f>
+      </c>
+      <c r="F155" s="204">
+        <f>IF($K155="","",INDEX('_Datos'!$H$7:$H$200,$K155))</f>
+      </c>
+      <c r="G155" s="202">
+        <f>IF($K155="","",INDEX('_Datos'!$J$7:$J$200,$K155))</f>
+      </c>
+      <c r="H155" s="206">
+        <f>IF($K155="","",INDEX('_Datos'!$K$7:$K$200,$K155))</f>
+      </c>
+      <c r="I155" s="205">
+        <f>IF($K155="","",INDEX('_Datos'!$I$7:$I$200,$K155))</f>
+      </c>
+      <c r="K155" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
+      </c>
+    </row>
+    <row r="156">
+      <c r="B156" s="202">
+        <f>IF($K156="","",INDEX('_Datos'!$M$7:$M$200,$K156))</f>
+      </c>
+      <c r="C156" s="203">
+        <f>IF($K156="","",INDEX('_Datos'!$D$7:$D$200,$K156))</f>
+      </c>
+      <c r="D156" s="203">
+        <f>IF($K156="","",INDEX('_Datos'!$F$7:$F$200,$K156))</f>
+      </c>
+      <c r="E156" s="203">
+        <f>IF($K156="","",INDEX('_Datos'!$G$7:$G$200,$K156))</f>
+      </c>
+      <c r="F156" s="204">
+        <f>IF($K156="","",INDEX('_Datos'!$H$7:$H$200,$K156))</f>
+      </c>
+      <c r="G156" s="202">
+        <f>IF($K156="","",INDEX('_Datos'!$J$7:$J$200,$K156))</f>
+      </c>
+      <c r="H156" s="206">
+        <f>IF($K156="","",INDEX('_Datos'!$K$7:$K$200,$K156))</f>
+      </c>
+      <c r="I156" s="205">
+        <f>IF($K156="","",INDEX('_Datos'!$I$7:$I$200,$K156))</f>
+      </c>
+      <c r="K156" s="200">
+        <f>IFERROR(MATCH(SMALL('_Datos'!$L$7:$L$200,ROW()-7+1),'_Datos'!$L$7:$L$200,0),"")</f>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B17:I17"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="B5:I5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B8:I14">
-    <cfRule type="expression" dxfId="21" priority="40">
-      <formula>$C8&lt;&gt;""</formula>
+  <conditionalFormatting sqref="B7:I156">
+    <cfRule type="expression" dxfId="22" priority="31">
+      <formula>AND($D7&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="21" priority="32">
+      <formula>$D7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B19:I98">
-    <cfRule type="expression" dxfId="22" priority="31">
-      <formula>AND($D19&lt;&gt;"",MOD(ROW(),2)=0)</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="21" priority="32">
-      <formula>$D19&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G19:H98">
+  <conditionalFormatting sqref="G7:H156">
     <cfRule type="expression" dxfId="23" priority="33">
-      <formula>$G19="Vencido"</formula>
+      <formula>$G7="Vencido"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="24" priority="34">
-      <formula>$G19="Próximo a vencer"</formula>
+      <formula>$G7="Próximo a vencer"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="25" priority="35">
-      <formula>$G19="En curso"</formula>
+      <formula>$G7="En curso"</formula>
     </cfRule>
     <cfRule type="expression" dxfId="26" priority="36">
-      <formula>$G19="Completado"</formula>
+      <formula>$G7="Completado"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
@@ -19193,353 +21140,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
-    <col min="2" max="9" width="14" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="26" customHeight="1">
-      <c r="B1" s="196" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GUÍA DE USO Y DOCUMENTACIÓN DE FÓRMULAS</t>
-        </is>
-      </c>
-      <c r="C1" s="196"/>
-      <c r="D1" s="196"/>
-      <c r="E1" s="196"/>
-      <c r="F1" s="196"/>
-      <c r="G1" s="196"/>
-      <c r="H1" s="196"/>
-      <c r="I1" s="196"/>
-    </row>
-    <row r="2" ht="34" customHeight="1">
-      <c r="B2" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Este libro fue ampliado SIN modificar ningún dato, fecha, nombre, estado ni fórmula existente. Todas las mejoras son aditivas: formato condicional, hojas auxiliares y fórmulas nuevas.</t>
-        </is>
-      </c>
-      <c r="C2" s="198"/>
-      <c r="D2" s="198"/>
-      <c r="E2" s="198"/>
-      <c r="F2" s="198"/>
-      <c r="G2" s="198"/>
-      <c r="H2" s="198"/>
-      <c r="I2" s="198"/>
-    </row>
-    <row r="4">
-      <c r="B4" s="197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">HOJAS NUEVAS</t>
-        </is>
-      </c>
-      <c r="C4" s="197"/>
-      <c r="D4" s="197"/>
-      <c r="E4" s="197"/>
-      <c r="F4" s="197"/>
-      <c r="G4" s="197"/>
-      <c r="H4" s="197"/>
-      <c r="I4" s="197"/>
-    </row>
-    <row r="5" ht="28" customHeight="1">
-      <c r="B5" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Tablero: resumen ejecutivo (KPIs, avance por módulo OKR y por sprint). Ideal para reuniones de seguimiento.</t>
-        </is>
-      </c>
-      <c r="C5" s="198"/>
-      <c r="D5" s="198"/>
-      <c r="E5" s="198"/>
-      <c r="F5" s="198"/>
-      <c r="G5" s="198"/>
-      <c r="H5" s="198"/>
-      <c r="I5" s="198"/>
-    </row>
-    <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Entregas Próximas: lista automática de entregas ordenada por sprint y fecha (columna F), con semáforo y resumen por sprint.</t>
-        </is>
-      </c>
-      <c r="C6" s="198"/>
-      <c r="D6" s="198"/>
-      <c r="E6" s="198"/>
-      <c r="F6" s="198"/>
-      <c r="G6" s="198"/>
-      <c r="H6" s="198"/>
-      <c r="I6" s="198"/>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="B7" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• _Datos (oculta): motor de cálculo. Lee la hoja Gantt y prepara los datos. No editar.</t>
-        </is>
-      </c>
-      <c r="C7" s="198"/>
-      <c r="D7" s="198"/>
-      <c r="E7" s="198"/>
-      <c r="F7" s="198"/>
-      <c r="G7" s="198"/>
-      <c r="H7" s="198"/>
-      <c r="I7" s="198"/>
-    </row>
-    <row r="9">
-      <c r="B9" s="197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CRITERIOS DE ESTADO (semáforo)</t>
-        </is>
-      </c>
-      <c r="C9" s="197"/>
-      <c r="D9" s="197"/>
-      <c r="E9" s="197"/>
-      <c r="F9" s="197"/>
-      <c r="G9" s="197"/>
-      <c r="H9" s="197"/>
-      <c r="I9" s="197"/>
-    </row>
-    <row r="10" ht="26" customHeight="1">
-      <c r="B10" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fecha de entrega = columna F (Fecha) si existe; si está vacía se usa la columna L (FIN) como respaldo.</t>
-        </is>
-      </c>
-      <c r="C10" s="198"/>
-      <c r="D10" s="198"/>
-      <c r="E10" s="198"/>
-      <c r="F10" s="198"/>
-      <c r="G10" s="198"/>
-      <c r="H10" s="198"/>
-      <c r="I10" s="198"/>
-    </row>
-    <row r="11" ht="24" customHeight="1">
-      <c r="B11" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Completado: Progreso ≥ 100%.   • Vencido: fecha de entrega anterior a HOY y progreso &lt; 100%.</t>
-        </is>
-      </c>
-      <c r="C11" s="198"/>
-      <c r="D11" s="198"/>
-      <c r="E11" s="198"/>
-      <c r="F11" s="198"/>
-      <c r="G11" s="198"/>
-      <c r="H11" s="198"/>
-      <c r="I11" s="198"/>
-    </row>
-    <row r="12" ht="26" customHeight="1">
-      <c r="B12" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Próximo a vencer: faltan entre 0 y el 'umbral' de días (editable en Entregas Próximas, por defecto 7).   • En curso: dentro de plazo.</t>
-        </is>
-      </c>
-      <c r="C12" s="198"/>
-      <c r="D12" s="198"/>
-      <c r="E12" s="198"/>
-      <c r="F12" s="198"/>
-      <c r="G12" s="198"/>
-      <c r="H12" s="198"/>
-      <c r="I12" s="198"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="B13" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Colores: Rojo = Vencido · Amarillo = Próximo a vencer · Verde = En curso/Completado.</t>
-        </is>
-      </c>
-      <c r="C13" s="198"/>
-      <c r="D13" s="198"/>
-      <c r="E13" s="198"/>
-      <c r="F13" s="198"/>
-      <c r="G13" s="198"/>
-      <c r="H13" s="198"/>
-      <c r="I13" s="198"/>
-    </row>
-    <row r="15">
-      <c r="B15" s="197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">FÓRMULAS CLAVE</t>
-        </is>
-      </c>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
-      <c r="F15" s="197"/>
-      <c r="G15" s="197"/>
-      <c r="H15" s="197"/>
-      <c r="I15" s="197"/>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="B16" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Ordenamiento sin macros: SMALL + MATCH + INDEX sobre una 'ClaveOrden' = Sprint×1.000.000 + Fecha + Fila/100.000.</t>
-        </is>
-      </c>
-      <c r="C16" s="198"/>
-      <c r="D16" s="198"/>
-      <c r="E16" s="198"/>
-      <c r="F16" s="198"/>
-      <c r="G16" s="198"/>
-      <c r="H16" s="198"/>
-      <c r="I16" s="198"/>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="B17" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Detección de tareas vs. fases: las filas de fase tienen texto en la columna INICIO (K); las tareas tienen una fecha. EsTarea = Y(hay tarea, no es fase, hay fecha).</t>
-        </is>
-      </c>
-      <c r="C17" s="198"/>
-      <c r="D17" s="198"/>
-      <c r="E17" s="198"/>
-      <c r="F17" s="198"/>
-      <c r="G17" s="198"/>
-      <c r="H17" s="198"/>
-      <c r="I17" s="198"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="B18" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Módulo de cada tarea: LOOKUP(2,1/(...)) localiza el último título de fase situado por encima.</t>
-        </is>
-      </c>
-      <c r="C18" s="198"/>
-      <c r="D18" s="198"/>
-      <c r="E18" s="198"/>
-      <c r="F18" s="198"/>
-      <c r="G18" s="198"/>
-      <c r="H18" s="198"/>
-      <c r="I18" s="198"/>
-    </row>
-    <row r="19" ht="28" customHeight="1">
-      <c r="B19" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Conteos y promedios: COUNTIF/COUNTIFS, MINIFS y AVERAGEIF sobre rangos amplios (filas 7 a 200) para que el libro escale solo.</t>
-        </is>
-      </c>
-      <c r="C19" s="198"/>
-      <c r="D19" s="198"/>
-      <c r="E19" s="198"/>
-      <c r="F19" s="198"/>
-      <c r="G19" s="198"/>
-      <c r="H19" s="198"/>
-      <c r="I19" s="198"/>
-    </row>
-    <row r="21">
-      <c r="B21" s="197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ESCALABILIDAD</t>
-        </is>
-      </c>
-      <c r="C21" s="197"/>
-      <c r="D21" s="197"/>
-      <c r="E21" s="197"/>
-      <c r="F21" s="197"/>
-      <c r="G21" s="197"/>
-      <c r="H21" s="197"/>
-      <c r="I21" s="197"/>
-    </row>
-    <row r="22" ht="36" customHeight="1">
-      <c r="B22" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Todas las fórmulas abarcan hasta la fila 200 de la hoja Gantt. Puede agregar sprints, tareas, entregables, responsables y fechas: el Tablero y Entregas Próximas se actualizan solos. Para más de 200 filas, amplíe el rango en la hoja _Datos.</t>
-        </is>
-      </c>
-      <c r="C22" s="198"/>
-      <c r="D22" s="198"/>
-      <c r="E22" s="198"/>
-      <c r="F22" s="198"/>
-      <c r="G22" s="198"/>
-      <c r="H22" s="198"/>
-      <c r="I22" s="198"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="197" t="inlineStr">
-        <is>
-          <t xml:space="preserve">OBSERVACIONES DETECTADAS (no se modificaron datos; se informan para su revisión)</t>
-        </is>
-      </c>
-      <c r="C24" s="197"/>
-      <c r="D24" s="197"/>
-      <c r="E24" s="197"/>
-      <c r="F24" s="197"/>
-      <c r="G24" s="197"/>
-      <c r="H24" s="197"/>
-      <c r="I24" s="197"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="B25" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Promedios de fase: las celdas J27 y J36 (filas de fase 4 y 5) promedian rangos que no corresponden a sus tareas. El Tablero recalcula el avance por módulo de forma independiente y correcta. Si desea corregir el origen: J27 → =PROMEDIO(J28:J35) ; J36 → =PROMEDIO(J37:J47).</t>
-        </is>
-      </c>
-      <c r="C25" s="198"/>
-      <c r="D25" s="198"/>
-      <c r="E25" s="198"/>
-      <c r="F25" s="198"/>
-      <c r="G25" s="198"/>
-      <c r="H25" s="198"/>
-      <c r="I25" s="198"/>
-    </row>
-    <row r="26" ht="36" customHeight="1">
-      <c r="B26" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Fechas a revisar (posibles errores de carga, no modificadas): K13 = 19/11/2026 (posterior a su FIN), K40 = 01/12/2026 y filas con INICIO mayor que FIN (41, 42, 46, 47), que generan DÍAS negativos.</t>
-        </is>
-      </c>
-      <c r="C26" s="198"/>
-      <c r="D26" s="198"/>
-      <c r="E26" s="198"/>
-      <c r="F26" s="198"/>
-      <c r="G26" s="198"/>
-      <c r="H26" s="198"/>
-      <c r="I26" s="198"/>
-    </row>
-    <row r="27" ht="26" customHeight="1">
-      <c r="B27" s="198" t="inlineStr">
-        <is>
-          <t xml:space="preserve">• Filas 79-80 contienen textos sueltos sin fecha; quedan excluidos de los cálculos automáticamente.</t>
-        </is>
-      </c>
-      <c r="C27" s="198"/>
-      <c r="D27" s="198"/>
-      <c r="E27" s="198"/>
-      <c r="F27" s="198"/>
-      <c r="G27" s="198"/>
-      <c r="H27" s="198"/>
-      <c r="I27" s="198"/>
-    </row>
-  </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B1:I1"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="B4:I4"/>
-    <mergeCell ref="B5:I5"/>
-    <mergeCell ref="B6:I6"/>
-    <mergeCell ref="B7:I7"/>
-    <mergeCell ref="B9:I9"/>
-    <mergeCell ref="B10:I10"/>
-    <mergeCell ref="B11:I11"/>
-    <mergeCell ref="B12:I12"/>
-    <mergeCell ref="B13:I13"/>
-    <mergeCell ref="B15:I15"/>
-    <mergeCell ref="B16:I16"/>
-    <mergeCell ref="B17:I17"/>
-    <mergeCell ref="B18:I18"/>
-    <mergeCell ref="B19:I19"/>
-    <mergeCell ref="B21:I21"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B25:I25"/>
-    <mergeCell ref="B26:I26"/>
-    <mergeCell ref="B27:I27"/>
-  </mergeCells>
-  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N200"/>
+  <dimension ref="A1:Q200"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -19630,6 +21231,16 @@
           <t xml:space="preserve">SprintNum</t>
         </is>
       </c>
+      <c r="P6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CandSprint</t>
+        </is>
+      </c>
+      <c r="Q6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SprintExiste</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="200">
@@ -19660,7 +21271,7 @@
         <f>IF($C7,'Proyecto Datos (OKR´s)'!$J7,"")</f>
       </c>
       <c r="J7" s="201">
-        <f>IF($C7,IF($I7&gt;=1,"Completado",IF($H7&lt;TODAY(),"Vencido",IF(($H7-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C7,IF($I7&gt;=1,"Completado",IF($H7&lt;TODAY(),"Vencido",IF(($H7-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K7" s="200">
         <f>IF($C7,$H7-TODAY(),"")</f>
@@ -19673,6 +21284,12 @@
       </c>
       <c r="N7" s="200">
         <f>IF($C7,IF('Proyecto Datos (OKR´s)'!$E7="",9999,'Proyecto Datos (OKR´s)'!$E7),"")</f>
+      </c>
+      <c r="P7" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q7" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P7)&gt;0,$P7,"")</f>
       </c>
     </row>
     <row r="8">
@@ -19704,7 +21321,7 @@
         <f>IF($C8,'Proyecto Datos (OKR´s)'!$J8,"")</f>
       </c>
       <c r="J8" s="201">
-        <f>IF($C8,IF($I8&gt;=1,"Completado",IF($H8&lt;TODAY(),"Vencido",IF(($H8-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C8,IF($I8&gt;=1,"Completado",IF($H8&lt;TODAY(),"Vencido",IF(($H8-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K8" s="200">
         <f>IF($C8,$H8-TODAY(),"")</f>
@@ -19717,6 +21334,12 @@
       </c>
       <c r="N8" s="200">
         <f>IF($C8,IF('Proyecto Datos (OKR´s)'!$E8="",9999,'Proyecto Datos (OKR´s)'!$E8),"")</f>
+      </c>
+      <c r="P8" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q8" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P8)&gt;0,$P8,"")</f>
       </c>
     </row>
     <row r="9">
@@ -19748,7 +21371,7 @@
         <f>IF($C9,'Proyecto Datos (OKR´s)'!$J9,"")</f>
       </c>
       <c r="J9" s="201">
-        <f>IF($C9,IF($I9&gt;=1,"Completado",IF($H9&lt;TODAY(),"Vencido",IF(($H9-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C9,IF($I9&gt;=1,"Completado",IF($H9&lt;TODAY(),"Vencido",IF(($H9-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K9" s="200">
         <f>IF($C9,$H9-TODAY(),"")</f>
@@ -19761,6 +21384,12 @@
       </c>
       <c r="N9" s="200">
         <f>IF($C9,IF('Proyecto Datos (OKR´s)'!$E9="",9999,'Proyecto Datos (OKR´s)'!$E9),"")</f>
+      </c>
+      <c r="P9" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q9" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P9)&gt;0,$P9,"")</f>
       </c>
     </row>
     <row r="10">
@@ -19792,7 +21421,7 @@
         <f>IF($C10,'Proyecto Datos (OKR´s)'!$J10,"")</f>
       </c>
       <c r="J10" s="201">
-        <f>IF($C10,IF($I10&gt;=1,"Completado",IF($H10&lt;TODAY(),"Vencido",IF(($H10-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C10,IF($I10&gt;=1,"Completado",IF($H10&lt;TODAY(),"Vencido",IF(($H10-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K10" s="200">
         <f>IF($C10,$H10-TODAY(),"")</f>
@@ -19805,6 +21434,12 @@
       </c>
       <c r="N10" s="200">
         <f>IF($C10,IF('Proyecto Datos (OKR´s)'!$E10="",9999,'Proyecto Datos (OKR´s)'!$E10),"")</f>
+      </c>
+      <c r="P10" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q10" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P10)&gt;0,$P10,"")</f>
       </c>
     </row>
     <row r="11">
@@ -19836,7 +21471,7 @@
         <f>IF($C11,'Proyecto Datos (OKR´s)'!$J11,"")</f>
       </c>
       <c r="J11" s="201">
-        <f>IF($C11,IF($I11&gt;=1,"Completado",IF($H11&lt;TODAY(),"Vencido",IF(($H11-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C11,IF($I11&gt;=1,"Completado",IF($H11&lt;TODAY(),"Vencido",IF(($H11-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K11" s="200">
         <f>IF($C11,$H11-TODAY(),"")</f>
@@ -19849,6 +21484,12 @@
       </c>
       <c r="N11" s="200">
         <f>IF($C11,IF('Proyecto Datos (OKR´s)'!$E11="",9999,'Proyecto Datos (OKR´s)'!$E11),"")</f>
+      </c>
+      <c r="P11" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q11" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P11)&gt;0,$P11,"")</f>
       </c>
     </row>
     <row r="12">
@@ -19880,7 +21521,7 @@
         <f>IF($C12,'Proyecto Datos (OKR´s)'!$J12,"")</f>
       </c>
       <c r="J12" s="201">
-        <f>IF($C12,IF($I12&gt;=1,"Completado",IF($H12&lt;TODAY(),"Vencido",IF(($H12-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C12,IF($I12&gt;=1,"Completado",IF($H12&lt;TODAY(),"Vencido",IF(($H12-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K12" s="200">
         <f>IF($C12,$H12-TODAY(),"")</f>
@@ -19893,6 +21534,12 @@
       </c>
       <c r="N12" s="200">
         <f>IF($C12,IF('Proyecto Datos (OKR´s)'!$E12="",9999,'Proyecto Datos (OKR´s)'!$E12),"")</f>
+      </c>
+      <c r="P12" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q12" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P12)&gt;0,$P12,"")</f>
       </c>
     </row>
     <row r="13">
@@ -19924,7 +21571,7 @@
         <f>IF($C13,'Proyecto Datos (OKR´s)'!$J13,"")</f>
       </c>
       <c r="J13" s="201">
-        <f>IF($C13,IF($I13&gt;=1,"Completado",IF($H13&lt;TODAY(),"Vencido",IF(($H13-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C13,IF($I13&gt;=1,"Completado",IF($H13&lt;TODAY(),"Vencido",IF(($H13-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K13" s="200">
         <f>IF($C13,$H13-TODAY(),"")</f>
@@ -19937,6 +21584,12 @@
       </c>
       <c r="N13" s="200">
         <f>IF($C13,IF('Proyecto Datos (OKR´s)'!$E13="",9999,'Proyecto Datos (OKR´s)'!$E13),"")</f>
+      </c>
+      <c r="P13" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q13" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P13)&gt;0,$P13,"")</f>
       </c>
     </row>
     <row r="14">
@@ -19968,7 +21621,7 @@
         <f>IF($C14,'Proyecto Datos (OKR´s)'!$J14,"")</f>
       </c>
       <c r="J14" s="201">
-        <f>IF($C14,IF($I14&gt;=1,"Completado",IF($H14&lt;TODAY(),"Vencido",IF(($H14-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C14,IF($I14&gt;=1,"Completado",IF($H14&lt;TODAY(),"Vencido",IF(($H14-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K14" s="200">
         <f>IF($C14,$H14-TODAY(),"")</f>
@@ -19981,6 +21634,12 @@
       </c>
       <c r="N14" s="200">
         <f>IF($C14,IF('Proyecto Datos (OKR´s)'!$E14="",9999,'Proyecto Datos (OKR´s)'!$E14),"")</f>
+      </c>
+      <c r="P14" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q14" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P14)&gt;0,$P14,"")</f>
       </c>
     </row>
     <row r="15">
@@ -20012,7 +21671,7 @@
         <f>IF($C15,'Proyecto Datos (OKR´s)'!$J15,"")</f>
       </c>
       <c r="J15" s="201">
-        <f>IF($C15,IF($I15&gt;=1,"Completado",IF($H15&lt;TODAY(),"Vencido",IF(($H15-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C15,IF($I15&gt;=1,"Completado",IF($H15&lt;TODAY(),"Vencido",IF(($H15-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K15" s="200">
         <f>IF($C15,$H15-TODAY(),"")</f>
@@ -20025,6 +21684,12 @@
       </c>
       <c r="N15" s="200">
         <f>IF($C15,IF('Proyecto Datos (OKR´s)'!$E15="",9999,'Proyecto Datos (OKR´s)'!$E15),"")</f>
+      </c>
+      <c r="P15" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q15" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P15)&gt;0,$P15,"")</f>
       </c>
     </row>
     <row r="16">
@@ -20056,7 +21721,7 @@
         <f>IF($C16,'Proyecto Datos (OKR´s)'!$J16,"")</f>
       </c>
       <c r="J16" s="201">
-        <f>IF($C16,IF($I16&gt;=1,"Completado",IF($H16&lt;TODAY(),"Vencido",IF(($H16-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C16,IF($I16&gt;=1,"Completado",IF($H16&lt;TODAY(),"Vencido",IF(($H16-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K16" s="200">
         <f>IF($C16,$H16-TODAY(),"")</f>
@@ -20069,6 +21734,12 @@
       </c>
       <c r="N16" s="200">
         <f>IF($C16,IF('Proyecto Datos (OKR´s)'!$E16="",9999,'Proyecto Datos (OKR´s)'!$E16),"")</f>
+      </c>
+      <c r="P16" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q16" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P16)&gt;0,$P16,"")</f>
       </c>
     </row>
     <row r="17">
@@ -20100,7 +21771,7 @@
         <f>IF($C17,'Proyecto Datos (OKR´s)'!$J17,"")</f>
       </c>
       <c r="J17" s="201">
-        <f>IF($C17,IF($I17&gt;=1,"Completado",IF($H17&lt;TODAY(),"Vencido",IF(($H17-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C17,IF($I17&gt;=1,"Completado",IF($H17&lt;TODAY(),"Vencido",IF(($H17-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K17" s="200">
         <f>IF($C17,$H17-TODAY(),"")</f>
@@ -20113,6 +21784,12 @@
       </c>
       <c r="N17" s="200">
         <f>IF($C17,IF('Proyecto Datos (OKR´s)'!$E17="",9999,'Proyecto Datos (OKR´s)'!$E17),"")</f>
+      </c>
+      <c r="P17" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q17" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P17)&gt;0,$P17,"")</f>
       </c>
     </row>
     <row r="18">
@@ -20144,7 +21821,7 @@
         <f>IF($C18,'Proyecto Datos (OKR´s)'!$J18,"")</f>
       </c>
       <c r="J18" s="201">
-        <f>IF($C18,IF($I18&gt;=1,"Completado",IF($H18&lt;TODAY(),"Vencido",IF(($H18-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C18,IF($I18&gt;=1,"Completado",IF($H18&lt;TODAY(),"Vencido",IF(($H18-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K18" s="200">
         <f>IF($C18,$H18-TODAY(),"")</f>
@@ -20157,6 +21834,12 @@
       </c>
       <c r="N18" s="200">
         <f>IF($C18,IF('Proyecto Datos (OKR´s)'!$E18="",9999,'Proyecto Datos (OKR´s)'!$E18),"")</f>
+      </c>
+      <c r="P18" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q18" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P18)&gt;0,$P18,"")</f>
       </c>
     </row>
     <row r="19">
@@ -20188,7 +21871,7 @@
         <f>IF($C19,'Proyecto Datos (OKR´s)'!$J19,"")</f>
       </c>
       <c r="J19" s="201">
-        <f>IF($C19,IF($I19&gt;=1,"Completado",IF($H19&lt;TODAY(),"Vencido",IF(($H19-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C19,IF($I19&gt;=1,"Completado",IF($H19&lt;TODAY(),"Vencido",IF(($H19-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K19" s="200">
         <f>IF($C19,$H19-TODAY(),"")</f>
@@ -20201,6 +21884,12 @@
       </c>
       <c r="N19" s="200">
         <f>IF($C19,IF('Proyecto Datos (OKR´s)'!$E19="",9999,'Proyecto Datos (OKR´s)'!$E19),"")</f>
+      </c>
+      <c r="P19" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q19" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P19)&gt;0,$P19,"")</f>
       </c>
     </row>
     <row r="20">
@@ -20232,7 +21921,7 @@
         <f>IF($C20,'Proyecto Datos (OKR´s)'!$J20,"")</f>
       </c>
       <c r="J20" s="201">
-        <f>IF($C20,IF($I20&gt;=1,"Completado",IF($H20&lt;TODAY(),"Vencido",IF(($H20-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C20,IF($I20&gt;=1,"Completado",IF($H20&lt;TODAY(),"Vencido",IF(($H20-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K20" s="200">
         <f>IF($C20,$H20-TODAY(),"")</f>
@@ -20245,6 +21934,12 @@
       </c>
       <c r="N20" s="200">
         <f>IF($C20,IF('Proyecto Datos (OKR´s)'!$E20="",9999,'Proyecto Datos (OKR´s)'!$E20),"")</f>
+      </c>
+      <c r="P20" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q20" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P20)&gt;0,$P20,"")</f>
       </c>
     </row>
     <row r="21">
@@ -20276,7 +21971,7 @@
         <f>IF($C21,'Proyecto Datos (OKR´s)'!$J21,"")</f>
       </c>
       <c r="J21" s="201">
-        <f>IF($C21,IF($I21&gt;=1,"Completado",IF($H21&lt;TODAY(),"Vencido",IF(($H21-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C21,IF($I21&gt;=1,"Completado",IF($H21&lt;TODAY(),"Vencido",IF(($H21-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K21" s="200">
         <f>IF($C21,$H21-TODAY(),"")</f>
@@ -20289,6 +21984,12 @@
       </c>
       <c r="N21" s="200">
         <f>IF($C21,IF('Proyecto Datos (OKR´s)'!$E21="",9999,'Proyecto Datos (OKR´s)'!$E21),"")</f>
+      </c>
+      <c r="P21" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q21" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P21)&gt;0,$P21,"")</f>
       </c>
     </row>
     <row r="22">
@@ -20320,7 +22021,7 @@
         <f>IF($C22,'Proyecto Datos (OKR´s)'!$J22,"")</f>
       </c>
       <c r="J22" s="201">
-        <f>IF($C22,IF($I22&gt;=1,"Completado",IF($H22&lt;TODAY(),"Vencido",IF(($H22-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C22,IF($I22&gt;=1,"Completado",IF($H22&lt;TODAY(),"Vencido",IF(($H22-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K22" s="200">
         <f>IF($C22,$H22-TODAY(),"")</f>
@@ -20333,6 +22034,12 @@
       </c>
       <c r="N22" s="200">
         <f>IF($C22,IF('Proyecto Datos (OKR´s)'!$E22="",9999,'Proyecto Datos (OKR´s)'!$E22),"")</f>
+      </c>
+      <c r="P22" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q22" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P22)&gt;0,$P22,"")</f>
       </c>
     </row>
     <row r="23">
@@ -20364,7 +22071,7 @@
         <f>IF($C23,'Proyecto Datos (OKR´s)'!$J23,"")</f>
       </c>
       <c r="J23" s="201">
-        <f>IF($C23,IF($I23&gt;=1,"Completado",IF($H23&lt;TODAY(),"Vencido",IF(($H23-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C23,IF($I23&gt;=1,"Completado",IF($H23&lt;TODAY(),"Vencido",IF(($H23-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K23" s="200">
         <f>IF($C23,$H23-TODAY(),"")</f>
@@ -20377,6 +22084,12 @@
       </c>
       <c r="N23" s="200">
         <f>IF($C23,IF('Proyecto Datos (OKR´s)'!$E23="",9999,'Proyecto Datos (OKR´s)'!$E23),"")</f>
+      </c>
+      <c r="P23" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q23" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P23)&gt;0,$P23,"")</f>
       </c>
     </row>
     <row r="24">
@@ -20408,7 +22121,7 @@
         <f>IF($C24,'Proyecto Datos (OKR´s)'!$J24,"")</f>
       </c>
       <c r="J24" s="201">
-        <f>IF($C24,IF($I24&gt;=1,"Completado",IF($H24&lt;TODAY(),"Vencido",IF(($H24-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C24,IF($I24&gt;=1,"Completado",IF($H24&lt;TODAY(),"Vencido",IF(($H24-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K24" s="200">
         <f>IF($C24,$H24-TODAY(),"")</f>
@@ -20421,6 +22134,12 @@
       </c>
       <c r="N24" s="200">
         <f>IF($C24,IF('Proyecto Datos (OKR´s)'!$E24="",9999,'Proyecto Datos (OKR´s)'!$E24),"")</f>
+      </c>
+      <c r="P24" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q24" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P24)&gt;0,$P24,"")</f>
       </c>
     </row>
     <row r="25">
@@ -20452,7 +22171,7 @@
         <f>IF($C25,'Proyecto Datos (OKR´s)'!$J25,"")</f>
       </c>
       <c r="J25" s="201">
-        <f>IF($C25,IF($I25&gt;=1,"Completado",IF($H25&lt;TODAY(),"Vencido",IF(($H25-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C25,IF($I25&gt;=1,"Completado",IF($H25&lt;TODAY(),"Vencido",IF(($H25-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K25" s="200">
         <f>IF($C25,$H25-TODAY(),"")</f>
@@ -20465,6 +22184,12 @@
       </c>
       <c r="N25" s="200">
         <f>IF($C25,IF('Proyecto Datos (OKR´s)'!$E25="",9999,'Proyecto Datos (OKR´s)'!$E25),"")</f>
+      </c>
+      <c r="P25" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q25" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P25)&gt;0,$P25,"")</f>
       </c>
     </row>
     <row r="26">
@@ -20496,7 +22221,7 @@
         <f>IF($C26,'Proyecto Datos (OKR´s)'!$J26,"")</f>
       </c>
       <c r="J26" s="201">
-        <f>IF($C26,IF($I26&gt;=1,"Completado",IF($H26&lt;TODAY(),"Vencido",IF(($H26-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C26,IF($I26&gt;=1,"Completado",IF($H26&lt;TODAY(),"Vencido",IF(($H26-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K26" s="200">
         <f>IF($C26,$H26-TODAY(),"")</f>
@@ -20509,6 +22234,12 @@
       </c>
       <c r="N26" s="200">
         <f>IF($C26,IF('Proyecto Datos (OKR´s)'!$E26="",9999,'Proyecto Datos (OKR´s)'!$E26),"")</f>
+      </c>
+      <c r="P26" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q26" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P26)&gt;0,$P26,"")</f>
       </c>
     </row>
     <row r="27">
@@ -20540,7 +22271,7 @@
         <f>IF($C27,'Proyecto Datos (OKR´s)'!$J27,"")</f>
       </c>
       <c r="J27" s="201">
-        <f>IF($C27,IF($I27&gt;=1,"Completado",IF($H27&lt;TODAY(),"Vencido",IF(($H27-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C27,IF($I27&gt;=1,"Completado",IF($H27&lt;TODAY(),"Vencido",IF(($H27-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K27" s="200">
         <f>IF($C27,$H27-TODAY(),"")</f>
@@ -20553,6 +22284,12 @@
       </c>
       <c r="N27" s="200">
         <f>IF($C27,IF('Proyecto Datos (OKR´s)'!$E27="",9999,'Proyecto Datos (OKR´s)'!$E27),"")</f>
+      </c>
+      <c r="P27" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q27" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P27)&gt;0,$P27,"")</f>
       </c>
     </row>
     <row r="28">
@@ -20584,7 +22321,7 @@
         <f>IF($C28,'Proyecto Datos (OKR´s)'!$J28,"")</f>
       </c>
       <c r="J28" s="201">
-        <f>IF($C28,IF($I28&gt;=1,"Completado",IF($H28&lt;TODAY(),"Vencido",IF(($H28-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C28,IF($I28&gt;=1,"Completado",IF($H28&lt;TODAY(),"Vencido",IF(($H28-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K28" s="200">
         <f>IF($C28,$H28-TODAY(),"")</f>
@@ -20597,6 +22334,12 @@
       </c>
       <c r="N28" s="200">
         <f>IF($C28,IF('Proyecto Datos (OKR´s)'!$E28="",9999,'Proyecto Datos (OKR´s)'!$E28),"")</f>
+      </c>
+      <c r="P28" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q28" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P28)&gt;0,$P28,"")</f>
       </c>
     </row>
     <row r="29">
@@ -20628,7 +22371,7 @@
         <f>IF($C29,'Proyecto Datos (OKR´s)'!$J29,"")</f>
       </c>
       <c r="J29" s="201">
-        <f>IF($C29,IF($I29&gt;=1,"Completado",IF($H29&lt;TODAY(),"Vencido",IF(($H29-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C29,IF($I29&gt;=1,"Completado",IF($H29&lt;TODAY(),"Vencido",IF(($H29-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K29" s="200">
         <f>IF($C29,$H29-TODAY(),"")</f>
@@ -20641,6 +22384,12 @@
       </c>
       <c r="N29" s="200">
         <f>IF($C29,IF('Proyecto Datos (OKR´s)'!$E29="",9999,'Proyecto Datos (OKR´s)'!$E29),"")</f>
+      </c>
+      <c r="P29" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q29" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P29)&gt;0,$P29,"")</f>
       </c>
     </row>
     <row r="30">
@@ -20672,7 +22421,7 @@
         <f>IF($C30,'Proyecto Datos (OKR´s)'!$J30,"")</f>
       </c>
       <c r="J30" s="201">
-        <f>IF($C30,IF($I30&gt;=1,"Completado",IF($H30&lt;TODAY(),"Vencido",IF(($H30-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C30,IF($I30&gt;=1,"Completado",IF($H30&lt;TODAY(),"Vencido",IF(($H30-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K30" s="200">
         <f>IF($C30,$H30-TODAY(),"")</f>
@@ -20685,6 +22434,12 @@
       </c>
       <c r="N30" s="200">
         <f>IF($C30,IF('Proyecto Datos (OKR´s)'!$E30="",9999,'Proyecto Datos (OKR´s)'!$E30),"")</f>
+      </c>
+      <c r="P30" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q30" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P30)&gt;0,$P30,"")</f>
       </c>
     </row>
     <row r="31">
@@ -20716,7 +22471,7 @@
         <f>IF($C31,'Proyecto Datos (OKR´s)'!$J31,"")</f>
       </c>
       <c r="J31" s="201">
-        <f>IF($C31,IF($I31&gt;=1,"Completado",IF($H31&lt;TODAY(),"Vencido",IF(($H31-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C31,IF($I31&gt;=1,"Completado",IF($H31&lt;TODAY(),"Vencido",IF(($H31-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K31" s="200">
         <f>IF($C31,$H31-TODAY(),"")</f>
@@ -20729,6 +22484,12 @@
       </c>
       <c r="N31" s="200">
         <f>IF($C31,IF('Proyecto Datos (OKR´s)'!$E31="",9999,'Proyecto Datos (OKR´s)'!$E31),"")</f>
+      </c>
+      <c r="P31" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q31" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P31)&gt;0,$P31,"")</f>
       </c>
     </row>
     <row r="32">
@@ -20760,7 +22521,7 @@
         <f>IF($C32,'Proyecto Datos (OKR´s)'!$J32,"")</f>
       </c>
       <c r="J32" s="201">
-        <f>IF($C32,IF($I32&gt;=1,"Completado",IF($H32&lt;TODAY(),"Vencido",IF(($H32-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C32,IF($I32&gt;=1,"Completado",IF($H32&lt;TODAY(),"Vencido",IF(($H32-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K32" s="200">
         <f>IF($C32,$H32-TODAY(),"")</f>
@@ -20773,6 +22534,12 @@
       </c>
       <c r="N32" s="200">
         <f>IF($C32,IF('Proyecto Datos (OKR´s)'!$E32="",9999,'Proyecto Datos (OKR´s)'!$E32),"")</f>
+      </c>
+      <c r="P32" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q32" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P32)&gt;0,$P32,"")</f>
       </c>
     </row>
     <row r="33">
@@ -20804,7 +22571,7 @@
         <f>IF($C33,'Proyecto Datos (OKR´s)'!$J33,"")</f>
       </c>
       <c r="J33" s="201">
-        <f>IF($C33,IF($I33&gt;=1,"Completado",IF($H33&lt;TODAY(),"Vencido",IF(($H33-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C33,IF($I33&gt;=1,"Completado",IF($H33&lt;TODAY(),"Vencido",IF(($H33-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K33" s="200">
         <f>IF($C33,$H33-TODAY(),"")</f>
@@ -20817,6 +22584,12 @@
       </c>
       <c r="N33" s="200">
         <f>IF($C33,IF('Proyecto Datos (OKR´s)'!$E33="",9999,'Proyecto Datos (OKR´s)'!$E33),"")</f>
+      </c>
+      <c r="P33" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q33" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P33)&gt;0,$P33,"")</f>
       </c>
     </row>
     <row r="34">
@@ -20848,7 +22621,7 @@
         <f>IF($C34,'Proyecto Datos (OKR´s)'!$J34,"")</f>
       </c>
       <c r="J34" s="201">
-        <f>IF($C34,IF($I34&gt;=1,"Completado",IF($H34&lt;TODAY(),"Vencido",IF(($H34-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C34,IF($I34&gt;=1,"Completado",IF($H34&lt;TODAY(),"Vencido",IF(($H34-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K34" s="200">
         <f>IF($C34,$H34-TODAY(),"")</f>
@@ -20861,6 +22634,12 @@
       </c>
       <c r="N34" s="200">
         <f>IF($C34,IF('Proyecto Datos (OKR´s)'!$E34="",9999,'Proyecto Datos (OKR´s)'!$E34),"")</f>
+      </c>
+      <c r="P34" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q34" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P34)&gt;0,$P34,"")</f>
       </c>
     </row>
     <row r="35">
@@ -20892,7 +22671,7 @@
         <f>IF($C35,'Proyecto Datos (OKR´s)'!$J35,"")</f>
       </c>
       <c r="J35" s="201">
-        <f>IF($C35,IF($I35&gt;=1,"Completado",IF($H35&lt;TODAY(),"Vencido",IF(($H35-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C35,IF($I35&gt;=1,"Completado",IF($H35&lt;TODAY(),"Vencido",IF(($H35-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K35" s="200">
         <f>IF($C35,$H35-TODAY(),"")</f>
@@ -20905,6 +22684,12 @@
       </c>
       <c r="N35" s="200">
         <f>IF($C35,IF('Proyecto Datos (OKR´s)'!$E35="",9999,'Proyecto Datos (OKR´s)'!$E35),"")</f>
+      </c>
+      <c r="P35" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q35" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P35)&gt;0,$P35,"")</f>
       </c>
     </row>
     <row r="36">
@@ -20936,7 +22721,7 @@
         <f>IF($C36,'Proyecto Datos (OKR´s)'!$J36,"")</f>
       </c>
       <c r="J36" s="201">
-        <f>IF($C36,IF($I36&gt;=1,"Completado",IF($H36&lt;TODAY(),"Vencido",IF(($H36-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C36,IF($I36&gt;=1,"Completado",IF($H36&lt;TODAY(),"Vencido",IF(($H36-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K36" s="200">
         <f>IF($C36,$H36-TODAY(),"")</f>
@@ -20949,6 +22734,12 @@
       </c>
       <c r="N36" s="200">
         <f>IF($C36,IF('Proyecto Datos (OKR´s)'!$E36="",9999,'Proyecto Datos (OKR´s)'!$E36),"")</f>
+      </c>
+      <c r="P36" s="200">
+        <f>ROW()-6</f>
+      </c>
+      <c r="Q36" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,$P36)&gt;0,$P36,"")</f>
       </c>
     </row>
     <row r="37">
@@ -20980,7 +22771,7 @@
         <f>IF($C37,'Proyecto Datos (OKR´s)'!$J37,"")</f>
       </c>
       <c r="J37" s="201">
-        <f>IF($C37,IF($I37&gt;=1,"Completado",IF($H37&lt;TODAY(),"Vencido",IF(($H37-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C37,IF($I37&gt;=1,"Completado",IF($H37&lt;TODAY(),"Vencido",IF(($H37-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K37" s="200">
         <f>IF($C37,$H37-TODAY(),"")</f>
@@ -20993,6 +22784,12 @@
       </c>
       <c r="N37" s="200">
         <f>IF($C37,IF('Proyecto Datos (OKR´s)'!$E37="",9999,'Proyecto Datos (OKR´s)'!$E37),"")</f>
+      </c>
+      <c r="P37" s="200">
+        <v>9999</v>
+      </c>
+      <c r="Q37" s="200">
+        <f>IF(COUNTIF($N$7:$N$200,9999)&gt;0,9999,"")</f>
       </c>
     </row>
     <row r="38">
@@ -21024,7 +22821,7 @@
         <f>IF($C38,'Proyecto Datos (OKR´s)'!$J38,"")</f>
       </c>
       <c r="J38" s="201">
-        <f>IF($C38,IF($I38&gt;=1,"Completado",IF($H38&lt;TODAY(),"Vencido",IF(($H38-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C38,IF($I38&gt;=1,"Completado",IF($H38&lt;TODAY(),"Vencido",IF(($H38-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K38" s="200">
         <f>IF($C38,$H38-TODAY(),"")</f>
@@ -21068,7 +22865,7 @@
         <f>IF($C39,'Proyecto Datos (OKR´s)'!$J39,"")</f>
       </c>
       <c r="J39" s="201">
-        <f>IF($C39,IF($I39&gt;=1,"Completado",IF($H39&lt;TODAY(),"Vencido",IF(($H39-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C39,IF($I39&gt;=1,"Completado",IF($H39&lt;TODAY(),"Vencido",IF(($H39-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K39" s="200">
         <f>IF($C39,$H39-TODAY(),"")</f>
@@ -21112,7 +22909,7 @@
         <f>IF($C40,'Proyecto Datos (OKR´s)'!$J40,"")</f>
       </c>
       <c r="J40" s="201">
-        <f>IF($C40,IF($I40&gt;=1,"Completado",IF($H40&lt;TODAY(),"Vencido",IF(($H40-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C40,IF($I40&gt;=1,"Completado",IF($H40&lt;TODAY(),"Vencido",IF(($H40-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K40" s="200">
         <f>IF($C40,$H40-TODAY(),"")</f>
@@ -21156,7 +22953,7 @@
         <f>IF($C41,'Proyecto Datos (OKR´s)'!$J41,"")</f>
       </c>
       <c r="J41" s="201">
-        <f>IF($C41,IF($I41&gt;=1,"Completado",IF($H41&lt;TODAY(),"Vencido",IF(($H41-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C41,IF($I41&gt;=1,"Completado",IF($H41&lt;TODAY(),"Vencido",IF(($H41-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K41" s="200">
         <f>IF($C41,$H41-TODAY(),"")</f>
@@ -21200,7 +22997,7 @@
         <f>IF($C42,'Proyecto Datos (OKR´s)'!$J42,"")</f>
       </c>
       <c r="J42" s="201">
-        <f>IF($C42,IF($I42&gt;=1,"Completado",IF($H42&lt;TODAY(),"Vencido",IF(($H42-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C42,IF($I42&gt;=1,"Completado",IF($H42&lt;TODAY(),"Vencido",IF(($H42-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K42" s="200">
         <f>IF($C42,$H42-TODAY(),"")</f>
@@ -21244,7 +23041,7 @@
         <f>IF($C43,'Proyecto Datos (OKR´s)'!$J43,"")</f>
       </c>
       <c r="J43" s="201">
-        <f>IF($C43,IF($I43&gt;=1,"Completado",IF($H43&lt;TODAY(),"Vencido",IF(($H43-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C43,IF($I43&gt;=1,"Completado",IF($H43&lt;TODAY(),"Vencido",IF(($H43-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K43" s="200">
         <f>IF($C43,$H43-TODAY(),"")</f>
@@ -21288,7 +23085,7 @@
         <f>IF($C44,'Proyecto Datos (OKR´s)'!$J44,"")</f>
       </c>
       <c r="J44" s="201">
-        <f>IF($C44,IF($I44&gt;=1,"Completado",IF($H44&lt;TODAY(),"Vencido",IF(($H44-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C44,IF($I44&gt;=1,"Completado",IF($H44&lt;TODAY(),"Vencido",IF(($H44-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K44" s="200">
         <f>IF($C44,$H44-TODAY(),"")</f>
@@ -21332,7 +23129,7 @@
         <f>IF($C45,'Proyecto Datos (OKR´s)'!$J45,"")</f>
       </c>
       <c r="J45" s="201">
-        <f>IF($C45,IF($I45&gt;=1,"Completado",IF($H45&lt;TODAY(),"Vencido",IF(($H45-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C45,IF($I45&gt;=1,"Completado",IF($H45&lt;TODAY(),"Vencido",IF(($H45-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K45" s="200">
         <f>IF($C45,$H45-TODAY(),"")</f>
@@ -21376,7 +23173,7 @@
         <f>IF($C46,'Proyecto Datos (OKR´s)'!$J46,"")</f>
       </c>
       <c r="J46" s="201">
-        <f>IF($C46,IF($I46&gt;=1,"Completado",IF($H46&lt;TODAY(),"Vencido",IF(($H46-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C46,IF($I46&gt;=1,"Completado",IF($H46&lt;TODAY(),"Vencido",IF(($H46-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K46" s="200">
         <f>IF($C46,$H46-TODAY(),"")</f>
@@ -21420,7 +23217,7 @@
         <f>IF($C47,'Proyecto Datos (OKR´s)'!$J47,"")</f>
       </c>
       <c r="J47" s="201">
-        <f>IF($C47,IF($I47&gt;=1,"Completado",IF($H47&lt;TODAY(),"Vencido",IF(($H47-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C47,IF($I47&gt;=1,"Completado",IF($H47&lt;TODAY(),"Vencido",IF(($H47-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K47" s="200">
         <f>IF($C47,$H47-TODAY(),"")</f>
@@ -21464,7 +23261,7 @@
         <f>IF($C48,'Proyecto Datos (OKR´s)'!$J48,"")</f>
       </c>
       <c r="J48" s="201">
-        <f>IF($C48,IF($I48&gt;=1,"Completado",IF($H48&lt;TODAY(),"Vencido",IF(($H48-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C48,IF($I48&gt;=1,"Completado",IF($H48&lt;TODAY(),"Vencido",IF(($H48-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K48" s="200">
         <f>IF($C48,$H48-TODAY(),"")</f>
@@ -21508,7 +23305,7 @@
         <f>IF($C49,'Proyecto Datos (OKR´s)'!$J49,"")</f>
       </c>
       <c r="J49" s="201">
-        <f>IF($C49,IF($I49&gt;=1,"Completado",IF($H49&lt;TODAY(),"Vencido",IF(($H49-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C49,IF($I49&gt;=1,"Completado",IF($H49&lt;TODAY(),"Vencido",IF(($H49-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K49" s="200">
         <f>IF($C49,$H49-TODAY(),"")</f>
@@ -21552,7 +23349,7 @@
         <f>IF($C50,'Proyecto Datos (OKR´s)'!$J50,"")</f>
       </c>
       <c r="J50" s="201">
-        <f>IF($C50,IF($I50&gt;=1,"Completado",IF($H50&lt;TODAY(),"Vencido",IF(($H50-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C50,IF($I50&gt;=1,"Completado",IF($H50&lt;TODAY(),"Vencido",IF(($H50-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K50" s="200">
         <f>IF($C50,$H50-TODAY(),"")</f>
@@ -21596,7 +23393,7 @@
         <f>IF($C51,'Proyecto Datos (OKR´s)'!$J51,"")</f>
       </c>
       <c r="J51" s="201">
-        <f>IF($C51,IF($I51&gt;=1,"Completado",IF($H51&lt;TODAY(),"Vencido",IF(($H51-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C51,IF($I51&gt;=1,"Completado",IF($H51&lt;TODAY(),"Vencido",IF(($H51-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K51" s="200">
         <f>IF($C51,$H51-TODAY(),"")</f>
@@ -21640,7 +23437,7 @@
         <f>IF($C52,'Proyecto Datos (OKR´s)'!$J52,"")</f>
       </c>
       <c r="J52" s="201">
-        <f>IF($C52,IF($I52&gt;=1,"Completado",IF($H52&lt;TODAY(),"Vencido",IF(($H52-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C52,IF($I52&gt;=1,"Completado",IF($H52&lt;TODAY(),"Vencido",IF(($H52-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K52" s="200">
         <f>IF($C52,$H52-TODAY(),"")</f>
@@ -21684,7 +23481,7 @@
         <f>IF($C53,'Proyecto Datos (OKR´s)'!$J53,"")</f>
       </c>
       <c r="J53" s="201">
-        <f>IF($C53,IF($I53&gt;=1,"Completado",IF($H53&lt;TODAY(),"Vencido",IF(($H53-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C53,IF($I53&gt;=1,"Completado",IF($H53&lt;TODAY(),"Vencido",IF(($H53-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K53" s="200">
         <f>IF($C53,$H53-TODAY(),"")</f>
@@ -21728,7 +23525,7 @@
         <f>IF($C54,'Proyecto Datos (OKR´s)'!$J54,"")</f>
       </c>
       <c r="J54" s="201">
-        <f>IF($C54,IF($I54&gt;=1,"Completado",IF($H54&lt;TODAY(),"Vencido",IF(($H54-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C54,IF($I54&gt;=1,"Completado",IF($H54&lt;TODAY(),"Vencido",IF(($H54-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K54" s="200">
         <f>IF($C54,$H54-TODAY(),"")</f>
@@ -21772,7 +23569,7 @@
         <f>IF($C55,'Proyecto Datos (OKR´s)'!$J55,"")</f>
       </c>
       <c r="J55" s="201">
-        <f>IF($C55,IF($I55&gt;=1,"Completado",IF($H55&lt;TODAY(),"Vencido",IF(($H55-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C55,IF($I55&gt;=1,"Completado",IF($H55&lt;TODAY(),"Vencido",IF(($H55-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K55" s="200">
         <f>IF($C55,$H55-TODAY(),"")</f>
@@ -21816,7 +23613,7 @@
         <f>IF($C56,'Proyecto Datos (OKR´s)'!$J56,"")</f>
       </c>
       <c r="J56" s="201">
-        <f>IF($C56,IF($I56&gt;=1,"Completado",IF($H56&lt;TODAY(),"Vencido",IF(($H56-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C56,IF($I56&gt;=1,"Completado",IF($H56&lt;TODAY(),"Vencido",IF(($H56-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K56" s="200">
         <f>IF($C56,$H56-TODAY(),"")</f>
@@ -21860,7 +23657,7 @@
         <f>IF($C57,'Proyecto Datos (OKR´s)'!$J57,"")</f>
       </c>
       <c r="J57" s="201">
-        <f>IF($C57,IF($I57&gt;=1,"Completado",IF($H57&lt;TODAY(),"Vencido",IF(($H57-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C57,IF($I57&gt;=1,"Completado",IF($H57&lt;TODAY(),"Vencido",IF(($H57-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K57" s="200">
         <f>IF($C57,$H57-TODAY(),"")</f>
@@ -21904,7 +23701,7 @@
         <f>IF($C58,'Proyecto Datos (OKR´s)'!$J58,"")</f>
       </c>
       <c r="J58" s="201">
-        <f>IF($C58,IF($I58&gt;=1,"Completado",IF($H58&lt;TODAY(),"Vencido",IF(($H58-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C58,IF($I58&gt;=1,"Completado",IF($H58&lt;TODAY(),"Vencido",IF(($H58-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K58" s="200">
         <f>IF($C58,$H58-TODAY(),"")</f>
@@ -21948,7 +23745,7 @@
         <f>IF($C59,'Proyecto Datos (OKR´s)'!$J59,"")</f>
       </c>
       <c r="J59" s="201">
-        <f>IF($C59,IF($I59&gt;=1,"Completado",IF($H59&lt;TODAY(),"Vencido",IF(($H59-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C59,IF($I59&gt;=1,"Completado",IF($H59&lt;TODAY(),"Vencido",IF(($H59-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K59" s="200">
         <f>IF($C59,$H59-TODAY(),"")</f>
@@ -21992,7 +23789,7 @@
         <f>IF($C60,'Proyecto Datos (OKR´s)'!$J60,"")</f>
       </c>
       <c r="J60" s="201">
-        <f>IF($C60,IF($I60&gt;=1,"Completado",IF($H60&lt;TODAY(),"Vencido",IF(($H60-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C60,IF($I60&gt;=1,"Completado",IF($H60&lt;TODAY(),"Vencido",IF(($H60-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K60" s="200">
         <f>IF($C60,$H60-TODAY(),"")</f>
@@ -22036,7 +23833,7 @@
         <f>IF($C61,'Proyecto Datos (OKR´s)'!$J61,"")</f>
       </c>
       <c r="J61" s="201">
-        <f>IF($C61,IF($I61&gt;=1,"Completado",IF($H61&lt;TODAY(),"Vencido",IF(($H61-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C61,IF($I61&gt;=1,"Completado",IF($H61&lt;TODAY(),"Vencido",IF(($H61-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K61" s="200">
         <f>IF($C61,$H61-TODAY(),"")</f>
@@ -22080,7 +23877,7 @@
         <f>IF($C62,'Proyecto Datos (OKR´s)'!$J62,"")</f>
       </c>
       <c r="J62" s="201">
-        <f>IF($C62,IF($I62&gt;=1,"Completado",IF($H62&lt;TODAY(),"Vencido",IF(($H62-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C62,IF($I62&gt;=1,"Completado",IF($H62&lt;TODAY(),"Vencido",IF(($H62-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K62" s="200">
         <f>IF($C62,$H62-TODAY(),"")</f>
@@ -22124,7 +23921,7 @@
         <f>IF($C63,'Proyecto Datos (OKR´s)'!$J63,"")</f>
       </c>
       <c r="J63" s="201">
-        <f>IF($C63,IF($I63&gt;=1,"Completado",IF($H63&lt;TODAY(),"Vencido",IF(($H63-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C63,IF($I63&gt;=1,"Completado",IF($H63&lt;TODAY(),"Vencido",IF(($H63-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K63" s="200">
         <f>IF($C63,$H63-TODAY(),"")</f>
@@ -22168,7 +23965,7 @@
         <f>IF($C64,'Proyecto Datos (OKR´s)'!$J64,"")</f>
       </c>
       <c r="J64" s="201">
-        <f>IF($C64,IF($I64&gt;=1,"Completado",IF($H64&lt;TODAY(),"Vencido",IF(($H64-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C64,IF($I64&gt;=1,"Completado",IF($H64&lt;TODAY(),"Vencido",IF(($H64-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K64" s="200">
         <f>IF($C64,$H64-TODAY(),"")</f>
@@ -22212,7 +24009,7 @@
         <f>IF($C65,'Proyecto Datos (OKR´s)'!$J65,"")</f>
       </c>
       <c r="J65" s="201">
-        <f>IF($C65,IF($I65&gt;=1,"Completado",IF($H65&lt;TODAY(),"Vencido",IF(($H65-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C65,IF($I65&gt;=1,"Completado",IF($H65&lt;TODAY(),"Vencido",IF(($H65-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K65" s="200">
         <f>IF($C65,$H65-TODAY(),"")</f>
@@ -22256,7 +24053,7 @@
         <f>IF($C66,'Proyecto Datos (OKR´s)'!$J66,"")</f>
       </c>
       <c r="J66" s="201">
-        <f>IF($C66,IF($I66&gt;=1,"Completado",IF($H66&lt;TODAY(),"Vencido",IF(($H66-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C66,IF($I66&gt;=1,"Completado",IF($H66&lt;TODAY(),"Vencido",IF(($H66-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K66" s="200">
         <f>IF($C66,$H66-TODAY(),"")</f>
@@ -22300,7 +24097,7 @@
         <f>IF($C67,'Proyecto Datos (OKR´s)'!$J67,"")</f>
       </c>
       <c r="J67" s="201">
-        <f>IF($C67,IF($I67&gt;=1,"Completado",IF($H67&lt;TODAY(),"Vencido",IF(($H67-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C67,IF($I67&gt;=1,"Completado",IF($H67&lt;TODAY(),"Vencido",IF(($H67-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K67" s="200">
         <f>IF($C67,$H67-TODAY(),"")</f>
@@ -22344,7 +24141,7 @@
         <f>IF($C68,'Proyecto Datos (OKR´s)'!$J68,"")</f>
       </c>
       <c r="J68" s="201">
-        <f>IF($C68,IF($I68&gt;=1,"Completado",IF($H68&lt;TODAY(),"Vencido",IF(($H68-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C68,IF($I68&gt;=1,"Completado",IF($H68&lt;TODAY(),"Vencido",IF(($H68-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K68" s="200">
         <f>IF($C68,$H68-TODAY(),"")</f>
@@ -22388,7 +24185,7 @@
         <f>IF($C69,'Proyecto Datos (OKR´s)'!$J69,"")</f>
       </c>
       <c r="J69" s="201">
-        <f>IF($C69,IF($I69&gt;=1,"Completado",IF($H69&lt;TODAY(),"Vencido",IF(($H69-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C69,IF($I69&gt;=1,"Completado",IF($H69&lt;TODAY(),"Vencido",IF(($H69-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K69" s="200">
         <f>IF($C69,$H69-TODAY(),"")</f>
@@ -22432,7 +24229,7 @@
         <f>IF($C70,'Proyecto Datos (OKR´s)'!$J70,"")</f>
       </c>
       <c r="J70" s="201">
-        <f>IF($C70,IF($I70&gt;=1,"Completado",IF($H70&lt;TODAY(),"Vencido",IF(($H70-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C70,IF($I70&gt;=1,"Completado",IF($H70&lt;TODAY(),"Vencido",IF(($H70-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K70" s="200">
         <f>IF($C70,$H70-TODAY(),"")</f>
@@ -22476,7 +24273,7 @@
         <f>IF($C71,'Proyecto Datos (OKR´s)'!$J71,"")</f>
       </c>
       <c r="J71" s="201">
-        <f>IF($C71,IF($I71&gt;=1,"Completado",IF($H71&lt;TODAY(),"Vencido",IF(($H71-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C71,IF($I71&gt;=1,"Completado",IF($H71&lt;TODAY(),"Vencido",IF(($H71-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K71" s="200">
         <f>IF($C71,$H71-TODAY(),"")</f>
@@ -22520,7 +24317,7 @@
         <f>IF($C72,'Proyecto Datos (OKR´s)'!$J72,"")</f>
       </c>
       <c r="J72" s="201">
-        <f>IF($C72,IF($I72&gt;=1,"Completado",IF($H72&lt;TODAY(),"Vencido",IF(($H72-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C72,IF($I72&gt;=1,"Completado",IF($H72&lt;TODAY(),"Vencido",IF(($H72-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K72" s="200">
         <f>IF($C72,$H72-TODAY(),"")</f>
@@ -22564,7 +24361,7 @@
         <f>IF($C73,'Proyecto Datos (OKR´s)'!$J73,"")</f>
       </c>
       <c r="J73" s="201">
-        <f>IF($C73,IF($I73&gt;=1,"Completado",IF($H73&lt;TODAY(),"Vencido",IF(($H73-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C73,IF($I73&gt;=1,"Completado",IF($H73&lt;TODAY(),"Vencido",IF(($H73-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K73" s="200">
         <f>IF($C73,$H73-TODAY(),"")</f>
@@ -22608,7 +24405,7 @@
         <f>IF($C74,'Proyecto Datos (OKR´s)'!$J74,"")</f>
       </c>
       <c r="J74" s="201">
-        <f>IF($C74,IF($I74&gt;=1,"Completado",IF($H74&lt;TODAY(),"Vencido",IF(($H74-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C74,IF($I74&gt;=1,"Completado",IF($H74&lt;TODAY(),"Vencido",IF(($H74-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K74" s="200">
         <f>IF($C74,$H74-TODAY(),"")</f>
@@ -22652,7 +24449,7 @@
         <f>IF($C75,'Proyecto Datos (OKR´s)'!$J75,"")</f>
       </c>
       <c r="J75" s="201">
-        <f>IF($C75,IF($I75&gt;=1,"Completado",IF($H75&lt;TODAY(),"Vencido",IF(($H75-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C75,IF($I75&gt;=1,"Completado",IF($H75&lt;TODAY(),"Vencido",IF(($H75-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K75" s="200">
         <f>IF($C75,$H75-TODAY(),"")</f>
@@ -22696,7 +24493,7 @@
         <f>IF($C76,'Proyecto Datos (OKR´s)'!$J76,"")</f>
       </c>
       <c r="J76" s="201">
-        <f>IF($C76,IF($I76&gt;=1,"Completado",IF($H76&lt;TODAY(),"Vencido",IF(($H76-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C76,IF($I76&gt;=1,"Completado",IF($H76&lt;TODAY(),"Vencido",IF(($H76-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K76" s="200">
         <f>IF($C76,$H76-TODAY(),"")</f>
@@ -22740,7 +24537,7 @@
         <f>IF($C77,'Proyecto Datos (OKR´s)'!$J77,"")</f>
       </c>
       <c r="J77" s="201">
-        <f>IF($C77,IF($I77&gt;=1,"Completado",IF($H77&lt;TODAY(),"Vencido",IF(($H77-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C77,IF($I77&gt;=1,"Completado",IF($H77&lt;TODAY(),"Vencido",IF(($H77-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K77" s="200">
         <f>IF($C77,$H77-TODAY(),"")</f>
@@ -22784,7 +24581,7 @@
         <f>IF($C78,'Proyecto Datos (OKR´s)'!$J78,"")</f>
       </c>
       <c r="J78" s="201">
-        <f>IF($C78,IF($I78&gt;=1,"Completado",IF($H78&lt;TODAY(),"Vencido",IF(($H78-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C78,IF($I78&gt;=1,"Completado",IF($H78&lt;TODAY(),"Vencido",IF(($H78-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K78" s="200">
         <f>IF($C78,$H78-TODAY(),"")</f>
@@ -22828,7 +24625,7 @@
         <f>IF($C79,'Proyecto Datos (OKR´s)'!$J79,"")</f>
       </c>
       <c r="J79" s="201">
-        <f>IF($C79,IF($I79&gt;=1,"Completado",IF($H79&lt;TODAY(),"Vencido",IF(($H79-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C79,IF($I79&gt;=1,"Completado",IF($H79&lt;TODAY(),"Vencido",IF(($H79-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K79" s="200">
         <f>IF($C79,$H79-TODAY(),"")</f>
@@ -22872,7 +24669,7 @@
         <f>IF($C80,'Proyecto Datos (OKR´s)'!$J80,"")</f>
       </c>
       <c r="J80" s="201">
-        <f>IF($C80,IF($I80&gt;=1,"Completado",IF($H80&lt;TODAY(),"Vencido",IF(($H80-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C80,IF($I80&gt;=1,"Completado",IF($H80&lt;TODAY(),"Vencido",IF(($H80-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K80" s="200">
         <f>IF($C80,$H80-TODAY(),"")</f>
@@ -22916,7 +24713,7 @@
         <f>IF($C81,'Proyecto Datos (OKR´s)'!$J81,"")</f>
       </c>
       <c r="J81" s="201">
-        <f>IF($C81,IF($I81&gt;=1,"Completado",IF($H81&lt;TODAY(),"Vencido",IF(($H81-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C81,IF($I81&gt;=1,"Completado",IF($H81&lt;TODAY(),"Vencido",IF(($H81-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K81" s="200">
         <f>IF($C81,$H81-TODAY(),"")</f>
@@ -22960,7 +24757,7 @@
         <f>IF($C82,'Proyecto Datos (OKR´s)'!$J82,"")</f>
       </c>
       <c r="J82" s="201">
-        <f>IF($C82,IF($I82&gt;=1,"Completado",IF($H82&lt;TODAY(),"Vencido",IF(($H82-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C82,IF($I82&gt;=1,"Completado",IF($H82&lt;TODAY(),"Vencido",IF(($H82-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K82" s="200">
         <f>IF($C82,$H82-TODAY(),"")</f>
@@ -23004,7 +24801,7 @@
         <f>IF($C83,'Proyecto Datos (OKR´s)'!$J83,"")</f>
       </c>
       <c r="J83" s="201">
-        <f>IF($C83,IF($I83&gt;=1,"Completado",IF($H83&lt;TODAY(),"Vencido",IF(($H83-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C83,IF($I83&gt;=1,"Completado",IF($H83&lt;TODAY(),"Vencido",IF(($H83-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K83" s="200">
         <f>IF($C83,$H83-TODAY(),"")</f>
@@ -23048,7 +24845,7 @@
         <f>IF($C84,'Proyecto Datos (OKR´s)'!$J84,"")</f>
       </c>
       <c r="J84" s="201">
-        <f>IF($C84,IF($I84&gt;=1,"Completado",IF($H84&lt;TODAY(),"Vencido",IF(($H84-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C84,IF($I84&gt;=1,"Completado",IF($H84&lt;TODAY(),"Vencido",IF(($H84-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K84" s="200">
         <f>IF($C84,$H84-TODAY(),"")</f>
@@ -23092,7 +24889,7 @@
         <f>IF($C85,'Proyecto Datos (OKR´s)'!$J85,"")</f>
       </c>
       <c r="J85" s="201">
-        <f>IF($C85,IF($I85&gt;=1,"Completado",IF($H85&lt;TODAY(),"Vencido",IF(($H85-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C85,IF($I85&gt;=1,"Completado",IF($H85&lt;TODAY(),"Vencido",IF(($H85-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K85" s="200">
         <f>IF($C85,$H85-TODAY(),"")</f>
@@ -23136,7 +24933,7 @@
         <f>IF($C86,'Proyecto Datos (OKR´s)'!$J86,"")</f>
       </c>
       <c r="J86" s="201">
-        <f>IF($C86,IF($I86&gt;=1,"Completado",IF($H86&lt;TODAY(),"Vencido",IF(($H86-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C86,IF($I86&gt;=1,"Completado",IF($H86&lt;TODAY(),"Vencido",IF(($H86-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K86" s="200">
         <f>IF($C86,$H86-TODAY(),"")</f>
@@ -23180,7 +24977,7 @@
         <f>IF($C87,'Proyecto Datos (OKR´s)'!$J87,"")</f>
       </c>
       <c r="J87" s="201">
-        <f>IF($C87,IF($I87&gt;=1,"Completado",IF($H87&lt;TODAY(),"Vencido",IF(($H87-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C87,IF($I87&gt;=1,"Completado",IF($H87&lt;TODAY(),"Vencido",IF(($H87-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K87" s="200">
         <f>IF($C87,$H87-TODAY(),"")</f>
@@ -23224,7 +25021,7 @@
         <f>IF($C88,'Proyecto Datos (OKR´s)'!$J88,"")</f>
       </c>
       <c r="J88" s="201">
-        <f>IF($C88,IF($I88&gt;=1,"Completado",IF($H88&lt;TODAY(),"Vencido",IF(($H88-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C88,IF($I88&gt;=1,"Completado",IF($H88&lt;TODAY(),"Vencido",IF(($H88-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K88" s="200">
         <f>IF($C88,$H88-TODAY(),"")</f>
@@ -23268,7 +25065,7 @@
         <f>IF($C89,'Proyecto Datos (OKR´s)'!$J89,"")</f>
       </c>
       <c r="J89" s="201">
-        <f>IF($C89,IF($I89&gt;=1,"Completado",IF($H89&lt;TODAY(),"Vencido",IF(($H89-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C89,IF($I89&gt;=1,"Completado",IF($H89&lt;TODAY(),"Vencido",IF(($H89-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K89" s="200">
         <f>IF($C89,$H89-TODAY(),"")</f>
@@ -23312,7 +25109,7 @@
         <f>IF($C90,'Proyecto Datos (OKR´s)'!$J90,"")</f>
       </c>
       <c r="J90" s="201">
-        <f>IF($C90,IF($I90&gt;=1,"Completado",IF($H90&lt;TODAY(),"Vencido",IF(($H90-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C90,IF($I90&gt;=1,"Completado",IF($H90&lt;TODAY(),"Vencido",IF(($H90-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K90" s="200">
         <f>IF($C90,$H90-TODAY(),"")</f>
@@ -23356,7 +25153,7 @@
         <f>IF($C91,'Proyecto Datos (OKR´s)'!$J91,"")</f>
       </c>
       <c r="J91" s="201">
-        <f>IF($C91,IF($I91&gt;=1,"Completado",IF($H91&lt;TODAY(),"Vencido",IF(($H91-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C91,IF($I91&gt;=1,"Completado",IF($H91&lt;TODAY(),"Vencido",IF(($H91-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K91" s="200">
         <f>IF($C91,$H91-TODAY(),"")</f>
@@ -23400,7 +25197,7 @@
         <f>IF($C92,'Proyecto Datos (OKR´s)'!$J92,"")</f>
       </c>
       <c r="J92" s="201">
-        <f>IF($C92,IF($I92&gt;=1,"Completado",IF($H92&lt;TODAY(),"Vencido",IF(($H92-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C92,IF($I92&gt;=1,"Completado",IF($H92&lt;TODAY(),"Vencido",IF(($H92-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K92" s="200">
         <f>IF($C92,$H92-TODAY(),"")</f>
@@ -23444,7 +25241,7 @@
         <f>IF($C93,'Proyecto Datos (OKR´s)'!$J93,"")</f>
       </c>
       <c r="J93" s="201">
-        <f>IF($C93,IF($I93&gt;=1,"Completado",IF($H93&lt;TODAY(),"Vencido",IF(($H93-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C93,IF($I93&gt;=1,"Completado",IF($H93&lt;TODAY(),"Vencido",IF(($H93-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K93" s="200">
         <f>IF($C93,$H93-TODAY(),"")</f>
@@ -23488,7 +25285,7 @@
         <f>IF($C94,'Proyecto Datos (OKR´s)'!$J94,"")</f>
       </c>
       <c r="J94" s="201">
-        <f>IF($C94,IF($I94&gt;=1,"Completado",IF($H94&lt;TODAY(),"Vencido",IF(($H94-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C94,IF($I94&gt;=1,"Completado",IF($H94&lt;TODAY(),"Vencido",IF(($H94-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K94" s="200">
         <f>IF($C94,$H94-TODAY(),"")</f>
@@ -23532,7 +25329,7 @@
         <f>IF($C95,'Proyecto Datos (OKR´s)'!$J95,"")</f>
       </c>
       <c r="J95" s="201">
-        <f>IF($C95,IF($I95&gt;=1,"Completado",IF($H95&lt;TODAY(),"Vencido",IF(($H95-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C95,IF($I95&gt;=1,"Completado",IF($H95&lt;TODAY(),"Vencido",IF(($H95-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K95" s="200">
         <f>IF($C95,$H95-TODAY(),"")</f>
@@ -23576,7 +25373,7 @@
         <f>IF($C96,'Proyecto Datos (OKR´s)'!$J96,"")</f>
       </c>
       <c r="J96" s="201">
-        <f>IF($C96,IF($I96&gt;=1,"Completado",IF($H96&lt;TODAY(),"Vencido",IF(($H96-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C96,IF($I96&gt;=1,"Completado",IF($H96&lt;TODAY(),"Vencido",IF(($H96-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K96" s="200">
         <f>IF($C96,$H96-TODAY(),"")</f>
@@ -23620,7 +25417,7 @@
         <f>IF($C97,'Proyecto Datos (OKR´s)'!$J97,"")</f>
       </c>
       <c r="J97" s="201">
-        <f>IF($C97,IF($I97&gt;=1,"Completado",IF($H97&lt;TODAY(),"Vencido",IF(($H97-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C97,IF($I97&gt;=1,"Completado",IF($H97&lt;TODAY(),"Vencido",IF(($H97-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K97" s="200">
         <f>IF($C97,$H97-TODAY(),"")</f>
@@ -23664,7 +25461,7 @@
         <f>IF($C98,'Proyecto Datos (OKR´s)'!$J98,"")</f>
       </c>
       <c r="J98" s="201">
-        <f>IF($C98,IF($I98&gt;=1,"Completado",IF($H98&lt;TODAY(),"Vencido",IF(($H98-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C98,IF($I98&gt;=1,"Completado",IF($H98&lt;TODAY(),"Vencido",IF(($H98-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K98" s="200">
         <f>IF($C98,$H98-TODAY(),"")</f>
@@ -23708,7 +25505,7 @@
         <f>IF($C99,'Proyecto Datos (OKR´s)'!$J99,"")</f>
       </c>
       <c r="J99" s="201">
-        <f>IF($C99,IF($I99&gt;=1,"Completado",IF($H99&lt;TODAY(),"Vencido",IF(($H99-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C99,IF($I99&gt;=1,"Completado",IF($H99&lt;TODAY(),"Vencido",IF(($H99-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K99" s="200">
         <f>IF($C99,$H99-TODAY(),"")</f>
@@ -23752,7 +25549,7 @@
         <f>IF($C100,'Proyecto Datos (OKR´s)'!$J100,"")</f>
       </c>
       <c r="J100" s="201">
-        <f>IF($C100,IF($I100&gt;=1,"Completado",IF($H100&lt;TODAY(),"Vencido",IF(($H100-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C100,IF($I100&gt;=1,"Completado",IF($H100&lt;TODAY(),"Vencido",IF(($H100-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K100" s="200">
         <f>IF($C100,$H100-TODAY(),"")</f>
@@ -23796,7 +25593,7 @@
         <f>IF($C101,'Proyecto Datos (OKR´s)'!$J101,"")</f>
       </c>
       <c r="J101" s="201">
-        <f>IF($C101,IF($I101&gt;=1,"Completado",IF($H101&lt;TODAY(),"Vencido",IF(($H101-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C101,IF($I101&gt;=1,"Completado",IF($H101&lt;TODAY(),"Vencido",IF(($H101-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K101" s="200">
         <f>IF($C101,$H101-TODAY(),"")</f>
@@ -23840,7 +25637,7 @@
         <f>IF($C102,'Proyecto Datos (OKR´s)'!$J102,"")</f>
       </c>
       <c r="J102" s="201">
-        <f>IF($C102,IF($I102&gt;=1,"Completado",IF($H102&lt;TODAY(),"Vencido",IF(($H102-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C102,IF($I102&gt;=1,"Completado",IF($H102&lt;TODAY(),"Vencido",IF(($H102-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K102" s="200">
         <f>IF($C102,$H102-TODAY(),"")</f>
@@ -23884,7 +25681,7 @@
         <f>IF($C103,'Proyecto Datos (OKR´s)'!$J103,"")</f>
       </c>
       <c r="J103" s="201">
-        <f>IF($C103,IF($I103&gt;=1,"Completado",IF($H103&lt;TODAY(),"Vencido",IF(($H103-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C103,IF($I103&gt;=1,"Completado",IF($H103&lt;TODAY(),"Vencido",IF(($H103-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K103" s="200">
         <f>IF($C103,$H103-TODAY(),"")</f>
@@ -23928,7 +25725,7 @@
         <f>IF($C104,'Proyecto Datos (OKR´s)'!$J104,"")</f>
       </c>
       <c r="J104" s="201">
-        <f>IF($C104,IF($I104&gt;=1,"Completado",IF($H104&lt;TODAY(),"Vencido",IF(($H104-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C104,IF($I104&gt;=1,"Completado",IF($H104&lt;TODAY(),"Vencido",IF(($H104-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K104" s="200">
         <f>IF($C104,$H104-TODAY(),"")</f>
@@ -23972,7 +25769,7 @@
         <f>IF($C105,'Proyecto Datos (OKR´s)'!$J105,"")</f>
       </c>
       <c r="J105" s="201">
-        <f>IF($C105,IF($I105&gt;=1,"Completado",IF($H105&lt;TODAY(),"Vencido",IF(($H105-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C105,IF($I105&gt;=1,"Completado",IF($H105&lt;TODAY(),"Vencido",IF(($H105-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K105" s="200">
         <f>IF($C105,$H105-TODAY(),"")</f>
@@ -24016,7 +25813,7 @@
         <f>IF($C106,'Proyecto Datos (OKR´s)'!$J106,"")</f>
       </c>
       <c r="J106" s="201">
-        <f>IF($C106,IF($I106&gt;=1,"Completado",IF($H106&lt;TODAY(),"Vencido",IF(($H106-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C106,IF($I106&gt;=1,"Completado",IF($H106&lt;TODAY(),"Vencido",IF(($H106-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K106" s="200">
         <f>IF($C106,$H106-TODAY(),"")</f>
@@ -24060,7 +25857,7 @@
         <f>IF($C107,'Proyecto Datos (OKR´s)'!$J107,"")</f>
       </c>
       <c r="J107" s="201">
-        <f>IF($C107,IF($I107&gt;=1,"Completado",IF($H107&lt;TODAY(),"Vencido",IF(($H107-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C107,IF($I107&gt;=1,"Completado",IF($H107&lt;TODAY(),"Vencido",IF(($H107-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K107" s="200">
         <f>IF($C107,$H107-TODAY(),"")</f>
@@ -24104,7 +25901,7 @@
         <f>IF($C108,'Proyecto Datos (OKR´s)'!$J108,"")</f>
       </c>
       <c r="J108" s="201">
-        <f>IF($C108,IF($I108&gt;=1,"Completado",IF($H108&lt;TODAY(),"Vencido",IF(($H108-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C108,IF($I108&gt;=1,"Completado",IF($H108&lt;TODAY(),"Vencido",IF(($H108-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K108" s="200">
         <f>IF($C108,$H108-TODAY(),"")</f>
@@ -24148,7 +25945,7 @@
         <f>IF($C109,'Proyecto Datos (OKR´s)'!$J109,"")</f>
       </c>
       <c r="J109" s="201">
-        <f>IF($C109,IF($I109&gt;=1,"Completado",IF($H109&lt;TODAY(),"Vencido",IF(($H109-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C109,IF($I109&gt;=1,"Completado",IF($H109&lt;TODAY(),"Vencido",IF(($H109-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K109" s="200">
         <f>IF($C109,$H109-TODAY(),"")</f>
@@ -24192,7 +25989,7 @@
         <f>IF($C110,'Proyecto Datos (OKR´s)'!$J110,"")</f>
       </c>
       <c r="J110" s="201">
-        <f>IF($C110,IF($I110&gt;=1,"Completado",IF($H110&lt;TODAY(),"Vencido",IF(($H110-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C110,IF($I110&gt;=1,"Completado",IF($H110&lt;TODAY(),"Vencido",IF(($H110-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K110" s="200">
         <f>IF($C110,$H110-TODAY(),"")</f>
@@ -24236,7 +26033,7 @@
         <f>IF($C111,'Proyecto Datos (OKR´s)'!$J111,"")</f>
       </c>
       <c r="J111" s="201">
-        <f>IF($C111,IF($I111&gt;=1,"Completado",IF($H111&lt;TODAY(),"Vencido",IF(($H111-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C111,IF($I111&gt;=1,"Completado",IF($H111&lt;TODAY(),"Vencido",IF(($H111-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K111" s="200">
         <f>IF($C111,$H111-TODAY(),"")</f>
@@ -24280,7 +26077,7 @@
         <f>IF($C112,'Proyecto Datos (OKR´s)'!$J112,"")</f>
       </c>
       <c r="J112" s="201">
-        <f>IF($C112,IF($I112&gt;=1,"Completado",IF($H112&lt;TODAY(),"Vencido",IF(($H112-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C112,IF($I112&gt;=1,"Completado",IF($H112&lt;TODAY(),"Vencido",IF(($H112-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K112" s="200">
         <f>IF($C112,$H112-TODAY(),"")</f>
@@ -24324,7 +26121,7 @@
         <f>IF($C113,'Proyecto Datos (OKR´s)'!$J113,"")</f>
       </c>
       <c r="J113" s="201">
-        <f>IF($C113,IF($I113&gt;=1,"Completado",IF($H113&lt;TODAY(),"Vencido",IF(($H113-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C113,IF($I113&gt;=1,"Completado",IF($H113&lt;TODAY(),"Vencido",IF(($H113-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K113" s="200">
         <f>IF($C113,$H113-TODAY(),"")</f>
@@ -24368,7 +26165,7 @@
         <f>IF($C114,'Proyecto Datos (OKR´s)'!$J114,"")</f>
       </c>
       <c r="J114" s="201">
-        <f>IF($C114,IF($I114&gt;=1,"Completado",IF($H114&lt;TODAY(),"Vencido",IF(($H114-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C114,IF($I114&gt;=1,"Completado",IF($H114&lt;TODAY(),"Vencido",IF(($H114-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K114" s="200">
         <f>IF($C114,$H114-TODAY(),"")</f>
@@ -24412,7 +26209,7 @@
         <f>IF($C115,'Proyecto Datos (OKR´s)'!$J115,"")</f>
       </c>
       <c r="J115" s="201">
-        <f>IF($C115,IF($I115&gt;=1,"Completado",IF($H115&lt;TODAY(),"Vencido",IF(($H115-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C115,IF($I115&gt;=1,"Completado",IF($H115&lt;TODAY(),"Vencido",IF(($H115-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K115" s="200">
         <f>IF($C115,$H115-TODAY(),"")</f>
@@ -24456,7 +26253,7 @@
         <f>IF($C116,'Proyecto Datos (OKR´s)'!$J116,"")</f>
       </c>
       <c r="J116" s="201">
-        <f>IF($C116,IF($I116&gt;=1,"Completado",IF($H116&lt;TODAY(),"Vencido",IF(($H116-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C116,IF($I116&gt;=1,"Completado",IF($H116&lt;TODAY(),"Vencido",IF(($H116-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K116" s="200">
         <f>IF($C116,$H116-TODAY(),"")</f>
@@ -24500,7 +26297,7 @@
         <f>IF($C117,'Proyecto Datos (OKR´s)'!$J117,"")</f>
       </c>
       <c r="J117" s="201">
-        <f>IF($C117,IF($I117&gt;=1,"Completado",IF($H117&lt;TODAY(),"Vencido",IF(($H117-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C117,IF($I117&gt;=1,"Completado",IF($H117&lt;TODAY(),"Vencido",IF(($H117-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K117" s="200">
         <f>IF($C117,$H117-TODAY(),"")</f>
@@ -24544,7 +26341,7 @@
         <f>IF($C118,'Proyecto Datos (OKR´s)'!$J118,"")</f>
       </c>
       <c r="J118" s="201">
-        <f>IF($C118,IF($I118&gt;=1,"Completado",IF($H118&lt;TODAY(),"Vencido",IF(($H118-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C118,IF($I118&gt;=1,"Completado",IF($H118&lt;TODAY(),"Vencido",IF(($H118-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K118" s="200">
         <f>IF($C118,$H118-TODAY(),"")</f>
@@ -24588,7 +26385,7 @@
         <f>IF($C119,'Proyecto Datos (OKR´s)'!$J119,"")</f>
       </c>
       <c r="J119" s="201">
-        <f>IF($C119,IF($I119&gt;=1,"Completado",IF($H119&lt;TODAY(),"Vencido",IF(($H119-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C119,IF($I119&gt;=1,"Completado",IF($H119&lt;TODAY(),"Vencido",IF(($H119-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K119" s="200">
         <f>IF($C119,$H119-TODAY(),"")</f>
@@ -24632,7 +26429,7 @@
         <f>IF($C120,'Proyecto Datos (OKR´s)'!$J120,"")</f>
       </c>
       <c r="J120" s="201">
-        <f>IF($C120,IF($I120&gt;=1,"Completado",IF($H120&lt;TODAY(),"Vencido",IF(($H120-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C120,IF($I120&gt;=1,"Completado",IF($H120&lt;TODAY(),"Vencido",IF(($H120-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K120" s="200">
         <f>IF($C120,$H120-TODAY(),"")</f>
@@ -24676,7 +26473,7 @@
         <f>IF($C121,'Proyecto Datos (OKR´s)'!$J121,"")</f>
       </c>
       <c r="J121" s="201">
-        <f>IF($C121,IF($I121&gt;=1,"Completado",IF($H121&lt;TODAY(),"Vencido",IF(($H121-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C121,IF($I121&gt;=1,"Completado",IF($H121&lt;TODAY(),"Vencido",IF(($H121-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K121" s="200">
         <f>IF($C121,$H121-TODAY(),"")</f>
@@ -24720,7 +26517,7 @@
         <f>IF($C122,'Proyecto Datos (OKR´s)'!$J122,"")</f>
       </c>
       <c r="J122" s="201">
-        <f>IF($C122,IF($I122&gt;=1,"Completado",IF($H122&lt;TODAY(),"Vencido",IF(($H122-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C122,IF($I122&gt;=1,"Completado",IF($H122&lt;TODAY(),"Vencido",IF(($H122-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K122" s="200">
         <f>IF($C122,$H122-TODAY(),"")</f>
@@ -24764,7 +26561,7 @@
         <f>IF($C123,'Proyecto Datos (OKR´s)'!$J123,"")</f>
       </c>
       <c r="J123" s="201">
-        <f>IF($C123,IF($I123&gt;=1,"Completado",IF($H123&lt;TODAY(),"Vencido",IF(($H123-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C123,IF($I123&gt;=1,"Completado",IF($H123&lt;TODAY(),"Vencido",IF(($H123-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K123" s="200">
         <f>IF($C123,$H123-TODAY(),"")</f>
@@ -24808,7 +26605,7 @@
         <f>IF($C124,'Proyecto Datos (OKR´s)'!$J124,"")</f>
       </c>
       <c r="J124" s="201">
-        <f>IF($C124,IF($I124&gt;=1,"Completado",IF($H124&lt;TODAY(),"Vencido",IF(($H124-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C124,IF($I124&gt;=1,"Completado",IF($H124&lt;TODAY(),"Vencido",IF(($H124-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K124" s="200">
         <f>IF($C124,$H124-TODAY(),"")</f>
@@ -24852,7 +26649,7 @@
         <f>IF($C125,'Proyecto Datos (OKR´s)'!$J125,"")</f>
       </c>
       <c r="J125" s="201">
-        <f>IF($C125,IF($I125&gt;=1,"Completado",IF($H125&lt;TODAY(),"Vencido",IF(($H125-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C125,IF($I125&gt;=1,"Completado",IF($H125&lt;TODAY(),"Vencido",IF(($H125-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K125" s="200">
         <f>IF($C125,$H125-TODAY(),"")</f>
@@ -24896,7 +26693,7 @@
         <f>IF($C126,'Proyecto Datos (OKR´s)'!$J126,"")</f>
       </c>
       <c r="J126" s="201">
-        <f>IF($C126,IF($I126&gt;=1,"Completado",IF($H126&lt;TODAY(),"Vencido",IF(($H126-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C126,IF($I126&gt;=1,"Completado",IF($H126&lt;TODAY(),"Vencido",IF(($H126-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K126" s="200">
         <f>IF($C126,$H126-TODAY(),"")</f>
@@ -24940,7 +26737,7 @@
         <f>IF($C127,'Proyecto Datos (OKR´s)'!$J127,"")</f>
       </c>
       <c r="J127" s="201">
-        <f>IF($C127,IF($I127&gt;=1,"Completado",IF($H127&lt;TODAY(),"Vencido",IF(($H127-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C127,IF($I127&gt;=1,"Completado",IF($H127&lt;TODAY(),"Vencido",IF(($H127-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K127" s="200">
         <f>IF($C127,$H127-TODAY(),"")</f>
@@ -24984,7 +26781,7 @@
         <f>IF($C128,'Proyecto Datos (OKR´s)'!$J128,"")</f>
       </c>
       <c r="J128" s="201">
-        <f>IF($C128,IF($I128&gt;=1,"Completado",IF($H128&lt;TODAY(),"Vencido",IF(($H128-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C128,IF($I128&gt;=1,"Completado",IF($H128&lt;TODAY(),"Vencido",IF(($H128-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K128" s="200">
         <f>IF($C128,$H128-TODAY(),"")</f>
@@ -25028,7 +26825,7 @@
         <f>IF($C129,'Proyecto Datos (OKR´s)'!$J129,"")</f>
       </c>
       <c r="J129" s="201">
-        <f>IF($C129,IF($I129&gt;=1,"Completado",IF($H129&lt;TODAY(),"Vencido",IF(($H129-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C129,IF($I129&gt;=1,"Completado",IF($H129&lt;TODAY(),"Vencido",IF(($H129-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K129" s="200">
         <f>IF($C129,$H129-TODAY(),"")</f>
@@ -25072,7 +26869,7 @@
         <f>IF($C130,'Proyecto Datos (OKR´s)'!$J130,"")</f>
       </c>
       <c r="J130" s="201">
-        <f>IF($C130,IF($I130&gt;=1,"Completado",IF($H130&lt;TODAY(),"Vencido",IF(($H130-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C130,IF($I130&gt;=1,"Completado",IF($H130&lt;TODAY(),"Vencido",IF(($H130-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K130" s="200">
         <f>IF($C130,$H130-TODAY(),"")</f>
@@ -25116,7 +26913,7 @@
         <f>IF($C131,'Proyecto Datos (OKR´s)'!$J131,"")</f>
       </c>
       <c r="J131" s="201">
-        <f>IF($C131,IF($I131&gt;=1,"Completado",IF($H131&lt;TODAY(),"Vencido",IF(($H131-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C131,IF($I131&gt;=1,"Completado",IF($H131&lt;TODAY(),"Vencido",IF(($H131-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K131" s="200">
         <f>IF($C131,$H131-TODAY(),"")</f>
@@ -25160,7 +26957,7 @@
         <f>IF($C132,'Proyecto Datos (OKR´s)'!$J132,"")</f>
       </c>
       <c r="J132" s="201">
-        <f>IF($C132,IF($I132&gt;=1,"Completado",IF($H132&lt;TODAY(),"Vencido",IF(($H132-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C132,IF($I132&gt;=1,"Completado",IF($H132&lt;TODAY(),"Vencido",IF(($H132-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K132" s="200">
         <f>IF($C132,$H132-TODAY(),"")</f>
@@ -25204,7 +27001,7 @@
         <f>IF($C133,'Proyecto Datos (OKR´s)'!$J133,"")</f>
       </c>
       <c r="J133" s="201">
-        <f>IF($C133,IF($I133&gt;=1,"Completado",IF($H133&lt;TODAY(),"Vencido",IF(($H133-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C133,IF($I133&gt;=1,"Completado",IF($H133&lt;TODAY(),"Vencido",IF(($H133-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K133" s="200">
         <f>IF($C133,$H133-TODAY(),"")</f>
@@ -25248,7 +27045,7 @@
         <f>IF($C134,'Proyecto Datos (OKR´s)'!$J134,"")</f>
       </c>
       <c r="J134" s="201">
-        <f>IF($C134,IF($I134&gt;=1,"Completado",IF($H134&lt;TODAY(),"Vencido",IF(($H134-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C134,IF($I134&gt;=1,"Completado",IF($H134&lt;TODAY(),"Vencido",IF(($H134-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K134" s="200">
         <f>IF($C134,$H134-TODAY(),"")</f>
@@ -25292,7 +27089,7 @@
         <f>IF($C135,'Proyecto Datos (OKR´s)'!$J135,"")</f>
       </c>
       <c r="J135" s="201">
-        <f>IF($C135,IF($I135&gt;=1,"Completado",IF($H135&lt;TODAY(),"Vencido",IF(($H135-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C135,IF($I135&gt;=1,"Completado",IF($H135&lt;TODAY(),"Vencido",IF(($H135-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K135" s="200">
         <f>IF($C135,$H135-TODAY(),"")</f>
@@ -25336,7 +27133,7 @@
         <f>IF($C136,'Proyecto Datos (OKR´s)'!$J136,"")</f>
       </c>
       <c r="J136" s="201">
-        <f>IF($C136,IF($I136&gt;=1,"Completado",IF($H136&lt;TODAY(),"Vencido",IF(($H136-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C136,IF($I136&gt;=1,"Completado",IF($H136&lt;TODAY(),"Vencido",IF(($H136-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K136" s="200">
         <f>IF($C136,$H136-TODAY(),"")</f>
@@ -25380,7 +27177,7 @@
         <f>IF($C137,'Proyecto Datos (OKR´s)'!$J137,"")</f>
       </c>
       <c r="J137" s="201">
-        <f>IF($C137,IF($I137&gt;=1,"Completado",IF($H137&lt;TODAY(),"Vencido",IF(($H137-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C137,IF($I137&gt;=1,"Completado",IF($H137&lt;TODAY(),"Vencido",IF(($H137-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K137" s="200">
         <f>IF($C137,$H137-TODAY(),"")</f>
@@ -25424,7 +27221,7 @@
         <f>IF($C138,'Proyecto Datos (OKR´s)'!$J138,"")</f>
       </c>
       <c r="J138" s="201">
-        <f>IF($C138,IF($I138&gt;=1,"Completado",IF($H138&lt;TODAY(),"Vencido",IF(($H138-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C138,IF($I138&gt;=1,"Completado",IF($H138&lt;TODAY(),"Vencido",IF(($H138-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K138" s="200">
         <f>IF($C138,$H138-TODAY(),"")</f>
@@ -25468,7 +27265,7 @@
         <f>IF($C139,'Proyecto Datos (OKR´s)'!$J139,"")</f>
       </c>
       <c r="J139" s="201">
-        <f>IF($C139,IF($I139&gt;=1,"Completado",IF($H139&lt;TODAY(),"Vencido",IF(($H139-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C139,IF($I139&gt;=1,"Completado",IF($H139&lt;TODAY(),"Vencido",IF(($H139-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K139" s="200">
         <f>IF($C139,$H139-TODAY(),"")</f>
@@ -25512,7 +27309,7 @@
         <f>IF($C140,'Proyecto Datos (OKR´s)'!$J140,"")</f>
       </c>
       <c r="J140" s="201">
-        <f>IF($C140,IF($I140&gt;=1,"Completado",IF($H140&lt;TODAY(),"Vencido",IF(($H140-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C140,IF($I140&gt;=1,"Completado",IF($H140&lt;TODAY(),"Vencido",IF(($H140-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K140" s="200">
         <f>IF($C140,$H140-TODAY(),"")</f>
@@ -25556,7 +27353,7 @@
         <f>IF($C141,'Proyecto Datos (OKR´s)'!$J141,"")</f>
       </c>
       <c r="J141" s="201">
-        <f>IF($C141,IF($I141&gt;=1,"Completado",IF($H141&lt;TODAY(),"Vencido",IF(($H141-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C141,IF($I141&gt;=1,"Completado",IF($H141&lt;TODAY(),"Vencido",IF(($H141-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K141" s="200">
         <f>IF($C141,$H141-TODAY(),"")</f>
@@ -25600,7 +27397,7 @@
         <f>IF($C142,'Proyecto Datos (OKR´s)'!$J142,"")</f>
       </c>
       <c r="J142" s="201">
-        <f>IF($C142,IF($I142&gt;=1,"Completado",IF($H142&lt;TODAY(),"Vencido",IF(($H142-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C142,IF($I142&gt;=1,"Completado",IF($H142&lt;TODAY(),"Vencido",IF(($H142-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K142" s="200">
         <f>IF($C142,$H142-TODAY(),"")</f>
@@ -25644,7 +27441,7 @@
         <f>IF($C143,'Proyecto Datos (OKR´s)'!$J143,"")</f>
       </c>
       <c r="J143" s="201">
-        <f>IF($C143,IF($I143&gt;=1,"Completado",IF($H143&lt;TODAY(),"Vencido",IF(($H143-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C143,IF($I143&gt;=1,"Completado",IF($H143&lt;TODAY(),"Vencido",IF(($H143-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K143" s="200">
         <f>IF($C143,$H143-TODAY(),"")</f>
@@ -25688,7 +27485,7 @@
         <f>IF($C144,'Proyecto Datos (OKR´s)'!$J144,"")</f>
       </c>
       <c r="J144" s="201">
-        <f>IF($C144,IF($I144&gt;=1,"Completado",IF($H144&lt;TODAY(),"Vencido",IF(($H144-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C144,IF($I144&gt;=1,"Completado",IF($H144&lt;TODAY(),"Vencido",IF(($H144-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K144" s="200">
         <f>IF($C144,$H144-TODAY(),"")</f>
@@ -25732,7 +27529,7 @@
         <f>IF($C145,'Proyecto Datos (OKR´s)'!$J145,"")</f>
       </c>
       <c r="J145" s="201">
-        <f>IF($C145,IF($I145&gt;=1,"Completado",IF($H145&lt;TODAY(),"Vencido",IF(($H145-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C145,IF($I145&gt;=1,"Completado",IF($H145&lt;TODAY(),"Vencido",IF(($H145-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K145" s="200">
         <f>IF($C145,$H145-TODAY(),"")</f>
@@ -25776,7 +27573,7 @@
         <f>IF($C146,'Proyecto Datos (OKR´s)'!$J146,"")</f>
       </c>
       <c r="J146" s="201">
-        <f>IF($C146,IF($I146&gt;=1,"Completado",IF($H146&lt;TODAY(),"Vencido",IF(($H146-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C146,IF($I146&gt;=1,"Completado",IF($H146&lt;TODAY(),"Vencido",IF(($H146-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K146" s="200">
         <f>IF($C146,$H146-TODAY(),"")</f>
@@ -25820,7 +27617,7 @@
         <f>IF($C147,'Proyecto Datos (OKR´s)'!$J147,"")</f>
       </c>
       <c r="J147" s="201">
-        <f>IF($C147,IF($I147&gt;=1,"Completado",IF($H147&lt;TODAY(),"Vencido",IF(($H147-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C147,IF($I147&gt;=1,"Completado",IF($H147&lt;TODAY(),"Vencido",IF(($H147-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K147" s="200">
         <f>IF($C147,$H147-TODAY(),"")</f>
@@ -25864,7 +27661,7 @@
         <f>IF($C148,'Proyecto Datos (OKR´s)'!$J148,"")</f>
       </c>
       <c r="J148" s="201">
-        <f>IF($C148,IF($I148&gt;=1,"Completado",IF($H148&lt;TODAY(),"Vencido",IF(($H148-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C148,IF($I148&gt;=1,"Completado",IF($H148&lt;TODAY(),"Vencido",IF(($H148-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K148" s="200">
         <f>IF($C148,$H148-TODAY(),"")</f>
@@ -25908,7 +27705,7 @@
         <f>IF($C149,'Proyecto Datos (OKR´s)'!$J149,"")</f>
       </c>
       <c r="J149" s="201">
-        <f>IF($C149,IF($I149&gt;=1,"Completado",IF($H149&lt;TODAY(),"Vencido",IF(($H149-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C149,IF($I149&gt;=1,"Completado",IF($H149&lt;TODAY(),"Vencido",IF(($H149-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K149" s="200">
         <f>IF($C149,$H149-TODAY(),"")</f>
@@ -25952,7 +27749,7 @@
         <f>IF($C150,'Proyecto Datos (OKR´s)'!$J150,"")</f>
       </c>
       <c r="J150" s="201">
-        <f>IF($C150,IF($I150&gt;=1,"Completado",IF($H150&lt;TODAY(),"Vencido",IF(($H150-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C150,IF($I150&gt;=1,"Completado",IF($H150&lt;TODAY(),"Vencido",IF(($H150-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K150" s="200">
         <f>IF($C150,$H150-TODAY(),"")</f>
@@ -25996,7 +27793,7 @@
         <f>IF($C151,'Proyecto Datos (OKR´s)'!$J151,"")</f>
       </c>
       <c r="J151" s="201">
-        <f>IF($C151,IF($I151&gt;=1,"Completado",IF($H151&lt;TODAY(),"Vencido",IF(($H151-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C151,IF($I151&gt;=1,"Completado",IF($H151&lt;TODAY(),"Vencido",IF(($H151-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K151" s="200">
         <f>IF($C151,$H151-TODAY(),"")</f>
@@ -26040,7 +27837,7 @@
         <f>IF($C152,'Proyecto Datos (OKR´s)'!$J152,"")</f>
       </c>
       <c r="J152" s="201">
-        <f>IF($C152,IF($I152&gt;=1,"Completado",IF($H152&lt;TODAY(),"Vencido",IF(($H152-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C152,IF($I152&gt;=1,"Completado",IF($H152&lt;TODAY(),"Vencido",IF(($H152-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K152" s="200">
         <f>IF($C152,$H152-TODAY(),"")</f>
@@ -26084,7 +27881,7 @@
         <f>IF($C153,'Proyecto Datos (OKR´s)'!$J153,"")</f>
       </c>
       <c r="J153" s="201">
-        <f>IF($C153,IF($I153&gt;=1,"Completado",IF($H153&lt;TODAY(),"Vencido",IF(($H153-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C153,IF($I153&gt;=1,"Completado",IF($H153&lt;TODAY(),"Vencido",IF(($H153-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K153" s="200">
         <f>IF($C153,$H153-TODAY(),"")</f>
@@ -26128,7 +27925,7 @@
         <f>IF($C154,'Proyecto Datos (OKR´s)'!$J154,"")</f>
       </c>
       <c r="J154" s="201">
-        <f>IF($C154,IF($I154&gt;=1,"Completado",IF($H154&lt;TODAY(),"Vencido",IF(($H154-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C154,IF($I154&gt;=1,"Completado",IF($H154&lt;TODAY(),"Vencido",IF(($H154-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K154" s="200">
         <f>IF($C154,$H154-TODAY(),"")</f>
@@ -26172,7 +27969,7 @@
         <f>IF($C155,'Proyecto Datos (OKR´s)'!$J155,"")</f>
       </c>
       <c r="J155" s="201">
-        <f>IF($C155,IF($I155&gt;=1,"Completado",IF($H155&lt;TODAY(),"Vencido",IF(($H155-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C155,IF($I155&gt;=1,"Completado",IF($H155&lt;TODAY(),"Vencido",IF(($H155-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K155" s="200">
         <f>IF($C155,$H155-TODAY(),"")</f>
@@ -26216,7 +28013,7 @@
         <f>IF($C156,'Proyecto Datos (OKR´s)'!$J156,"")</f>
       </c>
       <c r="J156" s="201">
-        <f>IF($C156,IF($I156&gt;=1,"Completado",IF($H156&lt;TODAY(),"Vencido",IF(($H156-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C156,IF($I156&gt;=1,"Completado",IF($H156&lt;TODAY(),"Vencido",IF(($H156-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K156" s="200">
         <f>IF($C156,$H156-TODAY(),"")</f>
@@ -26260,7 +28057,7 @@
         <f>IF($C157,'Proyecto Datos (OKR´s)'!$J157,"")</f>
       </c>
       <c r="J157" s="201">
-        <f>IF($C157,IF($I157&gt;=1,"Completado",IF($H157&lt;TODAY(),"Vencido",IF(($H157-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C157,IF($I157&gt;=1,"Completado",IF($H157&lt;TODAY(),"Vencido",IF(($H157-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K157" s="200">
         <f>IF($C157,$H157-TODAY(),"")</f>
@@ -26304,7 +28101,7 @@
         <f>IF($C158,'Proyecto Datos (OKR´s)'!$J158,"")</f>
       </c>
       <c r="J158" s="201">
-        <f>IF($C158,IF($I158&gt;=1,"Completado",IF($H158&lt;TODAY(),"Vencido",IF(($H158-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C158,IF($I158&gt;=1,"Completado",IF($H158&lt;TODAY(),"Vencido",IF(($H158-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K158" s="200">
         <f>IF($C158,$H158-TODAY(),"")</f>
@@ -26348,7 +28145,7 @@
         <f>IF($C159,'Proyecto Datos (OKR´s)'!$J159,"")</f>
       </c>
       <c r="J159" s="201">
-        <f>IF($C159,IF($I159&gt;=1,"Completado",IF($H159&lt;TODAY(),"Vencido",IF(($H159-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C159,IF($I159&gt;=1,"Completado",IF($H159&lt;TODAY(),"Vencido",IF(($H159-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K159" s="200">
         <f>IF($C159,$H159-TODAY(),"")</f>
@@ -26392,7 +28189,7 @@
         <f>IF($C160,'Proyecto Datos (OKR´s)'!$J160,"")</f>
       </c>
       <c r="J160" s="201">
-        <f>IF($C160,IF($I160&gt;=1,"Completado",IF($H160&lt;TODAY(),"Vencido",IF(($H160-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C160,IF($I160&gt;=1,"Completado",IF($H160&lt;TODAY(),"Vencido",IF(($H160-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K160" s="200">
         <f>IF($C160,$H160-TODAY(),"")</f>
@@ -26436,7 +28233,7 @@
         <f>IF($C161,'Proyecto Datos (OKR´s)'!$J161,"")</f>
       </c>
       <c r="J161" s="201">
-        <f>IF($C161,IF($I161&gt;=1,"Completado",IF($H161&lt;TODAY(),"Vencido",IF(($H161-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C161,IF($I161&gt;=1,"Completado",IF($H161&lt;TODAY(),"Vencido",IF(($H161-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K161" s="200">
         <f>IF($C161,$H161-TODAY(),"")</f>
@@ -26480,7 +28277,7 @@
         <f>IF($C162,'Proyecto Datos (OKR´s)'!$J162,"")</f>
       </c>
       <c r="J162" s="201">
-        <f>IF($C162,IF($I162&gt;=1,"Completado",IF($H162&lt;TODAY(),"Vencido",IF(($H162-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C162,IF($I162&gt;=1,"Completado",IF($H162&lt;TODAY(),"Vencido",IF(($H162-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K162" s="200">
         <f>IF($C162,$H162-TODAY(),"")</f>
@@ -26524,7 +28321,7 @@
         <f>IF($C163,'Proyecto Datos (OKR´s)'!$J163,"")</f>
       </c>
       <c r="J163" s="201">
-        <f>IF($C163,IF($I163&gt;=1,"Completado",IF($H163&lt;TODAY(),"Vencido",IF(($H163-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C163,IF($I163&gt;=1,"Completado",IF($H163&lt;TODAY(),"Vencido",IF(($H163-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K163" s="200">
         <f>IF($C163,$H163-TODAY(),"")</f>
@@ -26568,7 +28365,7 @@
         <f>IF($C164,'Proyecto Datos (OKR´s)'!$J164,"")</f>
       </c>
       <c r="J164" s="201">
-        <f>IF($C164,IF($I164&gt;=1,"Completado",IF($H164&lt;TODAY(),"Vencido",IF(($H164-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C164,IF($I164&gt;=1,"Completado",IF($H164&lt;TODAY(),"Vencido",IF(($H164-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K164" s="200">
         <f>IF($C164,$H164-TODAY(),"")</f>
@@ -26612,7 +28409,7 @@
         <f>IF($C165,'Proyecto Datos (OKR´s)'!$J165,"")</f>
       </c>
       <c r="J165" s="201">
-        <f>IF($C165,IF($I165&gt;=1,"Completado",IF($H165&lt;TODAY(),"Vencido",IF(($H165-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C165,IF($I165&gt;=1,"Completado",IF($H165&lt;TODAY(),"Vencido",IF(($H165-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K165" s="200">
         <f>IF($C165,$H165-TODAY(),"")</f>
@@ -26656,7 +28453,7 @@
         <f>IF($C166,'Proyecto Datos (OKR´s)'!$J166,"")</f>
       </c>
       <c r="J166" s="201">
-        <f>IF($C166,IF($I166&gt;=1,"Completado",IF($H166&lt;TODAY(),"Vencido",IF(($H166-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C166,IF($I166&gt;=1,"Completado",IF($H166&lt;TODAY(),"Vencido",IF(($H166-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K166" s="200">
         <f>IF($C166,$H166-TODAY(),"")</f>
@@ -26700,7 +28497,7 @@
         <f>IF($C167,'Proyecto Datos (OKR´s)'!$J167,"")</f>
       </c>
       <c r="J167" s="201">
-        <f>IF($C167,IF($I167&gt;=1,"Completado",IF($H167&lt;TODAY(),"Vencido",IF(($H167-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C167,IF($I167&gt;=1,"Completado",IF($H167&lt;TODAY(),"Vencido",IF(($H167-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K167" s="200">
         <f>IF($C167,$H167-TODAY(),"")</f>
@@ -26744,7 +28541,7 @@
         <f>IF($C168,'Proyecto Datos (OKR´s)'!$J168,"")</f>
       </c>
       <c r="J168" s="201">
-        <f>IF($C168,IF($I168&gt;=1,"Completado",IF($H168&lt;TODAY(),"Vencido",IF(($H168-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C168,IF($I168&gt;=1,"Completado",IF($H168&lt;TODAY(),"Vencido",IF(($H168-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K168" s="200">
         <f>IF($C168,$H168-TODAY(),"")</f>
@@ -26788,7 +28585,7 @@
         <f>IF($C169,'Proyecto Datos (OKR´s)'!$J169,"")</f>
       </c>
       <c r="J169" s="201">
-        <f>IF($C169,IF($I169&gt;=1,"Completado",IF($H169&lt;TODAY(),"Vencido",IF(($H169-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C169,IF($I169&gt;=1,"Completado",IF($H169&lt;TODAY(),"Vencido",IF(($H169-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K169" s="200">
         <f>IF($C169,$H169-TODAY(),"")</f>
@@ -26832,7 +28629,7 @@
         <f>IF($C170,'Proyecto Datos (OKR´s)'!$J170,"")</f>
       </c>
       <c r="J170" s="201">
-        <f>IF($C170,IF($I170&gt;=1,"Completado",IF($H170&lt;TODAY(),"Vencido",IF(($H170-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C170,IF($I170&gt;=1,"Completado",IF($H170&lt;TODAY(),"Vencido",IF(($H170-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K170" s="200">
         <f>IF($C170,$H170-TODAY(),"")</f>
@@ -26876,7 +28673,7 @@
         <f>IF($C171,'Proyecto Datos (OKR´s)'!$J171,"")</f>
       </c>
       <c r="J171" s="201">
-        <f>IF($C171,IF($I171&gt;=1,"Completado",IF($H171&lt;TODAY(),"Vencido",IF(($H171-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C171,IF($I171&gt;=1,"Completado",IF($H171&lt;TODAY(),"Vencido",IF(($H171-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K171" s="200">
         <f>IF($C171,$H171-TODAY(),"")</f>
@@ -26920,7 +28717,7 @@
         <f>IF($C172,'Proyecto Datos (OKR´s)'!$J172,"")</f>
       </c>
       <c r="J172" s="201">
-        <f>IF($C172,IF($I172&gt;=1,"Completado",IF($H172&lt;TODAY(),"Vencido",IF(($H172-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C172,IF($I172&gt;=1,"Completado",IF($H172&lt;TODAY(),"Vencido",IF(($H172-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K172" s="200">
         <f>IF($C172,$H172-TODAY(),"")</f>
@@ -26964,7 +28761,7 @@
         <f>IF($C173,'Proyecto Datos (OKR´s)'!$J173,"")</f>
       </c>
       <c r="J173" s="201">
-        <f>IF($C173,IF($I173&gt;=1,"Completado",IF($H173&lt;TODAY(),"Vencido",IF(($H173-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C173,IF($I173&gt;=1,"Completado",IF($H173&lt;TODAY(),"Vencido",IF(($H173-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K173" s="200">
         <f>IF($C173,$H173-TODAY(),"")</f>
@@ -27008,7 +28805,7 @@
         <f>IF($C174,'Proyecto Datos (OKR´s)'!$J174,"")</f>
       </c>
       <c r="J174" s="201">
-        <f>IF($C174,IF($I174&gt;=1,"Completado",IF($H174&lt;TODAY(),"Vencido",IF(($H174-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C174,IF($I174&gt;=1,"Completado",IF($H174&lt;TODAY(),"Vencido",IF(($H174-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K174" s="200">
         <f>IF($C174,$H174-TODAY(),"")</f>
@@ -27052,7 +28849,7 @@
         <f>IF($C175,'Proyecto Datos (OKR´s)'!$J175,"")</f>
       </c>
       <c r="J175" s="201">
-        <f>IF($C175,IF($I175&gt;=1,"Completado",IF($H175&lt;TODAY(),"Vencido",IF(($H175-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C175,IF($I175&gt;=1,"Completado",IF($H175&lt;TODAY(),"Vencido",IF(($H175-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K175" s="200">
         <f>IF($C175,$H175-TODAY(),"")</f>
@@ -27096,7 +28893,7 @@
         <f>IF($C176,'Proyecto Datos (OKR´s)'!$J176,"")</f>
       </c>
       <c r="J176" s="201">
-        <f>IF($C176,IF($I176&gt;=1,"Completado",IF($H176&lt;TODAY(),"Vencido",IF(($H176-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C176,IF($I176&gt;=1,"Completado",IF($H176&lt;TODAY(),"Vencido",IF(($H176-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K176" s="200">
         <f>IF($C176,$H176-TODAY(),"")</f>
@@ -27140,7 +28937,7 @@
         <f>IF($C177,'Proyecto Datos (OKR´s)'!$J177,"")</f>
       </c>
       <c r="J177" s="201">
-        <f>IF($C177,IF($I177&gt;=1,"Completado",IF($H177&lt;TODAY(),"Vencido",IF(($H177-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C177,IF($I177&gt;=1,"Completado",IF($H177&lt;TODAY(),"Vencido",IF(($H177-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K177" s="200">
         <f>IF($C177,$H177-TODAY(),"")</f>
@@ -27184,7 +28981,7 @@
         <f>IF($C178,'Proyecto Datos (OKR´s)'!$J178,"")</f>
       </c>
       <c r="J178" s="201">
-        <f>IF($C178,IF($I178&gt;=1,"Completado",IF($H178&lt;TODAY(),"Vencido",IF(($H178-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C178,IF($I178&gt;=1,"Completado",IF($H178&lt;TODAY(),"Vencido",IF(($H178-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K178" s="200">
         <f>IF($C178,$H178-TODAY(),"")</f>
@@ -27228,7 +29025,7 @@
         <f>IF($C179,'Proyecto Datos (OKR´s)'!$J179,"")</f>
       </c>
       <c r="J179" s="201">
-        <f>IF($C179,IF($I179&gt;=1,"Completado",IF($H179&lt;TODAY(),"Vencido",IF(($H179-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C179,IF($I179&gt;=1,"Completado",IF($H179&lt;TODAY(),"Vencido",IF(($H179-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K179" s="200">
         <f>IF($C179,$H179-TODAY(),"")</f>
@@ -27272,7 +29069,7 @@
         <f>IF($C180,'Proyecto Datos (OKR´s)'!$J180,"")</f>
       </c>
       <c r="J180" s="201">
-        <f>IF($C180,IF($I180&gt;=1,"Completado",IF($H180&lt;TODAY(),"Vencido",IF(($H180-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C180,IF($I180&gt;=1,"Completado",IF($H180&lt;TODAY(),"Vencido",IF(($H180-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K180" s="200">
         <f>IF($C180,$H180-TODAY(),"")</f>
@@ -27316,7 +29113,7 @@
         <f>IF($C181,'Proyecto Datos (OKR´s)'!$J181,"")</f>
       </c>
       <c r="J181" s="201">
-        <f>IF($C181,IF($I181&gt;=1,"Completado",IF($H181&lt;TODAY(),"Vencido",IF(($H181-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C181,IF($I181&gt;=1,"Completado",IF($H181&lt;TODAY(),"Vencido",IF(($H181-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K181" s="200">
         <f>IF($C181,$H181-TODAY(),"")</f>
@@ -27360,7 +29157,7 @@
         <f>IF($C182,'Proyecto Datos (OKR´s)'!$J182,"")</f>
       </c>
       <c r="J182" s="201">
-        <f>IF($C182,IF($I182&gt;=1,"Completado",IF($H182&lt;TODAY(),"Vencido",IF(($H182-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C182,IF($I182&gt;=1,"Completado",IF($H182&lt;TODAY(),"Vencido",IF(($H182-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K182" s="200">
         <f>IF($C182,$H182-TODAY(),"")</f>
@@ -27404,7 +29201,7 @@
         <f>IF($C183,'Proyecto Datos (OKR´s)'!$J183,"")</f>
       </c>
       <c r="J183" s="201">
-        <f>IF($C183,IF($I183&gt;=1,"Completado",IF($H183&lt;TODAY(),"Vencido",IF(($H183-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C183,IF($I183&gt;=1,"Completado",IF($H183&lt;TODAY(),"Vencido",IF(($H183-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K183" s="200">
         <f>IF($C183,$H183-TODAY(),"")</f>
@@ -27448,7 +29245,7 @@
         <f>IF($C184,'Proyecto Datos (OKR´s)'!$J184,"")</f>
       </c>
       <c r="J184" s="201">
-        <f>IF($C184,IF($I184&gt;=1,"Completado",IF($H184&lt;TODAY(),"Vencido",IF(($H184-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C184,IF($I184&gt;=1,"Completado",IF($H184&lt;TODAY(),"Vencido",IF(($H184-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K184" s="200">
         <f>IF($C184,$H184-TODAY(),"")</f>
@@ -27492,7 +29289,7 @@
         <f>IF($C185,'Proyecto Datos (OKR´s)'!$J185,"")</f>
       </c>
       <c r="J185" s="201">
-        <f>IF($C185,IF($I185&gt;=1,"Completado",IF($H185&lt;TODAY(),"Vencido",IF(($H185-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C185,IF($I185&gt;=1,"Completado",IF($H185&lt;TODAY(),"Vencido",IF(($H185-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K185" s="200">
         <f>IF($C185,$H185-TODAY(),"")</f>
@@ -27536,7 +29333,7 @@
         <f>IF($C186,'Proyecto Datos (OKR´s)'!$J186,"")</f>
       </c>
       <c r="J186" s="201">
-        <f>IF($C186,IF($I186&gt;=1,"Completado",IF($H186&lt;TODAY(),"Vencido",IF(($H186-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C186,IF($I186&gt;=1,"Completado",IF($H186&lt;TODAY(),"Vencido",IF(($H186-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K186" s="200">
         <f>IF($C186,$H186-TODAY(),"")</f>
@@ -27580,7 +29377,7 @@
         <f>IF($C187,'Proyecto Datos (OKR´s)'!$J187,"")</f>
       </c>
       <c r="J187" s="201">
-        <f>IF($C187,IF($I187&gt;=1,"Completado",IF($H187&lt;TODAY(),"Vencido",IF(($H187-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C187,IF($I187&gt;=1,"Completado",IF($H187&lt;TODAY(),"Vencido",IF(($H187-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K187" s="200">
         <f>IF($C187,$H187-TODAY(),"")</f>
@@ -27624,7 +29421,7 @@
         <f>IF($C188,'Proyecto Datos (OKR´s)'!$J188,"")</f>
       </c>
       <c r="J188" s="201">
-        <f>IF($C188,IF($I188&gt;=1,"Completado",IF($H188&lt;TODAY(),"Vencido",IF(($H188-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C188,IF($I188&gt;=1,"Completado",IF($H188&lt;TODAY(),"Vencido",IF(($H188-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K188" s="200">
         <f>IF($C188,$H188-TODAY(),"")</f>
@@ -27668,7 +29465,7 @@
         <f>IF($C189,'Proyecto Datos (OKR´s)'!$J189,"")</f>
       </c>
       <c r="J189" s="201">
-        <f>IF($C189,IF($I189&gt;=1,"Completado",IF($H189&lt;TODAY(),"Vencido",IF(($H189-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C189,IF($I189&gt;=1,"Completado",IF($H189&lt;TODAY(),"Vencido",IF(($H189-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K189" s="200">
         <f>IF($C189,$H189-TODAY(),"")</f>
@@ -27712,7 +29509,7 @@
         <f>IF($C190,'Proyecto Datos (OKR´s)'!$J190,"")</f>
       </c>
       <c r="J190" s="201">
-        <f>IF($C190,IF($I190&gt;=1,"Completado",IF($H190&lt;TODAY(),"Vencido",IF(($H190-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C190,IF($I190&gt;=1,"Completado",IF($H190&lt;TODAY(),"Vencido",IF(($H190-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K190" s="200">
         <f>IF($C190,$H190-TODAY(),"")</f>
@@ -27756,7 +29553,7 @@
         <f>IF($C191,'Proyecto Datos (OKR´s)'!$J191,"")</f>
       </c>
       <c r="J191" s="201">
-        <f>IF($C191,IF($I191&gt;=1,"Completado",IF($H191&lt;TODAY(),"Vencido",IF(($H191-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C191,IF($I191&gt;=1,"Completado",IF($H191&lt;TODAY(),"Vencido",IF(($H191-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K191" s="200">
         <f>IF($C191,$H191-TODAY(),"")</f>
@@ -27800,7 +29597,7 @@
         <f>IF($C192,'Proyecto Datos (OKR´s)'!$J192,"")</f>
       </c>
       <c r="J192" s="201">
-        <f>IF($C192,IF($I192&gt;=1,"Completado",IF($H192&lt;TODAY(),"Vencido",IF(($H192-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C192,IF($I192&gt;=1,"Completado",IF($H192&lt;TODAY(),"Vencido",IF(($H192-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K192" s="200">
         <f>IF($C192,$H192-TODAY(),"")</f>
@@ -27844,7 +29641,7 @@
         <f>IF($C193,'Proyecto Datos (OKR´s)'!$J193,"")</f>
       </c>
       <c r="J193" s="201">
-        <f>IF($C193,IF($I193&gt;=1,"Completado",IF($H193&lt;TODAY(),"Vencido",IF(($H193-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C193,IF($I193&gt;=1,"Completado",IF($H193&lt;TODAY(),"Vencido",IF(($H193-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K193" s="200">
         <f>IF($C193,$H193-TODAY(),"")</f>
@@ -27888,7 +29685,7 @@
         <f>IF($C194,'Proyecto Datos (OKR´s)'!$J194,"")</f>
       </c>
       <c r="J194" s="201">
-        <f>IF($C194,IF($I194&gt;=1,"Completado",IF($H194&lt;TODAY(),"Vencido",IF(($H194-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C194,IF($I194&gt;=1,"Completado",IF($H194&lt;TODAY(),"Vencido",IF(($H194-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K194" s="200">
         <f>IF($C194,$H194-TODAY(),"")</f>
@@ -27932,7 +29729,7 @@
         <f>IF($C195,'Proyecto Datos (OKR´s)'!$J195,"")</f>
       </c>
       <c r="J195" s="201">
-        <f>IF($C195,IF($I195&gt;=1,"Completado",IF($H195&lt;TODAY(),"Vencido",IF(($H195-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C195,IF($I195&gt;=1,"Completado",IF($H195&lt;TODAY(),"Vencido",IF(($H195-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K195" s="200">
         <f>IF($C195,$H195-TODAY(),"")</f>
@@ -27976,7 +29773,7 @@
         <f>IF($C196,'Proyecto Datos (OKR´s)'!$J196,"")</f>
       </c>
       <c r="J196" s="201">
-        <f>IF($C196,IF($I196&gt;=1,"Completado",IF($H196&lt;TODAY(),"Vencido",IF(($H196-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C196,IF($I196&gt;=1,"Completado",IF($H196&lt;TODAY(),"Vencido",IF(($H196-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K196" s="200">
         <f>IF($C196,$H196-TODAY(),"")</f>
@@ -28020,7 +29817,7 @@
         <f>IF($C197,'Proyecto Datos (OKR´s)'!$J197,"")</f>
       </c>
       <c r="J197" s="201">
-        <f>IF($C197,IF($I197&gt;=1,"Completado",IF($H197&lt;TODAY(),"Vencido",IF(($H197-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C197,IF($I197&gt;=1,"Completado",IF($H197&lt;TODAY(),"Vencido",IF(($H197-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K197" s="200">
         <f>IF($C197,$H197-TODAY(),"")</f>
@@ -28064,7 +29861,7 @@
         <f>IF($C198,'Proyecto Datos (OKR´s)'!$J198,"")</f>
       </c>
       <c r="J198" s="201">
-        <f>IF($C198,IF($I198&gt;=1,"Completado",IF($H198&lt;TODAY(),"Vencido",IF(($H198-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C198,IF($I198&gt;=1,"Completado",IF($H198&lt;TODAY(),"Vencido",IF(($H198-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K198" s="200">
         <f>IF($C198,$H198-TODAY(),"")</f>
@@ -28108,7 +29905,7 @@
         <f>IF($C199,'Proyecto Datos (OKR´s)'!$J199,"")</f>
       </c>
       <c r="J199" s="201">
-        <f>IF($C199,IF($I199&gt;=1,"Completado",IF($H199&lt;TODAY(),"Vencido",IF(($H199-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C199,IF($I199&gt;=1,"Completado",IF($H199&lt;TODAY(),"Vencido",IF(($H199-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K199" s="200">
         <f>IF($C199,$H199-TODAY(),"")</f>
@@ -28152,7 +29949,7 @@
         <f>IF($C200,'Proyecto Datos (OKR´s)'!$J200,"")</f>
       </c>
       <c r="J200" s="201">
-        <f>IF($C200,IF($I200&gt;=1,"Completado",IF($H200&lt;TODAY(),"Vencido",IF(($H200-TODAY())&lt;='Entregas Próximas'!$I$4,"Próximo a vencer","En curso"))),"")</f>
+        <f>IF($C200,IF($I200&gt;=1,"Completado",IF($H200&lt;TODAY(),"Vencido",IF(($H200-TODAY())&lt;='Entregas Próximas'!$I$3,"Próximo a vencer","En curso"))),"")</f>
       </c>
       <c r="K200" s="200">
         <f>IF($C200,$H200-TODAY(),"")</f>

--- a/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
+++ b/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
@@ -21112,26 +21112,23 @@
     <mergeCell ref="G3:H3"/>
     <mergeCell ref="B5:I5"/>
   </mergeCells>
-  <conditionalFormatting sqref="B7:I156">
-    <cfRule type="expression" dxfId="22" priority="31">
-      <formula>AND($D7&lt;&gt;"",MOD(ROW(),2)=0)</formula>
+  <conditionalFormatting sqref="G7:H156">
+    <cfRule type="expression" dxfId="23" priority="21">
+      <formula>$G7="Vencido"</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="21" priority="32">
-      <formula>$D7&lt;&gt;""</formula>
+    <cfRule type="expression" dxfId="24" priority="22">
+      <formula>$G7="Próximo a vencer"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="25" priority="23">
+      <formula>$G7="En curso"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="26" priority="24">
+      <formula>$G7="Completado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:H156">
-    <cfRule type="expression" dxfId="23" priority="33">
-      <formula>$G7="Vencido"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="24" priority="34">
-      <formula>$G7="Próximo a vencer"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="25" priority="35">
-      <formula>$G7="En curso"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="26" priority="36">
-      <formula>$G7="Completado"</formula>
+  <conditionalFormatting sqref="B7:I156">
+    <cfRule type="expression" dxfId="21" priority="40">
+      <formula>$D7&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>

--- a/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
+++ b/Diagrama_de_Gantt___Proyecto_Datos_Op._Complejas_080626.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Acerca de" sheetId="12" state="hidden" r:id="rId4"/>
     <sheet name="Tablero" sheetId="15" r:id="rId12"/>
     <sheet name="Entregas Próximas" sheetId="16" r:id="rId13"/>
+    <sheet name="Postergar" sheetId="20" r:id="rId16"/>
     <sheet name="Historial de Sprints" sheetId="19" r:id="rId15"/>
     <sheet name="_Datos" sheetId="18" state="hidden" r:id="rId14"/>
   </sheets>
@@ -2793,7 +2794,7 @@
     <cellStyle name="Total" xfId="29" builtinId="25" customBuiltin="1"/>
     <cellStyle name="zTextoOculto" xfId="3" xr:uid="{26E66EE6-E33F-4D77-BAE4-0FB4F5BBF673}"/>
   </cellStyles>
-  <dxfs count="27">
+  <dxfs count="28">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3078,6 +3079,13 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF38761D"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF2CC"/>
         </patternFill>
       </fill>
     </dxf>
@@ -23374,7 +23382,7 @@
         <f>IF($C7,IF(LEN(TRIM($AN7))=0,"—",TRIM($AN7)),"")</f>
       </c>
       <c r="AD7" s="201">
-        <f>IF($C7,IF($N7=9999,9999,IF($J7="Completado",$N7,MAX($N7,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C7,IF($N7=9999,9999,IF($J7="Completado",$N7,MAX($N7,'Historial de Sprints'!$C$7)+N('Postergar'!$F7))),"")</f>
       </c>
       <c r="AE7" s="201">
         <f>IF($C7,IF($AD7=9999,"(Sin sprint)",$AD7),"")</f>
@@ -23386,7 +23394,7 @@
         <f>IF($AF7,'Historial de Sprints'!$C$5+$N7*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH7" s="202">
-        <f>IF($AF7,"No completada al cierre del Sprint "&amp;$N7&amp;" -&gt; reasignada al Sprint "&amp;$AD7,"")</f>
+        <f>IF($AF7,IF('Postergar'!$G7&lt;&gt;"",'Postergar'!$G7,"No completada al cierre del Sprint "&amp;$N7)&amp;" -&gt; Sprint "&amp;$AD7,"")</f>
       </c>
       <c r="AI7" s="201">
         <f>IF($AF7,$N7*100000+ROW(),"")</f>
@@ -23496,7 +23504,7 @@
         <f>IF($C8,IF(LEN(TRIM($AN8))=0,"—",TRIM($AN8)),"")</f>
       </c>
       <c r="AD8" s="201">
-        <f>IF($C8,IF($N8=9999,9999,IF($J8="Completado",$N8,MAX($N8,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C8,IF($N8=9999,9999,IF($J8="Completado",$N8,MAX($N8,'Historial de Sprints'!$C$7)+N('Postergar'!$F8))),"")</f>
       </c>
       <c r="AE8" s="201">
         <f>IF($C8,IF($AD8=9999,"(Sin sprint)",$AD8),"")</f>
@@ -23508,7 +23516,7 @@
         <f>IF($AF8,'Historial de Sprints'!$C$5+$N8*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH8" s="202">
-        <f>IF($AF8,"No completada al cierre del Sprint "&amp;$N8&amp;" -&gt; reasignada al Sprint "&amp;$AD8,"")</f>
+        <f>IF($AF8,IF('Postergar'!$G8&lt;&gt;"",'Postergar'!$G8,"No completada al cierre del Sprint "&amp;$N8)&amp;" -&gt; Sprint "&amp;$AD8,"")</f>
       </c>
       <c r="AI8" s="201">
         <f>IF($AF8,$N8*100000+ROW(),"")</f>
@@ -23618,7 +23626,7 @@
         <f>IF($C9,IF(LEN(TRIM($AN9))=0,"—",TRIM($AN9)),"")</f>
       </c>
       <c r="AD9" s="201">
-        <f>IF($C9,IF($N9=9999,9999,IF($J9="Completado",$N9,MAX($N9,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C9,IF($N9=9999,9999,IF($J9="Completado",$N9,MAX($N9,'Historial de Sprints'!$C$7)+N('Postergar'!$F9))),"")</f>
       </c>
       <c r="AE9" s="201">
         <f>IF($C9,IF($AD9=9999,"(Sin sprint)",$AD9),"")</f>
@@ -23630,7 +23638,7 @@
         <f>IF($AF9,'Historial de Sprints'!$C$5+$N9*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH9" s="202">
-        <f>IF($AF9,"No completada al cierre del Sprint "&amp;$N9&amp;" -&gt; reasignada al Sprint "&amp;$AD9,"")</f>
+        <f>IF($AF9,IF('Postergar'!$G9&lt;&gt;"",'Postergar'!$G9,"No completada al cierre del Sprint "&amp;$N9)&amp;" -&gt; Sprint "&amp;$AD9,"")</f>
       </c>
       <c r="AI9" s="201">
         <f>IF($AF9,$N9*100000+ROW(),"")</f>
@@ -23740,7 +23748,7 @@
         <f>IF($C10,IF(LEN(TRIM($AN10))=0,"—",TRIM($AN10)),"")</f>
       </c>
       <c r="AD10" s="201">
-        <f>IF($C10,IF($N10=9999,9999,IF($J10="Completado",$N10,MAX($N10,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C10,IF($N10=9999,9999,IF($J10="Completado",$N10,MAX($N10,'Historial de Sprints'!$C$7)+N('Postergar'!$F10))),"")</f>
       </c>
       <c r="AE10" s="201">
         <f>IF($C10,IF($AD10=9999,"(Sin sprint)",$AD10),"")</f>
@@ -23752,7 +23760,7 @@
         <f>IF($AF10,'Historial de Sprints'!$C$5+$N10*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH10" s="202">
-        <f>IF($AF10,"No completada al cierre del Sprint "&amp;$N10&amp;" -&gt; reasignada al Sprint "&amp;$AD10,"")</f>
+        <f>IF($AF10,IF('Postergar'!$G10&lt;&gt;"",'Postergar'!$G10,"No completada al cierre del Sprint "&amp;$N10)&amp;" -&gt; Sprint "&amp;$AD10,"")</f>
       </c>
       <c r="AI10" s="201">
         <f>IF($AF10,$N10*100000+ROW(),"")</f>
@@ -23862,7 +23870,7 @@
         <f>IF($C11,IF(LEN(TRIM($AN11))=0,"—",TRIM($AN11)),"")</f>
       </c>
       <c r="AD11" s="201">
-        <f>IF($C11,IF($N11=9999,9999,IF($J11="Completado",$N11,MAX($N11,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C11,IF($N11=9999,9999,IF($J11="Completado",$N11,MAX($N11,'Historial de Sprints'!$C$7)+N('Postergar'!$F11))),"")</f>
       </c>
       <c r="AE11" s="201">
         <f>IF($C11,IF($AD11=9999,"(Sin sprint)",$AD11),"")</f>
@@ -23874,7 +23882,7 @@
         <f>IF($AF11,'Historial de Sprints'!$C$5+$N11*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH11" s="202">
-        <f>IF($AF11,"No completada al cierre del Sprint "&amp;$N11&amp;" -&gt; reasignada al Sprint "&amp;$AD11,"")</f>
+        <f>IF($AF11,IF('Postergar'!$G11&lt;&gt;"",'Postergar'!$G11,"No completada al cierre del Sprint "&amp;$N11)&amp;" -&gt; Sprint "&amp;$AD11,"")</f>
       </c>
       <c r="AI11" s="201">
         <f>IF($AF11,$N11*100000+ROW(),"")</f>
@@ -23984,7 +23992,7 @@
         <f>IF($C12,IF(LEN(TRIM($AN12))=0,"—",TRIM($AN12)),"")</f>
       </c>
       <c r="AD12" s="201">
-        <f>IF($C12,IF($N12=9999,9999,IF($J12="Completado",$N12,MAX($N12,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C12,IF($N12=9999,9999,IF($J12="Completado",$N12,MAX($N12,'Historial de Sprints'!$C$7)+N('Postergar'!$F12))),"")</f>
       </c>
       <c r="AE12" s="201">
         <f>IF($C12,IF($AD12=9999,"(Sin sprint)",$AD12),"")</f>
@@ -23996,7 +24004,7 @@
         <f>IF($AF12,'Historial de Sprints'!$C$5+$N12*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH12" s="202">
-        <f>IF($AF12,"No completada al cierre del Sprint "&amp;$N12&amp;" -&gt; reasignada al Sprint "&amp;$AD12,"")</f>
+        <f>IF($AF12,IF('Postergar'!$G12&lt;&gt;"",'Postergar'!$G12,"No completada al cierre del Sprint "&amp;$N12)&amp;" -&gt; Sprint "&amp;$AD12,"")</f>
       </c>
       <c r="AI12" s="201">
         <f>IF($AF12,$N12*100000+ROW(),"")</f>
@@ -24106,7 +24114,7 @@
         <f>IF($C13,IF(LEN(TRIM($AN13))=0,"—",TRIM($AN13)),"")</f>
       </c>
       <c r="AD13" s="201">
-        <f>IF($C13,IF($N13=9999,9999,IF($J13="Completado",$N13,MAX($N13,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C13,IF($N13=9999,9999,IF($J13="Completado",$N13,MAX($N13,'Historial de Sprints'!$C$7)+N('Postergar'!$F13))),"")</f>
       </c>
       <c r="AE13" s="201">
         <f>IF($C13,IF($AD13=9999,"(Sin sprint)",$AD13),"")</f>
@@ -24118,7 +24126,7 @@
         <f>IF($AF13,'Historial de Sprints'!$C$5+$N13*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH13" s="202">
-        <f>IF($AF13,"No completada al cierre del Sprint "&amp;$N13&amp;" -&gt; reasignada al Sprint "&amp;$AD13,"")</f>
+        <f>IF($AF13,IF('Postergar'!$G13&lt;&gt;"",'Postergar'!$G13,"No completada al cierre del Sprint "&amp;$N13)&amp;" -&gt; Sprint "&amp;$AD13,"")</f>
       </c>
       <c r="AI13" s="201">
         <f>IF($AF13,$N13*100000+ROW(),"")</f>
@@ -24228,7 +24236,7 @@
         <f>IF($C14,IF(LEN(TRIM($AN14))=0,"—",TRIM($AN14)),"")</f>
       </c>
       <c r="AD14" s="201">
-        <f>IF($C14,IF($N14=9999,9999,IF($J14="Completado",$N14,MAX($N14,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C14,IF($N14=9999,9999,IF($J14="Completado",$N14,MAX($N14,'Historial de Sprints'!$C$7)+N('Postergar'!$F14))),"")</f>
       </c>
       <c r="AE14" s="201">
         <f>IF($C14,IF($AD14=9999,"(Sin sprint)",$AD14),"")</f>
@@ -24240,7 +24248,7 @@
         <f>IF($AF14,'Historial de Sprints'!$C$5+$N14*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH14" s="202">
-        <f>IF($AF14,"No completada al cierre del Sprint "&amp;$N14&amp;" -&gt; reasignada al Sprint "&amp;$AD14,"")</f>
+        <f>IF($AF14,IF('Postergar'!$G14&lt;&gt;"",'Postergar'!$G14,"No completada al cierre del Sprint "&amp;$N14)&amp;" -&gt; Sprint "&amp;$AD14,"")</f>
       </c>
       <c r="AI14" s="201">
         <f>IF($AF14,$N14*100000+ROW(),"")</f>
@@ -24350,7 +24358,7 @@
         <f>IF($C15,IF(LEN(TRIM($AN15))=0,"—",TRIM($AN15)),"")</f>
       </c>
       <c r="AD15" s="201">
-        <f>IF($C15,IF($N15=9999,9999,IF($J15="Completado",$N15,MAX($N15,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C15,IF($N15=9999,9999,IF($J15="Completado",$N15,MAX($N15,'Historial de Sprints'!$C$7)+N('Postergar'!$F15))),"")</f>
       </c>
       <c r="AE15" s="201">
         <f>IF($C15,IF($AD15=9999,"(Sin sprint)",$AD15),"")</f>
@@ -24362,7 +24370,7 @@
         <f>IF($AF15,'Historial de Sprints'!$C$5+$N15*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH15" s="202">
-        <f>IF($AF15,"No completada al cierre del Sprint "&amp;$N15&amp;" -&gt; reasignada al Sprint "&amp;$AD15,"")</f>
+        <f>IF($AF15,IF('Postergar'!$G15&lt;&gt;"",'Postergar'!$G15,"No completada al cierre del Sprint "&amp;$N15)&amp;" -&gt; Sprint "&amp;$AD15,"")</f>
       </c>
       <c r="AI15" s="201">
         <f>IF($AF15,$N15*100000+ROW(),"")</f>
@@ -24472,7 +24480,7 @@
         <f>IF($C16,IF(LEN(TRIM($AN16))=0,"—",TRIM($AN16)),"")</f>
       </c>
       <c r="AD16" s="201">
-        <f>IF($C16,IF($N16=9999,9999,IF($J16="Completado",$N16,MAX($N16,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C16,IF($N16=9999,9999,IF($J16="Completado",$N16,MAX($N16,'Historial de Sprints'!$C$7)+N('Postergar'!$F16))),"")</f>
       </c>
       <c r="AE16" s="201">
         <f>IF($C16,IF($AD16=9999,"(Sin sprint)",$AD16),"")</f>
@@ -24484,7 +24492,7 @@
         <f>IF($AF16,'Historial de Sprints'!$C$5+$N16*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH16" s="202">
-        <f>IF($AF16,"No completada al cierre del Sprint "&amp;$N16&amp;" -&gt; reasignada al Sprint "&amp;$AD16,"")</f>
+        <f>IF($AF16,IF('Postergar'!$G16&lt;&gt;"",'Postergar'!$G16,"No completada al cierre del Sprint "&amp;$N16)&amp;" -&gt; Sprint "&amp;$AD16,"")</f>
       </c>
       <c r="AI16" s="201">
         <f>IF($AF16,$N16*100000+ROW(),"")</f>
@@ -24594,7 +24602,7 @@
         <f>IF($C17,IF(LEN(TRIM($AN17))=0,"—",TRIM($AN17)),"")</f>
       </c>
       <c r="AD17" s="201">
-        <f>IF($C17,IF($N17=9999,9999,IF($J17="Completado",$N17,MAX($N17,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C17,IF($N17=9999,9999,IF($J17="Completado",$N17,MAX($N17,'Historial de Sprints'!$C$7)+N('Postergar'!$F17))),"")</f>
       </c>
       <c r="AE17" s="201">
         <f>IF($C17,IF($AD17=9999,"(Sin sprint)",$AD17),"")</f>
@@ -24606,7 +24614,7 @@
         <f>IF($AF17,'Historial de Sprints'!$C$5+$N17*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH17" s="202">
-        <f>IF($AF17,"No completada al cierre del Sprint "&amp;$N17&amp;" -&gt; reasignada al Sprint "&amp;$AD17,"")</f>
+        <f>IF($AF17,IF('Postergar'!$G17&lt;&gt;"",'Postergar'!$G17,"No completada al cierre del Sprint "&amp;$N17)&amp;" -&gt; Sprint "&amp;$AD17,"")</f>
       </c>
       <c r="AI17" s="201">
         <f>IF($AF17,$N17*100000+ROW(),"")</f>
@@ -24716,7 +24724,7 @@
         <f>IF($C18,IF(LEN(TRIM($AN18))=0,"—",TRIM($AN18)),"")</f>
       </c>
       <c r="AD18" s="201">
-        <f>IF($C18,IF($N18=9999,9999,IF($J18="Completado",$N18,MAX($N18,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C18,IF($N18=9999,9999,IF($J18="Completado",$N18,MAX($N18,'Historial de Sprints'!$C$7)+N('Postergar'!$F18))),"")</f>
       </c>
       <c r="AE18" s="201">
         <f>IF($C18,IF($AD18=9999,"(Sin sprint)",$AD18),"")</f>
@@ -24728,7 +24736,7 @@
         <f>IF($AF18,'Historial de Sprints'!$C$5+$N18*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH18" s="202">
-        <f>IF($AF18,"No completada al cierre del Sprint "&amp;$N18&amp;" -&gt; reasignada al Sprint "&amp;$AD18,"")</f>
+        <f>IF($AF18,IF('Postergar'!$G18&lt;&gt;"",'Postergar'!$G18,"No completada al cierre del Sprint "&amp;$N18)&amp;" -&gt; Sprint "&amp;$AD18,"")</f>
       </c>
       <c r="AI18" s="201">
         <f>IF($AF18,$N18*100000+ROW(),"")</f>
@@ -24838,7 +24846,7 @@
         <f>IF($C19,IF(LEN(TRIM($AN19))=0,"—",TRIM($AN19)),"")</f>
       </c>
       <c r="AD19" s="201">
-        <f>IF($C19,IF($N19=9999,9999,IF($J19="Completado",$N19,MAX($N19,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C19,IF($N19=9999,9999,IF($J19="Completado",$N19,MAX($N19,'Historial de Sprints'!$C$7)+N('Postergar'!$F19))),"")</f>
       </c>
       <c r="AE19" s="201">
         <f>IF($C19,IF($AD19=9999,"(Sin sprint)",$AD19),"")</f>
@@ -24850,7 +24858,7 @@
         <f>IF($AF19,'Historial de Sprints'!$C$5+$N19*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH19" s="202">
-        <f>IF($AF19,"No completada al cierre del Sprint "&amp;$N19&amp;" -&gt; reasignada al Sprint "&amp;$AD19,"")</f>
+        <f>IF($AF19,IF('Postergar'!$G19&lt;&gt;"",'Postergar'!$G19,"No completada al cierre del Sprint "&amp;$N19)&amp;" -&gt; Sprint "&amp;$AD19,"")</f>
       </c>
       <c r="AI19" s="201">
         <f>IF($AF19,$N19*100000+ROW(),"")</f>
@@ -24960,7 +24968,7 @@
         <f>IF($C20,IF(LEN(TRIM($AN20))=0,"—",TRIM($AN20)),"")</f>
       </c>
       <c r="AD20" s="201">
-        <f>IF($C20,IF($N20=9999,9999,IF($J20="Completado",$N20,MAX($N20,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C20,IF($N20=9999,9999,IF($J20="Completado",$N20,MAX($N20,'Historial de Sprints'!$C$7)+N('Postergar'!$F20))),"")</f>
       </c>
       <c r="AE20" s="201">
         <f>IF($C20,IF($AD20=9999,"(Sin sprint)",$AD20),"")</f>
@@ -24972,7 +24980,7 @@
         <f>IF($AF20,'Historial de Sprints'!$C$5+$N20*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH20" s="202">
-        <f>IF($AF20,"No completada al cierre del Sprint "&amp;$N20&amp;" -&gt; reasignada al Sprint "&amp;$AD20,"")</f>
+        <f>IF($AF20,IF('Postergar'!$G20&lt;&gt;"",'Postergar'!$G20,"No completada al cierre del Sprint "&amp;$N20)&amp;" -&gt; Sprint "&amp;$AD20,"")</f>
       </c>
       <c r="AI20" s="201">
         <f>IF($AF20,$N20*100000+ROW(),"")</f>
@@ -25082,7 +25090,7 @@
         <f>IF($C21,IF(LEN(TRIM($AN21))=0,"—",TRIM($AN21)),"")</f>
       </c>
       <c r="AD21" s="201">
-        <f>IF($C21,IF($N21=9999,9999,IF($J21="Completado",$N21,MAX($N21,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C21,IF($N21=9999,9999,IF($J21="Completado",$N21,MAX($N21,'Historial de Sprints'!$C$7)+N('Postergar'!$F21))),"")</f>
       </c>
       <c r="AE21" s="201">
         <f>IF($C21,IF($AD21=9999,"(Sin sprint)",$AD21),"")</f>
@@ -25094,7 +25102,7 @@
         <f>IF($AF21,'Historial de Sprints'!$C$5+$N21*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH21" s="202">
-        <f>IF($AF21,"No completada al cierre del Sprint "&amp;$N21&amp;" -&gt; reasignada al Sprint "&amp;$AD21,"")</f>
+        <f>IF($AF21,IF('Postergar'!$G21&lt;&gt;"",'Postergar'!$G21,"No completada al cierre del Sprint "&amp;$N21)&amp;" -&gt; Sprint "&amp;$AD21,"")</f>
       </c>
       <c r="AI21" s="201">
         <f>IF($AF21,$N21*100000+ROW(),"")</f>
@@ -25204,7 +25212,7 @@
         <f>IF($C22,IF(LEN(TRIM($AN22))=0,"—",TRIM($AN22)),"")</f>
       </c>
       <c r="AD22" s="201">
-        <f>IF($C22,IF($N22=9999,9999,IF($J22="Completado",$N22,MAX($N22,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C22,IF($N22=9999,9999,IF($J22="Completado",$N22,MAX($N22,'Historial de Sprints'!$C$7)+N('Postergar'!$F22))),"")</f>
       </c>
       <c r="AE22" s="201">
         <f>IF($C22,IF($AD22=9999,"(Sin sprint)",$AD22),"")</f>
@@ -25216,7 +25224,7 @@
         <f>IF($AF22,'Historial de Sprints'!$C$5+$N22*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH22" s="202">
-        <f>IF($AF22,"No completada al cierre del Sprint "&amp;$N22&amp;" -&gt; reasignada al Sprint "&amp;$AD22,"")</f>
+        <f>IF($AF22,IF('Postergar'!$G22&lt;&gt;"",'Postergar'!$G22,"No completada al cierre del Sprint "&amp;$N22)&amp;" -&gt; Sprint "&amp;$AD22,"")</f>
       </c>
       <c r="AI22" s="201">
         <f>IF($AF22,$N22*100000+ROW(),"")</f>
@@ -25326,7 +25334,7 @@
         <f>IF($C23,IF(LEN(TRIM($AN23))=0,"—",TRIM($AN23)),"")</f>
       </c>
       <c r="AD23" s="201">
-        <f>IF($C23,IF($N23=9999,9999,IF($J23="Completado",$N23,MAX($N23,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C23,IF($N23=9999,9999,IF($J23="Completado",$N23,MAX($N23,'Historial de Sprints'!$C$7)+N('Postergar'!$F23))),"")</f>
       </c>
       <c r="AE23" s="201">
         <f>IF($C23,IF($AD23=9999,"(Sin sprint)",$AD23),"")</f>
@@ -25338,7 +25346,7 @@
         <f>IF($AF23,'Historial de Sprints'!$C$5+$N23*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH23" s="202">
-        <f>IF($AF23,"No completada al cierre del Sprint "&amp;$N23&amp;" -&gt; reasignada al Sprint "&amp;$AD23,"")</f>
+        <f>IF($AF23,IF('Postergar'!$G23&lt;&gt;"",'Postergar'!$G23,"No completada al cierre del Sprint "&amp;$N23)&amp;" -&gt; Sprint "&amp;$AD23,"")</f>
       </c>
       <c r="AI23" s="201">
         <f>IF($AF23,$N23*100000+ROW(),"")</f>
@@ -25448,7 +25456,7 @@
         <f>IF($C24,IF(LEN(TRIM($AN24))=0,"—",TRIM($AN24)),"")</f>
       </c>
       <c r="AD24" s="201">
-        <f>IF($C24,IF($N24=9999,9999,IF($J24="Completado",$N24,MAX($N24,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C24,IF($N24=9999,9999,IF($J24="Completado",$N24,MAX($N24,'Historial de Sprints'!$C$7)+N('Postergar'!$F24))),"")</f>
       </c>
       <c r="AE24" s="201">
         <f>IF($C24,IF($AD24=9999,"(Sin sprint)",$AD24),"")</f>
@@ -25460,7 +25468,7 @@
         <f>IF($AF24,'Historial de Sprints'!$C$5+$N24*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH24" s="202">
-        <f>IF($AF24,"No completada al cierre del Sprint "&amp;$N24&amp;" -&gt; reasignada al Sprint "&amp;$AD24,"")</f>
+        <f>IF($AF24,IF('Postergar'!$G24&lt;&gt;"",'Postergar'!$G24,"No completada al cierre del Sprint "&amp;$N24)&amp;" -&gt; Sprint "&amp;$AD24,"")</f>
       </c>
       <c r="AI24" s="201">
         <f>IF($AF24,$N24*100000+ROW(),"")</f>
@@ -25570,7 +25578,7 @@
         <f>IF($C25,IF(LEN(TRIM($AN25))=0,"—",TRIM($AN25)),"")</f>
       </c>
       <c r="AD25" s="201">
-        <f>IF($C25,IF($N25=9999,9999,IF($J25="Completado",$N25,MAX($N25,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C25,IF($N25=9999,9999,IF($J25="Completado",$N25,MAX($N25,'Historial de Sprints'!$C$7)+N('Postergar'!$F25))),"")</f>
       </c>
       <c r="AE25" s="201">
         <f>IF($C25,IF($AD25=9999,"(Sin sprint)",$AD25),"")</f>
@@ -25582,7 +25590,7 @@
         <f>IF($AF25,'Historial de Sprints'!$C$5+$N25*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH25" s="202">
-        <f>IF($AF25,"No completada al cierre del Sprint "&amp;$N25&amp;" -&gt; reasignada al Sprint "&amp;$AD25,"")</f>
+        <f>IF($AF25,IF('Postergar'!$G25&lt;&gt;"",'Postergar'!$G25,"No completada al cierre del Sprint "&amp;$N25)&amp;" -&gt; Sprint "&amp;$AD25,"")</f>
       </c>
       <c r="AI25" s="201">
         <f>IF($AF25,$N25*100000+ROW(),"")</f>
@@ -25692,7 +25700,7 @@
         <f>IF($C26,IF(LEN(TRIM($AN26))=0,"—",TRIM($AN26)),"")</f>
       </c>
       <c r="AD26" s="201">
-        <f>IF($C26,IF($N26=9999,9999,IF($J26="Completado",$N26,MAX($N26,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C26,IF($N26=9999,9999,IF($J26="Completado",$N26,MAX($N26,'Historial de Sprints'!$C$7)+N('Postergar'!$F26))),"")</f>
       </c>
       <c r="AE26" s="201">
         <f>IF($C26,IF($AD26=9999,"(Sin sprint)",$AD26),"")</f>
@@ -25704,7 +25712,7 @@
         <f>IF($AF26,'Historial de Sprints'!$C$5+$N26*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH26" s="202">
-        <f>IF($AF26,"No completada al cierre del Sprint "&amp;$N26&amp;" -&gt; reasignada al Sprint "&amp;$AD26,"")</f>
+        <f>IF($AF26,IF('Postergar'!$G26&lt;&gt;"",'Postergar'!$G26,"No completada al cierre del Sprint "&amp;$N26)&amp;" -&gt; Sprint "&amp;$AD26,"")</f>
       </c>
       <c r="AI26" s="201">
         <f>IF($AF26,$N26*100000+ROW(),"")</f>
@@ -25814,7 +25822,7 @@
         <f>IF($C27,IF(LEN(TRIM($AN27))=0,"—",TRIM($AN27)),"")</f>
       </c>
       <c r="AD27" s="201">
-        <f>IF($C27,IF($N27=9999,9999,IF($J27="Completado",$N27,MAX($N27,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C27,IF($N27=9999,9999,IF($J27="Completado",$N27,MAX($N27,'Historial de Sprints'!$C$7)+N('Postergar'!$F27))),"")</f>
       </c>
       <c r="AE27" s="201">
         <f>IF($C27,IF($AD27=9999,"(Sin sprint)",$AD27),"")</f>
@@ -25826,7 +25834,7 @@
         <f>IF($AF27,'Historial de Sprints'!$C$5+$N27*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH27" s="202">
-        <f>IF($AF27,"No completada al cierre del Sprint "&amp;$N27&amp;" -&gt; reasignada al Sprint "&amp;$AD27,"")</f>
+        <f>IF($AF27,IF('Postergar'!$G27&lt;&gt;"",'Postergar'!$G27,"No completada al cierre del Sprint "&amp;$N27)&amp;" -&gt; Sprint "&amp;$AD27,"")</f>
       </c>
       <c r="AI27" s="201">
         <f>IF($AF27,$N27*100000+ROW(),"")</f>
@@ -25936,7 +25944,7 @@
         <f>IF($C28,IF(LEN(TRIM($AN28))=0,"—",TRIM($AN28)),"")</f>
       </c>
       <c r="AD28" s="201">
-        <f>IF($C28,IF($N28=9999,9999,IF($J28="Completado",$N28,MAX($N28,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C28,IF($N28=9999,9999,IF($J28="Completado",$N28,MAX($N28,'Historial de Sprints'!$C$7)+N('Postergar'!$F28))),"")</f>
       </c>
       <c r="AE28" s="201">
         <f>IF($C28,IF($AD28=9999,"(Sin sprint)",$AD28),"")</f>
@@ -25948,7 +25956,7 @@
         <f>IF($AF28,'Historial de Sprints'!$C$5+$N28*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH28" s="202">
-        <f>IF($AF28,"No completada al cierre del Sprint "&amp;$N28&amp;" -&gt; reasignada al Sprint "&amp;$AD28,"")</f>
+        <f>IF($AF28,IF('Postergar'!$G28&lt;&gt;"",'Postergar'!$G28,"No completada al cierre del Sprint "&amp;$N28)&amp;" -&gt; Sprint "&amp;$AD28,"")</f>
       </c>
       <c r="AI28" s="201">
         <f>IF($AF28,$N28*100000+ROW(),"")</f>
@@ -26058,7 +26066,7 @@
         <f>IF($C29,IF(LEN(TRIM($AN29))=0,"—",TRIM($AN29)),"")</f>
       </c>
       <c r="AD29" s="201">
-        <f>IF($C29,IF($N29=9999,9999,IF($J29="Completado",$N29,MAX($N29,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C29,IF($N29=9999,9999,IF($J29="Completado",$N29,MAX($N29,'Historial de Sprints'!$C$7)+N('Postergar'!$F29))),"")</f>
       </c>
       <c r="AE29" s="201">
         <f>IF($C29,IF($AD29=9999,"(Sin sprint)",$AD29),"")</f>
@@ -26070,7 +26078,7 @@
         <f>IF($AF29,'Historial de Sprints'!$C$5+$N29*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH29" s="202">
-        <f>IF($AF29,"No completada al cierre del Sprint "&amp;$N29&amp;" -&gt; reasignada al Sprint "&amp;$AD29,"")</f>
+        <f>IF($AF29,IF('Postergar'!$G29&lt;&gt;"",'Postergar'!$G29,"No completada al cierre del Sprint "&amp;$N29)&amp;" -&gt; Sprint "&amp;$AD29,"")</f>
       </c>
       <c r="AI29" s="201">
         <f>IF($AF29,$N29*100000+ROW(),"")</f>
@@ -26180,7 +26188,7 @@
         <f>IF($C30,IF(LEN(TRIM($AN30))=0,"—",TRIM($AN30)),"")</f>
       </c>
       <c r="AD30" s="201">
-        <f>IF($C30,IF($N30=9999,9999,IF($J30="Completado",$N30,MAX($N30,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C30,IF($N30=9999,9999,IF($J30="Completado",$N30,MAX($N30,'Historial de Sprints'!$C$7)+N('Postergar'!$F30))),"")</f>
       </c>
       <c r="AE30" s="201">
         <f>IF($C30,IF($AD30=9999,"(Sin sprint)",$AD30),"")</f>
@@ -26192,7 +26200,7 @@
         <f>IF($AF30,'Historial de Sprints'!$C$5+$N30*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH30" s="202">
-        <f>IF($AF30,"No completada al cierre del Sprint "&amp;$N30&amp;" -&gt; reasignada al Sprint "&amp;$AD30,"")</f>
+        <f>IF($AF30,IF('Postergar'!$G30&lt;&gt;"",'Postergar'!$G30,"No completada al cierre del Sprint "&amp;$N30)&amp;" -&gt; Sprint "&amp;$AD30,"")</f>
       </c>
       <c r="AI30" s="201">
         <f>IF($AF30,$N30*100000+ROW(),"")</f>
@@ -26302,7 +26310,7 @@
         <f>IF($C31,IF(LEN(TRIM($AN31))=0,"—",TRIM($AN31)),"")</f>
       </c>
       <c r="AD31" s="201">
-        <f>IF($C31,IF($N31=9999,9999,IF($J31="Completado",$N31,MAX($N31,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C31,IF($N31=9999,9999,IF($J31="Completado",$N31,MAX($N31,'Historial de Sprints'!$C$7)+N('Postergar'!$F31))),"")</f>
       </c>
       <c r="AE31" s="201">
         <f>IF($C31,IF($AD31=9999,"(Sin sprint)",$AD31),"")</f>
@@ -26314,7 +26322,7 @@
         <f>IF($AF31,'Historial de Sprints'!$C$5+$N31*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH31" s="202">
-        <f>IF($AF31,"No completada al cierre del Sprint "&amp;$N31&amp;" -&gt; reasignada al Sprint "&amp;$AD31,"")</f>
+        <f>IF($AF31,IF('Postergar'!$G31&lt;&gt;"",'Postergar'!$G31,"No completada al cierre del Sprint "&amp;$N31)&amp;" -&gt; Sprint "&amp;$AD31,"")</f>
       </c>
       <c r="AI31" s="201">
         <f>IF($AF31,$N31*100000+ROW(),"")</f>
@@ -26424,7 +26432,7 @@
         <f>IF($C32,IF(LEN(TRIM($AN32))=0,"—",TRIM($AN32)),"")</f>
       </c>
       <c r="AD32" s="201">
-        <f>IF($C32,IF($N32=9999,9999,IF($J32="Completado",$N32,MAX($N32,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C32,IF($N32=9999,9999,IF($J32="Completado",$N32,MAX($N32,'Historial de Sprints'!$C$7)+N('Postergar'!$F32))),"")</f>
       </c>
       <c r="AE32" s="201">
         <f>IF($C32,IF($AD32=9999,"(Sin sprint)",$AD32),"")</f>
@@ -26436,7 +26444,7 @@
         <f>IF($AF32,'Historial de Sprints'!$C$5+$N32*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH32" s="202">
-        <f>IF($AF32,"No completada al cierre del Sprint "&amp;$N32&amp;" -&gt; reasignada al Sprint "&amp;$AD32,"")</f>
+        <f>IF($AF32,IF('Postergar'!$G32&lt;&gt;"",'Postergar'!$G32,"No completada al cierre del Sprint "&amp;$N32)&amp;" -&gt; Sprint "&amp;$AD32,"")</f>
       </c>
       <c r="AI32" s="201">
         <f>IF($AF32,$N32*100000+ROW(),"")</f>
@@ -26546,7 +26554,7 @@
         <f>IF($C33,IF(LEN(TRIM($AN33))=0,"—",TRIM($AN33)),"")</f>
       </c>
       <c r="AD33" s="201">
-        <f>IF($C33,IF($N33=9999,9999,IF($J33="Completado",$N33,MAX($N33,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C33,IF($N33=9999,9999,IF($J33="Completado",$N33,MAX($N33,'Historial de Sprints'!$C$7)+N('Postergar'!$F33))),"")</f>
       </c>
       <c r="AE33" s="201">
         <f>IF($C33,IF($AD33=9999,"(Sin sprint)",$AD33),"")</f>
@@ -26558,7 +26566,7 @@
         <f>IF($AF33,'Historial de Sprints'!$C$5+$N33*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH33" s="202">
-        <f>IF($AF33,"No completada al cierre del Sprint "&amp;$N33&amp;" -&gt; reasignada al Sprint "&amp;$AD33,"")</f>
+        <f>IF($AF33,IF('Postergar'!$G33&lt;&gt;"",'Postergar'!$G33,"No completada al cierre del Sprint "&amp;$N33)&amp;" -&gt; Sprint "&amp;$AD33,"")</f>
       </c>
       <c r="AI33" s="201">
         <f>IF($AF33,$N33*100000+ROW(),"")</f>
@@ -26668,7 +26676,7 @@
         <f>IF($C34,IF(LEN(TRIM($AN34))=0,"—",TRIM($AN34)),"")</f>
       </c>
       <c r="AD34" s="201">
-        <f>IF($C34,IF($N34=9999,9999,IF($J34="Completado",$N34,MAX($N34,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C34,IF($N34=9999,9999,IF($J34="Completado",$N34,MAX($N34,'Historial de Sprints'!$C$7)+N('Postergar'!$F34))),"")</f>
       </c>
       <c r="AE34" s="201">
         <f>IF($C34,IF($AD34=9999,"(Sin sprint)",$AD34),"")</f>
@@ -26680,7 +26688,7 @@
         <f>IF($AF34,'Historial de Sprints'!$C$5+$N34*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH34" s="202">
-        <f>IF($AF34,"No completada al cierre del Sprint "&amp;$N34&amp;" -&gt; reasignada al Sprint "&amp;$AD34,"")</f>
+        <f>IF($AF34,IF('Postergar'!$G34&lt;&gt;"",'Postergar'!$G34,"No completada al cierre del Sprint "&amp;$N34)&amp;" -&gt; Sprint "&amp;$AD34,"")</f>
       </c>
       <c r="AI34" s="201">
         <f>IF($AF34,$N34*100000+ROW(),"")</f>
@@ -26790,7 +26798,7 @@
         <f>IF($C35,IF(LEN(TRIM($AN35))=0,"—",TRIM($AN35)),"")</f>
       </c>
       <c r="AD35" s="201">
-        <f>IF($C35,IF($N35=9999,9999,IF($J35="Completado",$N35,MAX($N35,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C35,IF($N35=9999,9999,IF($J35="Completado",$N35,MAX($N35,'Historial de Sprints'!$C$7)+N('Postergar'!$F35))),"")</f>
       </c>
       <c r="AE35" s="201">
         <f>IF($C35,IF($AD35=9999,"(Sin sprint)",$AD35),"")</f>
@@ -26802,7 +26810,7 @@
         <f>IF($AF35,'Historial de Sprints'!$C$5+$N35*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH35" s="202">
-        <f>IF($AF35,"No completada al cierre del Sprint "&amp;$N35&amp;" -&gt; reasignada al Sprint "&amp;$AD35,"")</f>
+        <f>IF($AF35,IF('Postergar'!$G35&lt;&gt;"",'Postergar'!$G35,"No completada al cierre del Sprint "&amp;$N35)&amp;" -&gt; Sprint "&amp;$AD35,"")</f>
       </c>
       <c r="AI35" s="201">
         <f>IF($AF35,$N35*100000+ROW(),"")</f>
@@ -26912,7 +26920,7 @@
         <f>IF($C36,IF(LEN(TRIM($AN36))=0,"—",TRIM($AN36)),"")</f>
       </c>
       <c r="AD36" s="201">
-        <f>IF($C36,IF($N36=9999,9999,IF($J36="Completado",$N36,MAX($N36,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C36,IF($N36=9999,9999,IF($J36="Completado",$N36,MAX($N36,'Historial de Sprints'!$C$7)+N('Postergar'!$F36))),"")</f>
       </c>
       <c r="AE36" s="201">
         <f>IF($C36,IF($AD36=9999,"(Sin sprint)",$AD36),"")</f>
@@ -26924,7 +26932,7 @@
         <f>IF($AF36,'Historial de Sprints'!$C$5+$N36*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH36" s="202">
-        <f>IF($AF36,"No completada al cierre del Sprint "&amp;$N36&amp;" -&gt; reasignada al Sprint "&amp;$AD36,"")</f>
+        <f>IF($AF36,IF('Postergar'!$G36&lt;&gt;"",'Postergar'!$G36,"No completada al cierre del Sprint "&amp;$N36)&amp;" -&gt; Sprint "&amp;$AD36,"")</f>
       </c>
       <c r="AI36" s="201">
         <f>IF($AF36,$N36*100000+ROW(),"")</f>
@@ -27034,7 +27042,7 @@
         <f>IF($C37,IF(LEN(TRIM($AN37))=0,"—",TRIM($AN37)),"")</f>
       </c>
       <c r="AD37" s="201">
-        <f>IF($C37,IF($N37=9999,9999,IF($J37="Completado",$N37,MAX($N37,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C37,IF($N37=9999,9999,IF($J37="Completado",$N37,MAX($N37,'Historial de Sprints'!$C$7)+N('Postergar'!$F37))),"")</f>
       </c>
       <c r="AE37" s="201">
         <f>IF($C37,IF($AD37=9999,"(Sin sprint)",$AD37),"")</f>
@@ -27046,7 +27054,7 @@
         <f>IF($AF37,'Historial de Sprints'!$C$5+$N37*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH37" s="202">
-        <f>IF($AF37,"No completada al cierre del Sprint "&amp;$N37&amp;" -&gt; reasignada al Sprint "&amp;$AD37,"")</f>
+        <f>IF($AF37,IF('Postergar'!$G37&lt;&gt;"",'Postergar'!$G37,"No completada al cierre del Sprint "&amp;$N37)&amp;" -&gt; Sprint "&amp;$AD37,"")</f>
       </c>
       <c r="AI37" s="201">
         <f>IF($AF37,$N37*100000+ROW(),"")</f>
@@ -27150,7 +27158,7 @@
         <f>IF($C38,IF(LEN(TRIM($AN38))=0,"—",TRIM($AN38)),"")</f>
       </c>
       <c r="AD38" s="201">
-        <f>IF($C38,IF($N38=9999,9999,IF($J38="Completado",$N38,MAX($N38,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C38,IF($N38=9999,9999,IF($J38="Completado",$N38,MAX($N38,'Historial de Sprints'!$C$7)+N('Postergar'!$F38))),"")</f>
       </c>
       <c r="AE38" s="201">
         <f>IF($C38,IF($AD38=9999,"(Sin sprint)",$AD38),"")</f>
@@ -27162,7 +27170,7 @@
         <f>IF($AF38,'Historial de Sprints'!$C$5+$N38*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH38" s="202">
-        <f>IF($AF38,"No completada al cierre del Sprint "&amp;$N38&amp;" -&gt; reasignada al Sprint "&amp;$AD38,"")</f>
+        <f>IF($AF38,IF('Postergar'!$G38&lt;&gt;"",'Postergar'!$G38,"No completada al cierre del Sprint "&amp;$N38)&amp;" -&gt; Sprint "&amp;$AD38,"")</f>
       </c>
       <c r="AI38" s="201">
         <f>IF($AF38,$N38*100000+ROW(),"")</f>
@@ -27266,7 +27274,7 @@
         <f>IF($C39,IF(LEN(TRIM($AN39))=0,"—",TRIM($AN39)),"")</f>
       </c>
       <c r="AD39" s="201">
-        <f>IF($C39,IF($N39=9999,9999,IF($J39="Completado",$N39,MAX($N39,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C39,IF($N39=9999,9999,IF($J39="Completado",$N39,MAX($N39,'Historial de Sprints'!$C$7)+N('Postergar'!$F39))),"")</f>
       </c>
       <c r="AE39" s="201">
         <f>IF($C39,IF($AD39=9999,"(Sin sprint)",$AD39),"")</f>
@@ -27278,7 +27286,7 @@
         <f>IF($AF39,'Historial de Sprints'!$C$5+$N39*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH39" s="202">
-        <f>IF($AF39,"No completada al cierre del Sprint "&amp;$N39&amp;" -&gt; reasignada al Sprint "&amp;$AD39,"")</f>
+        <f>IF($AF39,IF('Postergar'!$G39&lt;&gt;"",'Postergar'!$G39,"No completada al cierre del Sprint "&amp;$N39)&amp;" -&gt; Sprint "&amp;$AD39,"")</f>
       </c>
       <c r="AI39" s="201">
         <f>IF($AF39,$N39*100000+ROW(),"")</f>
@@ -27382,7 +27390,7 @@
         <f>IF($C40,IF(LEN(TRIM($AN40))=0,"—",TRIM($AN40)),"")</f>
       </c>
       <c r="AD40" s="201">
-        <f>IF($C40,IF($N40=9999,9999,IF($J40="Completado",$N40,MAX($N40,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C40,IF($N40=9999,9999,IF($J40="Completado",$N40,MAX($N40,'Historial de Sprints'!$C$7)+N('Postergar'!$F40))),"")</f>
       </c>
       <c r="AE40" s="201">
         <f>IF($C40,IF($AD40=9999,"(Sin sprint)",$AD40),"")</f>
@@ -27394,7 +27402,7 @@
         <f>IF($AF40,'Historial de Sprints'!$C$5+$N40*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH40" s="202">
-        <f>IF($AF40,"No completada al cierre del Sprint "&amp;$N40&amp;" -&gt; reasignada al Sprint "&amp;$AD40,"")</f>
+        <f>IF($AF40,IF('Postergar'!$G40&lt;&gt;"",'Postergar'!$G40,"No completada al cierre del Sprint "&amp;$N40)&amp;" -&gt; Sprint "&amp;$AD40,"")</f>
       </c>
       <c r="AI40" s="201">
         <f>IF($AF40,$N40*100000+ROW(),"")</f>
@@ -27498,7 +27506,7 @@
         <f>IF($C41,IF(LEN(TRIM($AN41))=0,"—",TRIM($AN41)),"")</f>
       </c>
       <c r="AD41" s="201">
-        <f>IF($C41,IF($N41=9999,9999,IF($J41="Completado",$N41,MAX($N41,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C41,IF($N41=9999,9999,IF($J41="Completado",$N41,MAX($N41,'Historial de Sprints'!$C$7)+N('Postergar'!$F41))),"")</f>
       </c>
       <c r="AE41" s="201">
         <f>IF($C41,IF($AD41=9999,"(Sin sprint)",$AD41),"")</f>
@@ -27510,7 +27518,7 @@
         <f>IF($AF41,'Historial de Sprints'!$C$5+$N41*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH41" s="202">
-        <f>IF($AF41,"No completada al cierre del Sprint "&amp;$N41&amp;" -&gt; reasignada al Sprint "&amp;$AD41,"")</f>
+        <f>IF($AF41,IF('Postergar'!$G41&lt;&gt;"",'Postergar'!$G41,"No completada al cierre del Sprint "&amp;$N41)&amp;" -&gt; Sprint "&amp;$AD41,"")</f>
       </c>
       <c r="AI41" s="201">
         <f>IF($AF41,$N41*100000+ROW(),"")</f>
@@ -27614,7 +27622,7 @@
         <f>IF($C42,IF(LEN(TRIM($AN42))=0,"—",TRIM($AN42)),"")</f>
       </c>
       <c r="AD42" s="201">
-        <f>IF($C42,IF($N42=9999,9999,IF($J42="Completado",$N42,MAX($N42,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C42,IF($N42=9999,9999,IF($J42="Completado",$N42,MAX($N42,'Historial de Sprints'!$C$7)+N('Postergar'!$F42))),"")</f>
       </c>
       <c r="AE42" s="201">
         <f>IF($C42,IF($AD42=9999,"(Sin sprint)",$AD42),"")</f>
@@ -27626,7 +27634,7 @@
         <f>IF($AF42,'Historial de Sprints'!$C$5+$N42*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH42" s="202">
-        <f>IF($AF42,"No completada al cierre del Sprint "&amp;$N42&amp;" -&gt; reasignada al Sprint "&amp;$AD42,"")</f>
+        <f>IF($AF42,IF('Postergar'!$G42&lt;&gt;"",'Postergar'!$G42,"No completada al cierre del Sprint "&amp;$N42)&amp;" -&gt; Sprint "&amp;$AD42,"")</f>
       </c>
       <c r="AI42" s="201">
         <f>IF($AF42,$N42*100000+ROW(),"")</f>
@@ -27730,7 +27738,7 @@
         <f>IF($C43,IF(LEN(TRIM($AN43))=0,"—",TRIM($AN43)),"")</f>
       </c>
       <c r="AD43" s="201">
-        <f>IF($C43,IF($N43=9999,9999,IF($J43="Completado",$N43,MAX($N43,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C43,IF($N43=9999,9999,IF($J43="Completado",$N43,MAX($N43,'Historial de Sprints'!$C$7)+N('Postergar'!$F43))),"")</f>
       </c>
       <c r="AE43" s="201">
         <f>IF($C43,IF($AD43=9999,"(Sin sprint)",$AD43),"")</f>
@@ -27742,7 +27750,7 @@
         <f>IF($AF43,'Historial de Sprints'!$C$5+$N43*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH43" s="202">
-        <f>IF($AF43,"No completada al cierre del Sprint "&amp;$N43&amp;" -&gt; reasignada al Sprint "&amp;$AD43,"")</f>
+        <f>IF($AF43,IF('Postergar'!$G43&lt;&gt;"",'Postergar'!$G43,"No completada al cierre del Sprint "&amp;$N43)&amp;" -&gt; Sprint "&amp;$AD43,"")</f>
       </c>
       <c r="AI43" s="201">
         <f>IF($AF43,$N43*100000+ROW(),"")</f>
@@ -27846,7 +27854,7 @@
         <f>IF($C44,IF(LEN(TRIM($AN44))=0,"—",TRIM($AN44)),"")</f>
       </c>
       <c r="AD44" s="201">
-        <f>IF($C44,IF($N44=9999,9999,IF($J44="Completado",$N44,MAX($N44,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C44,IF($N44=9999,9999,IF($J44="Completado",$N44,MAX($N44,'Historial de Sprints'!$C$7)+N('Postergar'!$F44))),"")</f>
       </c>
       <c r="AE44" s="201">
         <f>IF($C44,IF($AD44=9999,"(Sin sprint)",$AD44),"")</f>
@@ -27858,7 +27866,7 @@
         <f>IF($AF44,'Historial de Sprints'!$C$5+$N44*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH44" s="202">
-        <f>IF($AF44,"No completada al cierre del Sprint "&amp;$N44&amp;" -&gt; reasignada al Sprint "&amp;$AD44,"")</f>
+        <f>IF($AF44,IF('Postergar'!$G44&lt;&gt;"",'Postergar'!$G44,"No completada al cierre del Sprint "&amp;$N44)&amp;" -&gt; Sprint "&amp;$AD44,"")</f>
       </c>
       <c r="AI44" s="201">
         <f>IF($AF44,$N44*100000+ROW(),"")</f>
@@ -27962,7 +27970,7 @@
         <f>IF($C45,IF(LEN(TRIM($AN45))=0,"—",TRIM($AN45)),"")</f>
       </c>
       <c r="AD45" s="201">
-        <f>IF($C45,IF($N45=9999,9999,IF($J45="Completado",$N45,MAX($N45,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C45,IF($N45=9999,9999,IF($J45="Completado",$N45,MAX($N45,'Historial de Sprints'!$C$7)+N('Postergar'!$F45))),"")</f>
       </c>
       <c r="AE45" s="201">
         <f>IF($C45,IF($AD45=9999,"(Sin sprint)",$AD45),"")</f>
@@ -27974,7 +27982,7 @@
         <f>IF($AF45,'Historial de Sprints'!$C$5+$N45*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH45" s="202">
-        <f>IF($AF45,"No completada al cierre del Sprint "&amp;$N45&amp;" -&gt; reasignada al Sprint "&amp;$AD45,"")</f>
+        <f>IF($AF45,IF('Postergar'!$G45&lt;&gt;"",'Postergar'!$G45,"No completada al cierre del Sprint "&amp;$N45)&amp;" -&gt; Sprint "&amp;$AD45,"")</f>
       </c>
       <c r="AI45" s="201">
         <f>IF($AF45,$N45*100000+ROW(),"")</f>
@@ -28078,7 +28086,7 @@
         <f>IF($C46,IF(LEN(TRIM($AN46))=0,"—",TRIM($AN46)),"")</f>
       </c>
       <c r="AD46" s="201">
-        <f>IF($C46,IF($N46=9999,9999,IF($J46="Completado",$N46,MAX($N46,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C46,IF($N46=9999,9999,IF($J46="Completado",$N46,MAX($N46,'Historial de Sprints'!$C$7)+N('Postergar'!$F46))),"")</f>
       </c>
       <c r="AE46" s="201">
         <f>IF($C46,IF($AD46=9999,"(Sin sprint)",$AD46),"")</f>
@@ -28090,7 +28098,7 @@
         <f>IF($AF46,'Historial de Sprints'!$C$5+$N46*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH46" s="202">
-        <f>IF($AF46,"No completada al cierre del Sprint "&amp;$N46&amp;" -&gt; reasignada al Sprint "&amp;$AD46,"")</f>
+        <f>IF($AF46,IF('Postergar'!$G46&lt;&gt;"",'Postergar'!$G46,"No completada al cierre del Sprint "&amp;$N46)&amp;" -&gt; Sprint "&amp;$AD46,"")</f>
       </c>
       <c r="AI46" s="201">
         <f>IF($AF46,$N46*100000+ROW(),"")</f>
@@ -28194,7 +28202,7 @@
         <f>IF($C47,IF(LEN(TRIM($AN47))=0,"—",TRIM($AN47)),"")</f>
       </c>
       <c r="AD47" s="201">
-        <f>IF($C47,IF($N47=9999,9999,IF($J47="Completado",$N47,MAX($N47,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C47,IF($N47=9999,9999,IF($J47="Completado",$N47,MAX($N47,'Historial de Sprints'!$C$7)+N('Postergar'!$F47))),"")</f>
       </c>
       <c r="AE47" s="201">
         <f>IF($C47,IF($AD47=9999,"(Sin sprint)",$AD47),"")</f>
@@ -28206,7 +28214,7 @@
         <f>IF($AF47,'Historial de Sprints'!$C$5+$N47*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH47" s="202">
-        <f>IF($AF47,"No completada al cierre del Sprint "&amp;$N47&amp;" -&gt; reasignada al Sprint "&amp;$AD47,"")</f>
+        <f>IF($AF47,IF('Postergar'!$G47&lt;&gt;"",'Postergar'!$G47,"No completada al cierre del Sprint "&amp;$N47)&amp;" -&gt; Sprint "&amp;$AD47,"")</f>
       </c>
       <c r="AI47" s="201">
         <f>IF($AF47,$N47*100000+ROW(),"")</f>
@@ -28310,7 +28318,7 @@
         <f>IF($C48,IF(LEN(TRIM($AN48))=0,"—",TRIM($AN48)),"")</f>
       </c>
       <c r="AD48" s="201">
-        <f>IF($C48,IF($N48=9999,9999,IF($J48="Completado",$N48,MAX($N48,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C48,IF($N48=9999,9999,IF($J48="Completado",$N48,MAX($N48,'Historial de Sprints'!$C$7)+N('Postergar'!$F48))),"")</f>
       </c>
       <c r="AE48" s="201">
         <f>IF($C48,IF($AD48=9999,"(Sin sprint)",$AD48),"")</f>
@@ -28322,7 +28330,7 @@
         <f>IF($AF48,'Historial de Sprints'!$C$5+$N48*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH48" s="202">
-        <f>IF($AF48,"No completada al cierre del Sprint "&amp;$N48&amp;" -&gt; reasignada al Sprint "&amp;$AD48,"")</f>
+        <f>IF($AF48,IF('Postergar'!$G48&lt;&gt;"",'Postergar'!$G48,"No completada al cierre del Sprint "&amp;$N48)&amp;" -&gt; Sprint "&amp;$AD48,"")</f>
       </c>
       <c r="AI48" s="201">
         <f>IF($AF48,$N48*100000+ROW(),"")</f>
@@ -28426,7 +28434,7 @@
         <f>IF($C49,IF(LEN(TRIM($AN49))=0,"—",TRIM($AN49)),"")</f>
       </c>
       <c r="AD49" s="201">
-        <f>IF($C49,IF($N49=9999,9999,IF($J49="Completado",$N49,MAX($N49,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C49,IF($N49=9999,9999,IF($J49="Completado",$N49,MAX($N49,'Historial de Sprints'!$C$7)+N('Postergar'!$F49))),"")</f>
       </c>
       <c r="AE49" s="201">
         <f>IF($C49,IF($AD49=9999,"(Sin sprint)",$AD49),"")</f>
@@ -28438,7 +28446,7 @@
         <f>IF($AF49,'Historial de Sprints'!$C$5+$N49*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH49" s="202">
-        <f>IF($AF49,"No completada al cierre del Sprint "&amp;$N49&amp;" -&gt; reasignada al Sprint "&amp;$AD49,"")</f>
+        <f>IF($AF49,IF('Postergar'!$G49&lt;&gt;"",'Postergar'!$G49,"No completada al cierre del Sprint "&amp;$N49)&amp;" -&gt; Sprint "&amp;$AD49,"")</f>
       </c>
       <c r="AI49" s="201">
         <f>IF($AF49,$N49*100000+ROW(),"")</f>
@@ -28542,7 +28550,7 @@
         <f>IF($C50,IF(LEN(TRIM($AN50))=0,"—",TRIM($AN50)),"")</f>
       </c>
       <c r="AD50" s="201">
-        <f>IF($C50,IF($N50=9999,9999,IF($J50="Completado",$N50,MAX($N50,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C50,IF($N50=9999,9999,IF($J50="Completado",$N50,MAX($N50,'Historial de Sprints'!$C$7)+N('Postergar'!$F50))),"")</f>
       </c>
       <c r="AE50" s="201">
         <f>IF($C50,IF($AD50=9999,"(Sin sprint)",$AD50),"")</f>
@@ -28554,7 +28562,7 @@
         <f>IF($AF50,'Historial de Sprints'!$C$5+$N50*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH50" s="202">
-        <f>IF($AF50,"No completada al cierre del Sprint "&amp;$N50&amp;" -&gt; reasignada al Sprint "&amp;$AD50,"")</f>
+        <f>IF($AF50,IF('Postergar'!$G50&lt;&gt;"",'Postergar'!$G50,"No completada al cierre del Sprint "&amp;$N50)&amp;" -&gt; Sprint "&amp;$AD50,"")</f>
       </c>
       <c r="AI50" s="201">
         <f>IF($AF50,$N50*100000+ROW(),"")</f>
@@ -28658,7 +28666,7 @@
         <f>IF($C51,IF(LEN(TRIM($AN51))=0,"—",TRIM($AN51)),"")</f>
       </c>
       <c r="AD51" s="201">
-        <f>IF($C51,IF($N51=9999,9999,IF($J51="Completado",$N51,MAX($N51,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C51,IF($N51=9999,9999,IF($J51="Completado",$N51,MAX($N51,'Historial de Sprints'!$C$7)+N('Postergar'!$F51))),"")</f>
       </c>
       <c r="AE51" s="201">
         <f>IF($C51,IF($AD51=9999,"(Sin sprint)",$AD51),"")</f>
@@ -28670,7 +28678,7 @@
         <f>IF($AF51,'Historial de Sprints'!$C$5+$N51*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH51" s="202">
-        <f>IF($AF51,"No completada al cierre del Sprint "&amp;$N51&amp;" -&gt; reasignada al Sprint "&amp;$AD51,"")</f>
+        <f>IF($AF51,IF('Postergar'!$G51&lt;&gt;"",'Postergar'!$G51,"No completada al cierre del Sprint "&amp;$N51)&amp;" -&gt; Sprint "&amp;$AD51,"")</f>
       </c>
       <c r="AI51" s="201">
         <f>IF($AF51,$N51*100000+ROW(),"")</f>
@@ -28774,7 +28782,7 @@
         <f>IF($C52,IF(LEN(TRIM($AN52))=0,"—",TRIM($AN52)),"")</f>
       </c>
       <c r="AD52" s="201">
-        <f>IF($C52,IF($N52=9999,9999,IF($J52="Completado",$N52,MAX($N52,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C52,IF($N52=9999,9999,IF($J52="Completado",$N52,MAX($N52,'Historial de Sprints'!$C$7)+N('Postergar'!$F52))),"")</f>
       </c>
       <c r="AE52" s="201">
         <f>IF($C52,IF($AD52=9999,"(Sin sprint)",$AD52),"")</f>
@@ -28786,7 +28794,7 @@
         <f>IF($AF52,'Historial de Sprints'!$C$5+$N52*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH52" s="202">
-        <f>IF($AF52,"No completada al cierre del Sprint "&amp;$N52&amp;" -&gt; reasignada al Sprint "&amp;$AD52,"")</f>
+        <f>IF($AF52,IF('Postergar'!$G52&lt;&gt;"",'Postergar'!$G52,"No completada al cierre del Sprint "&amp;$N52)&amp;" -&gt; Sprint "&amp;$AD52,"")</f>
       </c>
       <c r="AI52" s="201">
         <f>IF($AF52,$N52*100000+ROW(),"")</f>
@@ -28890,7 +28898,7 @@
         <f>IF($C53,IF(LEN(TRIM($AN53))=0,"—",TRIM($AN53)),"")</f>
       </c>
       <c r="AD53" s="201">
-        <f>IF($C53,IF($N53=9999,9999,IF($J53="Completado",$N53,MAX($N53,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C53,IF($N53=9999,9999,IF($J53="Completado",$N53,MAX($N53,'Historial de Sprints'!$C$7)+N('Postergar'!$F53))),"")</f>
       </c>
       <c r="AE53" s="201">
         <f>IF($C53,IF($AD53=9999,"(Sin sprint)",$AD53),"")</f>
@@ -28902,7 +28910,7 @@
         <f>IF($AF53,'Historial de Sprints'!$C$5+$N53*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH53" s="202">
-        <f>IF($AF53,"No completada al cierre del Sprint "&amp;$N53&amp;" -&gt; reasignada al Sprint "&amp;$AD53,"")</f>
+        <f>IF($AF53,IF('Postergar'!$G53&lt;&gt;"",'Postergar'!$G53,"No completada al cierre del Sprint "&amp;$N53)&amp;" -&gt; Sprint "&amp;$AD53,"")</f>
       </c>
       <c r="AI53" s="201">
         <f>IF($AF53,$N53*100000+ROW(),"")</f>
@@ -29006,7 +29014,7 @@
         <f>IF($C54,IF(LEN(TRIM($AN54))=0,"—",TRIM($AN54)),"")</f>
       </c>
       <c r="AD54" s="201">
-        <f>IF($C54,IF($N54=9999,9999,IF($J54="Completado",$N54,MAX($N54,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C54,IF($N54=9999,9999,IF($J54="Completado",$N54,MAX($N54,'Historial de Sprints'!$C$7)+N('Postergar'!$F54))),"")</f>
       </c>
       <c r="AE54" s="201">
         <f>IF($C54,IF($AD54=9999,"(Sin sprint)",$AD54),"")</f>
@@ -29018,7 +29026,7 @@
         <f>IF($AF54,'Historial de Sprints'!$C$5+$N54*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH54" s="202">
-        <f>IF($AF54,"No completada al cierre del Sprint "&amp;$N54&amp;" -&gt; reasignada al Sprint "&amp;$AD54,"")</f>
+        <f>IF($AF54,IF('Postergar'!$G54&lt;&gt;"",'Postergar'!$G54,"No completada al cierre del Sprint "&amp;$N54)&amp;" -&gt; Sprint "&amp;$AD54,"")</f>
       </c>
       <c r="AI54" s="201">
         <f>IF($AF54,$N54*100000+ROW(),"")</f>
@@ -29122,7 +29130,7 @@
         <f>IF($C55,IF(LEN(TRIM($AN55))=0,"—",TRIM($AN55)),"")</f>
       </c>
       <c r="AD55" s="201">
-        <f>IF($C55,IF($N55=9999,9999,IF($J55="Completado",$N55,MAX($N55,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C55,IF($N55=9999,9999,IF($J55="Completado",$N55,MAX($N55,'Historial de Sprints'!$C$7)+N('Postergar'!$F55))),"")</f>
       </c>
       <c r="AE55" s="201">
         <f>IF($C55,IF($AD55=9999,"(Sin sprint)",$AD55),"")</f>
@@ -29134,7 +29142,7 @@
         <f>IF($AF55,'Historial de Sprints'!$C$5+$N55*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH55" s="202">
-        <f>IF($AF55,"No completada al cierre del Sprint "&amp;$N55&amp;" -&gt; reasignada al Sprint "&amp;$AD55,"")</f>
+        <f>IF($AF55,IF('Postergar'!$G55&lt;&gt;"",'Postergar'!$G55,"No completada al cierre del Sprint "&amp;$N55)&amp;" -&gt; Sprint "&amp;$AD55,"")</f>
       </c>
       <c r="AI55" s="201">
         <f>IF($AF55,$N55*100000+ROW(),"")</f>
@@ -29238,7 +29246,7 @@
         <f>IF($C56,IF(LEN(TRIM($AN56))=0,"—",TRIM($AN56)),"")</f>
       </c>
       <c r="AD56" s="201">
-        <f>IF($C56,IF($N56=9999,9999,IF($J56="Completado",$N56,MAX($N56,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C56,IF($N56=9999,9999,IF($J56="Completado",$N56,MAX($N56,'Historial de Sprints'!$C$7)+N('Postergar'!$F56))),"")</f>
       </c>
       <c r="AE56" s="201">
         <f>IF($C56,IF($AD56=9999,"(Sin sprint)",$AD56),"")</f>
@@ -29250,7 +29258,7 @@
         <f>IF($AF56,'Historial de Sprints'!$C$5+$N56*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH56" s="202">
-        <f>IF($AF56,"No completada al cierre del Sprint "&amp;$N56&amp;" -&gt; reasignada al Sprint "&amp;$AD56,"")</f>
+        <f>IF($AF56,IF('Postergar'!$G56&lt;&gt;"",'Postergar'!$G56,"No completada al cierre del Sprint "&amp;$N56)&amp;" -&gt; Sprint "&amp;$AD56,"")</f>
       </c>
       <c r="AI56" s="201">
         <f>IF($AF56,$N56*100000+ROW(),"")</f>
@@ -29354,7 +29362,7 @@
         <f>IF($C57,IF(LEN(TRIM($AN57))=0,"—",TRIM($AN57)),"")</f>
       </c>
       <c r="AD57" s="201">
-        <f>IF($C57,IF($N57=9999,9999,IF($J57="Completado",$N57,MAX($N57,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C57,IF($N57=9999,9999,IF($J57="Completado",$N57,MAX($N57,'Historial de Sprints'!$C$7)+N('Postergar'!$F57))),"")</f>
       </c>
       <c r="AE57" s="201">
         <f>IF($C57,IF($AD57=9999,"(Sin sprint)",$AD57),"")</f>
@@ -29366,7 +29374,7 @@
         <f>IF($AF57,'Historial de Sprints'!$C$5+$N57*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH57" s="202">
-        <f>IF($AF57,"No completada al cierre del Sprint "&amp;$N57&amp;" -&gt; reasignada al Sprint "&amp;$AD57,"")</f>
+        <f>IF($AF57,IF('Postergar'!$G57&lt;&gt;"",'Postergar'!$G57,"No completada al cierre del Sprint "&amp;$N57)&amp;" -&gt; Sprint "&amp;$AD57,"")</f>
       </c>
       <c r="AI57" s="201">
         <f>IF($AF57,$N57*100000+ROW(),"")</f>
@@ -29470,7 +29478,7 @@
         <f>IF($C58,IF(LEN(TRIM($AN58))=0,"—",TRIM($AN58)),"")</f>
       </c>
       <c r="AD58" s="201">
-        <f>IF($C58,IF($N58=9999,9999,IF($J58="Completado",$N58,MAX($N58,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C58,IF($N58=9999,9999,IF($J58="Completado",$N58,MAX($N58,'Historial de Sprints'!$C$7)+N('Postergar'!$F58))),"")</f>
       </c>
       <c r="AE58" s="201">
         <f>IF($C58,IF($AD58=9999,"(Sin sprint)",$AD58),"")</f>
@@ -29482,7 +29490,7 @@
         <f>IF($AF58,'Historial de Sprints'!$C$5+$N58*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH58" s="202">
-        <f>IF($AF58,"No completada al cierre del Sprint "&amp;$N58&amp;" -&gt; reasignada al Sprint "&amp;$AD58,"")</f>
+        <f>IF($AF58,IF('Postergar'!$G58&lt;&gt;"",'Postergar'!$G58,"No completada al cierre del Sprint "&amp;$N58)&amp;" -&gt; Sprint "&amp;$AD58,"")</f>
       </c>
       <c r="AI58" s="201">
         <f>IF($AF58,$N58*100000+ROW(),"")</f>
@@ -29586,7 +29594,7 @@
         <f>IF($C59,IF(LEN(TRIM($AN59))=0,"—",TRIM($AN59)),"")</f>
       </c>
       <c r="AD59" s="201">
-        <f>IF($C59,IF($N59=9999,9999,IF($J59="Completado",$N59,MAX($N59,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C59,IF($N59=9999,9999,IF($J59="Completado",$N59,MAX($N59,'Historial de Sprints'!$C$7)+N('Postergar'!$F59))),"")</f>
       </c>
       <c r="AE59" s="201">
         <f>IF($C59,IF($AD59=9999,"(Sin sprint)",$AD59),"")</f>
@@ -29598,7 +29606,7 @@
         <f>IF($AF59,'Historial de Sprints'!$C$5+$N59*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH59" s="202">
-        <f>IF($AF59,"No completada al cierre del Sprint "&amp;$N59&amp;" -&gt; reasignada al Sprint "&amp;$AD59,"")</f>
+        <f>IF($AF59,IF('Postergar'!$G59&lt;&gt;"",'Postergar'!$G59,"No completada al cierre del Sprint "&amp;$N59)&amp;" -&gt; Sprint "&amp;$AD59,"")</f>
       </c>
       <c r="AI59" s="201">
         <f>IF($AF59,$N59*100000+ROW(),"")</f>
@@ -29702,7 +29710,7 @@
         <f>IF($C60,IF(LEN(TRIM($AN60))=0,"—",TRIM($AN60)),"")</f>
       </c>
       <c r="AD60" s="201">
-        <f>IF($C60,IF($N60=9999,9999,IF($J60="Completado",$N60,MAX($N60,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C60,IF($N60=9999,9999,IF($J60="Completado",$N60,MAX($N60,'Historial de Sprints'!$C$7)+N('Postergar'!$F60))),"")</f>
       </c>
       <c r="AE60" s="201">
         <f>IF($C60,IF($AD60=9999,"(Sin sprint)",$AD60),"")</f>
@@ -29714,7 +29722,7 @@
         <f>IF($AF60,'Historial de Sprints'!$C$5+$N60*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH60" s="202">
-        <f>IF($AF60,"No completada al cierre del Sprint "&amp;$N60&amp;" -&gt; reasignada al Sprint "&amp;$AD60,"")</f>
+        <f>IF($AF60,IF('Postergar'!$G60&lt;&gt;"",'Postergar'!$G60,"No completada al cierre del Sprint "&amp;$N60)&amp;" -&gt; Sprint "&amp;$AD60,"")</f>
       </c>
       <c r="AI60" s="201">
         <f>IF($AF60,$N60*100000+ROW(),"")</f>
@@ -29818,7 +29826,7 @@
         <f>IF($C61,IF(LEN(TRIM($AN61))=0,"—",TRIM($AN61)),"")</f>
       </c>
       <c r="AD61" s="201">
-        <f>IF($C61,IF($N61=9999,9999,IF($J61="Completado",$N61,MAX($N61,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C61,IF($N61=9999,9999,IF($J61="Completado",$N61,MAX($N61,'Historial de Sprints'!$C$7)+N('Postergar'!$F61))),"")</f>
       </c>
       <c r="AE61" s="201">
         <f>IF($C61,IF($AD61=9999,"(Sin sprint)",$AD61),"")</f>
@@ -29830,7 +29838,7 @@
         <f>IF($AF61,'Historial de Sprints'!$C$5+$N61*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH61" s="202">
-        <f>IF($AF61,"No completada al cierre del Sprint "&amp;$N61&amp;" -&gt; reasignada al Sprint "&amp;$AD61,"")</f>
+        <f>IF($AF61,IF('Postergar'!$G61&lt;&gt;"",'Postergar'!$G61,"No completada al cierre del Sprint "&amp;$N61)&amp;" -&gt; Sprint "&amp;$AD61,"")</f>
       </c>
       <c r="AI61" s="201">
         <f>IF($AF61,$N61*100000+ROW(),"")</f>
@@ -29934,7 +29942,7 @@
         <f>IF($C62,IF(LEN(TRIM($AN62))=0,"—",TRIM($AN62)),"")</f>
       </c>
       <c r="AD62" s="201">
-        <f>IF($C62,IF($N62=9999,9999,IF($J62="Completado",$N62,MAX($N62,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C62,IF($N62=9999,9999,IF($J62="Completado",$N62,MAX($N62,'Historial de Sprints'!$C$7)+N('Postergar'!$F62))),"")</f>
       </c>
       <c r="AE62" s="201">
         <f>IF($C62,IF($AD62=9999,"(Sin sprint)",$AD62),"")</f>
@@ -29946,7 +29954,7 @@
         <f>IF($AF62,'Historial de Sprints'!$C$5+$N62*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH62" s="202">
-        <f>IF($AF62,"No completada al cierre del Sprint "&amp;$N62&amp;" -&gt; reasignada al Sprint "&amp;$AD62,"")</f>
+        <f>IF($AF62,IF('Postergar'!$G62&lt;&gt;"",'Postergar'!$G62,"No completada al cierre del Sprint "&amp;$N62)&amp;" -&gt; Sprint "&amp;$AD62,"")</f>
       </c>
       <c r="AI62" s="201">
         <f>IF($AF62,$N62*100000+ROW(),"")</f>
@@ -30050,7 +30058,7 @@
         <f>IF($C63,IF(LEN(TRIM($AN63))=0,"—",TRIM($AN63)),"")</f>
       </c>
       <c r="AD63" s="201">
-        <f>IF($C63,IF($N63=9999,9999,IF($J63="Completado",$N63,MAX($N63,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C63,IF($N63=9999,9999,IF($J63="Completado",$N63,MAX($N63,'Historial de Sprints'!$C$7)+N('Postergar'!$F63))),"")</f>
       </c>
       <c r="AE63" s="201">
         <f>IF($C63,IF($AD63=9999,"(Sin sprint)",$AD63),"")</f>
@@ -30062,7 +30070,7 @@
         <f>IF($AF63,'Historial de Sprints'!$C$5+$N63*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH63" s="202">
-        <f>IF($AF63,"No completada al cierre del Sprint "&amp;$N63&amp;" -&gt; reasignada al Sprint "&amp;$AD63,"")</f>
+        <f>IF($AF63,IF('Postergar'!$G63&lt;&gt;"",'Postergar'!$G63,"No completada al cierre del Sprint "&amp;$N63)&amp;" -&gt; Sprint "&amp;$AD63,"")</f>
       </c>
       <c r="AI63" s="201">
         <f>IF($AF63,$N63*100000+ROW(),"")</f>
@@ -30166,7 +30174,7 @@
         <f>IF($C64,IF(LEN(TRIM($AN64))=0,"—",TRIM($AN64)),"")</f>
       </c>
       <c r="AD64" s="201">
-        <f>IF($C64,IF($N64=9999,9999,IF($J64="Completado",$N64,MAX($N64,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C64,IF($N64=9999,9999,IF($J64="Completado",$N64,MAX($N64,'Historial de Sprints'!$C$7)+N('Postergar'!$F64))),"")</f>
       </c>
       <c r="AE64" s="201">
         <f>IF($C64,IF($AD64=9999,"(Sin sprint)",$AD64),"")</f>
@@ -30178,7 +30186,7 @@
         <f>IF($AF64,'Historial de Sprints'!$C$5+$N64*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH64" s="202">
-        <f>IF($AF64,"No completada al cierre del Sprint "&amp;$N64&amp;" -&gt; reasignada al Sprint "&amp;$AD64,"")</f>
+        <f>IF($AF64,IF('Postergar'!$G64&lt;&gt;"",'Postergar'!$G64,"No completada al cierre del Sprint "&amp;$N64)&amp;" -&gt; Sprint "&amp;$AD64,"")</f>
       </c>
       <c r="AI64" s="201">
         <f>IF($AF64,$N64*100000+ROW(),"")</f>
@@ -30282,7 +30290,7 @@
         <f>IF($C65,IF(LEN(TRIM($AN65))=0,"—",TRIM($AN65)),"")</f>
       </c>
       <c r="AD65" s="201">
-        <f>IF($C65,IF($N65=9999,9999,IF($J65="Completado",$N65,MAX($N65,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C65,IF($N65=9999,9999,IF($J65="Completado",$N65,MAX($N65,'Historial de Sprints'!$C$7)+N('Postergar'!$F65))),"")</f>
       </c>
       <c r="AE65" s="201">
         <f>IF($C65,IF($AD65=9999,"(Sin sprint)",$AD65),"")</f>
@@ -30294,7 +30302,7 @@
         <f>IF($AF65,'Historial de Sprints'!$C$5+$N65*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH65" s="202">
-        <f>IF($AF65,"No completada al cierre del Sprint "&amp;$N65&amp;" -&gt; reasignada al Sprint "&amp;$AD65,"")</f>
+        <f>IF($AF65,IF('Postergar'!$G65&lt;&gt;"",'Postergar'!$G65,"No completada al cierre del Sprint "&amp;$N65)&amp;" -&gt; Sprint "&amp;$AD65,"")</f>
       </c>
       <c r="AI65" s="201">
         <f>IF($AF65,$N65*100000+ROW(),"")</f>
@@ -30398,7 +30406,7 @@
         <f>IF($C66,IF(LEN(TRIM($AN66))=0,"—",TRIM($AN66)),"")</f>
       </c>
       <c r="AD66" s="201">
-        <f>IF($C66,IF($N66=9999,9999,IF($J66="Completado",$N66,MAX($N66,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C66,IF($N66=9999,9999,IF($J66="Completado",$N66,MAX($N66,'Historial de Sprints'!$C$7)+N('Postergar'!$F66))),"")</f>
       </c>
       <c r="AE66" s="201">
         <f>IF($C66,IF($AD66=9999,"(Sin sprint)",$AD66),"")</f>
@@ -30410,7 +30418,7 @@
         <f>IF($AF66,'Historial de Sprints'!$C$5+$N66*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH66" s="202">
-        <f>IF($AF66,"No completada al cierre del Sprint "&amp;$N66&amp;" -&gt; reasignada al Sprint "&amp;$AD66,"")</f>
+        <f>IF($AF66,IF('Postergar'!$G66&lt;&gt;"",'Postergar'!$G66,"No completada al cierre del Sprint "&amp;$N66)&amp;" -&gt; Sprint "&amp;$AD66,"")</f>
       </c>
       <c r="AI66" s="201">
         <f>IF($AF66,$N66*100000+ROW(),"")</f>
@@ -30514,7 +30522,7 @@
         <f>IF($C67,IF(LEN(TRIM($AN67))=0,"—",TRIM($AN67)),"")</f>
       </c>
       <c r="AD67" s="201">
-        <f>IF($C67,IF($N67=9999,9999,IF($J67="Completado",$N67,MAX($N67,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C67,IF($N67=9999,9999,IF($J67="Completado",$N67,MAX($N67,'Historial de Sprints'!$C$7)+N('Postergar'!$F67))),"")</f>
       </c>
       <c r="AE67" s="201">
         <f>IF($C67,IF($AD67=9999,"(Sin sprint)",$AD67),"")</f>
@@ -30526,7 +30534,7 @@
         <f>IF($AF67,'Historial de Sprints'!$C$5+$N67*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH67" s="202">
-        <f>IF($AF67,"No completada al cierre del Sprint "&amp;$N67&amp;" -&gt; reasignada al Sprint "&amp;$AD67,"")</f>
+        <f>IF($AF67,IF('Postergar'!$G67&lt;&gt;"",'Postergar'!$G67,"No completada al cierre del Sprint "&amp;$N67)&amp;" -&gt; Sprint "&amp;$AD67,"")</f>
       </c>
       <c r="AI67" s="201">
         <f>IF($AF67,$N67*100000+ROW(),"")</f>
@@ -30630,7 +30638,7 @@
         <f>IF($C68,IF(LEN(TRIM($AN68))=0,"—",TRIM($AN68)),"")</f>
       </c>
       <c r="AD68" s="201">
-        <f>IF($C68,IF($N68=9999,9999,IF($J68="Completado",$N68,MAX($N68,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C68,IF($N68=9999,9999,IF($J68="Completado",$N68,MAX($N68,'Historial de Sprints'!$C$7)+N('Postergar'!$F68))),"")</f>
       </c>
       <c r="AE68" s="201">
         <f>IF($C68,IF($AD68=9999,"(Sin sprint)",$AD68),"")</f>
@@ -30642,7 +30650,7 @@
         <f>IF($AF68,'Historial de Sprints'!$C$5+$N68*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH68" s="202">
-        <f>IF($AF68,"No completada al cierre del Sprint "&amp;$N68&amp;" -&gt; reasignada al Sprint "&amp;$AD68,"")</f>
+        <f>IF($AF68,IF('Postergar'!$G68&lt;&gt;"",'Postergar'!$G68,"No completada al cierre del Sprint "&amp;$N68)&amp;" -&gt; Sprint "&amp;$AD68,"")</f>
       </c>
       <c r="AI68" s="201">
         <f>IF($AF68,$N68*100000+ROW(),"")</f>
@@ -30746,7 +30754,7 @@
         <f>IF($C69,IF(LEN(TRIM($AN69))=0,"—",TRIM($AN69)),"")</f>
       </c>
       <c r="AD69" s="201">
-        <f>IF($C69,IF($N69=9999,9999,IF($J69="Completado",$N69,MAX($N69,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C69,IF($N69=9999,9999,IF($J69="Completado",$N69,MAX($N69,'Historial de Sprints'!$C$7)+N('Postergar'!$F69))),"")</f>
       </c>
       <c r="AE69" s="201">
         <f>IF($C69,IF($AD69=9999,"(Sin sprint)",$AD69),"")</f>
@@ -30758,7 +30766,7 @@
         <f>IF($AF69,'Historial de Sprints'!$C$5+$N69*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH69" s="202">
-        <f>IF($AF69,"No completada al cierre del Sprint "&amp;$N69&amp;" -&gt; reasignada al Sprint "&amp;$AD69,"")</f>
+        <f>IF($AF69,IF('Postergar'!$G69&lt;&gt;"",'Postergar'!$G69,"No completada al cierre del Sprint "&amp;$N69)&amp;" -&gt; Sprint "&amp;$AD69,"")</f>
       </c>
       <c r="AI69" s="201">
         <f>IF($AF69,$N69*100000+ROW(),"")</f>
@@ -30862,7 +30870,7 @@
         <f>IF($C70,IF(LEN(TRIM($AN70))=0,"—",TRIM($AN70)),"")</f>
       </c>
       <c r="AD70" s="201">
-        <f>IF($C70,IF($N70=9999,9999,IF($J70="Completado",$N70,MAX($N70,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C70,IF($N70=9999,9999,IF($J70="Completado",$N70,MAX($N70,'Historial de Sprints'!$C$7)+N('Postergar'!$F70))),"")</f>
       </c>
       <c r="AE70" s="201">
         <f>IF($C70,IF($AD70=9999,"(Sin sprint)",$AD70),"")</f>
@@ -30874,7 +30882,7 @@
         <f>IF($AF70,'Historial de Sprints'!$C$5+$N70*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH70" s="202">
-        <f>IF($AF70,"No completada al cierre del Sprint "&amp;$N70&amp;" -&gt; reasignada al Sprint "&amp;$AD70,"")</f>
+        <f>IF($AF70,IF('Postergar'!$G70&lt;&gt;"",'Postergar'!$G70,"No completada al cierre del Sprint "&amp;$N70)&amp;" -&gt; Sprint "&amp;$AD70,"")</f>
       </c>
       <c r="AI70" s="201">
         <f>IF($AF70,$N70*100000+ROW(),"")</f>
@@ -30978,7 +30986,7 @@
         <f>IF($C71,IF(LEN(TRIM($AN71))=0,"—",TRIM($AN71)),"")</f>
       </c>
       <c r="AD71" s="201">
-        <f>IF($C71,IF($N71=9999,9999,IF($J71="Completado",$N71,MAX($N71,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C71,IF($N71=9999,9999,IF($J71="Completado",$N71,MAX($N71,'Historial de Sprints'!$C$7)+N('Postergar'!$F71))),"")</f>
       </c>
       <c r="AE71" s="201">
         <f>IF($C71,IF($AD71=9999,"(Sin sprint)",$AD71),"")</f>
@@ -30990,7 +30998,7 @@
         <f>IF($AF71,'Historial de Sprints'!$C$5+$N71*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH71" s="202">
-        <f>IF($AF71,"No completada al cierre del Sprint "&amp;$N71&amp;" -&gt; reasignada al Sprint "&amp;$AD71,"")</f>
+        <f>IF($AF71,IF('Postergar'!$G71&lt;&gt;"",'Postergar'!$G71,"No completada al cierre del Sprint "&amp;$N71)&amp;" -&gt; Sprint "&amp;$AD71,"")</f>
       </c>
       <c r="AI71" s="201">
         <f>IF($AF71,$N71*100000+ROW(),"")</f>
@@ -31094,7 +31102,7 @@
         <f>IF($C72,IF(LEN(TRIM($AN72))=0,"—",TRIM($AN72)),"")</f>
       </c>
       <c r="AD72" s="201">
-        <f>IF($C72,IF($N72=9999,9999,IF($J72="Completado",$N72,MAX($N72,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C72,IF($N72=9999,9999,IF($J72="Completado",$N72,MAX($N72,'Historial de Sprints'!$C$7)+N('Postergar'!$F72))),"")</f>
       </c>
       <c r="AE72" s="201">
         <f>IF($C72,IF($AD72=9999,"(Sin sprint)",$AD72),"")</f>
@@ -31106,7 +31114,7 @@
         <f>IF($AF72,'Historial de Sprints'!$C$5+$N72*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH72" s="202">
-        <f>IF($AF72,"No completada al cierre del Sprint "&amp;$N72&amp;" -&gt; reasignada al Sprint "&amp;$AD72,"")</f>
+        <f>IF($AF72,IF('Postergar'!$G72&lt;&gt;"",'Postergar'!$G72,"No completada al cierre del Sprint "&amp;$N72)&amp;" -&gt; Sprint "&amp;$AD72,"")</f>
       </c>
       <c r="AI72" s="201">
         <f>IF($AF72,$N72*100000+ROW(),"")</f>
@@ -31210,7 +31218,7 @@
         <f>IF($C73,IF(LEN(TRIM($AN73))=0,"—",TRIM($AN73)),"")</f>
       </c>
       <c r="AD73" s="201">
-        <f>IF($C73,IF($N73=9999,9999,IF($J73="Completado",$N73,MAX($N73,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C73,IF($N73=9999,9999,IF($J73="Completado",$N73,MAX($N73,'Historial de Sprints'!$C$7)+N('Postergar'!$F73))),"")</f>
       </c>
       <c r="AE73" s="201">
         <f>IF($C73,IF($AD73=9999,"(Sin sprint)",$AD73),"")</f>
@@ -31222,7 +31230,7 @@
         <f>IF($AF73,'Historial de Sprints'!$C$5+$N73*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH73" s="202">
-        <f>IF($AF73,"No completada al cierre del Sprint "&amp;$N73&amp;" -&gt; reasignada al Sprint "&amp;$AD73,"")</f>
+        <f>IF($AF73,IF('Postergar'!$G73&lt;&gt;"",'Postergar'!$G73,"No completada al cierre del Sprint "&amp;$N73)&amp;" -&gt; Sprint "&amp;$AD73,"")</f>
       </c>
       <c r="AI73" s="201">
         <f>IF($AF73,$N73*100000+ROW(),"")</f>
@@ -31326,7 +31334,7 @@
         <f>IF($C74,IF(LEN(TRIM($AN74))=0,"—",TRIM($AN74)),"")</f>
       </c>
       <c r="AD74" s="201">
-        <f>IF($C74,IF($N74=9999,9999,IF($J74="Completado",$N74,MAX($N74,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C74,IF($N74=9999,9999,IF($J74="Completado",$N74,MAX($N74,'Historial de Sprints'!$C$7)+N('Postergar'!$F74))),"")</f>
       </c>
       <c r="AE74" s="201">
         <f>IF($C74,IF($AD74=9999,"(Sin sprint)",$AD74),"")</f>
@@ -31338,7 +31346,7 @@
         <f>IF($AF74,'Historial de Sprints'!$C$5+$N74*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH74" s="202">
-        <f>IF($AF74,"No completada al cierre del Sprint "&amp;$N74&amp;" -&gt; reasignada al Sprint "&amp;$AD74,"")</f>
+        <f>IF($AF74,IF('Postergar'!$G74&lt;&gt;"",'Postergar'!$G74,"No completada al cierre del Sprint "&amp;$N74)&amp;" -&gt; Sprint "&amp;$AD74,"")</f>
       </c>
       <c r="AI74" s="201">
         <f>IF($AF74,$N74*100000+ROW(),"")</f>
@@ -31442,7 +31450,7 @@
         <f>IF($C75,IF(LEN(TRIM($AN75))=0,"—",TRIM($AN75)),"")</f>
       </c>
       <c r="AD75" s="201">
-        <f>IF($C75,IF($N75=9999,9999,IF($J75="Completado",$N75,MAX($N75,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C75,IF($N75=9999,9999,IF($J75="Completado",$N75,MAX($N75,'Historial de Sprints'!$C$7)+N('Postergar'!$F75))),"")</f>
       </c>
       <c r="AE75" s="201">
         <f>IF($C75,IF($AD75=9999,"(Sin sprint)",$AD75),"")</f>
@@ -31454,7 +31462,7 @@
         <f>IF($AF75,'Historial de Sprints'!$C$5+$N75*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH75" s="202">
-        <f>IF($AF75,"No completada al cierre del Sprint "&amp;$N75&amp;" -&gt; reasignada al Sprint "&amp;$AD75,"")</f>
+        <f>IF($AF75,IF('Postergar'!$G75&lt;&gt;"",'Postergar'!$G75,"No completada al cierre del Sprint "&amp;$N75)&amp;" -&gt; Sprint "&amp;$AD75,"")</f>
       </c>
       <c r="AI75" s="201">
         <f>IF($AF75,$N75*100000+ROW(),"")</f>
@@ -31558,7 +31566,7 @@
         <f>IF($C76,IF(LEN(TRIM($AN76))=0,"—",TRIM($AN76)),"")</f>
       </c>
       <c r="AD76" s="201">
-        <f>IF($C76,IF($N76=9999,9999,IF($J76="Completado",$N76,MAX($N76,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C76,IF($N76=9999,9999,IF($J76="Completado",$N76,MAX($N76,'Historial de Sprints'!$C$7)+N('Postergar'!$F76))),"")</f>
       </c>
       <c r="AE76" s="201">
         <f>IF($C76,IF($AD76=9999,"(Sin sprint)",$AD76),"")</f>
@@ -31570,7 +31578,7 @@
         <f>IF($AF76,'Historial de Sprints'!$C$5+$N76*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH76" s="202">
-        <f>IF($AF76,"No completada al cierre del Sprint "&amp;$N76&amp;" -&gt; reasignada al Sprint "&amp;$AD76,"")</f>
+        <f>IF($AF76,IF('Postergar'!$G76&lt;&gt;"",'Postergar'!$G76,"No completada al cierre del Sprint "&amp;$N76)&amp;" -&gt; Sprint "&amp;$AD76,"")</f>
       </c>
       <c r="AI76" s="201">
         <f>IF($AF76,$N76*100000+ROW(),"")</f>
@@ -31674,7 +31682,7 @@
         <f>IF($C77,IF(LEN(TRIM($AN77))=0,"—",TRIM($AN77)),"")</f>
       </c>
       <c r="AD77" s="201">
-        <f>IF($C77,IF($N77=9999,9999,IF($J77="Completado",$N77,MAX($N77,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C77,IF($N77=9999,9999,IF($J77="Completado",$N77,MAX($N77,'Historial de Sprints'!$C$7)+N('Postergar'!$F77))),"")</f>
       </c>
       <c r="AE77" s="201">
         <f>IF($C77,IF($AD77=9999,"(Sin sprint)",$AD77),"")</f>
@@ -31686,7 +31694,7 @@
         <f>IF($AF77,'Historial de Sprints'!$C$5+$N77*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH77" s="202">
-        <f>IF($AF77,"No completada al cierre del Sprint "&amp;$N77&amp;" -&gt; reasignada al Sprint "&amp;$AD77,"")</f>
+        <f>IF($AF77,IF('Postergar'!$G77&lt;&gt;"",'Postergar'!$G77,"No completada al cierre del Sprint "&amp;$N77)&amp;" -&gt; Sprint "&amp;$AD77,"")</f>
       </c>
       <c r="AI77" s="201">
         <f>IF($AF77,$N77*100000+ROW(),"")</f>
@@ -31790,7 +31798,7 @@
         <f>IF($C78,IF(LEN(TRIM($AN78))=0,"—",TRIM($AN78)),"")</f>
       </c>
       <c r="AD78" s="201">
-        <f>IF($C78,IF($N78=9999,9999,IF($J78="Completado",$N78,MAX($N78,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C78,IF($N78=9999,9999,IF($J78="Completado",$N78,MAX($N78,'Historial de Sprints'!$C$7)+N('Postergar'!$F78))),"")</f>
       </c>
       <c r="AE78" s="201">
         <f>IF($C78,IF($AD78=9999,"(Sin sprint)",$AD78),"")</f>
@@ -31802,7 +31810,7 @@
         <f>IF($AF78,'Historial de Sprints'!$C$5+$N78*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH78" s="202">
-        <f>IF($AF78,"No completada al cierre del Sprint "&amp;$N78&amp;" -&gt; reasignada al Sprint "&amp;$AD78,"")</f>
+        <f>IF($AF78,IF('Postergar'!$G78&lt;&gt;"",'Postergar'!$G78,"No completada al cierre del Sprint "&amp;$N78)&amp;" -&gt; Sprint "&amp;$AD78,"")</f>
       </c>
       <c r="AI78" s="201">
         <f>IF($AF78,$N78*100000+ROW(),"")</f>
@@ -31906,7 +31914,7 @@
         <f>IF($C79,IF(LEN(TRIM($AN79))=0,"—",TRIM($AN79)),"")</f>
       </c>
       <c r="AD79" s="201">
-        <f>IF($C79,IF($N79=9999,9999,IF($J79="Completado",$N79,MAX($N79,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C79,IF($N79=9999,9999,IF($J79="Completado",$N79,MAX($N79,'Historial de Sprints'!$C$7)+N('Postergar'!$F79))),"")</f>
       </c>
       <c r="AE79" s="201">
         <f>IF($C79,IF($AD79=9999,"(Sin sprint)",$AD79),"")</f>
@@ -31918,7 +31926,7 @@
         <f>IF($AF79,'Historial de Sprints'!$C$5+$N79*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH79" s="202">
-        <f>IF($AF79,"No completada al cierre del Sprint "&amp;$N79&amp;" -&gt; reasignada al Sprint "&amp;$AD79,"")</f>
+        <f>IF($AF79,IF('Postergar'!$G79&lt;&gt;"",'Postergar'!$G79,"No completada al cierre del Sprint "&amp;$N79)&amp;" -&gt; Sprint "&amp;$AD79,"")</f>
       </c>
       <c r="AI79" s="201">
         <f>IF($AF79,$N79*100000+ROW(),"")</f>
@@ -32022,7 +32030,7 @@
         <f>IF($C80,IF(LEN(TRIM($AN80))=0,"—",TRIM($AN80)),"")</f>
       </c>
       <c r="AD80" s="201">
-        <f>IF($C80,IF($N80=9999,9999,IF($J80="Completado",$N80,MAX($N80,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C80,IF($N80=9999,9999,IF($J80="Completado",$N80,MAX($N80,'Historial de Sprints'!$C$7)+N('Postergar'!$F80))),"")</f>
       </c>
       <c r="AE80" s="201">
         <f>IF($C80,IF($AD80=9999,"(Sin sprint)",$AD80),"")</f>
@@ -32034,7 +32042,7 @@
         <f>IF($AF80,'Historial de Sprints'!$C$5+$N80*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH80" s="202">
-        <f>IF($AF80,"No completada al cierre del Sprint "&amp;$N80&amp;" -&gt; reasignada al Sprint "&amp;$AD80,"")</f>
+        <f>IF($AF80,IF('Postergar'!$G80&lt;&gt;"",'Postergar'!$G80,"No completada al cierre del Sprint "&amp;$N80)&amp;" -&gt; Sprint "&amp;$AD80,"")</f>
       </c>
       <c r="AI80" s="201">
         <f>IF($AF80,$N80*100000+ROW(),"")</f>
@@ -32138,7 +32146,7 @@
         <f>IF($C81,IF(LEN(TRIM($AN81))=0,"—",TRIM($AN81)),"")</f>
       </c>
       <c r="AD81" s="201">
-        <f>IF($C81,IF($N81=9999,9999,IF($J81="Completado",$N81,MAX($N81,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C81,IF($N81=9999,9999,IF($J81="Completado",$N81,MAX($N81,'Historial de Sprints'!$C$7)+N('Postergar'!$F81))),"")</f>
       </c>
       <c r="AE81" s="201">
         <f>IF($C81,IF($AD81=9999,"(Sin sprint)",$AD81),"")</f>
@@ -32150,7 +32158,7 @@
         <f>IF($AF81,'Historial de Sprints'!$C$5+$N81*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH81" s="202">
-        <f>IF($AF81,"No completada al cierre del Sprint "&amp;$N81&amp;" -&gt; reasignada al Sprint "&amp;$AD81,"")</f>
+        <f>IF($AF81,IF('Postergar'!$G81&lt;&gt;"",'Postergar'!$G81,"No completada al cierre del Sprint "&amp;$N81)&amp;" -&gt; Sprint "&amp;$AD81,"")</f>
       </c>
       <c r="AI81" s="201">
         <f>IF($AF81,$N81*100000+ROW(),"")</f>
@@ -32254,7 +32262,7 @@
         <f>IF($C82,IF(LEN(TRIM($AN82))=0,"—",TRIM($AN82)),"")</f>
       </c>
       <c r="AD82" s="201">
-        <f>IF($C82,IF($N82=9999,9999,IF($J82="Completado",$N82,MAX($N82,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C82,IF($N82=9999,9999,IF($J82="Completado",$N82,MAX($N82,'Historial de Sprints'!$C$7)+N('Postergar'!$F82))),"")</f>
       </c>
       <c r="AE82" s="201">
         <f>IF($C82,IF($AD82=9999,"(Sin sprint)",$AD82),"")</f>
@@ -32266,7 +32274,7 @@
         <f>IF($AF82,'Historial de Sprints'!$C$5+$N82*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH82" s="202">
-        <f>IF($AF82,"No completada al cierre del Sprint "&amp;$N82&amp;" -&gt; reasignada al Sprint "&amp;$AD82,"")</f>
+        <f>IF($AF82,IF('Postergar'!$G82&lt;&gt;"",'Postergar'!$G82,"No completada al cierre del Sprint "&amp;$N82)&amp;" -&gt; Sprint "&amp;$AD82,"")</f>
       </c>
       <c r="AI82" s="201">
         <f>IF($AF82,$N82*100000+ROW(),"")</f>
@@ -32370,7 +32378,7 @@
         <f>IF($C83,IF(LEN(TRIM($AN83))=0,"—",TRIM($AN83)),"")</f>
       </c>
       <c r="AD83" s="201">
-        <f>IF($C83,IF($N83=9999,9999,IF($J83="Completado",$N83,MAX($N83,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C83,IF($N83=9999,9999,IF($J83="Completado",$N83,MAX($N83,'Historial de Sprints'!$C$7)+N('Postergar'!$F83))),"")</f>
       </c>
       <c r="AE83" s="201">
         <f>IF($C83,IF($AD83=9999,"(Sin sprint)",$AD83),"")</f>
@@ -32382,7 +32390,7 @@
         <f>IF($AF83,'Historial de Sprints'!$C$5+$N83*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH83" s="202">
-        <f>IF($AF83,"No completada al cierre del Sprint "&amp;$N83&amp;" -&gt; reasignada al Sprint "&amp;$AD83,"")</f>
+        <f>IF($AF83,IF('Postergar'!$G83&lt;&gt;"",'Postergar'!$G83,"No completada al cierre del Sprint "&amp;$N83)&amp;" -&gt; Sprint "&amp;$AD83,"")</f>
       </c>
       <c r="AI83" s="201">
         <f>IF($AF83,$N83*100000+ROW(),"")</f>
@@ -32486,7 +32494,7 @@
         <f>IF($C84,IF(LEN(TRIM($AN84))=0,"—",TRIM($AN84)),"")</f>
       </c>
       <c r="AD84" s="201">
-        <f>IF($C84,IF($N84=9999,9999,IF($J84="Completado",$N84,MAX($N84,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C84,IF($N84=9999,9999,IF($J84="Completado",$N84,MAX($N84,'Historial de Sprints'!$C$7)+N('Postergar'!$F84))),"")</f>
       </c>
       <c r="AE84" s="201">
         <f>IF($C84,IF($AD84=9999,"(Sin sprint)",$AD84),"")</f>
@@ -32498,7 +32506,7 @@
         <f>IF($AF84,'Historial de Sprints'!$C$5+$N84*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH84" s="202">
-        <f>IF($AF84,"No completada al cierre del Sprint "&amp;$N84&amp;" -&gt; reasignada al Sprint "&amp;$AD84,"")</f>
+        <f>IF($AF84,IF('Postergar'!$G84&lt;&gt;"",'Postergar'!$G84,"No completada al cierre del Sprint "&amp;$N84)&amp;" -&gt; Sprint "&amp;$AD84,"")</f>
       </c>
       <c r="AI84" s="201">
         <f>IF($AF84,$N84*100000+ROW(),"")</f>
@@ -32602,7 +32610,7 @@
         <f>IF($C85,IF(LEN(TRIM($AN85))=0,"—",TRIM($AN85)),"")</f>
       </c>
       <c r="AD85" s="201">
-        <f>IF($C85,IF($N85=9999,9999,IF($J85="Completado",$N85,MAX($N85,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C85,IF($N85=9999,9999,IF($J85="Completado",$N85,MAX($N85,'Historial de Sprints'!$C$7)+N('Postergar'!$F85))),"")</f>
       </c>
       <c r="AE85" s="201">
         <f>IF($C85,IF($AD85=9999,"(Sin sprint)",$AD85),"")</f>
@@ -32614,7 +32622,7 @@
         <f>IF($AF85,'Historial de Sprints'!$C$5+$N85*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH85" s="202">
-        <f>IF($AF85,"No completada al cierre del Sprint "&amp;$N85&amp;" -&gt; reasignada al Sprint "&amp;$AD85,"")</f>
+        <f>IF($AF85,IF('Postergar'!$G85&lt;&gt;"",'Postergar'!$G85,"No completada al cierre del Sprint "&amp;$N85)&amp;" -&gt; Sprint "&amp;$AD85,"")</f>
       </c>
       <c r="AI85" s="201">
         <f>IF($AF85,$N85*100000+ROW(),"")</f>
@@ -32718,7 +32726,7 @@
         <f>IF($C86,IF(LEN(TRIM($AN86))=0,"—",TRIM($AN86)),"")</f>
       </c>
       <c r="AD86" s="201">
-        <f>IF($C86,IF($N86=9999,9999,IF($J86="Completado",$N86,MAX($N86,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C86,IF($N86=9999,9999,IF($J86="Completado",$N86,MAX($N86,'Historial de Sprints'!$C$7)+N('Postergar'!$F86))),"")</f>
       </c>
       <c r="AE86" s="201">
         <f>IF($C86,IF($AD86=9999,"(Sin sprint)",$AD86),"")</f>
@@ -32730,7 +32738,7 @@
         <f>IF($AF86,'Historial de Sprints'!$C$5+$N86*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH86" s="202">
-        <f>IF($AF86,"No completada al cierre del Sprint "&amp;$N86&amp;" -&gt; reasignada al Sprint "&amp;$AD86,"")</f>
+        <f>IF($AF86,IF('Postergar'!$G86&lt;&gt;"",'Postergar'!$G86,"No completada al cierre del Sprint "&amp;$N86)&amp;" -&gt; Sprint "&amp;$AD86,"")</f>
       </c>
       <c r="AI86" s="201">
         <f>IF($AF86,$N86*100000+ROW(),"")</f>
@@ -32834,7 +32842,7 @@
         <f>IF($C87,IF(LEN(TRIM($AN87))=0,"—",TRIM($AN87)),"")</f>
       </c>
       <c r="AD87" s="201">
-        <f>IF($C87,IF($N87=9999,9999,IF($J87="Completado",$N87,MAX($N87,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C87,IF($N87=9999,9999,IF($J87="Completado",$N87,MAX($N87,'Historial de Sprints'!$C$7)+N('Postergar'!$F87))),"")</f>
       </c>
       <c r="AE87" s="201">
         <f>IF($C87,IF($AD87=9999,"(Sin sprint)",$AD87),"")</f>
@@ -32846,7 +32854,7 @@
         <f>IF($AF87,'Historial de Sprints'!$C$5+$N87*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH87" s="202">
-        <f>IF($AF87,"No completada al cierre del Sprint "&amp;$N87&amp;" -&gt; reasignada al Sprint "&amp;$AD87,"")</f>
+        <f>IF($AF87,IF('Postergar'!$G87&lt;&gt;"",'Postergar'!$G87,"No completada al cierre del Sprint "&amp;$N87)&amp;" -&gt; Sprint "&amp;$AD87,"")</f>
       </c>
       <c r="AI87" s="201">
         <f>IF($AF87,$N87*100000+ROW(),"")</f>
@@ -32950,7 +32958,7 @@
         <f>IF($C88,IF(LEN(TRIM($AN88))=0,"—",TRIM($AN88)),"")</f>
       </c>
       <c r="AD88" s="201">
-        <f>IF($C88,IF($N88=9999,9999,IF($J88="Completado",$N88,MAX($N88,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C88,IF($N88=9999,9999,IF($J88="Completado",$N88,MAX($N88,'Historial de Sprints'!$C$7)+N('Postergar'!$F88))),"")</f>
       </c>
       <c r="AE88" s="201">
         <f>IF($C88,IF($AD88=9999,"(Sin sprint)",$AD88),"")</f>
@@ -32962,7 +32970,7 @@
         <f>IF($AF88,'Historial de Sprints'!$C$5+$N88*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH88" s="202">
-        <f>IF($AF88,"No completada al cierre del Sprint "&amp;$N88&amp;" -&gt; reasignada al Sprint "&amp;$AD88,"")</f>
+        <f>IF($AF88,IF('Postergar'!$G88&lt;&gt;"",'Postergar'!$G88,"No completada al cierre del Sprint "&amp;$N88)&amp;" -&gt; Sprint "&amp;$AD88,"")</f>
       </c>
       <c r="AI88" s="201">
         <f>IF($AF88,$N88*100000+ROW(),"")</f>
@@ -33066,7 +33074,7 @@
         <f>IF($C89,IF(LEN(TRIM($AN89))=0,"—",TRIM($AN89)),"")</f>
       </c>
       <c r="AD89" s="201">
-        <f>IF($C89,IF($N89=9999,9999,IF($J89="Completado",$N89,MAX($N89,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C89,IF($N89=9999,9999,IF($J89="Completado",$N89,MAX($N89,'Historial de Sprints'!$C$7)+N('Postergar'!$F89))),"")</f>
       </c>
       <c r="AE89" s="201">
         <f>IF($C89,IF($AD89=9999,"(Sin sprint)",$AD89),"")</f>
@@ -33078,7 +33086,7 @@
         <f>IF($AF89,'Historial de Sprints'!$C$5+$N89*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH89" s="202">
-        <f>IF($AF89,"No completada al cierre del Sprint "&amp;$N89&amp;" -&gt; reasignada al Sprint "&amp;$AD89,"")</f>
+        <f>IF($AF89,IF('Postergar'!$G89&lt;&gt;"",'Postergar'!$G89,"No completada al cierre del Sprint "&amp;$N89)&amp;" -&gt; Sprint "&amp;$AD89,"")</f>
       </c>
       <c r="AI89" s="201">
         <f>IF($AF89,$N89*100000+ROW(),"")</f>
@@ -33182,7 +33190,7 @@
         <f>IF($C90,IF(LEN(TRIM($AN90))=0,"—",TRIM($AN90)),"")</f>
       </c>
       <c r="AD90" s="201">
-        <f>IF($C90,IF($N90=9999,9999,IF($J90="Completado",$N90,MAX($N90,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C90,IF($N90=9999,9999,IF($J90="Completado",$N90,MAX($N90,'Historial de Sprints'!$C$7)+N('Postergar'!$F90))),"")</f>
       </c>
       <c r="AE90" s="201">
         <f>IF($C90,IF($AD90=9999,"(Sin sprint)",$AD90),"")</f>
@@ -33194,7 +33202,7 @@
         <f>IF($AF90,'Historial de Sprints'!$C$5+$N90*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH90" s="202">
-        <f>IF($AF90,"No completada al cierre del Sprint "&amp;$N90&amp;" -&gt; reasignada al Sprint "&amp;$AD90,"")</f>
+        <f>IF($AF90,IF('Postergar'!$G90&lt;&gt;"",'Postergar'!$G90,"No completada al cierre del Sprint "&amp;$N90)&amp;" -&gt; Sprint "&amp;$AD90,"")</f>
       </c>
       <c r="AI90" s="201">
         <f>IF($AF90,$N90*100000+ROW(),"")</f>
@@ -33298,7 +33306,7 @@
         <f>IF($C91,IF(LEN(TRIM($AN91))=0,"—",TRIM($AN91)),"")</f>
       </c>
       <c r="AD91" s="201">
-        <f>IF($C91,IF($N91=9999,9999,IF($J91="Completado",$N91,MAX($N91,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C91,IF($N91=9999,9999,IF($J91="Completado",$N91,MAX($N91,'Historial de Sprints'!$C$7)+N('Postergar'!$F91))),"")</f>
       </c>
       <c r="AE91" s="201">
         <f>IF($C91,IF($AD91=9999,"(Sin sprint)",$AD91),"")</f>
@@ -33310,7 +33318,7 @@
         <f>IF($AF91,'Historial de Sprints'!$C$5+$N91*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH91" s="202">
-        <f>IF($AF91,"No completada al cierre del Sprint "&amp;$N91&amp;" -&gt; reasignada al Sprint "&amp;$AD91,"")</f>
+        <f>IF($AF91,IF('Postergar'!$G91&lt;&gt;"",'Postergar'!$G91,"No completada al cierre del Sprint "&amp;$N91)&amp;" -&gt; Sprint "&amp;$AD91,"")</f>
       </c>
       <c r="AI91" s="201">
         <f>IF($AF91,$N91*100000+ROW(),"")</f>
@@ -33414,7 +33422,7 @@
         <f>IF($C92,IF(LEN(TRIM($AN92))=0,"—",TRIM($AN92)),"")</f>
       </c>
       <c r="AD92" s="201">
-        <f>IF($C92,IF($N92=9999,9999,IF($J92="Completado",$N92,MAX($N92,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C92,IF($N92=9999,9999,IF($J92="Completado",$N92,MAX($N92,'Historial de Sprints'!$C$7)+N('Postergar'!$F92))),"")</f>
       </c>
       <c r="AE92" s="201">
         <f>IF($C92,IF($AD92=9999,"(Sin sprint)",$AD92),"")</f>
@@ -33426,7 +33434,7 @@
         <f>IF($AF92,'Historial de Sprints'!$C$5+$N92*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH92" s="202">
-        <f>IF($AF92,"No completada al cierre del Sprint "&amp;$N92&amp;" -&gt; reasignada al Sprint "&amp;$AD92,"")</f>
+        <f>IF($AF92,IF('Postergar'!$G92&lt;&gt;"",'Postergar'!$G92,"No completada al cierre del Sprint "&amp;$N92)&amp;" -&gt; Sprint "&amp;$AD92,"")</f>
       </c>
       <c r="AI92" s="201">
         <f>IF($AF92,$N92*100000+ROW(),"")</f>
@@ -33530,7 +33538,7 @@
         <f>IF($C93,IF(LEN(TRIM($AN93))=0,"—",TRIM($AN93)),"")</f>
       </c>
       <c r="AD93" s="201">
-        <f>IF($C93,IF($N93=9999,9999,IF($J93="Completado",$N93,MAX($N93,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C93,IF($N93=9999,9999,IF($J93="Completado",$N93,MAX($N93,'Historial de Sprints'!$C$7)+N('Postergar'!$F93))),"")</f>
       </c>
       <c r="AE93" s="201">
         <f>IF($C93,IF($AD93=9999,"(Sin sprint)",$AD93),"")</f>
@@ -33542,7 +33550,7 @@
         <f>IF($AF93,'Historial de Sprints'!$C$5+$N93*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH93" s="202">
-        <f>IF($AF93,"No completada al cierre del Sprint "&amp;$N93&amp;" -&gt; reasignada al Sprint "&amp;$AD93,"")</f>
+        <f>IF($AF93,IF('Postergar'!$G93&lt;&gt;"",'Postergar'!$G93,"No completada al cierre del Sprint "&amp;$N93)&amp;" -&gt; Sprint "&amp;$AD93,"")</f>
       </c>
       <c r="AI93" s="201">
         <f>IF($AF93,$N93*100000+ROW(),"")</f>
@@ -33646,7 +33654,7 @@
         <f>IF($C94,IF(LEN(TRIM($AN94))=0,"—",TRIM($AN94)),"")</f>
       </c>
       <c r="AD94" s="201">
-        <f>IF($C94,IF($N94=9999,9999,IF($J94="Completado",$N94,MAX($N94,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C94,IF($N94=9999,9999,IF($J94="Completado",$N94,MAX($N94,'Historial de Sprints'!$C$7)+N('Postergar'!$F94))),"")</f>
       </c>
       <c r="AE94" s="201">
         <f>IF($C94,IF($AD94=9999,"(Sin sprint)",$AD94),"")</f>
@@ -33658,7 +33666,7 @@
         <f>IF($AF94,'Historial de Sprints'!$C$5+$N94*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH94" s="202">
-        <f>IF($AF94,"No completada al cierre del Sprint "&amp;$N94&amp;" -&gt; reasignada al Sprint "&amp;$AD94,"")</f>
+        <f>IF($AF94,IF('Postergar'!$G94&lt;&gt;"",'Postergar'!$G94,"No completada al cierre del Sprint "&amp;$N94)&amp;" -&gt; Sprint "&amp;$AD94,"")</f>
       </c>
       <c r="AI94" s="201">
         <f>IF($AF94,$N94*100000+ROW(),"")</f>
@@ -33762,7 +33770,7 @@
         <f>IF($C95,IF(LEN(TRIM($AN95))=0,"—",TRIM($AN95)),"")</f>
       </c>
       <c r="AD95" s="201">
-        <f>IF($C95,IF($N95=9999,9999,IF($J95="Completado",$N95,MAX($N95,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C95,IF($N95=9999,9999,IF($J95="Completado",$N95,MAX($N95,'Historial de Sprints'!$C$7)+N('Postergar'!$F95))),"")</f>
       </c>
       <c r="AE95" s="201">
         <f>IF($C95,IF($AD95=9999,"(Sin sprint)",$AD95),"")</f>
@@ -33774,7 +33782,7 @@
         <f>IF($AF95,'Historial de Sprints'!$C$5+$N95*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH95" s="202">
-        <f>IF($AF95,"No completada al cierre del Sprint "&amp;$N95&amp;" -&gt; reasignada al Sprint "&amp;$AD95,"")</f>
+        <f>IF($AF95,IF('Postergar'!$G95&lt;&gt;"",'Postergar'!$G95,"No completada al cierre del Sprint "&amp;$N95)&amp;" -&gt; Sprint "&amp;$AD95,"")</f>
       </c>
       <c r="AI95" s="201">
         <f>IF($AF95,$N95*100000+ROW(),"")</f>
@@ -33878,7 +33886,7 @@
         <f>IF($C96,IF(LEN(TRIM($AN96))=0,"—",TRIM($AN96)),"")</f>
       </c>
       <c r="AD96" s="201">
-        <f>IF($C96,IF($N96=9999,9999,IF($J96="Completado",$N96,MAX($N96,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C96,IF($N96=9999,9999,IF($J96="Completado",$N96,MAX($N96,'Historial de Sprints'!$C$7)+N('Postergar'!$F96))),"")</f>
       </c>
       <c r="AE96" s="201">
         <f>IF($C96,IF($AD96=9999,"(Sin sprint)",$AD96),"")</f>
@@ -33890,7 +33898,7 @@
         <f>IF($AF96,'Historial de Sprints'!$C$5+$N96*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH96" s="202">
-        <f>IF($AF96,"No completada al cierre del Sprint "&amp;$N96&amp;" -&gt; reasignada al Sprint "&amp;$AD96,"")</f>
+        <f>IF($AF96,IF('Postergar'!$G96&lt;&gt;"",'Postergar'!$G96,"No completada al cierre del Sprint "&amp;$N96)&amp;" -&gt; Sprint "&amp;$AD96,"")</f>
       </c>
       <c r="AI96" s="201">
         <f>IF($AF96,$N96*100000+ROW(),"")</f>
@@ -33994,7 +34002,7 @@
         <f>IF($C97,IF(LEN(TRIM($AN97))=0,"—",TRIM($AN97)),"")</f>
       </c>
       <c r="AD97" s="201">
-        <f>IF($C97,IF($N97=9999,9999,IF($J97="Completado",$N97,MAX($N97,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C97,IF($N97=9999,9999,IF($J97="Completado",$N97,MAX($N97,'Historial de Sprints'!$C$7)+N('Postergar'!$F97))),"")</f>
       </c>
       <c r="AE97" s="201">
         <f>IF($C97,IF($AD97=9999,"(Sin sprint)",$AD97),"")</f>
@@ -34006,7 +34014,7 @@
         <f>IF($AF97,'Historial de Sprints'!$C$5+$N97*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH97" s="202">
-        <f>IF($AF97,"No completada al cierre del Sprint "&amp;$N97&amp;" -&gt; reasignada al Sprint "&amp;$AD97,"")</f>
+        <f>IF($AF97,IF('Postergar'!$G97&lt;&gt;"",'Postergar'!$G97,"No completada al cierre del Sprint "&amp;$N97)&amp;" -&gt; Sprint "&amp;$AD97,"")</f>
       </c>
       <c r="AI97" s="201">
         <f>IF($AF97,$N97*100000+ROW(),"")</f>
@@ -34110,7 +34118,7 @@
         <f>IF($C98,IF(LEN(TRIM($AN98))=0,"—",TRIM($AN98)),"")</f>
       </c>
       <c r="AD98" s="201">
-        <f>IF($C98,IF($N98=9999,9999,IF($J98="Completado",$N98,MAX($N98,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C98,IF($N98=9999,9999,IF($J98="Completado",$N98,MAX($N98,'Historial de Sprints'!$C$7)+N('Postergar'!$F98))),"")</f>
       </c>
       <c r="AE98" s="201">
         <f>IF($C98,IF($AD98=9999,"(Sin sprint)",$AD98),"")</f>
@@ -34122,7 +34130,7 @@
         <f>IF($AF98,'Historial de Sprints'!$C$5+$N98*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH98" s="202">
-        <f>IF($AF98,"No completada al cierre del Sprint "&amp;$N98&amp;" -&gt; reasignada al Sprint "&amp;$AD98,"")</f>
+        <f>IF($AF98,IF('Postergar'!$G98&lt;&gt;"",'Postergar'!$G98,"No completada al cierre del Sprint "&amp;$N98)&amp;" -&gt; Sprint "&amp;$AD98,"")</f>
       </c>
       <c r="AI98" s="201">
         <f>IF($AF98,$N98*100000+ROW(),"")</f>
@@ -34226,7 +34234,7 @@
         <f>IF($C99,IF(LEN(TRIM($AN99))=0,"—",TRIM($AN99)),"")</f>
       </c>
       <c r="AD99" s="201">
-        <f>IF($C99,IF($N99=9999,9999,IF($J99="Completado",$N99,MAX($N99,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C99,IF($N99=9999,9999,IF($J99="Completado",$N99,MAX($N99,'Historial de Sprints'!$C$7)+N('Postergar'!$F99))),"")</f>
       </c>
       <c r="AE99" s="201">
         <f>IF($C99,IF($AD99=9999,"(Sin sprint)",$AD99),"")</f>
@@ -34238,7 +34246,7 @@
         <f>IF($AF99,'Historial de Sprints'!$C$5+$N99*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH99" s="202">
-        <f>IF($AF99,"No completada al cierre del Sprint "&amp;$N99&amp;" -&gt; reasignada al Sprint "&amp;$AD99,"")</f>
+        <f>IF($AF99,IF('Postergar'!$G99&lt;&gt;"",'Postergar'!$G99,"No completada al cierre del Sprint "&amp;$N99)&amp;" -&gt; Sprint "&amp;$AD99,"")</f>
       </c>
       <c r="AI99" s="201">
         <f>IF($AF99,$N99*100000+ROW(),"")</f>
@@ -34342,7 +34350,7 @@
         <f>IF($C100,IF(LEN(TRIM($AN100))=0,"—",TRIM($AN100)),"")</f>
       </c>
       <c r="AD100" s="201">
-        <f>IF($C100,IF($N100=9999,9999,IF($J100="Completado",$N100,MAX($N100,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C100,IF($N100=9999,9999,IF($J100="Completado",$N100,MAX($N100,'Historial de Sprints'!$C$7)+N('Postergar'!$F100))),"")</f>
       </c>
       <c r="AE100" s="201">
         <f>IF($C100,IF($AD100=9999,"(Sin sprint)",$AD100),"")</f>
@@ -34354,7 +34362,7 @@
         <f>IF($AF100,'Historial de Sprints'!$C$5+$N100*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH100" s="202">
-        <f>IF($AF100,"No completada al cierre del Sprint "&amp;$N100&amp;" -&gt; reasignada al Sprint "&amp;$AD100,"")</f>
+        <f>IF($AF100,IF('Postergar'!$G100&lt;&gt;"",'Postergar'!$G100,"No completada al cierre del Sprint "&amp;$N100)&amp;" -&gt; Sprint "&amp;$AD100,"")</f>
       </c>
       <c r="AI100" s="201">
         <f>IF($AF100,$N100*100000+ROW(),"")</f>
@@ -34458,7 +34466,7 @@
         <f>IF($C101,IF(LEN(TRIM($AN101))=0,"—",TRIM($AN101)),"")</f>
       </c>
       <c r="AD101" s="201">
-        <f>IF($C101,IF($N101=9999,9999,IF($J101="Completado",$N101,MAX($N101,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C101,IF($N101=9999,9999,IF($J101="Completado",$N101,MAX($N101,'Historial de Sprints'!$C$7)+N('Postergar'!$F101))),"")</f>
       </c>
       <c r="AE101" s="201">
         <f>IF($C101,IF($AD101=9999,"(Sin sprint)",$AD101),"")</f>
@@ -34470,7 +34478,7 @@
         <f>IF($AF101,'Historial de Sprints'!$C$5+$N101*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH101" s="202">
-        <f>IF($AF101,"No completada al cierre del Sprint "&amp;$N101&amp;" -&gt; reasignada al Sprint "&amp;$AD101,"")</f>
+        <f>IF($AF101,IF('Postergar'!$G101&lt;&gt;"",'Postergar'!$G101,"No completada al cierre del Sprint "&amp;$N101)&amp;" -&gt; Sprint "&amp;$AD101,"")</f>
       </c>
       <c r="AI101" s="201">
         <f>IF($AF101,$N101*100000+ROW(),"")</f>
@@ -34574,7 +34582,7 @@
         <f>IF($C102,IF(LEN(TRIM($AN102))=0,"—",TRIM($AN102)),"")</f>
       </c>
       <c r="AD102" s="201">
-        <f>IF($C102,IF($N102=9999,9999,IF($J102="Completado",$N102,MAX($N102,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C102,IF($N102=9999,9999,IF($J102="Completado",$N102,MAX($N102,'Historial de Sprints'!$C$7)+N('Postergar'!$F102))),"")</f>
       </c>
       <c r="AE102" s="201">
         <f>IF($C102,IF($AD102=9999,"(Sin sprint)",$AD102),"")</f>
@@ -34586,7 +34594,7 @@
         <f>IF($AF102,'Historial de Sprints'!$C$5+$N102*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH102" s="202">
-        <f>IF($AF102,"No completada al cierre del Sprint "&amp;$N102&amp;" -&gt; reasignada al Sprint "&amp;$AD102,"")</f>
+        <f>IF($AF102,IF('Postergar'!$G102&lt;&gt;"",'Postergar'!$G102,"No completada al cierre del Sprint "&amp;$N102)&amp;" -&gt; Sprint "&amp;$AD102,"")</f>
       </c>
       <c r="AI102" s="201">
         <f>IF($AF102,$N102*100000+ROW(),"")</f>
@@ -34690,7 +34698,7 @@
         <f>IF($C103,IF(LEN(TRIM($AN103))=0,"—",TRIM($AN103)),"")</f>
       </c>
       <c r="AD103" s="201">
-        <f>IF($C103,IF($N103=9999,9999,IF($J103="Completado",$N103,MAX($N103,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C103,IF($N103=9999,9999,IF($J103="Completado",$N103,MAX($N103,'Historial de Sprints'!$C$7)+N('Postergar'!$F103))),"")</f>
       </c>
       <c r="AE103" s="201">
         <f>IF($C103,IF($AD103=9999,"(Sin sprint)",$AD103),"")</f>
@@ -34702,7 +34710,7 @@
         <f>IF($AF103,'Historial de Sprints'!$C$5+$N103*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH103" s="202">
-        <f>IF($AF103,"No completada al cierre del Sprint "&amp;$N103&amp;" -&gt; reasignada al Sprint "&amp;$AD103,"")</f>
+        <f>IF($AF103,IF('Postergar'!$G103&lt;&gt;"",'Postergar'!$G103,"No completada al cierre del Sprint "&amp;$N103)&amp;" -&gt; Sprint "&amp;$AD103,"")</f>
       </c>
       <c r="AI103" s="201">
         <f>IF($AF103,$N103*100000+ROW(),"")</f>
@@ -34806,7 +34814,7 @@
         <f>IF($C104,IF(LEN(TRIM($AN104))=0,"—",TRIM($AN104)),"")</f>
       </c>
       <c r="AD104" s="201">
-        <f>IF($C104,IF($N104=9999,9999,IF($J104="Completado",$N104,MAX($N104,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C104,IF($N104=9999,9999,IF($J104="Completado",$N104,MAX($N104,'Historial de Sprints'!$C$7)+N('Postergar'!$F104))),"")</f>
       </c>
       <c r="AE104" s="201">
         <f>IF($C104,IF($AD104=9999,"(Sin sprint)",$AD104),"")</f>
@@ -34818,7 +34826,7 @@
         <f>IF($AF104,'Historial de Sprints'!$C$5+$N104*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH104" s="202">
-        <f>IF($AF104,"No completada al cierre del Sprint "&amp;$N104&amp;" -&gt; reasignada al Sprint "&amp;$AD104,"")</f>
+        <f>IF($AF104,IF('Postergar'!$G104&lt;&gt;"",'Postergar'!$G104,"No completada al cierre del Sprint "&amp;$N104)&amp;" -&gt; Sprint "&amp;$AD104,"")</f>
       </c>
       <c r="AI104" s="201">
         <f>IF($AF104,$N104*100000+ROW(),"")</f>
@@ -34922,7 +34930,7 @@
         <f>IF($C105,IF(LEN(TRIM($AN105))=0,"—",TRIM($AN105)),"")</f>
       </c>
       <c r="AD105" s="201">
-        <f>IF($C105,IF($N105=9999,9999,IF($J105="Completado",$N105,MAX($N105,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C105,IF($N105=9999,9999,IF($J105="Completado",$N105,MAX($N105,'Historial de Sprints'!$C$7)+N('Postergar'!$F105))),"")</f>
       </c>
       <c r="AE105" s="201">
         <f>IF($C105,IF($AD105=9999,"(Sin sprint)",$AD105),"")</f>
@@ -34934,7 +34942,7 @@
         <f>IF($AF105,'Historial de Sprints'!$C$5+$N105*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH105" s="202">
-        <f>IF($AF105,"No completada al cierre del Sprint "&amp;$N105&amp;" -&gt; reasignada al Sprint "&amp;$AD105,"")</f>
+        <f>IF($AF105,IF('Postergar'!$G105&lt;&gt;"",'Postergar'!$G105,"No completada al cierre del Sprint "&amp;$N105)&amp;" -&gt; Sprint "&amp;$AD105,"")</f>
       </c>
       <c r="AI105" s="201">
         <f>IF($AF105,$N105*100000+ROW(),"")</f>
@@ -35038,7 +35046,7 @@
         <f>IF($C106,IF(LEN(TRIM($AN106))=0,"—",TRIM($AN106)),"")</f>
       </c>
       <c r="AD106" s="201">
-        <f>IF($C106,IF($N106=9999,9999,IF($J106="Completado",$N106,MAX($N106,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C106,IF($N106=9999,9999,IF($J106="Completado",$N106,MAX($N106,'Historial de Sprints'!$C$7)+N('Postergar'!$F106))),"")</f>
       </c>
       <c r="AE106" s="201">
         <f>IF($C106,IF($AD106=9999,"(Sin sprint)",$AD106),"")</f>
@@ -35050,7 +35058,7 @@
         <f>IF($AF106,'Historial de Sprints'!$C$5+$N106*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH106" s="202">
-        <f>IF($AF106,"No completada al cierre del Sprint "&amp;$N106&amp;" -&gt; reasignada al Sprint "&amp;$AD106,"")</f>
+        <f>IF($AF106,IF('Postergar'!$G106&lt;&gt;"",'Postergar'!$G106,"No completada al cierre del Sprint "&amp;$N106)&amp;" -&gt; Sprint "&amp;$AD106,"")</f>
       </c>
       <c r="AI106" s="201">
         <f>IF($AF106,$N106*100000+ROW(),"")</f>
@@ -35154,7 +35162,7 @@
         <f>IF($C107,IF(LEN(TRIM($AN107))=0,"—",TRIM($AN107)),"")</f>
       </c>
       <c r="AD107" s="201">
-        <f>IF($C107,IF($N107=9999,9999,IF($J107="Completado",$N107,MAX($N107,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C107,IF($N107=9999,9999,IF($J107="Completado",$N107,MAX($N107,'Historial de Sprints'!$C$7)+N('Postergar'!$F107))),"")</f>
       </c>
       <c r="AE107" s="201">
         <f>IF($C107,IF($AD107=9999,"(Sin sprint)",$AD107),"")</f>
@@ -35166,7 +35174,7 @@
         <f>IF($AF107,'Historial de Sprints'!$C$5+$N107*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH107" s="202">
-        <f>IF($AF107,"No completada al cierre del Sprint "&amp;$N107&amp;" -&gt; reasignada al Sprint "&amp;$AD107,"")</f>
+        <f>IF($AF107,IF('Postergar'!$G107&lt;&gt;"",'Postergar'!$G107,"No completada al cierre del Sprint "&amp;$N107)&amp;" -&gt; Sprint "&amp;$AD107,"")</f>
       </c>
       <c r="AI107" s="201">
         <f>IF($AF107,$N107*100000+ROW(),"")</f>
@@ -35270,7 +35278,7 @@
         <f>IF($C108,IF(LEN(TRIM($AN108))=0,"—",TRIM($AN108)),"")</f>
       </c>
       <c r="AD108" s="201">
-        <f>IF($C108,IF($N108=9999,9999,IF($J108="Completado",$N108,MAX($N108,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C108,IF($N108=9999,9999,IF($J108="Completado",$N108,MAX($N108,'Historial de Sprints'!$C$7)+N('Postergar'!$F108))),"")</f>
       </c>
       <c r="AE108" s="201">
         <f>IF($C108,IF($AD108=9999,"(Sin sprint)",$AD108),"")</f>
@@ -35282,7 +35290,7 @@
         <f>IF($AF108,'Historial de Sprints'!$C$5+$N108*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH108" s="202">
-        <f>IF($AF108,"No completada al cierre del Sprint "&amp;$N108&amp;" -&gt; reasignada al Sprint "&amp;$AD108,"")</f>
+        <f>IF($AF108,IF('Postergar'!$G108&lt;&gt;"",'Postergar'!$G108,"No completada al cierre del Sprint "&amp;$N108)&amp;" -&gt; Sprint "&amp;$AD108,"")</f>
       </c>
       <c r="AI108" s="201">
         <f>IF($AF108,$N108*100000+ROW(),"")</f>
@@ -35386,7 +35394,7 @@
         <f>IF($C109,IF(LEN(TRIM($AN109))=0,"—",TRIM($AN109)),"")</f>
       </c>
       <c r="AD109" s="201">
-        <f>IF($C109,IF($N109=9999,9999,IF($J109="Completado",$N109,MAX($N109,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C109,IF($N109=9999,9999,IF($J109="Completado",$N109,MAX($N109,'Historial de Sprints'!$C$7)+N('Postergar'!$F109))),"")</f>
       </c>
       <c r="AE109" s="201">
         <f>IF($C109,IF($AD109=9999,"(Sin sprint)",$AD109),"")</f>
@@ -35398,7 +35406,7 @@
         <f>IF($AF109,'Historial de Sprints'!$C$5+$N109*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH109" s="202">
-        <f>IF($AF109,"No completada al cierre del Sprint "&amp;$N109&amp;" -&gt; reasignada al Sprint "&amp;$AD109,"")</f>
+        <f>IF($AF109,IF('Postergar'!$G109&lt;&gt;"",'Postergar'!$G109,"No completada al cierre del Sprint "&amp;$N109)&amp;" -&gt; Sprint "&amp;$AD109,"")</f>
       </c>
       <c r="AI109" s="201">
         <f>IF($AF109,$N109*100000+ROW(),"")</f>
@@ -35502,7 +35510,7 @@
         <f>IF($C110,IF(LEN(TRIM($AN110))=0,"—",TRIM($AN110)),"")</f>
       </c>
       <c r="AD110" s="201">
-        <f>IF($C110,IF($N110=9999,9999,IF($J110="Completado",$N110,MAX($N110,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C110,IF($N110=9999,9999,IF($J110="Completado",$N110,MAX($N110,'Historial de Sprints'!$C$7)+N('Postergar'!$F110))),"")</f>
       </c>
       <c r="AE110" s="201">
         <f>IF($C110,IF($AD110=9999,"(Sin sprint)",$AD110),"")</f>
@@ -35514,7 +35522,7 @@
         <f>IF($AF110,'Historial de Sprints'!$C$5+$N110*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH110" s="202">
-        <f>IF($AF110,"No completada al cierre del Sprint "&amp;$N110&amp;" -&gt; reasignada al Sprint "&amp;$AD110,"")</f>
+        <f>IF($AF110,IF('Postergar'!$G110&lt;&gt;"",'Postergar'!$G110,"No completada al cierre del Sprint "&amp;$N110)&amp;" -&gt; Sprint "&amp;$AD110,"")</f>
       </c>
       <c r="AI110" s="201">
         <f>IF($AF110,$N110*100000+ROW(),"")</f>
@@ -35618,7 +35626,7 @@
         <f>IF($C111,IF(LEN(TRIM($AN111))=0,"—",TRIM($AN111)),"")</f>
       </c>
       <c r="AD111" s="201">
-        <f>IF($C111,IF($N111=9999,9999,IF($J111="Completado",$N111,MAX($N111,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C111,IF($N111=9999,9999,IF($J111="Completado",$N111,MAX($N111,'Historial de Sprints'!$C$7)+N('Postergar'!$F111))),"")</f>
       </c>
       <c r="AE111" s="201">
         <f>IF($C111,IF($AD111=9999,"(Sin sprint)",$AD111),"")</f>
@@ -35630,7 +35638,7 @@
         <f>IF($AF111,'Historial de Sprints'!$C$5+$N111*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH111" s="202">
-        <f>IF($AF111,"No completada al cierre del Sprint "&amp;$N111&amp;" -&gt; reasignada al Sprint "&amp;$AD111,"")</f>
+        <f>IF($AF111,IF('Postergar'!$G111&lt;&gt;"",'Postergar'!$G111,"No completada al cierre del Sprint "&amp;$N111)&amp;" -&gt; Sprint "&amp;$AD111,"")</f>
       </c>
       <c r="AI111" s="201">
         <f>IF($AF111,$N111*100000+ROW(),"")</f>
@@ -35734,7 +35742,7 @@
         <f>IF($C112,IF(LEN(TRIM($AN112))=0,"—",TRIM($AN112)),"")</f>
       </c>
       <c r="AD112" s="201">
-        <f>IF($C112,IF($N112=9999,9999,IF($J112="Completado",$N112,MAX($N112,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C112,IF($N112=9999,9999,IF($J112="Completado",$N112,MAX($N112,'Historial de Sprints'!$C$7)+N('Postergar'!$F112))),"")</f>
       </c>
       <c r="AE112" s="201">
         <f>IF($C112,IF($AD112=9999,"(Sin sprint)",$AD112),"")</f>
@@ -35746,7 +35754,7 @@
         <f>IF($AF112,'Historial de Sprints'!$C$5+$N112*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH112" s="202">
-        <f>IF($AF112,"No completada al cierre del Sprint "&amp;$N112&amp;" -&gt; reasignada al Sprint "&amp;$AD112,"")</f>
+        <f>IF($AF112,IF('Postergar'!$G112&lt;&gt;"",'Postergar'!$G112,"No completada al cierre del Sprint "&amp;$N112)&amp;" -&gt; Sprint "&amp;$AD112,"")</f>
       </c>
       <c r="AI112" s="201">
         <f>IF($AF112,$N112*100000+ROW(),"")</f>
@@ -35850,7 +35858,7 @@
         <f>IF($C113,IF(LEN(TRIM($AN113))=0,"—",TRIM($AN113)),"")</f>
       </c>
       <c r="AD113" s="201">
-        <f>IF($C113,IF($N113=9999,9999,IF($J113="Completado",$N113,MAX($N113,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C113,IF($N113=9999,9999,IF($J113="Completado",$N113,MAX($N113,'Historial de Sprints'!$C$7)+N('Postergar'!$F113))),"")</f>
       </c>
       <c r="AE113" s="201">
         <f>IF($C113,IF($AD113=9999,"(Sin sprint)",$AD113),"")</f>
@@ -35862,7 +35870,7 @@
         <f>IF($AF113,'Historial de Sprints'!$C$5+$N113*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH113" s="202">
-        <f>IF($AF113,"No completada al cierre del Sprint "&amp;$N113&amp;" -&gt; reasignada al Sprint "&amp;$AD113,"")</f>
+        <f>IF($AF113,IF('Postergar'!$G113&lt;&gt;"",'Postergar'!$G113,"No completada al cierre del Sprint "&amp;$N113)&amp;" -&gt; Sprint "&amp;$AD113,"")</f>
       </c>
       <c r="AI113" s="201">
         <f>IF($AF113,$N113*100000+ROW(),"")</f>
@@ -35966,7 +35974,7 @@
         <f>IF($C114,IF(LEN(TRIM($AN114))=0,"—",TRIM($AN114)),"")</f>
       </c>
       <c r="AD114" s="201">
-        <f>IF($C114,IF($N114=9999,9999,IF($J114="Completado",$N114,MAX($N114,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C114,IF($N114=9999,9999,IF($J114="Completado",$N114,MAX($N114,'Historial de Sprints'!$C$7)+N('Postergar'!$F114))),"")</f>
       </c>
       <c r="AE114" s="201">
         <f>IF($C114,IF($AD114=9999,"(Sin sprint)",$AD114),"")</f>
@@ -35978,7 +35986,7 @@
         <f>IF($AF114,'Historial de Sprints'!$C$5+$N114*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH114" s="202">
-        <f>IF($AF114,"No completada al cierre del Sprint "&amp;$N114&amp;" -&gt; reasignada al Sprint "&amp;$AD114,"")</f>
+        <f>IF($AF114,IF('Postergar'!$G114&lt;&gt;"",'Postergar'!$G114,"No completada al cierre del Sprint "&amp;$N114)&amp;" -&gt; Sprint "&amp;$AD114,"")</f>
       </c>
       <c r="AI114" s="201">
         <f>IF($AF114,$N114*100000+ROW(),"")</f>
@@ -36082,7 +36090,7 @@
         <f>IF($C115,IF(LEN(TRIM($AN115))=0,"—",TRIM($AN115)),"")</f>
       </c>
       <c r="AD115" s="201">
-        <f>IF($C115,IF($N115=9999,9999,IF($J115="Completado",$N115,MAX($N115,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C115,IF($N115=9999,9999,IF($J115="Completado",$N115,MAX($N115,'Historial de Sprints'!$C$7)+N('Postergar'!$F115))),"")</f>
       </c>
       <c r="AE115" s="201">
         <f>IF($C115,IF($AD115=9999,"(Sin sprint)",$AD115),"")</f>
@@ -36094,7 +36102,7 @@
         <f>IF($AF115,'Historial de Sprints'!$C$5+$N115*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH115" s="202">
-        <f>IF($AF115,"No completada al cierre del Sprint "&amp;$N115&amp;" -&gt; reasignada al Sprint "&amp;$AD115,"")</f>
+        <f>IF($AF115,IF('Postergar'!$G115&lt;&gt;"",'Postergar'!$G115,"No completada al cierre del Sprint "&amp;$N115)&amp;" -&gt; Sprint "&amp;$AD115,"")</f>
       </c>
       <c r="AI115" s="201">
         <f>IF($AF115,$N115*100000+ROW(),"")</f>
@@ -36198,7 +36206,7 @@
         <f>IF($C116,IF(LEN(TRIM($AN116))=0,"—",TRIM($AN116)),"")</f>
       </c>
       <c r="AD116" s="201">
-        <f>IF($C116,IF($N116=9999,9999,IF($J116="Completado",$N116,MAX($N116,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C116,IF($N116=9999,9999,IF($J116="Completado",$N116,MAX($N116,'Historial de Sprints'!$C$7)+N('Postergar'!$F116))),"")</f>
       </c>
       <c r="AE116" s="201">
         <f>IF($C116,IF($AD116=9999,"(Sin sprint)",$AD116),"")</f>
@@ -36210,7 +36218,7 @@
         <f>IF($AF116,'Historial de Sprints'!$C$5+$N116*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH116" s="202">
-        <f>IF($AF116,"No completada al cierre del Sprint "&amp;$N116&amp;" -&gt; reasignada al Sprint "&amp;$AD116,"")</f>
+        <f>IF($AF116,IF('Postergar'!$G116&lt;&gt;"",'Postergar'!$G116,"No completada al cierre del Sprint "&amp;$N116)&amp;" -&gt; Sprint "&amp;$AD116,"")</f>
       </c>
       <c r="AI116" s="201">
         <f>IF($AF116,$N116*100000+ROW(),"")</f>
@@ -36314,7 +36322,7 @@
         <f>IF($C117,IF(LEN(TRIM($AN117))=0,"—",TRIM($AN117)),"")</f>
       </c>
       <c r="AD117" s="201">
-        <f>IF($C117,IF($N117=9999,9999,IF($J117="Completado",$N117,MAX($N117,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C117,IF($N117=9999,9999,IF($J117="Completado",$N117,MAX($N117,'Historial de Sprints'!$C$7)+N('Postergar'!$F117))),"")</f>
       </c>
       <c r="AE117" s="201">
         <f>IF($C117,IF($AD117=9999,"(Sin sprint)",$AD117),"")</f>
@@ -36326,7 +36334,7 @@
         <f>IF($AF117,'Historial de Sprints'!$C$5+$N117*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH117" s="202">
-        <f>IF($AF117,"No completada al cierre del Sprint "&amp;$N117&amp;" -&gt; reasignada al Sprint "&amp;$AD117,"")</f>
+        <f>IF($AF117,IF('Postergar'!$G117&lt;&gt;"",'Postergar'!$G117,"No completada al cierre del Sprint "&amp;$N117)&amp;" -&gt; Sprint "&amp;$AD117,"")</f>
       </c>
       <c r="AI117" s="201">
         <f>IF($AF117,$N117*100000+ROW(),"")</f>
@@ -36430,7 +36438,7 @@
         <f>IF($C118,IF(LEN(TRIM($AN118))=0,"—",TRIM($AN118)),"")</f>
       </c>
       <c r="AD118" s="201">
-        <f>IF($C118,IF($N118=9999,9999,IF($J118="Completado",$N118,MAX($N118,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C118,IF($N118=9999,9999,IF($J118="Completado",$N118,MAX($N118,'Historial de Sprints'!$C$7)+N('Postergar'!$F118))),"")</f>
       </c>
       <c r="AE118" s="201">
         <f>IF($C118,IF($AD118=9999,"(Sin sprint)",$AD118),"")</f>
@@ -36442,7 +36450,7 @@
         <f>IF($AF118,'Historial de Sprints'!$C$5+$N118*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH118" s="202">
-        <f>IF($AF118,"No completada al cierre del Sprint "&amp;$N118&amp;" -&gt; reasignada al Sprint "&amp;$AD118,"")</f>
+        <f>IF($AF118,IF('Postergar'!$G118&lt;&gt;"",'Postergar'!$G118,"No completada al cierre del Sprint "&amp;$N118)&amp;" -&gt; Sprint "&amp;$AD118,"")</f>
       </c>
       <c r="AI118" s="201">
         <f>IF($AF118,$N118*100000+ROW(),"")</f>
@@ -36546,7 +36554,7 @@
         <f>IF($C119,IF(LEN(TRIM($AN119))=0,"—",TRIM($AN119)),"")</f>
       </c>
       <c r="AD119" s="201">
-        <f>IF($C119,IF($N119=9999,9999,IF($J119="Completado",$N119,MAX($N119,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C119,IF($N119=9999,9999,IF($J119="Completado",$N119,MAX($N119,'Historial de Sprints'!$C$7)+N('Postergar'!$F119))),"")</f>
       </c>
       <c r="AE119" s="201">
         <f>IF($C119,IF($AD119=9999,"(Sin sprint)",$AD119),"")</f>
@@ -36558,7 +36566,7 @@
         <f>IF($AF119,'Historial de Sprints'!$C$5+$N119*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH119" s="202">
-        <f>IF($AF119,"No completada al cierre del Sprint "&amp;$N119&amp;" -&gt; reasignada al Sprint "&amp;$AD119,"")</f>
+        <f>IF($AF119,IF('Postergar'!$G119&lt;&gt;"",'Postergar'!$G119,"No completada al cierre del Sprint "&amp;$N119)&amp;" -&gt; Sprint "&amp;$AD119,"")</f>
       </c>
       <c r="AI119" s="201">
         <f>IF($AF119,$N119*100000+ROW(),"")</f>
@@ -36662,7 +36670,7 @@
         <f>IF($C120,IF(LEN(TRIM($AN120))=0,"—",TRIM($AN120)),"")</f>
       </c>
       <c r="AD120" s="201">
-        <f>IF($C120,IF($N120=9999,9999,IF($J120="Completado",$N120,MAX($N120,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C120,IF($N120=9999,9999,IF($J120="Completado",$N120,MAX($N120,'Historial de Sprints'!$C$7)+N('Postergar'!$F120))),"")</f>
       </c>
       <c r="AE120" s="201">
         <f>IF($C120,IF($AD120=9999,"(Sin sprint)",$AD120),"")</f>
@@ -36674,7 +36682,7 @@
         <f>IF($AF120,'Historial de Sprints'!$C$5+$N120*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH120" s="202">
-        <f>IF($AF120,"No completada al cierre del Sprint "&amp;$N120&amp;" -&gt; reasignada al Sprint "&amp;$AD120,"")</f>
+        <f>IF($AF120,IF('Postergar'!$G120&lt;&gt;"",'Postergar'!$G120,"No completada al cierre del Sprint "&amp;$N120)&amp;" -&gt; Sprint "&amp;$AD120,"")</f>
       </c>
       <c r="AI120" s="201">
         <f>IF($AF120,$N120*100000+ROW(),"")</f>
@@ -36778,7 +36786,7 @@
         <f>IF($C121,IF(LEN(TRIM($AN121))=0,"—",TRIM($AN121)),"")</f>
       </c>
       <c r="AD121" s="201">
-        <f>IF($C121,IF($N121=9999,9999,IF($J121="Completado",$N121,MAX($N121,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C121,IF($N121=9999,9999,IF($J121="Completado",$N121,MAX($N121,'Historial de Sprints'!$C$7)+N('Postergar'!$F121))),"")</f>
       </c>
       <c r="AE121" s="201">
         <f>IF($C121,IF($AD121=9999,"(Sin sprint)",$AD121),"")</f>
@@ -36790,7 +36798,7 @@
         <f>IF($AF121,'Historial de Sprints'!$C$5+$N121*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH121" s="202">
-        <f>IF($AF121,"No completada al cierre del Sprint "&amp;$N121&amp;" -&gt; reasignada al Sprint "&amp;$AD121,"")</f>
+        <f>IF($AF121,IF('Postergar'!$G121&lt;&gt;"",'Postergar'!$G121,"No completada al cierre del Sprint "&amp;$N121)&amp;" -&gt; Sprint "&amp;$AD121,"")</f>
       </c>
       <c r="AI121" s="201">
         <f>IF($AF121,$N121*100000+ROW(),"")</f>
@@ -36894,7 +36902,7 @@
         <f>IF($C122,IF(LEN(TRIM($AN122))=0,"—",TRIM($AN122)),"")</f>
       </c>
       <c r="AD122" s="201">
-        <f>IF($C122,IF($N122=9999,9999,IF($J122="Completado",$N122,MAX($N122,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C122,IF($N122=9999,9999,IF($J122="Completado",$N122,MAX($N122,'Historial de Sprints'!$C$7)+N('Postergar'!$F122))),"")</f>
       </c>
       <c r="AE122" s="201">
         <f>IF($C122,IF($AD122=9999,"(Sin sprint)",$AD122),"")</f>
@@ -36906,7 +36914,7 @@
         <f>IF($AF122,'Historial de Sprints'!$C$5+$N122*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH122" s="202">
-        <f>IF($AF122,"No completada al cierre del Sprint "&amp;$N122&amp;" -&gt; reasignada al Sprint "&amp;$AD122,"")</f>
+        <f>IF($AF122,IF('Postergar'!$G122&lt;&gt;"",'Postergar'!$G122,"No completada al cierre del Sprint "&amp;$N122)&amp;" -&gt; Sprint "&amp;$AD122,"")</f>
       </c>
       <c r="AI122" s="201">
         <f>IF($AF122,$N122*100000+ROW(),"")</f>
@@ -37010,7 +37018,7 @@
         <f>IF($C123,IF(LEN(TRIM($AN123))=0,"—",TRIM($AN123)),"")</f>
       </c>
       <c r="AD123" s="201">
-        <f>IF($C123,IF($N123=9999,9999,IF($J123="Completado",$N123,MAX($N123,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C123,IF($N123=9999,9999,IF($J123="Completado",$N123,MAX($N123,'Historial de Sprints'!$C$7)+N('Postergar'!$F123))),"")</f>
       </c>
       <c r="AE123" s="201">
         <f>IF($C123,IF($AD123=9999,"(Sin sprint)",$AD123),"")</f>
@@ -37022,7 +37030,7 @@
         <f>IF($AF123,'Historial de Sprints'!$C$5+$N123*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH123" s="202">
-        <f>IF($AF123,"No completada al cierre del Sprint "&amp;$N123&amp;" -&gt; reasignada al Sprint "&amp;$AD123,"")</f>
+        <f>IF($AF123,IF('Postergar'!$G123&lt;&gt;"",'Postergar'!$G123,"No completada al cierre del Sprint "&amp;$N123)&amp;" -&gt; Sprint "&amp;$AD123,"")</f>
       </c>
       <c r="AI123" s="201">
         <f>IF($AF123,$N123*100000+ROW(),"")</f>
@@ -37126,7 +37134,7 @@
         <f>IF($C124,IF(LEN(TRIM($AN124))=0,"—",TRIM($AN124)),"")</f>
       </c>
       <c r="AD124" s="201">
-        <f>IF($C124,IF($N124=9999,9999,IF($J124="Completado",$N124,MAX($N124,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C124,IF($N124=9999,9999,IF($J124="Completado",$N124,MAX($N124,'Historial de Sprints'!$C$7)+N('Postergar'!$F124))),"")</f>
       </c>
       <c r="AE124" s="201">
         <f>IF($C124,IF($AD124=9999,"(Sin sprint)",$AD124),"")</f>
@@ -37138,7 +37146,7 @@
         <f>IF($AF124,'Historial de Sprints'!$C$5+$N124*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH124" s="202">
-        <f>IF($AF124,"No completada al cierre del Sprint "&amp;$N124&amp;" -&gt; reasignada al Sprint "&amp;$AD124,"")</f>
+        <f>IF($AF124,IF('Postergar'!$G124&lt;&gt;"",'Postergar'!$G124,"No completada al cierre del Sprint "&amp;$N124)&amp;" -&gt; Sprint "&amp;$AD124,"")</f>
       </c>
       <c r="AI124" s="201">
         <f>IF($AF124,$N124*100000+ROW(),"")</f>
@@ -37242,7 +37250,7 @@
         <f>IF($C125,IF(LEN(TRIM($AN125))=0,"—",TRIM($AN125)),"")</f>
       </c>
       <c r="AD125" s="201">
-        <f>IF($C125,IF($N125=9999,9999,IF($J125="Completado",$N125,MAX($N125,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C125,IF($N125=9999,9999,IF($J125="Completado",$N125,MAX($N125,'Historial de Sprints'!$C$7)+N('Postergar'!$F125))),"")</f>
       </c>
       <c r="AE125" s="201">
         <f>IF($C125,IF($AD125=9999,"(Sin sprint)",$AD125),"")</f>
@@ -37254,7 +37262,7 @@
         <f>IF($AF125,'Historial de Sprints'!$C$5+$N125*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH125" s="202">
-        <f>IF($AF125,"No completada al cierre del Sprint "&amp;$N125&amp;" -&gt; reasignada al Sprint "&amp;$AD125,"")</f>
+        <f>IF($AF125,IF('Postergar'!$G125&lt;&gt;"",'Postergar'!$G125,"No completada al cierre del Sprint "&amp;$N125)&amp;" -&gt; Sprint "&amp;$AD125,"")</f>
       </c>
       <c r="AI125" s="201">
         <f>IF($AF125,$N125*100000+ROW(),"")</f>
@@ -37358,7 +37366,7 @@
         <f>IF($C126,IF(LEN(TRIM($AN126))=0,"—",TRIM($AN126)),"")</f>
       </c>
       <c r="AD126" s="201">
-        <f>IF($C126,IF($N126=9999,9999,IF($J126="Completado",$N126,MAX($N126,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C126,IF($N126=9999,9999,IF($J126="Completado",$N126,MAX($N126,'Historial de Sprints'!$C$7)+N('Postergar'!$F126))),"")</f>
       </c>
       <c r="AE126" s="201">
         <f>IF($C126,IF($AD126=9999,"(Sin sprint)",$AD126),"")</f>
@@ -37370,7 +37378,7 @@
         <f>IF($AF126,'Historial de Sprints'!$C$5+$N126*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH126" s="202">
-        <f>IF($AF126,"No completada al cierre del Sprint "&amp;$N126&amp;" -&gt; reasignada al Sprint "&amp;$AD126,"")</f>
+        <f>IF($AF126,IF('Postergar'!$G126&lt;&gt;"",'Postergar'!$G126,"No completada al cierre del Sprint "&amp;$N126)&amp;" -&gt; Sprint "&amp;$AD126,"")</f>
       </c>
       <c r="AI126" s="201">
         <f>IF($AF126,$N126*100000+ROW(),"")</f>
@@ -37474,7 +37482,7 @@
         <f>IF($C127,IF(LEN(TRIM($AN127))=0,"—",TRIM($AN127)),"")</f>
       </c>
       <c r="AD127" s="201">
-        <f>IF($C127,IF($N127=9999,9999,IF($J127="Completado",$N127,MAX($N127,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C127,IF($N127=9999,9999,IF($J127="Completado",$N127,MAX($N127,'Historial de Sprints'!$C$7)+N('Postergar'!$F127))),"")</f>
       </c>
       <c r="AE127" s="201">
         <f>IF($C127,IF($AD127=9999,"(Sin sprint)",$AD127),"")</f>
@@ -37486,7 +37494,7 @@
         <f>IF($AF127,'Historial de Sprints'!$C$5+$N127*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH127" s="202">
-        <f>IF($AF127,"No completada al cierre del Sprint "&amp;$N127&amp;" -&gt; reasignada al Sprint "&amp;$AD127,"")</f>
+        <f>IF($AF127,IF('Postergar'!$G127&lt;&gt;"",'Postergar'!$G127,"No completada al cierre del Sprint "&amp;$N127)&amp;" -&gt; Sprint "&amp;$AD127,"")</f>
       </c>
       <c r="AI127" s="201">
         <f>IF($AF127,$N127*100000+ROW(),"")</f>
@@ -37590,7 +37598,7 @@
         <f>IF($C128,IF(LEN(TRIM($AN128))=0,"—",TRIM($AN128)),"")</f>
       </c>
       <c r="AD128" s="201">
-        <f>IF($C128,IF($N128=9999,9999,IF($J128="Completado",$N128,MAX($N128,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C128,IF($N128=9999,9999,IF($J128="Completado",$N128,MAX($N128,'Historial de Sprints'!$C$7)+N('Postergar'!$F128))),"")</f>
       </c>
       <c r="AE128" s="201">
         <f>IF($C128,IF($AD128=9999,"(Sin sprint)",$AD128),"")</f>
@@ -37602,7 +37610,7 @@
         <f>IF($AF128,'Historial de Sprints'!$C$5+$N128*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH128" s="202">
-        <f>IF($AF128,"No completada al cierre del Sprint "&amp;$N128&amp;" -&gt; reasignada al Sprint "&amp;$AD128,"")</f>
+        <f>IF($AF128,IF('Postergar'!$G128&lt;&gt;"",'Postergar'!$G128,"No completada al cierre del Sprint "&amp;$N128)&amp;" -&gt; Sprint "&amp;$AD128,"")</f>
       </c>
       <c r="AI128" s="201">
         <f>IF($AF128,$N128*100000+ROW(),"")</f>
@@ -37706,7 +37714,7 @@
         <f>IF($C129,IF(LEN(TRIM($AN129))=0,"—",TRIM($AN129)),"")</f>
       </c>
       <c r="AD129" s="201">
-        <f>IF($C129,IF($N129=9999,9999,IF($J129="Completado",$N129,MAX($N129,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C129,IF($N129=9999,9999,IF($J129="Completado",$N129,MAX($N129,'Historial de Sprints'!$C$7)+N('Postergar'!$F129))),"")</f>
       </c>
       <c r="AE129" s="201">
         <f>IF($C129,IF($AD129=9999,"(Sin sprint)",$AD129),"")</f>
@@ -37718,7 +37726,7 @@
         <f>IF($AF129,'Historial de Sprints'!$C$5+$N129*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH129" s="202">
-        <f>IF($AF129,"No completada al cierre del Sprint "&amp;$N129&amp;" -&gt; reasignada al Sprint "&amp;$AD129,"")</f>
+        <f>IF($AF129,IF('Postergar'!$G129&lt;&gt;"",'Postergar'!$G129,"No completada al cierre del Sprint "&amp;$N129)&amp;" -&gt; Sprint "&amp;$AD129,"")</f>
       </c>
       <c r="AI129" s="201">
         <f>IF($AF129,$N129*100000+ROW(),"")</f>
@@ -37822,7 +37830,7 @@
         <f>IF($C130,IF(LEN(TRIM($AN130))=0,"—",TRIM($AN130)),"")</f>
       </c>
       <c r="AD130" s="201">
-        <f>IF($C130,IF($N130=9999,9999,IF($J130="Completado",$N130,MAX($N130,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C130,IF($N130=9999,9999,IF($J130="Completado",$N130,MAX($N130,'Historial de Sprints'!$C$7)+N('Postergar'!$F130))),"")</f>
       </c>
       <c r="AE130" s="201">
         <f>IF($C130,IF($AD130=9999,"(Sin sprint)",$AD130),"")</f>
@@ -37834,7 +37842,7 @@
         <f>IF($AF130,'Historial de Sprints'!$C$5+$N130*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH130" s="202">
-        <f>IF($AF130,"No completada al cierre del Sprint "&amp;$N130&amp;" -&gt; reasignada al Sprint "&amp;$AD130,"")</f>
+        <f>IF($AF130,IF('Postergar'!$G130&lt;&gt;"",'Postergar'!$G130,"No completada al cierre del Sprint "&amp;$N130)&amp;" -&gt; Sprint "&amp;$AD130,"")</f>
       </c>
       <c r="AI130" s="201">
         <f>IF($AF130,$N130*100000+ROW(),"")</f>
@@ -37938,7 +37946,7 @@
         <f>IF($C131,IF(LEN(TRIM($AN131))=0,"—",TRIM($AN131)),"")</f>
       </c>
       <c r="AD131" s="201">
-        <f>IF($C131,IF($N131=9999,9999,IF($J131="Completado",$N131,MAX($N131,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C131,IF($N131=9999,9999,IF($J131="Completado",$N131,MAX($N131,'Historial de Sprints'!$C$7)+N('Postergar'!$F131))),"")</f>
       </c>
       <c r="AE131" s="201">
         <f>IF($C131,IF($AD131=9999,"(Sin sprint)",$AD131),"")</f>
@@ -37950,7 +37958,7 @@
         <f>IF($AF131,'Historial de Sprints'!$C$5+$N131*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH131" s="202">
-        <f>IF($AF131,"No completada al cierre del Sprint "&amp;$N131&amp;" -&gt; reasignada al Sprint "&amp;$AD131,"")</f>
+        <f>IF($AF131,IF('Postergar'!$G131&lt;&gt;"",'Postergar'!$G131,"No completada al cierre del Sprint "&amp;$N131)&amp;" -&gt; Sprint "&amp;$AD131,"")</f>
       </c>
       <c r="AI131" s="201">
         <f>IF($AF131,$N131*100000+ROW(),"")</f>
@@ -38054,7 +38062,7 @@
         <f>IF($C132,IF(LEN(TRIM($AN132))=0,"—",TRIM($AN132)),"")</f>
       </c>
       <c r="AD132" s="201">
-        <f>IF($C132,IF($N132=9999,9999,IF($J132="Completado",$N132,MAX($N132,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C132,IF($N132=9999,9999,IF($J132="Completado",$N132,MAX($N132,'Historial de Sprints'!$C$7)+N('Postergar'!$F132))),"")</f>
       </c>
       <c r="AE132" s="201">
         <f>IF($C132,IF($AD132=9999,"(Sin sprint)",$AD132),"")</f>
@@ -38066,7 +38074,7 @@
         <f>IF($AF132,'Historial de Sprints'!$C$5+$N132*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH132" s="202">
-        <f>IF($AF132,"No completada al cierre del Sprint "&amp;$N132&amp;" -&gt; reasignada al Sprint "&amp;$AD132,"")</f>
+        <f>IF($AF132,IF('Postergar'!$G132&lt;&gt;"",'Postergar'!$G132,"No completada al cierre del Sprint "&amp;$N132)&amp;" -&gt; Sprint "&amp;$AD132,"")</f>
       </c>
       <c r="AI132" s="201">
         <f>IF($AF132,$N132*100000+ROW(),"")</f>
@@ -38170,7 +38178,7 @@
         <f>IF($C133,IF(LEN(TRIM($AN133))=0,"—",TRIM($AN133)),"")</f>
       </c>
       <c r="AD133" s="201">
-        <f>IF($C133,IF($N133=9999,9999,IF($J133="Completado",$N133,MAX($N133,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C133,IF($N133=9999,9999,IF($J133="Completado",$N133,MAX($N133,'Historial de Sprints'!$C$7)+N('Postergar'!$F133))),"")</f>
       </c>
       <c r="AE133" s="201">
         <f>IF($C133,IF($AD133=9999,"(Sin sprint)",$AD133),"")</f>
@@ -38182,7 +38190,7 @@
         <f>IF($AF133,'Historial de Sprints'!$C$5+$N133*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH133" s="202">
-        <f>IF($AF133,"No completada al cierre del Sprint "&amp;$N133&amp;" -&gt; reasignada al Sprint "&amp;$AD133,"")</f>
+        <f>IF($AF133,IF('Postergar'!$G133&lt;&gt;"",'Postergar'!$G133,"No completada al cierre del Sprint "&amp;$N133)&amp;" -&gt; Sprint "&amp;$AD133,"")</f>
       </c>
       <c r="AI133" s="201">
         <f>IF($AF133,$N133*100000+ROW(),"")</f>
@@ -38286,7 +38294,7 @@
         <f>IF($C134,IF(LEN(TRIM($AN134))=0,"—",TRIM($AN134)),"")</f>
       </c>
       <c r="AD134" s="201">
-        <f>IF($C134,IF($N134=9999,9999,IF($J134="Completado",$N134,MAX($N134,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C134,IF($N134=9999,9999,IF($J134="Completado",$N134,MAX($N134,'Historial de Sprints'!$C$7)+N('Postergar'!$F134))),"")</f>
       </c>
       <c r="AE134" s="201">
         <f>IF($C134,IF($AD134=9999,"(Sin sprint)",$AD134),"")</f>
@@ -38298,7 +38306,7 @@
         <f>IF($AF134,'Historial de Sprints'!$C$5+$N134*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH134" s="202">
-        <f>IF($AF134,"No completada al cierre del Sprint "&amp;$N134&amp;" -&gt; reasignada al Sprint "&amp;$AD134,"")</f>
+        <f>IF($AF134,IF('Postergar'!$G134&lt;&gt;"",'Postergar'!$G134,"No completada al cierre del Sprint "&amp;$N134)&amp;" -&gt; Sprint "&amp;$AD134,"")</f>
       </c>
       <c r="AI134" s="201">
         <f>IF($AF134,$N134*100000+ROW(),"")</f>
@@ -38402,7 +38410,7 @@
         <f>IF($C135,IF(LEN(TRIM($AN135))=0,"—",TRIM($AN135)),"")</f>
       </c>
       <c r="AD135" s="201">
-        <f>IF($C135,IF($N135=9999,9999,IF($J135="Completado",$N135,MAX($N135,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C135,IF($N135=9999,9999,IF($J135="Completado",$N135,MAX($N135,'Historial de Sprints'!$C$7)+N('Postergar'!$F135))),"")</f>
       </c>
       <c r="AE135" s="201">
         <f>IF($C135,IF($AD135=9999,"(Sin sprint)",$AD135),"")</f>
@@ -38414,7 +38422,7 @@
         <f>IF($AF135,'Historial de Sprints'!$C$5+$N135*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH135" s="202">
-        <f>IF($AF135,"No completada al cierre del Sprint "&amp;$N135&amp;" -&gt; reasignada al Sprint "&amp;$AD135,"")</f>
+        <f>IF($AF135,IF('Postergar'!$G135&lt;&gt;"",'Postergar'!$G135,"No completada al cierre del Sprint "&amp;$N135)&amp;" -&gt; Sprint "&amp;$AD135,"")</f>
       </c>
       <c r="AI135" s="201">
         <f>IF($AF135,$N135*100000+ROW(),"")</f>
@@ -38518,7 +38526,7 @@
         <f>IF($C136,IF(LEN(TRIM($AN136))=0,"—",TRIM($AN136)),"")</f>
       </c>
       <c r="AD136" s="201">
-        <f>IF($C136,IF($N136=9999,9999,IF($J136="Completado",$N136,MAX($N136,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C136,IF($N136=9999,9999,IF($J136="Completado",$N136,MAX($N136,'Historial de Sprints'!$C$7)+N('Postergar'!$F136))),"")</f>
       </c>
       <c r="AE136" s="201">
         <f>IF($C136,IF($AD136=9999,"(Sin sprint)",$AD136),"")</f>
@@ -38530,7 +38538,7 @@
         <f>IF($AF136,'Historial de Sprints'!$C$5+$N136*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH136" s="202">
-        <f>IF($AF136,"No completada al cierre del Sprint "&amp;$N136&amp;" -&gt; reasignada al Sprint "&amp;$AD136,"")</f>
+        <f>IF($AF136,IF('Postergar'!$G136&lt;&gt;"",'Postergar'!$G136,"No completada al cierre del Sprint "&amp;$N136)&amp;" -&gt; Sprint "&amp;$AD136,"")</f>
       </c>
       <c r="AI136" s="201">
         <f>IF($AF136,$N136*100000+ROW(),"")</f>
@@ -38634,7 +38642,7 @@
         <f>IF($C137,IF(LEN(TRIM($AN137))=0,"—",TRIM($AN137)),"")</f>
       </c>
       <c r="AD137" s="201">
-        <f>IF($C137,IF($N137=9999,9999,IF($J137="Completado",$N137,MAX($N137,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C137,IF($N137=9999,9999,IF($J137="Completado",$N137,MAX($N137,'Historial de Sprints'!$C$7)+N('Postergar'!$F137))),"")</f>
       </c>
       <c r="AE137" s="201">
         <f>IF($C137,IF($AD137=9999,"(Sin sprint)",$AD137),"")</f>
@@ -38646,7 +38654,7 @@
         <f>IF($AF137,'Historial de Sprints'!$C$5+$N137*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH137" s="202">
-        <f>IF($AF137,"No completada al cierre del Sprint "&amp;$N137&amp;" -&gt; reasignada al Sprint "&amp;$AD137,"")</f>
+        <f>IF($AF137,IF('Postergar'!$G137&lt;&gt;"",'Postergar'!$G137,"No completada al cierre del Sprint "&amp;$N137)&amp;" -&gt; Sprint "&amp;$AD137,"")</f>
       </c>
       <c r="AI137" s="201">
         <f>IF($AF137,$N137*100000+ROW(),"")</f>
@@ -38750,7 +38758,7 @@
         <f>IF($C138,IF(LEN(TRIM($AN138))=0,"—",TRIM($AN138)),"")</f>
       </c>
       <c r="AD138" s="201">
-        <f>IF($C138,IF($N138=9999,9999,IF($J138="Completado",$N138,MAX($N138,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C138,IF($N138=9999,9999,IF($J138="Completado",$N138,MAX($N138,'Historial de Sprints'!$C$7)+N('Postergar'!$F138))),"")</f>
       </c>
       <c r="AE138" s="201">
         <f>IF($C138,IF($AD138=9999,"(Sin sprint)",$AD138),"")</f>
@@ -38762,7 +38770,7 @@
         <f>IF($AF138,'Historial de Sprints'!$C$5+$N138*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH138" s="202">
-        <f>IF($AF138,"No completada al cierre del Sprint "&amp;$N138&amp;" -&gt; reasignada al Sprint "&amp;$AD138,"")</f>
+        <f>IF($AF138,IF('Postergar'!$G138&lt;&gt;"",'Postergar'!$G138,"No completada al cierre del Sprint "&amp;$N138)&amp;" -&gt; Sprint "&amp;$AD138,"")</f>
       </c>
       <c r="AI138" s="201">
         <f>IF($AF138,$N138*100000+ROW(),"")</f>
@@ -38866,7 +38874,7 @@
         <f>IF($C139,IF(LEN(TRIM($AN139))=0,"—",TRIM($AN139)),"")</f>
       </c>
       <c r="AD139" s="201">
-        <f>IF($C139,IF($N139=9999,9999,IF($J139="Completado",$N139,MAX($N139,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C139,IF($N139=9999,9999,IF($J139="Completado",$N139,MAX($N139,'Historial de Sprints'!$C$7)+N('Postergar'!$F139))),"")</f>
       </c>
       <c r="AE139" s="201">
         <f>IF($C139,IF($AD139=9999,"(Sin sprint)",$AD139),"")</f>
@@ -38878,7 +38886,7 @@
         <f>IF($AF139,'Historial de Sprints'!$C$5+$N139*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH139" s="202">
-        <f>IF($AF139,"No completada al cierre del Sprint "&amp;$N139&amp;" -&gt; reasignada al Sprint "&amp;$AD139,"")</f>
+        <f>IF($AF139,IF('Postergar'!$G139&lt;&gt;"",'Postergar'!$G139,"No completada al cierre del Sprint "&amp;$N139)&amp;" -&gt; Sprint "&amp;$AD139,"")</f>
       </c>
       <c r="AI139" s="201">
         <f>IF($AF139,$N139*100000+ROW(),"")</f>
@@ -38982,7 +38990,7 @@
         <f>IF($C140,IF(LEN(TRIM($AN140))=0,"—",TRIM($AN140)),"")</f>
       </c>
       <c r="AD140" s="201">
-        <f>IF($C140,IF($N140=9999,9999,IF($J140="Completado",$N140,MAX($N140,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C140,IF($N140=9999,9999,IF($J140="Completado",$N140,MAX($N140,'Historial de Sprints'!$C$7)+N('Postergar'!$F140))),"")</f>
       </c>
       <c r="AE140" s="201">
         <f>IF($C140,IF($AD140=9999,"(Sin sprint)",$AD140),"")</f>
@@ -38994,7 +39002,7 @@
         <f>IF($AF140,'Historial de Sprints'!$C$5+$N140*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH140" s="202">
-        <f>IF($AF140,"No completada al cierre del Sprint "&amp;$N140&amp;" -&gt; reasignada al Sprint "&amp;$AD140,"")</f>
+        <f>IF($AF140,IF('Postergar'!$G140&lt;&gt;"",'Postergar'!$G140,"No completada al cierre del Sprint "&amp;$N140)&amp;" -&gt; Sprint "&amp;$AD140,"")</f>
       </c>
       <c r="AI140" s="201">
         <f>IF($AF140,$N140*100000+ROW(),"")</f>
@@ -39098,7 +39106,7 @@
         <f>IF($C141,IF(LEN(TRIM($AN141))=0,"—",TRIM($AN141)),"")</f>
       </c>
       <c r="AD141" s="201">
-        <f>IF($C141,IF($N141=9999,9999,IF($J141="Completado",$N141,MAX($N141,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C141,IF($N141=9999,9999,IF($J141="Completado",$N141,MAX($N141,'Historial de Sprints'!$C$7)+N('Postergar'!$F141))),"")</f>
       </c>
       <c r="AE141" s="201">
         <f>IF($C141,IF($AD141=9999,"(Sin sprint)",$AD141),"")</f>
@@ -39110,7 +39118,7 @@
         <f>IF($AF141,'Historial de Sprints'!$C$5+$N141*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH141" s="202">
-        <f>IF($AF141,"No completada al cierre del Sprint "&amp;$N141&amp;" -&gt; reasignada al Sprint "&amp;$AD141,"")</f>
+        <f>IF($AF141,IF('Postergar'!$G141&lt;&gt;"",'Postergar'!$G141,"No completada al cierre del Sprint "&amp;$N141)&amp;" -&gt; Sprint "&amp;$AD141,"")</f>
       </c>
       <c r="AI141" s="201">
         <f>IF($AF141,$N141*100000+ROW(),"")</f>
@@ -39214,7 +39222,7 @@
         <f>IF($C142,IF(LEN(TRIM($AN142))=0,"—",TRIM($AN142)),"")</f>
       </c>
       <c r="AD142" s="201">
-        <f>IF($C142,IF($N142=9999,9999,IF($J142="Completado",$N142,MAX($N142,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C142,IF($N142=9999,9999,IF($J142="Completado",$N142,MAX($N142,'Historial de Sprints'!$C$7)+N('Postergar'!$F142))),"")</f>
       </c>
       <c r="AE142" s="201">
         <f>IF($C142,IF($AD142=9999,"(Sin sprint)",$AD142),"")</f>
@@ -39226,7 +39234,7 @@
         <f>IF($AF142,'Historial de Sprints'!$C$5+$N142*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH142" s="202">
-        <f>IF($AF142,"No completada al cierre del Sprint "&amp;$N142&amp;" -&gt; reasignada al Sprint "&amp;$AD142,"")</f>
+        <f>IF($AF142,IF('Postergar'!$G142&lt;&gt;"",'Postergar'!$G142,"No completada al cierre del Sprint "&amp;$N142)&amp;" -&gt; Sprint "&amp;$AD142,"")</f>
       </c>
       <c r="AI142" s="201">
         <f>IF($AF142,$N142*100000+ROW(),"")</f>
@@ -39330,7 +39338,7 @@
         <f>IF($C143,IF(LEN(TRIM($AN143))=0,"—",TRIM($AN143)),"")</f>
       </c>
       <c r="AD143" s="201">
-        <f>IF($C143,IF($N143=9999,9999,IF($J143="Completado",$N143,MAX($N143,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C143,IF($N143=9999,9999,IF($J143="Completado",$N143,MAX($N143,'Historial de Sprints'!$C$7)+N('Postergar'!$F143))),"")</f>
       </c>
       <c r="AE143" s="201">
         <f>IF($C143,IF($AD143=9999,"(Sin sprint)",$AD143),"")</f>
@@ -39342,7 +39350,7 @@
         <f>IF($AF143,'Historial de Sprints'!$C$5+$N143*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH143" s="202">
-        <f>IF($AF143,"No completada al cierre del Sprint "&amp;$N143&amp;" -&gt; reasignada al Sprint "&amp;$AD143,"")</f>
+        <f>IF($AF143,IF('Postergar'!$G143&lt;&gt;"",'Postergar'!$G143,"No completada al cierre del Sprint "&amp;$N143)&amp;" -&gt; Sprint "&amp;$AD143,"")</f>
       </c>
       <c r="AI143" s="201">
         <f>IF($AF143,$N143*100000+ROW(),"")</f>
@@ -39446,7 +39454,7 @@
         <f>IF($C144,IF(LEN(TRIM($AN144))=0,"—",TRIM($AN144)),"")</f>
       </c>
       <c r="AD144" s="201">
-        <f>IF($C144,IF($N144=9999,9999,IF($J144="Completado",$N144,MAX($N144,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C144,IF($N144=9999,9999,IF($J144="Completado",$N144,MAX($N144,'Historial de Sprints'!$C$7)+N('Postergar'!$F144))),"")</f>
       </c>
       <c r="AE144" s="201">
         <f>IF($C144,IF($AD144=9999,"(Sin sprint)",$AD144),"")</f>
@@ -39458,7 +39466,7 @@
         <f>IF($AF144,'Historial de Sprints'!$C$5+$N144*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH144" s="202">
-        <f>IF($AF144,"No completada al cierre del Sprint "&amp;$N144&amp;" -&gt; reasignada al Sprint "&amp;$AD144,"")</f>
+        <f>IF($AF144,IF('Postergar'!$G144&lt;&gt;"",'Postergar'!$G144,"No completada al cierre del Sprint "&amp;$N144)&amp;" -&gt; Sprint "&amp;$AD144,"")</f>
       </c>
       <c r="AI144" s="201">
         <f>IF($AF144,$N144*100000+ROW(),"")</f>
@@ -39562,7 +39570,7 @@
         <f>IF($C145,IF(LEN(TRIM($AN145))=0,"—",TRIM($AN145)),"")</f>
       </c>
       <c r="AD145" s="201">
-        <f>IF($C145,IF($N145=9999,9999,IF($J145="Completado",$N145,MAX($N145,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C145,IF($N145=9999,9999,IF($J145="Completado",$N145,MAX($N145,'Historial de Sprints'!$C$7)+N('Postergar'!$F145))),"")</f>
       </c>
       <c r="AE145" s="201">
         <f>IF($C145,IF($AD145=9999,"(Sin sprint)",$AD145),"")</f>
@@ -39574,7 +39582,7 @@
         <f>IF($AF145,'Historial de Sprints'!$C$5+$N145*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH145" s="202">
-        <f>IF($AF145,"No completada al cierre del Sprint "&amp;$N145&amp;" -&gt; reasignada al Sprint "&amp;$AD145,"")</f>
+        <f>IF($AF145,IF('Postergar'!$G145&lt;&gt;"",'Postergar'!$G145,"No completada al cierre del Sprint "&amp;$N145)&amp;" -&gt; Sprint "&amp;$AD145,"")</f>
       </c>
       <c r="AI145" s="201">
         <f>IF($AF145,$N145*100000+ROW(),"")</f>
@@ -39678,7 +39686,7 @@
         <f>IF($C146,IF(LEN(TRIM($AN146))=0,"—",TRIM($AN146)),"")</f>
       </c>
       <c r="AD146" s="201">
-        <f>IF($C146,IF($N146=9999,9999,IF($J146="Completado",$N146,MAX($N146,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C146,IF($N146=9999,9999,IF($J146="Completado",$N146,MAX($N146,'Historial de Sprints'!$C$7)+N('Postergar'!$F146))),"")</f>
       </c>
       <c r="AE146" s="201">
         <f>IF($C146,IF($AD146=9999,"(Sin sprint)",$AD146),"")</f>
@@ -39690,7 +39698,7 @@
         <f>IF($AF146,'Historial de Sprints'!$C$5+$N146*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH146" s="202">
-        <f>IF($AF146,"No completada al cierre del Sprint "&amp;$N146&amp;" -&gt; reasignada al Sprint "&amp;$AD146,"")</f>
+        <f>IF($AF146,IF('Postergar'!$G146&lt;&gt;"",'Postergar'!$G146,"No completada al cierre del Sprint "&amp;$N146)&amp;" -&gt; Sprint "&amp;$AD146,"")</f>
       </c>
       <c r="AI146" s="201">
         <f>IF($AF146,$N146*100000+ROW(),"")</f>
@@ -39794,7 +39802,7 @@
         <f>IF($C147,IF(LEN(TRIM($AN147))=0,"—",TRIM($AN147)),"")</f>
       </c>
       <c r="AD147" s="201">
-        <f>IF($C147,IF($N147=9999,9999,IF($J147="Completado",$N147,MAX($N147,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C147,IF($N147=9999,9999,IF($J147="Completado",$N147,MAX($N147,'Historial de Sprints'!$C$7)+N('Postergar'!$F147))),"")</f>
       </c>
       <c r="AE147" s="201">
         <f>IF($C147,IF($AD147=9999,"(Sin sprint)",$AD147),"")</f>
@@ -39806,7 +39814,7 @@
         <f>IF($AF147,'Historial de Sprints'!$C$5+$N147*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH147" s="202">
-        <f>IF($AF147,"No completada al cierre del Sprint "&amp;$N147&amp;" -&gt; reasignada al Sprint "&amp;$AD147,"")</f>
+        <f>IF($AF147,IF('Postergar'!$G147&lt;&gt;"",'Postergar'!$G147,"No completada al cierre del Sprint "&amp;$N147)&amp;" -&gt; Sprint "&amp;$AD147,"")</f>
       </c>
       <c r="AI147" s="201">
         <f>IF($AF147,$N147*100000+ROW(),"")</f>
@@ -39910,7 +39918,7 @@
         <f>IF($C148,IF(LEN(TRIM($AN148))=0,"—",TRIM($AN148)),"")</f>
       </c>
       <c r="AD148" s="201">
-        <f>IF($C148,IF($N148=9999,9999,IF($J148="Completado",$N148,MAX($N148,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C148,IF($N148=9999,9999,IF($J148="Completado",$N148,MAX($N148,'Historial de Sprints'!$C$7)+N('Postergar'!$F148))),"")</f>
       </c>
       <c r="AE148" s="201">
         <f>IF($C148,IF($AD148=9999,"(Sin sprint)",$AD148),"")</f>
@@ -39922,7 +39930,7 @@
         <f>IF($AF148,'Historial de Sprints'!$C$5+$N148*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH148" s="202">
-        <f>IF($AF148,"No completada al cierre del Sprint "&amp;$N148&amp;" -&gt; reasignada al Sprint "&amp;$AD148,"")</f>
+        <f>IF($AF148,IF('Postergar'!$G148&lt;&gt;"",'Postergar'!$G148,"No completada al cierre del Sprint "&amp;$N148)&amp;" -&gt; Sprint "&amp;$AD148,"")</f>
       </c>
       <c r="AI148" s="201">
         <f>IF($AF148,$N148*100000+ROW(),"")</f>
@@ -40026,7 +40034,7 @@
         <f>IF($C149,IF(LEN(TRIM($AN149))=0,"—",TRIM($AN149)),"")</f>
       </c>
       <c r="AD149" s="201">
-        <f>IF($C149,IF($N149=9999,9999,IF($J149="Completado",$N149,MAX($N149,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C149,IF($N149=9999,9999,IF($J149="Completado",$N149,MAX($N149,'Historial de Sprints'!$C$7)+N('Postergar'!$F149))),"")</f>
       </c>
       <c r="AE149" s="201">
         <f>IF($C149,IF($AD149=9999,"(Sin sprint)",$AD149),"")</f>
@@ -40038,7 +40046,7 @@
         <f>IF($AF149,'Historial de Sprints'!$C$5+$N149*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH149" s="202">
-        <f>IF($AF149,"No completada al cierre del Sprint "&amp;$N149&amp;" -&gt; reasignada al Sprint "&amp;$AD149,"")</f>
+        <f>IF($AF149,IF('Postergar'!$G149&lt;&gt;"",'Postergar'!$G149,"No completada al cierre del Sprint "&amp;$N149)&amp;" -&gt; Sprint "&amp;$AD149,"")</f>
       </c>
       <c r="AI149" s="201">
         <f>IF($AF149,$N149*100000+ROW(),"")</f>
@@ -40142,7 +40150,7 @@
         <f>IF($C150,IF(LEN(TRIM($AN150))=0,"—",TRIM($AN150)),"")</f>
       </c>
       <c r="AD150" s="201">
-        <f>IF($C150,IF($N150=9999,9999,IF($J150="Completado",$N150,MAX($N150,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C150,IF($N150=9999,9999,IF($J150="Completado",$N150,MAX($N150,'Historial de Sprints'!$C$7)+N('Postergar'!$F150))),"")</f>
       </c>
       <c r="AE150" s="201">
         <f>IF($C150,IF($AD150=9999,"(Sin sprint)",$AD150),"")</f>
@@ -40154,7 +40162,7 @@
         <f>IF($AF150,'Historial de Sprints'!$C$5+$N150*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH150" s="202">
-        <f>IF($AF150,"No completada al cierre del Sprint "&amp;$N150&amp;" -&gt; reasignada al Sprint "&amp;$AD150,"")</f>
+        <f>IF($AF150,IF('Postergar'!$G150&lt;&gt;"",'Postergar'!$G150,"No completada al cierre del Sprint "&amp;$N150)&amp;" -&gt; Sprint "&amp;$AD150,"")</f>
       </c>
       <c r="AI150" s="201">
         <f>IF($AF150,$N150*100000+ROW(),"")</f>
@@ -40258,7 +40266,7 @@
         <f>IF($C151,IF(LEN(TRIM($AN151))=0,"—",TRIM($AN151)),"")</f>
       </c>
       <c r="AD151" s="201">
-        <f>IF($C151,IF($N151=9999,9999,IF($J151="Completado",$N151,MAX($N151,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C151,IF($N151=9999,9999,IF($J151="Completado",$N151,MAX($N151,'Historial de Sprints'!$C$7)+N('Postergar'!$F151))),"")</f>
       </c>
       <c r="AE151" s="201">
         <f>IF($C151,IF($AD151=9999,"(Sin sprint)",$AD151),"")</f>
@@ -40270,7 +40278,7 @@
         <f>IF($AF151,'Historial de Sprints'!$C$5+$N151*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH151" s="202">
-        <f>IF($AF151,"No completada al cierre del Sprint "&amp;$N151&amp;" -&gt; reasignada al Sprint "&amp;$AD151,"")</f>
+        <f>IF($AF151,IF('Postergar'!$G151&lt;&gt;"",'Postergar'!$G151,"No completada al cierre del Sprint "&amp;$N151)&amp;" -&gt; Sprint "&amp;$AD151,"")</f>
       </c>
       <c r="AI151" s="201">
         <f>IF($AF151,$N151*100000+ROW(),"")</f>
@@ -40374,7 +40382,7 @@
         <f>IF($C152,IF(LEN(TRIM($AN152))=0,"—",TRIM($AN152)),"")</f>
       </c>
       <c r="AD152" s="201">
-        <f>IF($C152,IF($N152=9999,9999,IF($J152="Completado",$N152,MAX($N152,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C152,IF($N152=9999,9999,IF($J152="Completado",$N152,MAX($N152,'Historial de Sprints'!$C$7)+N('Postergar'!$F152))),"")</f>
       </c>
       <c r="AE152" s="201">
         <f>IF($C152,IF($AD152=9999,"(Sin sprint)",$AD152),"")</f>
@@ -40386,7 +40394,7 @@
         <f>IF($AF152,'Historial de Sprints'!$C$5+$N152*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH152" s="202">
-        <f>IF($AF152,"No completada al cierre del Sprint "&amp;$N152&amp;" -&gt; reasignada al Sprint "&amp;$AD152,"")</f>
+        <f>IF($AF152,IF('Postergar'!$G152&lt;&gt;"",'Postergar'!$G152,"No completada al cierre del Sprint "&amp;$N152)&amp;" -&gt; Sprint "&amp;$AD152,"")</f>
       </c>
       <c r="AI152" s="201">
         <f>IF($AF152,$N152*100000+ROW(),"")</f>
@@ -40490,7 +40498,7 @@
         <f>IF($C153,IF(LEN(TRIM($AN153))=0,"—",TRIM($AN153)),"")</f>
       </c>
       <c r="AD153" s="201">
-        <f>IF($C153,IF($N153=9999,9999,IF($J153="Completado",$N153,MAX($N153,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C153,IF($N153=9999,9999,IF($J153="Completado",$N153,MAX($N153,'Historial de Sprints'!$C$7)+N('Postergar'!$F153))),"")</f>
       </c>
       <c r="AE153" s="201">
         <f>IF($C153,IF($AD153=9999,"(Sin sprint)",$AD153),"")</f>
@@ -40502,7 +40510,7 @@
         <f>IF($AF153,'Historial de Sprints'!$C$5+$N153*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH153" s="202">
-        <f>IF($AF153,"No completada al cierre del Sprint "&amp;$N153&amp;" -&gt; reasignada al Sprint "&amp;$AD153,"")</f>
+        <f>IF($AF153,IF('Postergar'!$G153&lt;&gt;"",'Postergar'!$G153,"No completada al cierre del Sprint "&amp;$N153)&amp;" -&gt; Sprint "&amp;$AD153,"")</f>
       </c>
       <c r="AI153" s="201">
         <f>IF($AF153,$N153*100000+ROW(),"")</f>
@@ -40606,7 +40614,7 @@
         <f>IF($C154,IF(LEN(TRIM($AN154))=0,"—",TRIM($AN154)),"")</f>
       </c>
       <c r="AD154" s="201">
-        <f>IF($C154,IF($N154=9999,9999,IF($J154="Completado",$N154,MAX($N154,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C154,IF($N154=9999,9999,IF($J154="Completado",$N154,MAX($N154,'Historial de Sprints'!$C$7)+N('Postergar'!$F154))),"")</f>
       </c>
       <c r="AE154" s="201">
         <f>IF($C154,IF($AD154=9999,"(Sin sprint)",$AD154),"")</f>
@@ -40618,7 +40626,7 @@
         <f>IF($AF154,'Historial de Sprints'!$C$5+$N154*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH154" s="202">
-        <f>IF($AF154,"No completada al cierre del Sprint "&amp;$N154&amp;" -&gt; reasignada al Sprint "&amp;$AD154,"")</f>
+        <f>IF($AF154,IF('Postergar'!$G154&lt;&gt;"",'Postergar'!$G154,"No completada al cierre del Sprint "&amp;$N154)&amp;" -&gt; Sprint "&amp;$AD154,"")</f>
       </c>
       <c r="AI154" s="201">
         <f>IF($AF154,$N154*100000+ROW(),"")</f>
@@ -40722,7 +40730,7 @@
         <f>IF($C155,IF(LEN(TRIM($AN155))=0,"—",TRIM($AN155)),"")</f>
       </c>
       <c r="AD155" s="201">
-        <f>IF($C155,IF($N155=9999,9999,IF($J155="Completado",$N155,MAX($N155,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C155,IF($N155=9999,9999,IF($J155="Completado",$N155,MAX($N155,'Historial de Sprints'!$C$7)+N('Postergar'!$F155))),"")</f>
       </c>
       <c r="AE155" s="201">
         <f>IF($C155,IF($AD155=9999,"(Sin sprint)",$AD155),"")</f>
@@ -40734,7 +40742,7 @@
         <f>IF($AF155,'Historial de Sprints'!$C$5+$N155*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH155" s="202">
-        <f>IF($AF155,"No completada al cierre del Sprint "&amp;$N155&amp;" -&gt; reasignada al Sprint "&amp;$AD155,"")</f>
+        <f>IF($AF155,IF('Postergar'!$G155&lt;&gt;"",'Postergar'!$G155,"No completada al cierre del Sprint "&amp;$N155)&amp;" -&gt; Sprint "&amp;$AD155,"")</f>
       </c>
       <c r="AI155" s="201">
         <f>IF($AF155,$N155*100000+ROW(),"")</f>
@@ -40838,7 +40846,7 @@
         <f>IF($C156,IF(LEN(TRIM($AN156))=0,"—",TRIM($AN156)),"")</f>
       </c>
       <c r="AD156" s="201">
-        <f>IF($C156,IF($N156=9999,9999,IF($J156="Completado",$N156,MAX($N156,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C156,IF($N156=9999,9999,IF($J156="Completado",$N156,MAX($N156,'Historial de Sprints'!$C$7)+N('Postergar'!$F156))),"")</f>
       </c>
       <c r="AE156" s="201">
         <f>IF($C156,IF($AD156=9999,"(Sin sprint)",$AD156),"")</f>
@@ -40850,7 +40858,7 @@
         <f>IF($AF156,'Historial de Sprints'!$C$5+$N156*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH156" s="202">
-        <f>IF($AF156,"No completada al cierre del Sprint "&amp;$N156&amp;" -&gt; reasignada al Sprint "&amp;$AD156,"")</f>
+        <f>IF($AF156,IF('Postergar'!$G156&lt;&gt;"",'Postergar'!$G156,"No completada al cierre del Sprint "&amp;$N156)&amp;" -&gt; Sprint "&amp;$AD156,"")</f>
       </c>
       <c r="AI156" s="201">
         <f>IF($AF156,$N156*100000+ROW(),"")</f>
@@ -40954,7 +40962,7 @@
         <f>IF($C157,IF(LEN(TRIM($AN157))=0,"—",TRIM($AN157)),"")</f>
       </c>
       <c r="AD157" s="201">
-        <f>IF($C157,IF($N157=9999,9999,IF($J157="Completado",$N157,MAX($N157,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C157,IF($N157=9999,9999,IF($J157="Completado",$N157,MAX($N157,'Historial de Sprints'!$C$7)+N('Postergar'!$F157))),"")</f>
       </c>
       <c r="AE157" s="201">
         <f>IF($C157,IF($AD157=9999,"(Sin sprint)",$AD157),"")</f>
@@ -40966,7 +40974,7 @@
         <f>IF($AF157,'Historial de Sprints'!$C$5+$N157*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH157" s="202">
-        <f>IF($AF157,"No completada al cierre del Sprint "&amp;$N157&amp;" -&gt; reasignada al Sprint "&amp;$AD157,"")</f>
+        <f>IF($AF157,IF('Postergar'!$G157&lt;&gt;"",'Postergar'!$G157,"No completada al cierre del Sprint "&amp;$N157)&amp;" -&gt; Sprint "&amp;$AD157,"")</f>
       </c>
       <c r="AI157" s="201">
         <f>IF($AF157,$N157*100000+ROW(),"")</f>
@@ -41070,7 +41078,7 @@
         <f>IF($C158,IF(LEN(TRIM($AN158))=0,"—",TRIM($AN158)),"")</f>
       </c>
       <c r="AD158" s="201">
-        <f>IF($C158,IF($N158=9999,9999,IF($J158="Completado",$N158,MAX($N158,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C158,IF($N158=9999,9999,IF($J158="Completado",$N158,MAX($N158,'Historial de Sprints'!$C$7)+N('Postergar'!$F158))),"")</f>
       </c>
       <c r="AE158" s="201">
         <f>IF($C158,IF($AD158=9999,"(Sin sprint)",$AD158),"")</f>
@@ -41082,7 +41090,7 @@
         <f>IF($AF158,'Historial de Sprints'!$C$5+$N158*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH158" s="202">
-        <f>IF($AF158,"No completada al cierre del Sprint "&amp;$N158&amp;" -&gt; reasignada al Sprint "&amp;$AD158,"")</f>
+        <f>IF($AF158,IF('Postergar'!$G158&lt;&gt;"",'Postergar'!$G158,"No completada al cierre del Sprint "&amp;$N158)&amp;" -&gt; Sprint "&amp;$AD158,"")</f>
       </c>
       <c r="AI158" s="201">
         <f>IF($AF158,$N158*100000+ROW(),"")</f>
@@ -41186,7 +41194,7 @@
         <f>IF($C159,IF(LEN(TRIM($AN159))=0,"—",TRIM($AN159)),"")</f>
       </c>
       <c r="AD159" s="201">
-        <f>IF($C159,IF($N159=9999,9999,IF($J159="Completado",$N159,MAX($N159,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C159,IF($N159=9999,9999,IF($J159="Completado",$N159,MAX($N159,'Historial de Sprints'!$C$7)+N('Postergar'!$F159))),"")</f>
       </c>
       <c r="AE159" s="201">
         <f>IF($C159,IF($AD159=9999,"(Sin sprint)",$AD159),"")</f>
@@ -41198,7 +41206,7 @@
         <f>IF($AF159,'Historial de Sprints'!$C$5+$N159*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH159" s="202">
-        <f>IF($AF159,"No completada al cierre del Sprint "&amp;$N159&amp;" -&gt; reasignada al Sprint "&amp;$AD159,"")</f>
+        <f>IF($AF159,IF('Postergar'!$G159&lt;&gt;"",'Postergar'!$G159,"No completada al cierre del Sprint "&amp;$N159)&amp;" -&gt; Sprint "&amp;$AD159,"")</f>
       </c>
       <c r="AI159" s="201">
         <f>IF($AF159,$N159*100000+ROW(),"")</f>
@@ -41302,7 +41310,7 @@
         <f>IF($C160,IF(LEN(TRIM($AN160))=0,"—",TRIM($AN160)),"")</f>
       </c>
       <c r="AD160" s="201">
-        <f>IF($C160,IF($N160=9999,9999,IF($J160="Completado",$N160,MAX($N160,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C160,IF($N160=9999,9999,IF($J160="Completado",$N160,MAX($N160,'Historial de Sprints'!$C$7)+N('Postergar'!$F160))),"")</f>
       </c>
       <c r="AE160" s="201">
         <f>IF($C160,IF($AD160=9999,"(Sin sprint)",$AD160),"")</f>
@@ -41314,7 +41322,7 @@
         <f>IF($AF160,'Historial de Sprints'!$C$5+$N160*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH160" s="202">
-        <f>IF($AF160,"No completada al cierre del Sprint "&amp;$N160&amp;" -&gt; reasignada al Sprint "&amp;$AD160,"")</f>
+        <f>IF($AF160,IF('Postergar'!$G160&lt;&gt;"",'Postergar'!$G160,"No completada al cierre del Sprint "&amp;$N160)&amp;" -&gt; Sprint "&amp;$AD160,"")</f>
       </c>
       <c r="AI160" s="201">
         <f>IF($AF160,$N160*100000+ROW(),"")</f>
@@ -41418,7 +41426,7 @@
         <f>IF($C161,IF(LEN(TRIM($AN161))=0,"—",TRIM($AN161)),"")</f>
       </c>
       <c r="AD161" s="201">
-        <f>IF($C161,IF($N161=9999,9999,IF($J161="Completado",$N161,MAX($N161,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C161,IF($N161=9999,9999,IF($J161="Completado",$N161,MAX($N161,'Historial de Sprints'!$C$7)+N('Postergar'!$F161))),"")</f>
       </c>
       <c r="AE161" s="201">
         <f>IF($C161,IF($AD161=9999,"(Sin sprint)",$AD161),"")</f>
@@ -41430,7 +41438,7 @@
         <f>IF($AF161,'Historial de Sprints'!$C$5+$N161*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH161" s="202">
-        <f>IF($AF161,"No completada al cierre del Sprint "&amp;$N161&amp;" -&gt; reasignada al Sprint "&amp;$AD161,"")</f>
+        <f>IF($AF161,IF('Postergar'!$G161&lt;&gt;"",'Postergar'!$G161,"No completada al cierre del Sprint "&amp;$N161)&amp;" -&gt; Sprint "&amp;$AD161,"")</f>
       </c>
       <c r="AI161" s="201">
         <f>IF($AF161,$N161*100000+ROW(),"")</f>
@@ -41534,7 +41542,7 @@
         <f>IF($C162,IF(LEN(TRIM($AN162))=0,"—",TRIM($AN162)),"")</f>
       </c>
       <c r="AD162" s="201">
-        <f>IF($C162,IF($N162=9999,9999,IF($J162="Completado",$N162,MAX($N162,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C162,IF($N162=9999,9999,IF($J162="Completado",$N162,MAX($N162,'Historial de Sprints'!$C$7)+N('Postergar'!$F162))),"")</f>
       </c>
       <c r="AE162" s="201">
         <f>IF($C162,IF($AD162=9999,"(Sin sprint)",$AD162),"")</f>
@@ -41546,7 +41554,7 @@
         <f>IF($AF162,'Historial de Sprints'!$C$5+$N162*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH162" s="202">
-        <f>IF($AF162,"No completada al cierre del Sprint "&amp;$N162&amp;" -&gt; reasignada al Sprint "&amp;$AD162,"")</f>
+        <f>IF($AF162,IF('Postergar'!$G162&lt;&gt;"",'Postergar'!$G162,"No completada al cierre del Sprint "&amp;$N162)&amp;" -&gt; Sprint "&amp;$AD162,"")</f>
       </c>
       <c r="AI162" s="201">
         <f>IF($AF162,$N162*100000+ROW(),"")</f>
@@ -41650,7 +41658,7 @@
         <f>IF($C163,IF(LEN(TRIM($AN163))=0,"—",TRIM($AN163)),"")</f>
       </c>
       <c r="AD163" s="201">
-        <f>IF($C163,IF($N163=9999,9999,IF($J163="Completado",$N163,MAX($N163,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C163,IF($N163=9999,9999,IF($J163="Completado",$N163,MAX($N163,'Historial de Sprints'!$C$7)+N('Postergar'!$F163))),"")</f>
       </c>
       <c r="AE163" s="201">
         <f>IF($C163,IF($AD163=9999,"(Sin sprint)",$AD163),"")</f>
@@ -41662,7 +41670,7 @@
         <f>IF($AF163,'Historial de Sprints'!$C$5+$N163*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH163" s="202">
-        <f>IF($AF163,"No completada al cierre del Sprint "&amp;$N163&amp;" -&gt; reasignada al Sprint "&amp;$AD163,"")</f>
+        <f>IF($AF163,IF('Postergar'!$G163&lt;&gt;"",'Postergar'!$G163,"No completada al cierre del Sprint "&amp;$N163)&amp;" -&gt; Sprint "&amp;$AD163,"")</f>
       </c>
       <c r="AI163" s="201">
         <f>IF($AF163,$N163*100000+ROW(),"")</f>
@@ -41766,7 +41774,7 @@
         <f>IF($C164,IF(LEN(TRIM($AN164))=0,"—",TRIM($AN164)),"")</f>
       </c>
       <c r="AD164" s="201">
-        <f>IF($C164,IF($N164=9999,9999,IF($J164="Completado",$N164,MAX($N164,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C164,IF($N164=9999,9999,IF($J164="Completado",$N164,MAX($N164,'Historial de Sprints'!$C$7)+N('Postergar'!$F164))),"")</f>
       </c>
       <c r="AE164" s="201">
         <f>IF($C164,IF($AD164=9999,"(Sin sprint)",$AD164),"")</f>
@@ -41778,7 +41786,7 @@
         <f>IF($AF164,'Historial de Sprints'!$C$5+$N164*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH164" s="202">
-        <f>IF($AF164,"No completada al cierre del Sprint "&amp;$N164&amp;" -&gt; reasignada al Sprint "&amp;$AD164,"")</f>
+        <f>IF($AF164,IF('Postergar'!$G164&lt;&gt;"",'Postergar'!$G164,"No completada al cierre del Sprint "&amp;$N164)&amp;" -&gt; Sprint "&amp;$AD164,"")</f>
       </c>
       <c r="AI164" s="201">
         <f>IF($AF164,$N164*100000+ROW(),"")</f>
@@ -41882,7 +41890,7 @@
         <f>IF($C165,IF(LEN(TRIM($AN165))=0,"—",TRIM($AN165)),"")</f>
       </c>
       <c r="AD165" s="201">
-        <f>IF($C165,IF($N165=9999,9999,IF($J165="Completado",$N165,MAX($N165,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C165,IF($N165=9999,9999,IF($J165="Completado",$N165,MAX($N165,'Historial de Sprints'!$C$7)+N('Postergar'!$F165))),"")</f>
       </c>
       <c r="AE165" s="201">
         <f>IF($C165,IF($AD165=9999,"(Sin sprint)",$AD165),"")</f>
@@ -41894,7 +41902,7 @@
         <f>IF($AF165,'Historial de Sprints'!$C$5+$N165*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH165" s="202">
-        <f>IF($AF165,"No completada al cierre del Sprint "&amp;$N165&amp;" -&gt; reasignada al Sprint "&amp;$AD165,"")</f>
+        <f>IF($AF165,IF('Postergar'!$G165&lt;&gt;"",'Postergar'!$G165,"No completada al cierre del Sprint "&amp;$N165)&amp;" -&gt; Sprint "&amp;$AD165,"")</f>
       </c>
       <c r="AI165" s="201">
         <f>IF($AF165,$N165*100000+ROW(),"")</f>
@@ -41998,7 +42006,7 @@
         <f>IF($C166,IF(LEN(TRIM($AN166))=0,"—",TRIM($AN166)),"")</f>
       </c>
       <c r="AD166" s="201">
-        <f>IF($C166,IF($N166=9999,9999,IF($J166="Completado",$N166,MAX($N166,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C166,IF($N166=9999,9999,IF($J166="Completado",$N166,MAX($N166,'Historial de Sprints'!$C$7)+N('Postergar'!$F166))),"")</f>
       </c>
       <c r="AE166" s="201">
         <f>IF($C166,IF($AD166=9999,"(Sin sprint)",$AD166),"")</f>
@@ -42010,7 +42018,7 @@
         <f>IF($AF166,'Historial de Sprints'!$C$5+$N166*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH166" s="202">
-        <f>IF($AF166,"No completada al cierre del Sprint "&amp;$N166&amp;" -&gt; reasignada al Sprint "&amp;$AD166,"")</f>
+        <f>IF($AF166,IF('Postergar'!$G166&lt;&gt;"",'Postergar'!$G166,"No completada al cierre del Sprint "&amp;$N166)&amp;" -&gt; Sprint "&amp;$AD166,"")</f>
       </c>
       <c r="AI166" s="201">
         <f>IF($AF166,$N166*100000+ROW(),"")</f>
@@ -42114,7 +42122,7 @@
         <f>IF($C167,IF(LEN(TRIM($AN167))=0,"—",TRIM($AN167)),"")</f>
       </c>
       <c r="AD167" s="201">
-        <f>IF($C167,IF($N167=9999,9999,IF($J167="Completado",$N167,MAX($N167,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C167,IF($N167=9999,9999,IF($J167="Completado",$N167,MAX($N167,'Historial de Sprints'!$C$7)+N('Postergar'!$F167))),"")</f>
       </c>
       <c r="AE167" s="201">
         <f>IF($C167,IF($AD167=9999,"(Sin sprint)",$AD167),"")</f>
@@ -42126,7 +42134,7 @@
         <f>IF($AF167,'Historial de Sprints'!$C$5+$N167*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH167" s="202">
-        <f>IF($AF167,"No completada al cierre del Sprint "&amp;$N167&amp;" -&gt; reasignada al Sprint "&amp;$AD167,"")</f>
+        <f>IF($AF167,IF('Postergar'!$G167&lt;&gt;"",'Postergar'!$G167,"No completada al cierre del Sprint "&amp;$N167)&amp;" -&gt; Sprint "&amp;$AD167,"")</f>
       </c>
       <c r="AI167" s="201">
         <f>IF($AF167,$N167*100000+ROW(),"")</f>
@@ -42230,7 +42238,7 @@
         <f>IF($C168,IF(LEN(TRIM($AN168))=0,"—",TRIM($AN168)),"")</f>
       </c>
       <c r="AD168" s="201">
-        <f>IF($C168,IF($N168=9999,9999,IF($J168="Completado",$N168,MAX($N168,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C168,IF($N168=9999,9999,IF($J168="Completado",$N168,MAX($N168,'Historial de Sprints'!$C$7)+N('Postergar'!$F168))),"")</f>
       </c>
       <c r="AE168" s="201">
         <f>IF($C168,IF($AD168=9999,"(Sin sprint)",$AD168),"")</f>
@@ -42242,7 +42250,7 @@
         <f>IF($AF168,'Historial de Sprints'!$C$5+$N168*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH168" s="202">
-        <f>IF($AF168,"No completada al cierre del Sprint "&amp;$N168&amp;" -&gt; reasignada al Sprint "&amp;$AD168,"")</f>
+        <f>IF($AF168,IF('Postergar'!$G168&lt;&gt;"",'Postergar'!$G168,"No completada al cierre del Sprint "&amp;$N168)&amp;" -&gt; Sprint "&amp;$AD168,"")</f>
       </c>
       <c r="AI168" s="201">
         <f>IF($AF168,$N168*100000+ROW(),"")</f>
@@ -42346,7 +42354,7 @@
         <f>IF($C169,IF(LEN(TRIM($AN169))=0,"—",TRIM($AN169)),"")</f>
       </c>
       <c r="AD169" s="201">
-        <f>IF($C169,IF($N169=9999,9999,IF($J169="Completado",$N169,MAX($N169,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C169,IF($N169=9999,9999,IF($J169="Completado",$N169,MAX($N169,'Historial de Sprints'!$C$7)+N('Postergar'!$F169))),"")</f>
       </c>
       <c r="AE169" s="201">
         <f>IF($C169,IF($AD169=9999,"(Sin sprint)",$AD169),"")</f>
@@ -42358,7 +42366,7 @@
         <f>IF($AF169,'Historial de Sprints'!$C$5+$N169*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH169" s="202">
-        <f>IF($AF169,"No completada al cierre del Sprint "&amp;$N169&amp;" -&gt; reasignada al Sprint "&amp;$AD169,"")</f>
+        <f>IF($AF169,IF('Postergar'!$G169&lt;&gt;"",'Postergar'!$G169,"No completada al cierre del Sprint "&amp;$N169)&amp;" -&gt; Sprint "&amp;$AD169,"")</f>
       </c>
       <c r="AI169" s="201">
         <f>IF($AF169,$N169*100000+ROW(),"")</f>
@@ -42462,7 +42470,7 @@
         <f>IF($C170,IF(LEN(TRIM($AN170))=0,"—",TRIM($AN170)),"")</f>
       </c>
       <c r="AD170" s="201">
-        <f>IF($C170,IF($N170=9999,9999,IF($J170="Completado",$N170,MAX($N170,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C170,IF($N170=9999,9999,IF($J170="Completado",$N170,MAX($N170,'Historial de Sprints'!$C$7)+N('Postergar'!$F170))),"")</f>
       </c>
       <c r="AE170" s="201">
         <f>IF($C170,IF($AD170=9999,"(Sin sprint)",$AD170),"")</f>
@@ -42474,7 +42482,7 @@
         <f>IF($AF170,'Historial de Sprints'!$C$5+$N170*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH170" s="202">
-        <f>IF($AF170,"No completada al cierre del Sprint "&amp;$N170&amp;" -&gt; reasignada al Sprint "&amp;$AD170,"")</f>
+        <f>IF($AF170,IF('Postergar'!$G170&lt;&gt;"",'Postergar'!$G170,"No completada al cierre del Sprint "&amp;$N170)&amp;" -&gt; Sprint "&amp;$AD170,"")</f>
       </c>
       <c r="AI170" s="201">
         <f>IF($AF170,$N170*100000+ROW(),"")</f>
@@ -42578,7 +42586,7 @@
         <f>IF($C171,IF(LEN(TRIM($AN171))=0,"—",TRIM($AN171)),"")</f>
       </c>
       <c r="AD171" s="201">
-        <f>IF($C171,IF($N171=9999,9999,IF($J171="Completado",$N171,MAX($N171,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C171,IF($N171=9999,9999,IF($J171="Completado",$N171,MAX($N171,'Historial de Sprints'!$C$7)+N('Postergar'!$F171))),"")</f>
       </c>
       <c r="AE171" s="201">
         <f>IF($C171,IF($AD171=9999,"(Sin sprint)",$AD171),"")</f>
@@ -42590,7 +42598,7 @@
         <f>IF($AF171,'Historial de Sprints'!$C$5+$N171*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH171" s="202">
-        <f>IF($AF171,"No completada al cierre del Sprint "&amp;$N171&amp;" -&gt; reasignada al Sprint "&amp;$AD171,"")</f>
+        <f>IF($AF171,IF('Postergar'!$G171&lt;&gt;"",'Postergar'!$G171,"No completada al cierre del Sprint "&amp;$N171)&amp;" -&gt; Sprint "&amp;$AD171,"")</f>
       </c>
       <c r="AI171" s="201">
         <f>IF($AF171,$N171*100000+ROW(),"")</f>
@@ -42694,7 +42702,7 @@
         <f>IF($C172,IF(LEN(TRIM($AN172))=0,"—",TRIM($AN172)),"")</f>
       </c>
       <c r="AD172" s="201">
-        <f>IF($C172,IF($N172=9999,9999,IF($J172="Completado",$N172,MAX($N172,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C172,IF($N172=9999,9999,IF($J172="Completado",$N172,MAX($N172,'Historial de Sprints'!$C$7)+N('Postergar'!$F172))),"")</f>
       </c>
       <c r="AE172" s="201">
         <f>IF($C172,IF($AD172=9999,"(Sin sprint)",$AD172),"")</f>
@@ -42706,7 +42714,7 @@
         <f>IF($AF172,'Historial de Sprints'!$C$5+$N172*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH172" s="202">
-        <f>IF($AF172,"No completada al cierre del Sprint "&amp;$N172&amp;" -&gt; reasignada al Sprint "&amp;$AD172,"")</f>
+        <f>IF($AF172,IF('Postergar'!$G172&lt;&gt;"",'Postergar'!$G172,"No completada al cierre del Sprint "&amp;$N172)&amp;" -&gt; Sprint "&amp;$AD172,"")</f>
       </c>
       <c r="AI172" s="201">
         <f>IF($AF172,$N172*100000+ROW(),"")</f>
@@ -42810,7 +42818,7 @@
         <f>IF($C173,IF(LEN(TRIM($AN173))=0,"—",TRIM($AN173)),"")</f>
       </c>
       <c r="AD173" s="201">
-        <f>IF($C173,IF($N173=9999,9999,IF($J173="Completado",$N173,MAX($N173,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C173,IF($N173=9999,9999,IF($J173="Completado",$N173,MAX($N173,'Historial de Sprints'!$C$7)+N('Postergar'!$F173))),"")</f>
       </c>
       <c r="AE173" s="201">
         <f>IF($C173,IF($AD173=9999,"(Sin sprint)",$AD173),"")</f>
@@ -42822,7 +42830,7 @@
         <f>IF($AF173,'Historial de Sprints'!$C$5+$N173*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH173" s="202">
-        <f>IF($AF173,"No completada al cierre del Sprint "&amp;$N173&amp;" -&gt; reasignada al Sprint "&amp;$AD173,"")</f>
+        <f>IF($AF173,IF('Postergar'!$G173&lt;&gt;"",'Postergar'!$G173,"No completada al cierre del Sprint "&amp;$N173)&amp;" -&gt; Sprint "&amp;$AD173,"")</f>
       </c>
       <c r="AI173" s="201">
         <f>IF($AF173,$N173*100000+ROW(),"")</f>
@@ -42926,7 +42934,7 @@
         <f>IF($C174,IF(LEN(TRIM($AN174))=0,"—",TRIM($AN174)),"")</f>
       </c>
       <c r="AD174" s="201">
-        <f>IF($C174,IF($N174=9999,9999,IF($J174="Completado",$N174,MAX($N174,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C174,IF($N174=9999,9999,IF($J174="Completado",$N174,MAX($N174,'Historial de Sprints'!$C$7)+N('Postergar'!$F174))),"")</f>
       </c>
       <c r="AE174" s="201">
         <f>IF($C174,IF($AD174=9999,"(Sin sprint)",$AD174),"")</f>
@@ -42938,7 +42946,7 @@
         <f>IF($AF174,'Historial de Sprints'!$C$5+$N174*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH174" s="202">
-        <f>IF($AF174,"No completada al cierre del Sprint "&amp;$N174&amp;" -&gt; reasignada al Sprint "&amp;$AD174,"")</f>
+        <f>IF($AF174,IF('Postergar'!$G174&lt;&gt;"",'Postergar'!$G174,"No completada al cierre del Sprint "&amp;$N174)&amp;" -&gt; Sprint "&amp;$AD174,"")</f>
       </c>
       <c r="AI174" s="201">
         <f>IF($AF174,$N174*100000+ROW(),"")</f>
@@ -43042,7 +43050,7 @@
         <f>IF($C175,IF(LEN(TRIM($AN175))=0,"—",TRIM($AN175)),"")</f>
       </c>
       <c r="AD175" s="201">
-        <f>IF($C175,IF($N175=9999,9999,IF($J175="Completado",$N175,MAX($N175,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C175,IF($N175=9999,9999,IF($J175="Completado",$N175,MAX($N175,'Historial de Sprints'!$C$7)+N('Postergar'!$F175))),"")</f>
       </c>
       <c r="AE175" s="201">
         <f>IF($C175,IF($AD175=9999,"(Sin sprint)",$AD175),"")</f>
@@ -43054,7 +43062,7 @@
         <f>IF($AF175,'Historial de Sprints'!$C$5+$N175*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH175" s="202">
-        <f>IF($AF175,"No completada al cierre del Sprint "&amp;$N175&amp;" -&gt; reasignada al Sprint "&amp;$AD175,"")</f>
+        <f>IF($AF175,IF('Postergar'!$G175&lt;&gt;"",'Postergar'!$G175,"No completada al cierre del Sprint "&amp;$N175)&amp;" -&gt; Sprint "&amp;$AD175,"")</f>
       </c>
       <c r="AI175" s="201">
         <f>IF($AF175,$N175*100000+ROW(),"")</f>
@@ -43158,7 +43166,7 @@
         <f>IF($C176,IF(LEN(TRIM($AN176))=0,"—",TRIM($AN176)),"")</f>
       </c>
       <c r="AD176" s="201">
-        <f>IF($C176,IF($N176=9999,9999,IF($J176="Completado",$N176,MAX($N176,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C176,IF($N176=9999,9999,IF($J176="Completado",$N176,MAX($N176,'Historial de Sprints'!$C$7)+N('Postergar'!$F176))),"")</f>
       </c>
       <c r="AE176" s="201">
         <f>IF($C176,IF($AD176=9999,"(Sin sprint)",$AD176),"")</f>
@@ -43170,7 +43178,7 @@
         <f>IF($AF176,'Historial de Sprints'!$C$5+$N176*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH176" s="202">
-        <f>IF($AF176,"No completada al cierre del Sprint "&amp;$N176&amp;" -&gt; reasignada al Sprint "&amp;$AD176,"")</f>
+        <f>IF($AF176,IF('Postergar'!$G176&lt;&gt;"",'Postergar'!$G176,"No completada al cierre del Sprint "&amp;$N176)&amp;" -&gt; Sprint "&amp;$AD176,"")</f>
       </c>
       <c r="AI176" s="201">
         <f>IF($AF176,$N176*100000+ROW(),"")</f>
@@ -43274,7 +43282,7 @@
         <f>IF($C177,IF(LEN(TRIM($AN177))=0,"—",TRIM($AN177)),"")</f>
       </c>
       <c r="AD177" s="201">
-        <f>IF($C177,IF($N177=9999,9999,IF($J177="Completado",$N177,MAX($N177,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C177,IF($N177=9999,9999,IF($J177="Completado",$N177,MAX($N177,'Historial de Sprints'!$C$7)+N('Postergar'!$F177))),"")</f>
       </c>
       <c r="AE177" s="201">
         <f>IF($C177,IF($AD177=9999,"(Sin sprint)",$AD177),"")</f>
@@ -43286,7 +43294,7 @@
         <f>IF($AF177,'Historial de Sprints'!$C$5+$N177*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH177" s="202">
-        <f>IF($AF177,"No completada al cierre del Sprint "&amp;$N177&amp;" -&gt; reasignada al Sprint "&amp;$AD177,"")</f>
+        <f>IF($AF177,IF('Postergar'!$G177&lt;&gt;"",'Postergar'!$G177,"No completada al cierre del Sprint "&amp;$N177)&amp;" -&gt; Sprint "&amp;$AD177,"")</f>
       </c>
       <c r="AI177" s="201">
         <f>IF($AF177,$N177*100000+ROW(),"")</f>
@@ -43390,7 +43398,7 @@
         <f>IF($C178,IF(LEN(TRIM($AN178))=0,"—",TRIM($AN178)),"")</f>
       </c>
       <c r="AD178" s="201">
-        <f>IF($C178,IF($N178=9999,9999,IF($J178="Completado",$N178,MAX($N178,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C178,IF($N178=9999,9999,IF($J178="Completado",$N178,MAX($N178,'Historial de Sprints'!$C$7)+N('Postergar'!$F178))),"")</f>
       </c>
       <c r="AE178" s="201">
         <f>IF($C178,IF($AD178=9999,"(Sin sprint)",$AD178),"")</f>
@@ -43402,7 +43410,7 @@
         <f>IF($AF178,'Historial de Sprints'!$C$5+$N178*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH178" s="202">
-        <f>IF($AF178,"No completada al cierre del Sprint "&amp;$N178&amp;" -&gt; reasignada al Sprint "&amp;$AD178,"")</f>
+        <f>IF($AF178,IF('Postergar'!$G178&lt;&gt;"",'Postergar'!$G178,"No completada al cierre del Sprint "&amp;$N178)&amp;" -&gt; Sprint "&amp;$AD178,"")</f>
       </c>
       <c r="AI178" s="201">
         <f>IF($AF178,$N178*100000+ROW(),"")</f>
@@ -43506,7 +43514,7 @@
         <f>IF($C179,IF(LEN(TRIM($AN179))=0,"—",TRIM($AN179)),"")</f>
       </c>
       <c r="AD179" s="201">
-        <f>IF($C179,IF($N179=9999,9999,IF($J179="Completado",$N179,MAX($N179,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C179,IF($N179=9999,9999,IF($J179="Completado",$N179,MAX($N179,'Historial de Sprints'!$C$7)+N('Postergar'!$F179))),"")</f>
       </c>
       <c r="AE179" s="201">
         <f>IF($C179,IF($AD179=9999,"(Sin sprint)",$AD179),"")</f>
@@ -43518,7 +43526,7 @@
         <f>IF($AF179,'Historial de Sprints'!$C$5+$N179*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH179" s="202">
-        <f>IF($AF179,"No completada al cierre del Sprint "&amp;$N179&amp;" -&gt; reasignada al Sprint "&amp;$AD179,"")</f>
+        <f>IF($AF179,IF('Postergar'!$G179&lt;&gt;"",'Postergar'!$G179,"No completada al cierre del Sprint "&amp;$N179)&amp;" -&gt; Sprint "&amp;$AD179,"")</f>
       </c>
       <c r="AI179" s="201">
         <f>IF($AF179,$N179*100000+ROW(),"")</f>
@@ -43622,7 +43630,7 @@
         <f>IF($C180,IF(LEN(TRIM($AN180))=0,"—",TRIM($AN180)),"")</f>
       </c>
       <c r="AD180" s="201">
-        <f>IF($C180,IF($N180=9999,9999,IF($J180="Completado",$N180,MAX($N180,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C180,IF($N180=9999,9999,IF($J180="Completado",$N180,MAX($N180,'Historial de Sprints'!$C$7)+N('Postergar'!$F180))),"")</f>
       </c>
       <c r="AE180" s="201">
         <f>IF($C180,IF($AD180=9999,"(Sin sprint)",$AD180),"")</f>
@@ -43634,7 +43642,7 @@
         <f>IF($AF180,'Historial de Sprints'!$C$5+$N180*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH180" s="202">
-        <f>IF($AF180,"No completada al cierre del Sprint "&amp;$N180&amp;" -&gt; reasignada al Sprint "&amp;$AD180,"")</f>
+        <f>IF($AF180,IF('Postergar'!$G180&lt;&gt;"",'Postergar'!$G180,"No completada al cierre del Sprint "&amp;$N180)&amp;" -&gt; Sprint "&amp;$AD180,"")</f>
       </c>
       <c r="AI180" s="201">
         <f>IF($AF180,$N180*100000+ROW(),"")</f>
@@ -43738,7 +43746,7 @@
         <f>IF($C181,IF(LEN(TRIM($AN181))=0,"—",TRIM($AN181)),"")</f>
       </c>
       <c r="AD181" s="201">
-        <f>IF($C181,IF($N181=9999,9999,IF($J181="Completado",$N181,MAX($N181,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C181,IF($N181=9999,9999,IF($J181="Completado",$N181,MAX($N181,'Historial de Sprints'!$C$7)+N('Postergar'!$F181))),"")</f>
       </c>
       <c r="AE181" s="201">
         <f>IF($C181,IF($AD181=9999,"(Sin sprint)",$AD181),"")</f>
@@ -43750,7 +43758,7 @@
         <f>IF($AF181,'Historial de Sprints'!$C$5+$N181*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH181" s="202">
-        <f>IF($AF181,"No completada al cierre del Sprint "&amp;$N181&amp;" -&gt; reasignada al Sprint "&amp;$AD181,"")</f>
+        <f>IF($AF181,IF('Postergar'!$G181&lt;&gt;"",'Postergar'!$G181,"No completada al cierre del Sprint "&amp;$N181)&amp;" -&gt; Sprint "&amp;$AD181,"")</f>
       </c>
       <c r="AI181" s="201">
         <f>IF($AF181,$N181*100000+ROW(),"")</f>
@@ -43854,7 +43862,7 @@
         <f>IF($C182,IF(LEN(TRIM($AN182))=0,"—",TRIM($AN182)),"")</f>
       </c>
       <c r="AD182" s="201">
-        <f>IF($C182,IF($N182=9999,9999,IF($J182="Completado",$N182,MAX($N182,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C182,IF($N182=9999,9999,IF($J182="Completado",$N182,MAX($N182,'Historial de Sprints'!$C$7)+N('Postergar'!$F182))),"")</f>
       </c>
       <c r="AE182" s="201">
         <f>IF($C182,IF($AD182=9999,"(Sin sprint)",$AD182),"")</f>
@@ -43866,7 +43874,7 @@
         <f>IF($AF182,'Historial de Sprints'!$C$5+$N182*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH182" s="202">
-        <f>IF($AF182,"No completada al cierre del Sprint "&amp;$N182&amp;" -&gt; reasignada al Sprint "&amp;$AD182,"")</f>
+        <f>IF($AF182,IF('Postergar'!$G182&lt;&gt;"",'Postergar'!$G182,"No completada al cierre del Sprint "&amp;$N182)&amp;" -&gt; Sprint "&amp;$AD182,"")</f>
       </c>
       <c r="AI182" s="201">
         <f>IF($AF182,$N182*100000+ROW(),"")</f>
@@ -43970,7 +43978,7 @@
         <f>IF($C183,IF(LEN(TRIM($AN183))=0,"—",TRIM($AN183)),"")</f>
       </c>
       <c r="AD183" s="201">
-        <f>IF($C183,IF($N183=9999,9999,IF($J183="Completado",$N183,MAX($N183,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C183,IF($N183=9999,9999,IF($J183="Completado",$N183,MAX($N183,'Historial de Sprints'!$C$7)+N('Postergar'!$F183))),"")</f>
       </c>
       <c r="AE183" s="201">
         <f>IF($C183,IF($AD183=9999,"(Sin sprint)",$AD183),"")</f>
@@ -43982,7 +43990,7 @@
         <f>IF($AF183,'Historial de Sprints'!$C$5+$N183*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH183" s="202">
-        <f>IF($AF183,"No completada al cierre del Sprint "&amp;$N183&amp;" -&gt; reasignada al Sprint "&amp;$AD183,"")</f>
+        <f>IF($AF183,IF('Postergar'!$G183&lt;&gt;"",'Postergar'!$G183,"No completada al cierre del Sprint "&amp;$N183)&amp;" -&gt; Sprint "&amp;$AD183,"")</f>
       </c>
       <c r="AI183" s="201">
         <f>IF($AF183,$N183*100000+ROW(),"")</f>
@@ -44086,7 +44094,7 @@
         <f>IF($C184,IF(LEN(TRIM($AN184))=0,"—",TRIM($AN184)),"")</f>
       </c>
       <c r="AD184" s="201">
-        <f>IF($C184,IF($N184=9999,9999,IF($J184="Completado",$N184,MAX($N184,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C184,IF($N184=9999,9999,IF($J184="Completado",$N184,MAX($N184,'Historial de Sprints'!$C$7)+N('Postergar'!$F184))),"")</f>
       </c>
       <c r="AE184" s="201">
         <f>IF($C184,IF($AD184=9999,"(Sin sprint)",$AD184),"")</f>
@@ -44098,7 +44106,7 @@
         <f>IF($AF184,'Historial de Sprints'!$C$5+$N184*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH184" s="202">
-        <f>IF($AF184,"No completada al cierre del Sprint "&amp;$N184&amp;" -&gt; reasignada al Sprint "&amp;$AD184,"")</f>
+        <f>IF($AF184,IF('Postergar'!$G184&lt;&gt;"",'Postergar'!$G184,"No completada al cierre del Sprint "&amp;$N184)&amp;" -&gt; Sprint "&amp;$AD184,"")</f>
       </c>
       <c r="AI184" s="201">
         <f>IF($AF184,$N184*100000+ROW(),"")</f>
@@ -44202,7 +44210,7 @@
         <f>IF($C185,IF(LEN(TRIM($AN185))=0,"—",TRIM($AN185)),"")</f>
       </c>
       <c r="AD185" s="201">
-        <f>IF($C185,IF($N185=9999,9999,IF($J185="Completado",$N185,MAX($N185,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C185,IF($N185=9999,9999,IF($J185="Completado",$N185,MAX($N185,'Historial de Sprints'!$C$7)+N('Postergar'!$F185))),"")</f>
       </c>
       <c r="AE185" s="201">
         <f>IF($C185,IF($AD185=9999,"(Sin sprint)",$AD185),"")</f>
@@ -44214,7 +44222,7 @@
         <f>IF($AF185,'Historial de Sprints'!$C$5+$N185*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH185" s="202">
-        <f>IF($AF185,"No completada al cierre del Sprint "&amp;$N185&amp;" -&gt; reasignada al Sprint "&amp;$AD185,"")</f>
+        <f>IF($AF185,IF('Postergar'!$G185&lt;&gt;"",'Postergar'!$G185,"No completada al cierre del Sprint "&amp;$N185)&amp;" -&gt; Sprint "&amp;$AD185,"")</f>
       </c>
       <c r="AI185" s="201">
         <f>IF($AF185,$N185*100000+ROW(),"")</f>
@@ -44318,7 +44326,7 @@
         <f>IF($C186,IF(LEN(TRIM($AN186))=0,"—",TRIM($AN186)),"")</f>
       </c>
       <c r="AD186" s="201">
-        <f>IF($C186,IF($N186=9999,9999,IF($J186="Completado",$N186,MAX($N186,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C186,IF($N186=9999,9999,IF($J186="Completado",$N186,MAX($N186,'Historial de Sprints'!$C$7)+N('Postergar'!$F186))),"")</f>
       </c>
       <c r="AE186" s="201">
         <f>IF($C186,IF($AD186=9999,"(Sin sprint)",$AD186),"")</f>
@@ -44330,7 +44338,7 @@
         <f>IF($AF186,'Historial de Sprints'!$C$5+$N186*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH186" s="202">
-        <f>IF($AF186,"No completada al cierre del Sprint "&amp;$N186&amp;" -&gt; reasignada al Sprint "&amp;$AD186,"")</f>
+        <f>IF($AF186,IF('Postergar'!$G186&lt;&gt;"",'Postergar'!$G186,"No completada al cierre del Sprint "&amp;$N186)&amp;" -&gt; Sprint "&amp;$AD186,"")</f>
       </c>
       <c r="AI186" s="201">
         <f>IF($AF186,$N186*100000+ROW(),"")</f>
@@ -44434,7 +44442,7 @@
         <f>IF($C187,IF(LEN(TRIM($AN187))=0,"—",TRIM($AN187)),"")</f>
       </c>
       <c r="AD187" s="201">
-        <f>IF($C187,IF($N187=9999,9999,IF($J187="Completado",$N187,MAX($N187,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C187,IF($N187=9999,9999,IF($J187="Completado",$N187,MAX($N187,'Historial de Sprints'!$C$7)+N('Postergar'!$F187))),"")</f>
       </c>
       <c r="AE187" s="201">
         <f>IF($C187,IF($AD187=9999,"(Sin sprint)",$AD187),"")</f>
@@ -44446,7 +44454,7 @@
         <f>IF($AF187,'Historial de Sprints'!$C$5+$N187*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH187" s="202">
-        <f>IF($AF187,"No completada al cierre del Sprint "&amp;$N187&amp;" -&gt; reasignada al Sprint "&amp;$AD187,"")</f>
+        <f>IF($AF187,IF('Postergar'!$G187&lt;&gt;"",'Postergar'!$G187,"No completada al cierre del Sprint "&amp;$N187)&amp;" -&gt; Sprint "&amp;$AD187,"")</f>
       </c>
       <c r="AI187" s="201">
         <f>IF($AF187,$N187*100000+ROW(),"")</f>
@@ -44550,7 +44558,7 @@
         <f>IF($C188,IF(LEN(TRIM($AN188))=0,"—",TRIM($AN188)),"")</f>
       </c>
       <c r="AD188" s="201">
-        <f>IF($C188,IF($N188=9999,9999,IF($J188="Completado",$N188,MAX($N188,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C188,IF($N188=9999,9999,IF($J188="Completado",$N188,MAX($N188,'Historial de Sprints'!$C$7)+N('Postergar'!$F188))),"")</f>
       </c>
       <c r="AE188" s="201">
         <f>IF($C188,IF($AD188=9999,"(Sin sprint)",$AD188),"")</f>
@@ -44562,7 +44570,7 @@
         <f>IF($AF188,'Historial de Sprints'!$C$5+$N188*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH188" s="202">
-        <f>IF($AF188,"No completada al cierre del Sprint "&amp;$N188&amp;" -&gt; reasignada al Sprint "&amp;$AD188,"")</f>
+        <f>IF($AF188,IF('Postergar'!$G188&lt;&gt;"",'Postergar'!$G188,"No completada al cierre del Sprint "&amp;$N188)&amp;" -&gt; Sprint "&amp;$AD188,"")</f>
       </c>
       <c r="AI188" s="201">
         <f>IF($AF188,$N188*100000+ROW(),"")</f>
@@ -44666,7 +44674,7 @@
         <f>IF($C189,IF(LEN(TRIM($AN189))=0,"—",TRIM($AN189)),"")</f>
       </c>
       <c r="AD189" s="201">
-        <f>IF($C189,IF($N189=9999,9999,IF($J189="Completado",$N189,MAX($N189,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C189,IF($N189=9999,9999,IF($J189="Completado",$N189,MAX($N189,'Historial de Sprints'!$C$7)+N('Postergar'!$F189))),"")</f>
       </c>
       <c r="AE189" s="201">
         <f>IF($C189,IF($AD189=9999,"(Sin sprint)",$AD189),"")</f>
@@ -44678,7 +44686,7 @@
         <f>IF($AF189,'Historial de Sprints'!$C$5+$N189*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH189" s="202">
-        <f>IF($AF189,"No completada al cierre del Sprint "&amp;$N189&amp;" -&gt; reasignada al Sprint "&amp;$AD189,"")</f>
+        <f>IF($AF189,IF('Postergar'!$G189&lt;&gt;"",'Postergar'!$G189,"No completada al cierre del Sprint "&amp;$N189)&amp;" -&gt; Sprint "&amp;$AD189,"")</f>
       </c>
       <c r="AI189" s="201">
         <f>IF($AF189,$N189*100000+ROW(),"")</f>
@@ -44782,7 +44790,7 @@
         <f>IF($C190,IF(LEN(TRIM($AN190))=0,"—",TRIM($AN190)),"")</f>
       </c>
       <c r="AD190" s="201">
-        <f>IF($C190,IF($N190=9999,9999,IF($J190="Completado",$N190,MAX($N190,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C190,IF($N190=9999,9999,IF($J190="Completado",$N190,MAX($N190,'Historial de Sprints'!$C$7)+N('Postergar'!$F190))),"")</f>
       </c>
       <c r="AE190" s="201">
         <f>IF($C190,IF($AD190=9999,"(Sin sprint)",$AD190),"")</f>
@@ -44794,7 +44802,7 @@
         <f>IF($AF190,'Historial de Sprints'!$C$5+$N190*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH190" s="202">
-        <f>IF($AF190,"No completada al cierre del Sprint "&amp;$N190&amp;" -&gt; reasignada al Sprint "&amp;$AD190,"")</f>
+        <f>IF($AF190,IF('Postergar'!$G190&lt;&gt;"",'Postergar'!$G190,"No completada al cierre del Sprint "&amp;$N190)&amp;" -&gt; Sprint "&amp;$AD190,"")</f>
       </c>
       <c r="AI190" s="201">
         <f>IF($AF190,$N190*100000+ROW(),"")</f>
@@ -44898,7 +44906,7 @@
         <f>IF($C191,IF(LEN(TRIM($AN191))=0,"—",TRIM($AN191)),"")</f>
       </c>
       <c r="AD191" s="201">
-        <f>IF($C191,IF($N191=9999,9999,IF($J191="Completado",$N191,MAX($N191,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C191,IF($N191=9999,9999,IF($J191="Completado",$N191,MAX($N191,'Historial de Sprints'!$C$7)+N('Postergar'!$F191))),"")</f>
       </c>
       <c r="AE191" s="201">
         <f>IF($C191,IF($AD191=9999,"(Sin sprint)",$AD191),"")</f>
@@ -44910,7 +44918,7 @@
         <f>IF($AF191,'Historial de Sprints'!$C$5+$N191*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH191" s="202">
-        <f>IF($AF191,"No completada al cierre del Sprint "&amp;$N191&amp;" -&gt; reasignada al Sprint "&amp;$AD191,"")</f>
+        <f>IF($AF191,IF('Postergar'!$G191&lt;&gt;"",'Postergar'!$G191,"No completada al cierre del Sprint "&amp;$N191)&amp;" -&gt; Sprint "&amp;$AD191,"")</f>
       </c>
       <c r="AI191" s="201">
         <f>IF($AF191,$N191*100000+ROW(),"")</f>
@@ -45014,7 +45022,7 @@
         <f>IF($C192,IF(LEN(TRIM($AN192))=0,"—",TRIM($AN192)),"")</f>
       </c>
       <c r="AD192" s="201">
-        <f>IF($C192,IF($N192=9999,9999,IF($J192="Completado",$N192,MAX($N192,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C192,IF($N192=9999,9999,IF($J192="Completado",$N192,MAX($N192,'Historial de Sprints'!$C$7)+N('Postergar'!$F192))),"")</f>
       </c>
       <c r="AE192" s="201">
         <f>IF($C192,IF($AD192=9999,"(Sin sprint)",$AD192),"")</f>
@@ -45026,7 +45034,7 @@
         <f>IF($AF192,'Historial de Sprints'!$C$5+$N192*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH192" s="202">
-        <f>IF($AF192,"No completada al cierre del Sprint "&amp;$N192&amp;" -&gt; reasignada al Sprint "&amp;$AD192,"")</f>
+        <f>IF($AF192,IF('Postergar'!$G192&lt;&gt;"",'Postergar'!$G192,"No completada al cierre del Sprint "&amp;$N192)&amp;" -&gt; Sprint "&amp;$AD192,"")</f>
       </c>
       <c r="AI192" s="201">
         <f>IF($AF192,$N192*100000+ROW(),"")</f>
@@ -45130,7 +45138,7 @@
         <f>IF($C193,IF(LEN(TRIM($AN193))=0,"—",TRIM($AN193)),"")</f>
       </c>
       <c r="AD193" s="201">
-        <f>IF($C193,IF($N193=9999,9999,IF($J193="Completado",$N193,MAX($N193,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C193,IF($N193=9999,9999,IF($J193="Completado",$N193,MAX($N193,'Historial de Sprints'!$C$7)+N('Postergar'!$F193))),"")</f>
       </c>
       <c r="AE193" s="201">
         <f>IF($C193,IF($AD193=9999,"(Sin sprint)",$AD193),"")</f>
@@ -45142,7 +45150,7 @@
         <f>IF($AF193,'Historial de Sprints'!$C$5+$N193*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH193" s="202">
-        <f>IF($AF193,"No completada al cierre del Sprint "&amp;$N193&amp;" -&gt; reasignada al Sprint "&amp;$AD193,"")</f>
+        <f>IF($AF193,IF('Postergar'!$G193&lt;&gt;"",'Postergar'!$G193,"No completada al cierre del Sprint "&amp;$N193)&amp;" -&gt; Sprint "&amp;$AD193,"")</f>
       </c>
       <c r="AI193" s="201">
         <f>IF($AF193,$N193*100000+ROW(),"")</f>
@@ -45246,7 +45254,7 @@
         <f>IF($C194,IF(LEN(TRIM($AN194))=0,"—",TRIM($AN194)),"")</f>
       </c>
       <c r="AD194" s="201">
-        <f>IF($C194,IF($N194=9999,9999,IF($J194="Completado",$N194,MAX($N194,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C194,IF($N194=9999,9999,IF($J194="Completado",$N194,MAX($N194,'Historial de Sprints'!$C$7)+N('Postergar'!$F194))),"")</f>
       </c>
       <c r="AE194" s="201">
         <f>IF($C194,IF($AD194=9999,"(Sin sprint)",$AD194),"")</f>
@@ -45258,7 +45266,7 @@
         <f>IF($AF194,'Historial de Sprints'!$C$5+$N194*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH194" s="202">
-        <f>IF($AF194,"No completada al cierre del Sprint "&amp;$N194&amp;" -&gt; reasignada al Sprint "&amp;$AD194,"")</f>
+        <f>IF($AF194,IF('Postergar'!$G194&lt;&gt;"",'Postergar'!$G194,"No completada al cierre del Sprint "&amp;$N194)&amp;" -&gt; Sprint "&amp;$AD194,"")</f>
       </c>
       <c r="AI194" s="201">
         <f>IF($AF194,$N194*100000+ROW(),"")</f>
@@ -45362,7 +45370,7 @@
         <f>IF($C195,IF(LEN(TRIM($AN195))=0,"—",TRIM($AN195)),"")</f>
       </c>
       <c r="AD195" s="201">
-        <f>IF($C195,IF($N195=9999,9999,IF($J195="Completado",$N195,MAX($N195,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C195,IF($N195=9999,9999,IF($J195="Completado",$N195,MAX($N195,'Historial de Sprints'!$C$7)+N('Postergar'!$F195))),"")</f>
       </c>
       <c r="AE195" s="201">
         <f>IF($C195,IF($AD195=9999,"(Sin sprint)",$AD195),"")</f>
@@ -45374,7 +45382,7 @@
         <f>IF($AF195,'Historial de Sprints'!$C$5+$N195*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH195" s="202">
-        <f>IF($AF195,"No completada al cierre del Sprint "&amp;$N195&amp;" -&gt; reasignada al Sprint "&amp;$AD195,"")</f>
+        <f>IF($AF195,IF('Postergar'!$G195&lt;&gt;"",'Postergar'!$G195,"No completada al cierre del Sprint "&amp;$N195)&amp;" -&gt; Sprint "&amp;$AD195,"")</f>
       </c>
       <c r="AI195" s="201">
         <f>IF($AF195,$N195*100000+ROW(),"")</f>
@@ -45478,7 +45486,7 @@
         <f>IF($C196,IF(LEN(TRIM($AN196))=0,"—",TRIM($AN196)),"")</f>
       </c>
       <c r="AD196" s="201">
-        <f>IF($C196,IF($N196=9999,9999,IF($J196="Completado",$N196,MAX($N196,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C196,IF($N196=9999,9999,IF($J196="Completado",$N196,MAX($N196,'Historial de Sprints'!$C$7)+N('Postergar'!$F196))),"")</f>
       </c>
       <c r="AE196" s="201">
         <f>IF($C196,IF($AD196=9999,"(Sin sprint)",$AD196),"")</f>
@@ -45490,7 +45498,7 @@
         <f>IF($AF196,'Historial de Sprints'!$C$5+$N196*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH196" s="202">
-        <f>IF($AF196,"No completada al cierre del Sprint "&amp;$N196&amp;" -&gt; reasignada al Sprint "&amp;$AD196,"")</f>
+        <f>IF($AF196,IF('Postergar'!$G196&lt;&gt;"",'Postergar'!$G196,"No completada al cierre del Sprint "&amp;$N196)&amp;" -&gt; Sprint "&amp;$AD196,"")</f>
       </c>
       <c r="AI196" s="201">
         <f>IF($AF196,$N196*100000+ROW(),"")</f>
@@ -45594,7 +45602,7 @@
         <f>IF($C197,IF(LEN(TRIM($AN197))=0,"—",TRIM($AN197)),"")</f>
       </c>
       <c r="AD197" s="201">
-        <f>IF($C197,IF($N197=9999,9999,IF($J197="Completado",$N197,MAX($N197,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C197,IF($N197=9999,9999,IF($J197="Completado",$N197,MAX($N197,'Historial de Sprints'!$C$7)+N('Postergar'!$F197))),"")</f>
       </c>
       <c r="AE197" s="201">
         <f>IF($C197,IF($AD197=9999,"(Sin sprint)",$AD197),"")</f>
@@ -45606,7 +45614,7 @@
         <f>IF($AF197,'Historial de Sprints'!$C$5+$N197*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH197" s="202">
-        <f>IF($AF197,"No completada al cierre del Sprint "&amp;$N197&amp;" -&gt; reasignada al Sprint "&amp;$AD197,"")</f>
+        <f>IF($AF197,IF('Postergar'!$G197&lt;&gt;"",'Postergar'!$G197,"No completada al cierre del Sprint "&amp;$N197)&amp;" -&gt; Sprint "&amp;$AD197,"")</f>
       </c>
       <c r="AI197" s="201">
         <f>IF($AF197,$N197*100000+ROW(),"")</f>
@@ -45710,7 +45718,7 @@
         <f>IF($C198,IF(LEN(TRIM($AN198))=0,"—",TRIM($AN198)),"")</f>
       </c>
       <c r="AD198" s="201">
-        <f>IF($C198,IF($N198=9999,9999,IF($J198="Completado",$N198,MAX($N198,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C198,IF($N198=9999,9999,IF($J198="Completado",$N198,MAX($N198,'Historial de Sprints'!$C$7)+N('Postergar'!$F198))),"")</f>
       </c>
       <c r="AE198" s="201">
         <f>IF($C198,IF($AD198=9999,"(Sin sprint)",$AD198),"")</f>
@@ -45722,7 +45730,7 @@
         <f>IF($AF198,'Historial de Sprints'!$C$5+$N198*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH198" s="202">
-        <f>IF($AF198,"No completada al cierre del Sprint "&amp;$N198&amp;" -&gt; reasignada al Sprint "&amp;$AD198,"")</f>
+        <f>IF($AF198,IF('Postergar'!$G198&lt;&gt;"",'Postergar'!$G198,"No completada al cierre del Sprint "&amp;$N198)&amp;" -&gt; Sprint "&amp;$AD198,"")</f>
       </c>
       <c r="AI198" s="201">
         <f>IF($AF198,$N198*100000+ROW(),"")</f>
@@ -45826,7 +45834,7 @@
         <f>IF($C199,IF(LEN(TRIM($AN199))=0,"—",TRIM($AN199)),"")</f>
       </c>
       <c r="AD199" s="201">
-        <f>IF($C199,IF($N199=9999,9999,IF($J199="Completado",$N199,MAX($N199,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C199,IF($N199=9999,9999,IF($J199="Completado",$N199,MAX($N199,'Historial de Sprints'!$C$7)+N('Postergar'!$F199))),"")</f>
       </c>
       <c r="AE199" s="201">
         <f>IF($C199,IF($AD199=9999,"(Sin sprint)",$AD199),"")</f>
@@ -45838,7 +45846,7 @@
         <f>IF($AF199,'Historial de Sprints'!$C$5+$N199*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH199" s="202">
-        <f>IF($AF199,"No completada al cierre del Sprint "&amp;$N199&amp;" -&gt; reasignada al Sprint "&amp;$AD199,"")</f>
+        <f>IF($AF199,IF('Postergar'!$G199&lt;&gt;"",'Postergar'!$G199,"No completada al cierre del Sprint "&amp;$N199)&amp;" -&gt; Sprint "&amp;$AD199,"")</f>
       </c>
       <c r="AI199" s="201">
         <f>IF($AF199,$N199*100000+ROW(),"")</f>
@@ -45942,7 +45950,7 @@
         <f>IF($C200,IF(LEN(TRIM($AN200))=0,"—",TRIM($AN200)),"")</f>
       </c>
       <c r="AD200" s="201">
-        <f>IF($C200,IF($N200=9999,9999,IF($J200="Completado",$N200,MAX($N200,'Historial de Sprints'!$C$7))),"")</f>
+        <f>IF($C200,IF($N200=9999,9999,IF($J200="Completado",$N200,MAX($N200,'Historial de Sprints'!$C$7)+N('Postergar'!$F200))),"")</f>
       </c>
       <c r="AE200" s="201">
         <f>IF($C200,IF($AD200=9999,"(Sin sprint)",$AD200),"")</f>
@@ -45954,7 +45962,7 @@
         <f>IF($AF200,'Historial de Sprints'!$C$5+$N200*'Historial de Sprints'!$C$6-1,"")</f>
       </c>
       <c r="AH200" s="202">
-        <f>IF($AF200,"No completada al cierre del Sprint "&amp;$N200&amp;" -&gt; reasignada al Sprint "&amp;$AD200,"")</f>
+        <f>IF($AF200,IF('Postergar'!$G200&lt;&gt;"",'Postergar'!$G200,"No completada al cierre del Sprint "&amp;$N200)&amp;" -&gt; Sprint "&amp;$AD200,"")</f>
       </c>
       <c r="AI200" s="201">
         <f>IF($AF200,$N200*100000+ROW(),"")</f>
@@ -48233,6 +48241,3267 @@
       <formula>$C13&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I200"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="3" max="3" width="46" customWidth="1"/>
+    <col min="4" max="5" width="14" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="30" customWidth="1"/>
+    <col min="9" max="9" width="32" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="B1" s="169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">POSTERGAR TAREAS  (acción por cuello de botella)</t>
+        </is>
+      </c>
+      <c r="C1" s="169"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="B2" s="170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">En la fila de la tarea, elija cuántos sprints postergar y el motivo. El cambio se aplica solo (Sprint vigente) y queda registrado en 'Historial de Sprints'. 1 = próximo sprint.</t>
+        </is>
+      </c>
+      <c r="C2" s="170"/>
+      <c r="D2" s="170"/>
+      <c r="E2" s="170"/>
+      <c r="F2" s="170"/>
+      <c r="G2" s="170"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ACCIÓN — POSTERGAR TAREA A PRÓXIMO SPRINT</t>
+        </is>
+      </c>
+      <c r="C4" s="172"/>
+      <c r="D4" s="172"/>
+      <c r="E4" s="172"/>
+      <c r="F4" s="172"/>
+      <c r="G4" s="172"/>
+      <c r="I4" s="174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motivos de cuello de botella (editable)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="I5" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dependencia bloqueada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ID</t>
+        </is>
+      </c>
+      <c r="C6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tarea</t>
+        </is>
+      </c>
+      <c r="D6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint plan.</t>
+        </is>
+      </c>
+      <c r="E6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sprint vigente</t>
+        </is>
+      </c>
+      <c r="F6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Postergar (nº sprints)</t>
+        </is>
+      </c>
+      <c r="G6" s="173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Motivo del cuello de botella</t>
+        </is>
+      </c>
+      <c r="I6" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sobrecarga del responsable</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="203">
+        <f>IF('_Datos'!$C7,'_Datos'!$O7,"")</f>
+      </c>
+      <c r="C7" s="204">
+        <f>IF('_Datos'!$C7,'_Datos'!$F7,"")</f>
+      </c>
+      <c r="D7" s="203">
+        <f>IF('_Datos'!$C7,IF('_Datos'!$N7=9999,"(Sin sprint)",'_Datos'!$N7),"")</f>
+      </c>
+      <c r="E7" s="203">
+        <f>IF('_Datos'!$C7,'_Datos'!$AE7,"")</f>
+      </c>
+      <c r="F7" s="203"/>
+      <c r="G7" s="204"/>
+      <c r="I7" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Falta de información / insumos</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="203">
+        <f>IF('_Datos'!$C8,'_Datos'!$O8,"")</f>
+      </c>
+      <c r="C8" s="204">
+        <f>IF('_Datos'!$C8,'_Datos'!$F8,"")</f>
+      </c>
+      <c r="D8" s="203">
+        <f>IF('_Datos'!$C8,IF('_Datos'!$N8=9999,"(Sin sprint)",'_Datos'!$N8),"")</f>
+      </c>
+      <c r="E8" s="203">
+        <f>IF('_Datos'!$C8,'_Datos'!$AE8,"")</f>
+      </c>
+      <c r="F8" s="203"/>
+      <c r="G8" s="204"/>
+      <c r="I8" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reestimación / mayor alcance</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="203">
+        <f>IF('_Datos'!$C9,'_Datos'!$O9,"")</f>
+      </c>
+      <c r="C9" s="204">
+        <f>IF('_Datos'!$C9,'_Datos'!$F9,"")</f>
+      </c>
+      <c r="D9" s="203">
+        <f>IF('_Datos'!$C9,IF('_Datos'!$N9=9999,"(Sin sprint)",'_Datos'!$N9),"")</f>
+      </c>
+      <c r="E9" s="203">
+        <f>IF('_Datos'!$C9,'_Datos'!$AE9,"")</f>
+      </c>
+      <c r="F9" s="203"/>
+      <c r="G9" s="204"/>
+      <c r="I9" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recurso no disponible</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="203">
+        <f>IF('_Datos'!$C10,'_Datos'!$O10,"")</f>
+      </c>
+      <c r="C10" s="204">
+        <f>IF('_Datos'!$C10,'_Datos'!$F10,"")</f>
+      </c>
+      <c r="D10" s="203">
+        <f>IF('_Datos'!$C10,IF('_Datos'!$N10=9999,"(Sin sprint)",'_Datos'!$N10),"")</f>
+      </c>
+      <c r="E10" s="203">
+        <f>IF('_Datos'!$C10,'_Datos'!$AE10,"")</f>
+      </c>
+      <c r="F10" s="203"/>
+      <c r="G10" s="204"/>
+      <c r="I10" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prioridad reasignada</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="203">
+        <f>IF('_Datos'!$C11,'_Datos'!$O11,"")</f>
+      </c>
+      <c r="C11" s="204">
+        <f>IF('_Datos'!$C11,'_Datos'!$F11,"")</f>
+      </c>
+      <c r="D11" s="203">
+        <f>IF('_Datos'!$C11,IF('_Datos'!$N11=9999,"(Sin sprint)",'_Datos'!$N11),"")</f>
+      </c>
+      <c r="E11" s="203">
+        <f>IF('_Datos'!$C11,'_Datos'!$AE11,"")</f>
+      </c>
+      <c r="F11" s="203"/>
+      <c r="G11" s="204"/>
+      <c r="I11" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bloqueo técnico</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="203">
+        <f>IF('_Datos'!$C12,'_Datos'!$O12,"")</f>
+      </c>
+      <c r="C12" s="204">
+        <f>IF('_Datos'!$C12,'_Datos'!$F12,"")</f>
+      </c>
+      <c r="D12" s="203">
+        <f>IF('_Datos'!$C12,IF('_Datos'!$N12=9999,"(Sin sprint)",'_Datos'!$N12),"")</f>
+      </c>
+      <c r="E12" s="203">
+        <f>IF('_Datos'!$C12,'_Datos'!$AE12,"")</f>
+      </c>
+      <c r="F12" s="203"/>
+      <c r="G12" s="204"/>
+      <c r="I12" s="204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="203">
+        <f>IF('_Datos'!$C13,'_Datos'!$O13,"")</f>
+      </c>
+      <c r="C13" s="204">
+        <f>IF('_Datos'!$C13,'_Datos'!$F13,"")</f>
+      </c>
+      <c r="D13" s="203">
+        <f>IF('_Datos'!$C13,IF('_Datos'!$N13=9999,"(Sin sprint)",'_Datos'!$N13),"")</f>
+      </c>
+      <c r="E13" s="203">
+        <f>IF('_Datos'!$C13,'_Datos'!$AE13,"")</f>
+      </c>
+      <c r="F13" s="203"/>
+      <c r="G13" s="204"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="203">
+        <f>IF('_Datos'!$C14,'_Datos'!$O14,"")</f>
+      </c>
+      <c r="C14" s="204">
+        <f>IF('_Datos'!$C14,'_Datos'!$F14,"")</f>
+      </c>
+      <c r="D14" s="203">
+        <f>IF('_Datos'!$C14,IF('_Datos'!$N14=9999,"(Sin sprint)",'_Datos'!$N14),"")</f>
+      </c>
+      <c r="E14" s="203">
+        <f>IF('_Datos'!$C14,'_Datos'!$AE14,"")</f>
+      </c>
+      <c r="F14" s="203"/>
+      <c r="G14" s="204"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="203">
+        <f>IF('_Datos'!$C15,'_Datos'!$O15,"")</f>
+      </c>
+      <c r="C15" s="204">
+        <f>IF('_Datos'!$C15,'_Datos'!$F15,"")</f>
+      </c>
+      <c r="D15" s="203">
+        <f>IF('_Datos'!$C15,IF('_Datos'!$N15=9999,"(Sin sprint)",'_Datos'!$N15),"")</f>
+      </c>
+      <c r="E15" s="203">
+        <f>IF('_Datos'!$C15,'_Datos'!$AE15,"")</f>
+      </c>
+      <c r="F15" s="203"/>
+      <c r="G15" s="204"/>
+    </row>
+    <row r="16">
+      <c r="B16" s="203">
+        <f>IF('_Datos'!$C16,'_Datos'!$O16,"")</f>
+      </c>
+      <c r="C16" s="204">
+        <f>IF('_Datos'!$C16,'_Datos'!$F16,"")</f>
+      </c>
+      <c r="D16" s="203">
+        <f>IF('_Datos'!$C16,IF('_Datos'!$N16=9999,"(Sin sprint)",'_Datos'!$N16),"")</f>
+      </c>
+      <c r="E16" s="203">
+        <f>IF('_Datos'!$C16,'_Datos'!$AE16,"")</f>
+      </c>
+      <c r="F16" s="203"/>
+      <c r="G16" s="204"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="203">
+        <f>IF('_Datos'!$C17,'_Datos'!$O17,"")</f>
+      </c>
+      <c r="C17" s="204">
+        <f>IF('_Datos'!$C17,'_Datos'!$F17,"")</f>
+      </c>
+      <c r="D17" s="203">
+        <f>IF('_Datos'!$C17,IF('_Datos'!$N17=9999,"(Sin sprint)",'_Datos'!$N17),"")</f>
+      </c>
+      <c r="E17" s="203">
+        <f>IF('_Datos'!$C17,'_Datos'!$AE17,"")</f>
+      </c>
+      <c r="F17" s="203"/>
+      <c r="G17" s="204"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="203">
+        <f>IF('_Datos'!$C18,'_Datos'!$O18,"")</f>
+      </c>
+      <c r="C18" s="204">
+        <f>IF('_Datos'!$C18,'_Datos'!$F18,"")</f>
+      </c>
+      <c r="D18" s="203">
+        <f>IF('_Datos'!$C18,IF('_Datos'!$N18=9999,"(Sin sprint)",'_Datos'!$N18),"")</f>
+      </c>
+      <c r="E18" s="203">
+        <f>IF('_Datos'!$C18,'_Datos'!$AE18,"")</f>
+      </c>
+      <c r="F18" s="203"/>
+      <c r="G18" s="204"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="203">
+        <f>IF('_Datos'!$C19,'_Datos'!$O19,"")</f>
+      </c>
+      <c r="C19" s="204">
+        <f>IF('_Datos'!$C19,'_Datos'!$F19,"")</f>
+      </c>
+      <c r="D19" s="203">
+        <f>IF('_Datos'!$C19,IF('_Datos'!$N19=9999,"(Sin sprint)",'_Datos'!$N19),"")</f>
+      </c>
+      <c r="E19" s="203">
+        <f>IF('_Datos'!$C19,'_Datos'!$AE19,"")</f>
+      </c>
+      <c r="F19" s="203"/>
+      <c r="G19" s="204"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="203">
+        <f>IF('_Datos'!$C20,'_Datos'!$O20,"")</f>
+      </c>
+      <c r="C20" s="204">
+        <f>IF('_Datos'!$C20,'_Datos'!$F20,"")</f>
+      </c>
+      <c r="D20" s="203">
+        <f>IF('_Datos'!$C20,IF('_Datos'!$N20=9999,"(Sin sprint)",'_Datos'!$N20),"")</f>
+      </c>
+      <c r="E20" s="203">
+        <f>IF('_Datos'!$C20,'_Datos'!$AE20,"")</f>
+      </c>
+      <c r="F20" s="203"/>
+      <c r="G20" s="204"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="203">
+        <f>IF('_Datos'!$C21,'_Datos'!$O21,"")</f>
+      </c>
+      <c r="C21" s="204">
+        <f>IF('_Datos'!$C21,'_Datos'!$F21,"")</f>
+      </c>
+      <c r="D21" s="203">
+        <f>IF('_Datos'!$C21,IF('_Datos'!$N21=9999,"(Sin sprint)",'_Datos'!$N21),"")</f>
+      </c>
+      <c r="E21" s="203">
+        <f>IF('_Datos'!$C21,'_Datos'!$AE21,"")</f>
+      </c>
+      <c r="F21" s="203"/>
+      <c r="G21" s="204"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="203">
+        <f>IF('_Datos'!$C22,'_Datos'!$O22,"")</f>
+      </c>
+      <c r="C22" s="204">
+        <f>IF('_Datos'!$C22,'_Datos'!$F22,"")</f>
+      </c>
+      <c r="D22" s="203">
+        <f>IF('_Datos'!$C22,IF('_Datos'!$N22=9999,"(Sin sprint)",'_Datos'!$N22),"")</f>
+      </c>
+      <c r="E22" s="203">
+        <f>IF('_Datos'!$C22,'_Datos'!$AE22,"")</f>
+      </c>
+      <c r="F22" s="203"/>
+      <c r="G22" s="204"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="203">
+        <f>IF('_Datos'!$C23,'_Datos'!$O23,"")</f>
+      </c>
+      <c r="C23" s="204">
+        <f>IF('_Datos'!$C23,'_Datos'!$F23,"")</f>
+      </c>
+      <c r="D23" s="203">
+        <f>IF('_Datos'!$C23,IF('_Datos'!$N23=9999,"(Sin sprint)",'_Datos'!$N23),"")</f>
+      </c>
+      <c r="E23" s="203">
+        <f>IF('_Datos'!$C23,'_Datos'!$AE23,"")</f>
+      </c>
+      <c r="F23" s="203"/>
+      <c r="G23" s="204"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="203">
+        <f>IF('_Datos'!$C24,'_Datos'!$O24,"")</f>
+      </c>
+      <c r="C24" s="204">
+        <f>IF('_Datos'!$C24,'_Datos'!$F24,"")</f>
+      </c>
+      <c r="D24" s="203">
+        <f>IF('_Datos'!$C24,IF('_Datos'!$N24=9999,"(Sin sprint)",'_Datos'!$N24),"")</f>
+      </c>
+      <c r="E24" s="203">
+        <f>IF('_Datos'!$C24,'_Datos'!$AE24,"")</f>
+      </c>
+      <c r="F24" s="203"/>
+      <c r="G24" s="204"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="203">
+        <f>IF('_Datos'!$C25,'_Datos'!$O25,"")</f>
+      </c>
+      <c r="C25" s="204">
+        <f>IF('_Datos'!$C25,'_Datos'!$F25,"")</f>
+      </c>
+      <c r="D25" s="203">
+        <f>IF('_Datos'!$C25,IF('_Datos'!$N25=9999,"(Sin sprint)",'_Datos'!$N25),"")</f>
+      </c>
+      <c r="E25" s="203">
+        <f>IF('_Datos'!$C25,'_Datos'!$AE25,"")</f>
+      </c>
+      <c r="F25" s="203"/>
+      <c r="G25" s="204"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="203">
+        <f>IF('_Datos'!$C26,'_Datos'!$O26,"")</f>
+      </c>
+      <c r="C26" s="204">
+        <f>IF('_Datos'!$C26,'_Datos'!$F26,"")</f>
+      </c>
+      <c r="D26" s="203">
+        <f>IF('_Datos'!$C26,IF('_Datos'!$N26=9999,"(Sin sprint)",'_Datos'!$N26),"")</f>
+      </c>
+      <c r="E26" s="203">
+        <f>IF('_Datos'!$C26,'_Datos'!$AE26,"")</f>
+      </c>
+      <c r="F26" s="203"/>
+      <c r="G26" s="204"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="203">
+        <f>IF('_Datos'!$C27,'_Datos'!$O27,"")</f>
+      </c>
+      <c r="C27" s="204">
+        <f>IF('_Datos'!$C27,'_Datos'!$F27,"")</f>
+      </c>
+      <c r="D27" s="203">
+        <f>IF('_Datos'!$C27,IF('_Datos'!$N27=9999,"(Sin sprint)",'_Datos'!$N27),"")</f>
+      </c>
+      <c r="E27" s="203">
+        <f>IF('_Datos'!$C27,'_Datos'!$AE27,"")</f>
+      </c>
+      <c r="F27" s="203"/>
+      <c r="G27" s="204"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="203">
+        <f>IF('_Datos'!$C28,'_Datos'!$O28,"")</f>
+      </c>
+      <c r="C28" s="204">
+        <f>IF('_Datos'!$C28,'_Datos'!$F28,"")</f>
+      </c>
+      <c r="D28" s="203">
+        <f>IF('_Datos'!$C28,IF('_Datos'!$N28=9999,"(Sin sprint)",'_Datos'!$N28),"")</f>
+      </c>
+      <c r="E28" s="203">
+        <f>IF('_Datos'!$C28,'_Datos'!$AE28,"")</f>
+      </c>
+      <c r="F28" s="203"/>
+      <c r="G28" s="204"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="203">
+        <f>IF('_Datos'!$C29,'_Datos'!$O29,"")</f>
+      </c>
+      <c r="C29" s="204">
+        <f>IF('_Datos'!$C29,'_Datos'!$F29,"")</f>
+      </c>
+      <c r="D29" s="203">
+        <f>IF('_Datos'!$C29,IF('_Datos'!$N29=9999,"(Sin sprint)",'_Datos'!$N29),"")</f>
+      </c>
+      <c r="E29" s="203">
+        <f>IF('_Datos'!$C29,'_Datos'!$AE29,"")</f>
+      </c>
+      <c r="F29" s="203"/>
+      <c r="G29" s="204"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="203">
+        <f>IF('_Datos'!$C30,'_Datos'!$O30,"")</f>
+      </c>
+      <c r="C30" s="204">
+        <f>IF('_Datos'!$C30,'_Datos'!$F30,"")</f>
+      </c>
+      <c r="D30" s="203">
+        <f>IF('_Datos'!$C30,IF('_Datos'!$N30=9999,"(Sin sprint)",'_Datos'!$N30),"")</f>
+      </c>
+      <c r="E30" s="203">
+        <f>IF('_Datos'!$C30,'_Datos'!$AE30,"")</f>
+      </c>
+      <c r="F30" s="203"/>
+      <c r="G30" s="204"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="203">
+        <f>IF('_Datos'!$C31,'_Datos'!$O31,"")</f>
+      </c>
+      <c r="C31" s="204">
+        <f>IF('_Datos'!$C31,'_Datos'!$F31,"")</f>
+      </c>
+      <c r="D31" s="203">
+        <f>IF('_Datos'!$C31,IF('_Datos'!$N31=9999,"(Sin sprint)",'_Datos'!$N31),"")</f>
+      </c>
+      <c r="E31" s="203">
+        <f>IF('_Datos'!$C31,'_Datos'!$AE31,"")</f>
+      </c>
+      <c r="F31" s="203"/>
+      <c r="G31" s="204"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="203">
+        <f>IF('_Datos'!$C32,'_Datos'!$O32,"")</f>
+      </c>
+      <c r="C32" s="204">
+        <f>IF('_Datos'!$C32,'_Datos'!$F32,"")</f>
+      </c>
+      <c r="D32" s="203">
+        <f>IF('_Datos'!$C32,IF('_Datos'!$N32=9999,"(Sin sprint)",'_Datos'!$N32),"")</f>
+      </c>
+      <c r="E32" s="203">
+        <f>IF('_Datos'!$C32,'_Datos'!$AE32,"")</f>
+      </c>
+      <c r="F32" s="203"/>
+      <c r="G32" s="204"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="203">
+        <f>IF('_Datos'!$C33,'_Datos'!$O33,"")</f>
+      </c>
+      <c r="C33" s="204">
+        <f>IF('_Datos'!$C33,'_Datos'!$F33,"")</f>
+      </c>
+      <c r="D33" s="203">
+        <f>IF('_Datos'!$C33,IF('_Datos'!$N33=9999,"(Sin sprint)",'_Datos'!$N33),"")</f>
+      </c>
+      <c r="E33" s="203">
+        <f>IF('_Datos'!$C33,'_Datos'!$AE33,"")</f>
+      </c>
+      <c r="F33" s="203"/>
+      <c r="G33" s="204"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="203">
+        <f>IF('_Datos'!$C34,'_Datos'!$O34,"")</f>
+      </c>
+      <c r="C34" s="204">
+        <f>IF('_Datos'!$C34,'_Datos'!$F34,"")</f>
+      </c>
+      <c r="D34" s="203">
+        <f>IF('_Datos'!$C34,IF('_Datos'!$N34=9999,"(Sin sprint)",'_Datos'!$N34),"")</f>
+      </c>
+      <c r="E34" s="203">
+        <f>IF('_Datos'!$C34,'_Datos'!$AE34,"")</f>
+      </c>
+      <c r="F34" s="203"/>
+      <c r="G34" s="204"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="203">
+        <f>IF('_Datos'!$C35,'_Datos'!$O35,"")</f>
+      </c>
+      <c r="C35" s="204">
+        <f>IF('_Datos'!$C35,'_Datos'!$F35,"")</f>
+      </c>
+      <c r="D35" s="203">
+        <f>IF('_Datos'!$C35,IF('_Datos'!$N35=9999,"(Sin sprint)",'_Datos'!$N35),"")</f>
+      </c>
+      <c r="E35" s="203">
+        <f>IF('_Datos'!$C35,'_Datos'!$AE35,"")</f>
+      </c>
+      <c r="F35" s="203"/>
+      <c r="G35" s="204"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="203">
+        <f>IF('_Datos'!$C36,'_Datos'!$O36,"")</f>
+      </c>
+      <c r="C36" s="204">
+        <f>IF('_Datos'!$C36,'_Datos'!$F36,"")</f>
+      </c>
+      <c r="D36" s="203">
+        <f>IF('_Datos'!$C36,IF('_Datos'!$N36=9999,"(Sin sprint)",'_Datos'!$N36),"")</f>
+      </c>
+      <c r="E36" s="203">
+        <f>IF('_Datos'!$C36,'_Datos'!$AE36,"")</f>
+      </c>
+      <c r="F36" s="203"/>
+      <c r="G36" s="204"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="203">
+        <f>IF('_Datos'!$C37,'_Datos'!$O37,"")</f>
+      </c>
+      <c r="C37" s="204">
+        <f>IF('_Datos'!$C37,'_Datos'!$F37,"")</f>
+      </c>
+      <c r="D37" s="203">
+        <f>IF('_Datos'!$C37,IF('_Datos'!$N37=9999,"(Sin sprint)",'_Datos'!$N37),"")</f>
+      </c>
+      <c r="E37" s="203">
+        <f>IF('_Datos'!$C37,'_Datos'!$AE37,"")</f>
+      </c>
+      <c r="F37" s="203"/>
+      <c r="G37" s="204"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="203">
+        <f>IF('_Datos'!$C38,'_Datos'!$O38,"")</f>
+      </c>
+      <c r="C38" s="204">
+        <f>IF('_Datos'!$C38,'_Datos'!$F38,"")</f>
+      </c>
+      <c r="D38" s="203">
+        <f>IF('_Datos'!$C38,IF('_Datos'!$N38=9999,"(Sin sprint)",'_Datos'!$N38),"")</f>
+      </c>
+      <c r="E38" s="203">
+        <f>IF('_Datos'!$C38,'_Datos'!$AE38,"")</f>
+      </c>
+      <c r="F38" s="203"/>
+      <c r="G38" s="204"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="203">
+        <f>IF('_Datos'!$C39,'_Datos'!$O39,"")</f>
+      </c>
+      <c r="C39" s="204">
+        <f>IF('_Datos'!$C39,'_Datos'!$F39,"")</f>
+      </c>
+      <c r="D39" s="203">
+        <f>IF('_Datos'!$C39,IF('_Datos'!$N39=9999,"(Sin sprint)",'_Datos'!$N39),"")</f>
+      </c>
+      <c r="E39" s="203">
+        <f>IF('_Datos'!$C39,'_Datos'!$AE39,"")</f>
+      </c>
+      <c r="F39" s="203"/>
+      <c r="G39" s="204"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="203">
+        <f>IF('_Datos'!$C40,'_Datos'!$O40,"")</f>
+      </c>
+      <c r="C40" s="204">
+        <f>IF('_Datos'!$C40,'_Datos'!$F40,"")</f>
+      </c>
+      <c r="D40" s="203">
+        <f>IF('_Datos'!$C40,IF('_Datos'!$N40=9999,"(Sin sprint)",'_Datos'!$N40),"")</f>
+      </c>
+      <c r="E40" s="203">
+        <f>IF('_Datos'!$C40,'_Datos'!$AE40,"")</f>
+      </c>
+      <c r="F40" s="203"/>
+      <c r="G40" s="204"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="203">
+        <f>IF('_Datos'!$C41,'_Datos'!$O41,"")</f>
+      </c>
+      <c r="C41" s="204">
+        <f>IF('_Datos'!$C41,'_Datos'!$F41,"")</f>
+      </c>
+      <c r="D41" s="203">
+        <f>IF('_Datos'!$C41,IF('_Datos'!$N41=9999,"(Sin sprint)",'_Datos'!$N41),"")</f>
+      </c>
+      <c r="E41" s="203">
+        <f>IF('_Datos'!$C41,'_Datos'!$AE41,"")</f>
+      </c>
+      <c r="F41" s="203"/>
+      <c r="G41" s="204"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="203">
+        <f>IF('_Datos'!$C42,'_Datos'!$O42,"")</f>
+      </c>
+      <c r="C42" s="204">
+        <f>IF('_Datos'!$C42,'_Datos'!$F42,"")</f>
+      </c>
+      <c r="D42" s="203">
+        <f>IF('_Datos'!$C42,IF('_Datos'!$N42=9999,"(Sin sprint)",'_Datos'!$N42),"")</f>
+      </c>
+      <c r="E42" s="203">
+        <f>IF('_Datos'!$C42,'_Datos'!$AE42,"")</f>
+      </c>
+      <c r="F42" s="203"/>
+      <c r="G42" s="204"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="203">
+        <f>IF('_Datos'!$C43,'_Datos'!$O43,"")</f>
+      </c>
+      <c r="C43" s="204">
+        <f>IF('_Datos'!$C43,'_Datos'!$F43,"")</f>
+      </c>
+      <c r="D43" s="203">
+        <f>IF('_Datos'!$C43,IF('_Datos'!$N43=9999,"(Sin sprint)",'_Datos'!$N43),"")</f>
+      </c>
+      <c r="E43" s="203">
+        <f>IF('_Datos'!$C43,'_Datos'!$AE43,"")</f>
+      </c>
+      <c r="F43" s="203"/>
+      <c r="G43" s="204"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="203">
+        <f>IF('_Datos'!$C44,'_Datos'!$O44,"")</f>
+      </c>
+      <c r="C44" s="204">
+        <f>IF('_Datos'!$C44,'_Datos'!$F44,"")</f>
+      </c>
+      <c r="D44" s="203">
+        <f>IF('_Datos'!$C44,IF('_Datos'!$N44=9999,"(Sin sprint)",'_Datos'!$N44),"")</f>
+      </c>
+      <c r="E44" s="203">
+        <f>IF('_Datos'!$C44,'_Datos'!$AE44,"")</f>
+      </c>
+      <c r="F44" s="203"/>
+      <c r="G44" s="204"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="203">
+        <f>IF('_Datos'!$C45,'_Datos'!$O45,"")</f>
+      </c>
+      <c r="C45" s="204">
+        <f>IF('_Datos'!$C45,'_Datos'!$F45,"")</f>
+      </c>
+      <c r="D45" s="203">
+        <f>IF('_Datos'!$C45,IF('_Datos'!$N45=9999,"(Sin sprint)",'_Datos'!$N45),"")</f>
+      </c>
+      <c r="E45" s="203">
+        <f>IF('_Datos'!$C45,'_Datos'!$AE45,"")</f>
+      </c>
+      <c r="F45" s="203"/>
+      <c r="G45" s="204"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="203">
+        <f>IF('_Datos'!$C46,'_Datos'!$O46,"")</f>
+      </c>
+      <c r="C46" s="204">
+        <f>IF('_Datos'!$C46,'_Datos'!$F46,"")</f>
+      </c>
+      <c r="D46" s="203">
+        <f>IF('_Datos'!$C46,IF('_Datos'!$N46=9999,"(Sin sprint)",'_Datos'!$N46),"")</f>
+      </c>
+      <c r="E46" s="203">
+        <f>IF('_Datos'!$C46,'_Datos'!$AE46,"")</f>
+      </c>
+      <c r="F46" s="203"/>
+      <c r="G46" s="204"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="203">
+        <f>IF('_Datos'!$C47,'_Datos'!$O47,"")</f>
+      </c>
+      <c r="C47" s="204">
+        <f>IF('_Datos'!$C47,'_Datos'!$F47,"")</f>
+      </c>
+      <c r="D47" s="203">
+        <f>IF('_Datos'!$C47,IF('_Datos'!$N47=9999,"(Sin sprint)",'_Datos'!$N47),"")</f>
+      </c>
+      <c r="E47" s="203">
+        <f>IF('_Datos'!$C47,'_Datos'!$AE47,"")</f>
+      </c>
+      <c r="F47" s="203"/>
+      <c r="G47" s="204"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="203">
+        <f>IF('_Datos'!$C48,'_Datos'!$O48,"")</f>
+      </c>
+      <c r="C48" s="204">
+        <f>IF('_Datos'!$C48,'_Datos'!$F48,"")</f>
+      </c>
+      <c r="D48" s="203">
+        <f>IF('_Datos'!$C48,IF('_Datos'!$N48=9999,"(Sin sprint)",'_Datos'!$N48),"")</f>
+      </c>
+      <c r="E48" s="203">
+        <f>IF('_Datos'!$C48,'_Datos'!$AE48,"")</f>
+      </c>
+      <c r="F48" s="203"/>
+      <c r="G48" s="204"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="203">
+        <f>IF('_Datos'!$C49,'_Datos'!$O49,"")</f>
+      </c>
+      <c r="C49" s="204">
+        <f>IF('_Datos'!$C49,'_Datos'!$F49,"")</f>
+      </c>
+      <c r="D49" s="203">
+        <f>IF('_Datos'!$C49,IF('_Datos'!$N49=9999,"(Sin sprint)",'_Datos'!$N49),"")</f>
+      </c>
+      <c r="E49" s="203">
+        <f>IF('_Datos'!$C49,'_Datos'!$AE49,"")</f>
+      </c>
+      <c r="F49" s="203"/>
+      <c r="G49" s="204"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="203">
+        <f>IF('_Datos'!$C50,'_Datos'!$O50,"")</f>
+      </c>
+      <c r="C50" s="204">
+        <f>IF('_Datos'!$C50,'_Datos'!$F50,"")</f>
+      </c>
+      <c r="D50" s="203">
+        <f>IF('_Datos'!$C50,IF('_Datos'!$N50=9999,"(Sin sprint)",'_Datos'!$N50),"")</f>
+      </c>
+      <c r="E50" s="203">
+        <f>IF('_Datos'!$C50,'_Datos'!$AE50,"")</f>
+      </c>
+      <c r="F50" s="203"/>
+      <c r="G50" s="204"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="203">
+        <f>IF('_Datos'!$C51,'_Datos'!$O51,"")</f>
+      </c>
+      <c r="C51" s="204">
+        <f>IF('_Datos'!$C51,'_Datos'!$F51,"")</f>
+      </c>
+      <c r="D51" s="203">
+        <f>IF('_Datos'!$C51,IF('_Datos'!$N51=9999,"(Sin sprint)",'_Datos'!$N51),"")</f>
+      </c>
+      <c r="E51" s="203">
+        <f>IF('_Datos'!$C51,'_Datos'!$AE51,"")</f>
+      </c>
+      <c r="F51" s="203"/>
+      <c r="G51" s="204"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="203">
+        <f>IF('_Datos'!$C52,'_Datos'!$O52,"")</f>
+      </c>
+      <c r="C52" s="204">
+        <f>IF('_Datos'!$C52,'_Datos'!$F52,"")</f>
+      </c>
+      <c r="D52" s="203">
+        <f>IF('_Datos'!$C52,IF('_Datos'!$N52=9999,"(Sin sprint)",'_Datos'!$N52),"")</f>
+      </c>
+      <c r="E52" s="203">
+        <f>IF('_Datos'!$C52,'_Datos'!$AE52,"")</f>
+      </c>
+      <c r="F52" s="203"/>
+      <c r="G52" s="204"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="203">
+        <f>IF('_Datos'!$C53,'_Datos'!$O53,"")</f>
+      </c>
+      <c r="C53" s="204">
+        <f>IF('_Datos'!$C53,'_Datos'!$F53,"")</f>
+      </c>
+      <c r="D53" s="203">
+        <f>IF('_Datos'!$C53,IF('_Datos'!$N53=9999,"(Sin sprint)",'_Datos'!$N53),"")</f>
+      </c>
+      <c r="E53" s="203">
+        <f>IF('_Datos'!$C53,'_Datos'!$AE53,"")</f>
+      </c>
+      <c r="F53" s="203"/>
+      <c r="G53" s="204"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="203">
+        <f>IF('_Datos'!$C54,'_Datos'!$O54,"")</f>
+      </c>
+      <c r="C54" s="204">
+        <f>IF('_Datos'!$C54,'_Datos'!$F54,"")</f>
+      </c>
+      <c r="D54" s="203">
+        <f>IF('_Datos'!$C54,IF('_Datos'!$N54=9999,"(Sin sprint)",'_Datos'!$N54),"")</f>
+      </c>
+      <c r="E54" s="203">
+        <f>IF('_Datos'!$C54,'_Datos'!$AE54,"")</f>
+      </c>
+      <c r="F54" s="203"/>
+      <c r="G54" s="204"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="203">
+        <f>IF('_Datos'!$C55,'_Datos'!$O55,"")</f>
+      </c>
+      <c r="C55" s="204">
+        <f>IF('_Datos'!$C55,'_Datos'!$F55,"")</f>
+      </c>
+      <c r="D55" s="203">
+        <f>IF('_Datos'!$C55,IF('_Datos'!$N55=9999,"(Sin sprint)",'_Datos'!$N55),"")</f>
+      </c>
+      <c r="E55" s="203">
+        <f>IF('_Datos'!$C55,'_Datos'!$AE55,"")</f>
+      </c>
+      <c r="F55" s="203"/>
+      <c r="G55" s="204"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="203">
+        <f>IF('_Datos'!$C56,'_Datos'!$O56,"")</f>
+      </c>
+      <c r="C56" s="204">
+        <f>IF('_Datos'!$C56,'_Datos'!$F56,"")</f>
+      </c>
+      <c r="D56" s="203">
+        <f>IF('_Datos'!$C56,IF('_Datos'!$N56=9999,"(Sin sprint)",'_Datos'!$N56),"")</f>
+      </c>
+      <c r="E56" s="203">
+        <f>IF('_Datos'!$C56,'_Datos'!$AE56,"")</f>
+      </c>
+      <c r="F56" s="203"/>
+      <c r="G56" s="204"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="203">
+        <f>IF('_Datos'!$C57,'_Datos'!$O57,"")</f>
+      </c>
+      <c r="C57" s="204">
+        <f>IF('_Datos'!$C57,'_Datos'!$F57,"")</f>
+      </c>
+      <c r="D57" s="203">
+        <f>IF('_Datos'!$C57,IF('_Datos'!$N57=9999,"(Sin sprint)",'_Datos'!$N57),"")</f>
+      </c>
+      <c r="E57" s="203">
+        <f>IF('_Datos'!$C57,'_Datos'!$AE57,"")</f>
+      </c>
+      <c r="F57" s="203"/>
+      <c r="G57" s="204"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="203">
+        <f>IF('_Datos'!$C58,'_Datos'!$O58,"")</f>
+      </c>
+      <c r="C58" s="204">
+        <f>IF('_Datos'!$C58,'_Datos'!$F58,"")</f>
+      </c>
+      <c r="D58" s="203">
+        <f>IF('_Datos'!$C58,IF('_Datos'!$N58=9999,"(Sin sprint)",'_Datos'!$N58),"")</f>
+      </c>
+      <c r="E58" s="203">
+        <f>IF('_Datos'!$C58,'_Datos'!$AE58,"")</f>
+      </c>
+      <c r="F58" s="203"/>
+      <c r="G58" s="204"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="203">
+        <f>IF('_Datos'!$C59,'_Datos'!$O59,"")</f>
+      </c>
+      <c r="C59" s="204">
+        <f>IF('_Datos'!$C59,'_Datos'!$F59,"")</f>
+      </c>
+      <c r="D59" s="203">
+        <f>IF('_Datos'!$C59,IF('_Datos'!$N59=9999,"(Sin sprint)",'_Datos'!$N59),"")</f>
+      </c>
+      <c r="E59" s="203">
+        <f>IF('_Datos'!$C59,'_Datos'!$AE59,"")</f>
+      </c>
+      <c r="F59" s="203"/>
+      <c r="G59" s="204"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="203">
+        <f>IF('_Datos'!$C60,'_Datos'!$O60,"")</f>
+      </c>
+      <c r="C60" s="204">
+        <f>IF('_Datos'!$C60,'_Datos'!$F60,"")</f>
+      </c>
+      <c r="D60" s="203">
+        <f>IF('_Datos'!$C60,IF('_Datos'!$N60=9999,"(Sin sprint)",'_Datos'!$N60),"")</f>
+      </c>
+      <c r="E60" s="203">
+        <f>IF('_Datos'!$C60,'_Datos'!$AE60,"")</f>
+      </c>
+      <c r="F60" s="203"/>
+      <c r="G60" s="204"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="203">
+        <f>IF('_Datos'!$C61,'_Datos'!$O61,"")</f>
+      </c>
+      <c r="C61" s="204">
+        <f>IF('_Datos'!$C61,'_Datos'!$F61,"")</f>
+      </c>
+      <c r="D61" s="203">
+        <f>IF('_Datos'!$C61,IF('_Datos'!$N61=9999,"(Sin sprint)",'_Datos'!$N61),"")</f>
+      </c>
+      <c r="E61" s="203">
+        <f>IF('_Datos'!$C61,'_Datos'!$AE61,"")</f>
+      </c>
+      <c r="F61" s="203"/>
+      <c r="G61" s="204"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="203">
+        <f>IF('_Datos'!$C62,'_Datos'!$O62,"")</f>
+      </c>
+      <c r="C62" s="204">
+        <f>IF('_Datos'!$C62,'_Datos'!$F62,"")</f>
+      </c>
+      <c r="D62" s="203">
+        <f>IF('_Datos'!$C62,IF('_Datos'!$N62=9999,"(Sin sprint)",'_Datos'!$N62),"")</f>
+      </c>
+      <c r="E62" s="203">
+        <f>IF('_Datos'!$C62,'_Datos'!$AE62,"")</f>
+      </c>
+      <c r="F62" s="203"/>
+      <c r="G62" s="204"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="203">
+        <f>IF('_Datos'!$C63,'_Datos'!$O63,"")</f>
+      </c>
+      <c r="C63" s="204">
+        <f>IF('_Datos'!$C63,'_Datos'!$F63,"")</f>
+      </c>
+      <c r="D63" s="203">
+        <f>IF('_Datos'!$C63,IF('_Datos'!$N63=9999,"(Sin sprint)",'_Datos'!$N63),"")</f>
+      </c>
+      <c r="E63" s="203">
+        <f>IF('_Datos'!$C63,'_Datos'!$AE63,"")</f>
+      </c>
+      <c r="F63" s="203"/>
+      <c r="G63" s="204"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="203">
+        <f>IF('_Datos'!$C64,'_Datos'!$O64,"")</f>
+      </c>
+      <c r="C64" s="204">
+        <f>IF('_Datos'!$C64,'_Datos'!$F64,"")</f>
+      </c>
+      <c r="D64" s="203">
+        <f>IF('_Datos'!$C64,IF('_Datos'!$N64=9999,"(Sin sprint)",'_Datos'!$N64),"")</f>
+      </c>
+      <c r="E64" s="203">
+        <f>IF('_Datos'!$C64,'_Datos'!$AE64,"")</f>
+      </c>
+      <c r="F64" s="203"/>
+      <c r="G64" s="204"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="203">
+        <f>IF('_Datos'!$C65,'_Datos'!$O65,"")</f>
+      </c>
+      <c r="C65" s="204">
+        <f>IF('_Datos'!$C65,'_Datos'!$F65,"")</f>
+      </c>
+      <c r="D65" s="203">
+        <f>IF('_Datos'!$C65,IF('_Datos'!$N65=9999,"(Sin sprint)",'_Datos'!$N65),"")</f>
+      </c>
+      <c r="E65" s="203">
+        <f>IF('_Datos'!$C65,'_Datos'!$AE65,"")</f>
+      </c>
+      <c r="F65" s="203"/>
+      <c r="G65" s="204"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="203">
+        <f>IF('_Datos'!$C66,'_Datos'!$O66,"")</f>
+      </c>
+      <c r="C66" s="204">
+        <f>IF('_Datos'!$C66,'_Datos'!$F66,"")</f>
+      </c>
+      <c r="D66" s="203">
+        <f>IF('_Datos'!$C66,IF('_Datos'!$N66=9999,"(Sin sprint)",'_Datos'!$N66),"")</f>
+      </c>
+      <c r="E66" s="203">
+        <f>IF('_Datos'!$C66,'_Datos'!$AE66,"")</f>
+      </c>
+      <c r="F66" s="203"/>
+      <c r="G66" s="204"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="203">
+        <f>IF('_Datos'!$C67,'_Datos'!$O67,"")</f>
+      </c>
+      <c r="C67" s="204">
+        <f>IF('_Datos'!$C67,'_Datos'!$F67,"")</f>
+      </c>
+      <c r="D67" s="203">
+        <f>IF('_Datos'!$C67,IF('_Datos'!$N67=9999,"(Sin sprint)",'_Datos'!$N67),"")</f>
+      </c>
+      <c r="E67" s="203">
+        <f>IF('_Datos'!$C67,'_Datos'!$AE67,"")</f>
+      </c>
+      <c r="F67" s="203"/>
+      <c r="G67" s="204"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="203">
+        <f>IF('_Datos'!$C68,'_Datos'!$O68,"")</f>
+      </c>
+      <c r="C68" s="204">
+        <f>IF('_Datos'!$C68,'_Datos'!$F68,"")</f>
+      </c>
+      <c r="D68" s="203">
+        <f>IF('_Datos'!$C68,IF('_Datos'!$N68=9999,"(Sin sprint)",'_Datos'!$N68),"")</f>
+      </c>
+      <c r="E68" s="203">
+        <f>IF('_Datos'!$C68,'_Datos'!$AE68,"")</f>
+      </c>
+      <c r="F68" s="203"/>
+      <c r="G68" s="204"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="203">
+        <f>IF('_Datos'!$C69,'_Datos'!$O69,"")</f>
+      </c>
+      <c r="C69" s="204">
+        <f>IF('_Datos'!$C69,'_Datos'!$F69,"")</f>
+      </c>
+      <c r="D69" s="203">
+        <f>IF('_Datos'!$C69,IF('_Datos'!$N69=9999,"(Sin sprint)",'_Datos'!$N69),"")</f>
+      </c>
+      <c r="E69" s="203">
+        <f>IF('_Datos'!$C69,'_Datos'!$AE69,"")</f>
+      </c>
+      <c r="F69" s="203"/>
+      <c r="G69" s="204"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="203">
+        <f>IF('_Datos'!$C70,'_Datos'!$O70,"")</f>
+      </c>
+      <c r="C70" s="204">
+        <f>IF('_Datos'!$C70,'_Datos'!$F70,"")</f>
+      </c>
+      <c r="D70" s="203">
+        <f>IF('_Datos'!$C70,IF('_Datos'!$N70=9999,"(Sin sprint)",'_Datos'!$N70),"")</f>
+      </c>
+      <c r="E70" s="203">
+        <f>IF('_Datos'!$C70,'_Datos'!$AE70,"")</f>
+      </c>
+      <c r="F70" s="203"/>
+      <c r="G70" s="204"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="203">
+        <f>IF('_Datos'!$C71,'_Datos'!$O71,"")</f>
+      </c>
+      <c r="C71" s="204">
+        <f>IF('_Datos'!$C71,'_Datos'!$F71,"")</f>
+      </c>
+      <c r="D71" s="203">
+        <f>IF('_Datos'!$C71,IF('_Datos'!$N71=9999,"(Sin sprint)",'_Datos'!$N71),"")</f>
+      </c>
+      <c r="E71" s="203">
+        <f>IF('_Datos'!$C71,'_Datos'!$AE71,"")</f>
+      </c>
+      <c r="F71" s="203"/>
+      <c r="G71" s="204"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="203">
+        <f>IF('_Datos'!$C72,'_Datos'!$O72,"")</f>
+      </c>
+      <c r="C72" s="204">
+        <f>IF('_Datos'!$C72,'_Datos'!$F72,"")</f>
+      </c>
+      <c r="D72" s="203">
+        <f>IF('_Datos'!$C72,IF('_Datos'!$N72=9999,"(Sin sprint)",'_Datos'!$N72),"")</f>
+      </c>
+      <c r="E72" s="203">
+        <f>IF('_Datos'!$C72,'_Datos'!$AE72,"")</f>
+      </c>
+      <c r="F72" s="203"/>
+      <c r="G72" s="204"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="203">
+        <f>IF('_Datos'!$C73,'_Datos'!$O73,"")</f>
+      </c>
+      <c r="C73" s="204">
+        <f>IF('_Datos'!$C73,'_Datos'!$F73,"")</f>
+      </c>
+      <c r="D73" s="203">
+        <f>IF('_Datos'!$C73,IF('_Datos'!$N73=9999,"(Sin sprint)",'_Datos'!$N73),"")</f>
+      </c>
+      <c r="E73" s="203">
+        <f>IF('_Datos'!$C73,'_Datos'!$AE73,"")</f>
+      </c>
+      <c r="F73" s="203"/>
+      <c r="G73" s="204"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="203">
+        <f>IF('_Datos'!$C74,'_Datos'!$O74,"")</f>
+      </c>
+      <c r="C74" s="204">
+        <f>IF('_Datos'!$C74,'_Datos'!$F74,"")</f>
+      </c>
+      <c r="D74" s="203">
+        <f>IF('_Datos'!$C74,IF('_Datos'!$N74=9999,"(Sin sprint)",'_Datos'!$N74),"")</f>
+      </c>
+      <c r="E74" s="203">
+        <f>IF('_Datos'!$C74,'_Datos'!$AE74,"")</f>
+      </c>
+      <c r="F74" s="203"/>
+      <c r="G74" s="204"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="203">
+        <f>IF('_Datos'!$C75,'_Datos'!$O75,"")</f>
+      </c>
+      <c r="C75" s="204">
+        <f>IF('_Datos'!$C75,'_Datos'!$F75,"")</f>
+      </c>
+      <c r="D75" s="203">
+        <f>IF('_Datos'!$C75,IF('_Datos'!$N75=9999,"(Sin sprint)",'_Datos'!$N75),"")</f>
+      </c>
+      <c r="E75" s="203">
+        <f>IF('_Datos'!$C75,'_Datos'!$AE75,"")</f>
+      </c>
+      <c r="F75" s="203"/>
+      <c r="G75" s="204"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="203">
+        <f>IF('_Datos'!$C76,'_Datos'!$O76,"")</f>
+      </c>
+      <c r="C76" s="204">
+        <f>IF('_Datos'!$C76,'_Datos'!$F76,"")</f>
+      </c>
+      <c r="D76" s="203">
+        <f>IF('_Datos'!$C76,IF('_Datos'!$N76=9999,"(Sin sprint)",'_Datos'!$N76),"")</f>
+      </c>
+      <c r="E76" s="203">
+        <f>IF('_Datos'!$C76,'_Datos'!$AE76,"")</f>
+      </c>
+      <c r="F76" s="203"/>
+      <c r="G76" s="204"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="203">
+        <f>IF('_Datos'!$C77,'_Datos'!$O77,"")</f>
+      </c>
+      <c r="C77" s="204">
+        <f>IF('_Datos'!$C77,'_Datos'!$F77,"")</f>
+      </c>
+      <c r="D77" s="203">
+        <f>IF('_Datos'!$C77,IF('_Datos'!$N77=9999,"(Sin sprint)",'_Datos'!$N77),"")</f>
+      </c>
+      <c r="E77" s="203">
+        <f>IF('_Datos'!$C77,'_Datos'!$AE77,"")</f>
+      </c>
+      <c r="F77" s="203"/>
+      <c r="G77" s="204"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="203">
+        <f>IF('_Datos'!$C78,'_Datos'!$O78,"")</f>
+      </c>
+      <c r="C78" s="204">
+        <f>IF('_Datos'!$C78,'_Datos'!$F78,"")</f>
+      </c>
+      <c r="D78" s="203">
+        <f>IF('_Datos'!$C78,IF('_Datos'!$N78=9999,"(Sin sprint)",'_Datos'!$N78),"")</f>
+      </c>
+      <c r="E78" s="203">
+        <f>IF('_Datos'!$C78,'_Datos'!$AE78,"")</f>
+      </c>
+      <c r="F78" s="203"/>
+      <c r="G78" s="204"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="203">
+        <f>IF('_Datos'!$C79,'_Datos'!$O79,"")</f>
+      </c>
+      <c r="C79" s="204">
+        <f>IF('_Datos'!$C79,'_Datos'!$F79,"")</f>
+      </c>
+      <c r="D79" s="203">
+        <f>IF('_Datos'!$C79,IF('_Datos'!$N79=9999,"(Sin sprint)",'_Datos'!$N79),"")</f>
+      </c>
+      <c r="E79" s="203">
+        <f>IF('_Datos'!$C79,'_Datos'!$AE79,"")</f>
+      </c>
+      <c r="F79" s="203"/>
+      <c r="G79" s="204"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="203">
+        <f>IF('_Datos'!$C80,'_Datos'!$O80,"")</f>
+      </c>
+      <c r="C80" s="204">
+        <f>IF('_Datos'!$C80,'_Datos'!$F80,"")</f>
+      </c>
+      <c r="D80" s="203">
+        <f>IF('_Datos'!$C80,IF('_Datos'!$N80=9999,"(Sin sprint)",'_Datos'!$N80),"")</f>
+      </c>
+      <c r="E80" s="203">
+        <f>IF('_Datos'!$C80,'_Datos'!$AE80,"")</f>
+      </c>
+      <c r="F80" s="203"/>
+      <c r="G80" s="204"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="203">
+        <f>IF('_Datos'!$C81,'_Datos'!$O81,"")</f>
+      </c>
+      <c r="C81" s="204">
+        <f>IF('_Datos'!$C81,'_Datos'!$F81,"")</f>
+      </c>
+      <c r="D81" s="203">
+        <f>IF('_Datos'!$C81,IF('_Datos'!$N81=9999,"(Sin sprint)",'_Datos'!$N81),"")</f>
+      </c>
+      <c r="E81" s="203">
+        <f>IF('_Datos'!$C81,'_Datos'!$AE81,"")</f>
+      </c>
+      <c r="F81" s="203"/>
+      <c r="G81" s="204"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="203">
+        <f>IF('_Datos'!$C82,'_Datos'!$O82,"")</f>
+      </c>
+      <c r="C82" s="204">
+        <f>IF('_Datos'!$C82,'_Datos'!$F82,"")</f>
+      </c>
+      <c r="D82" s="203">
+        <f>IF('_Datos'!$C82,IF('_Datos'!$N82=9999,"(Sin sprint)",'_Datos'!$N82),"")</f>
+      </c>
+      <c r="E82" s="203">
+        <f>IF('_Datos'!$C82,'_Datos'!$AE82,"")</f>
+      </c>
+      <c r="F82" s="203"/>
+      <c r="G82" s="204"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="203">
+        <f>IF('_Datos'!$C83,'_Datos'!$O83,"")</f>
+      </c>
+      <c r="C83" s="204">
+        <f>IF('_Datos'!$C83,'_Datos'!$F83,"")</f>
+      </c>
+      <c r="D83" s="203">
+        <f>IF('_Datos'!$C83,IF('_Datos'!$N83=9999,"(Sin sprint)",'_Datos'!$N83),"")</f>
+      </c>
+      <c r="E83" s="203">
+        <f>IF('_Datos'!$C83,'_Datos'!$AE83,"")</f>
+      </c>
+      <c r="F83" s="203"/>
+      <c r="G83" s="204"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="203">
+        <f>IF('_Datos'!$C84,'_Datos'!$O84,"")</f>
+      </c>
+      <c r="C84" s="204">
+        <f>IF('_Datos'!$C84,'_Datos'!$F84,"")</f>
+      </c>
+      <c r="D84" s="203">
+        <f>IF('_Datos'!$C84,IF('_Datos'!$N84=9999,"(Sin sprint)",'_Datos'!$N84),"")</f>
+      </c>
+      <c r="E84" s="203">
+        <f>IF('_Datos'!$C84,'_Datos'!$AE84,"")</f>
+      </c>
+      <c r="F84" s="203"/>
+      <c r="G84" s="204"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="203">
+        <f>IF('_Datos'!$C85,'_Datos'!$O85,"")</f>
+      </c>
+      <c r="C85" s="204">
+        <f>IF('_Datos'!$C85,'_Datos'!$F85,"")</f>
+      </c>
+      <c r="D85" s="203">
+        <f>IF('_Datos'!$C85,IF('_Datos'!$N85=9999,"(Sin sprint)",'_Datos'!$N85),"")</f>
+      </c>
+      <c r="E85" s="203">
+        <f>IF('_Datos'!$C85,'_Datos'!$AE85,"")</f>
+      </c>
+      <c r="F85" s="203"/>
+      <c r="G85" s="204"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="203">
+        <f>IF('_Datos'!$C86,'_Datos'!$O86,"")</f>
+      </c>
+      <c r="C86" s="204">
+        <f>IF('_Datos'!$C86,'_Datos'!$F86,"")</f>
+      </c>
+      <c r="D86" s="203">
+        <f>IF('_Datos'!$C86,IF('_Datos'!$N86=9999,"(Sin sprint)",'_Datos'!$N86),"")</f>
+      </c>
+      <c r="E86" s="203">
+        <f>IF('_Datos'!$C86,'_Datos'!$AE86,"")</f>
+      </c>
+      <c r="F86" s="203"/>
+      <c r="G86" s="204"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="203">
+        <f>IF('_Datos'!$C87,'_Datos'!$O87,"")</f>
+      </c>
+      <c r="C87" s="204">
+        <f>IF('_Datos'!$C87,'_Datos'!$F87,"")</f>
+      </c>
+      <c r="D87" s="203">
+        <f>IF('_Datos'!$C87,IF('_Datos'!$N87=9999,"(Sin sprint)",'_Datos'!$N87),"")</f>
+      </c>
+      <c r="E87" s="203">
+        <f>IF('_Datos'!$C87,'_Datos'!$AE87,"")</f>
+      </c>
+      <c r="F87" s="203"/>
+      <c r="G87" s="204"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="203">
+        <f>IF('_Datos'!$C88,'_Datos'!$O88,"")</f>
+      </c>
+      <c r="C88" s="204">
+        <f>IF('_Datos'!$C88,'_Datos'!$F88,"")</f>
+      </c>
+      <c r="D88" s="203">
+        <f>IF('_Datos'!$C88,IF('_Datos'!$N88=9999,"(Sin sprint)",'_Datos'!$N88),"")</f>
+      </c>
+      <c r="E88" s="203">
+        <f>IF('_Datos'!$C88,'_Datos'!$AE88,"")</f>
+      </c>
+      <c r="F88" s="203"/>
+      <c r="G88" s="204"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="203">
+        <f>IF('_Datos'!$C89,'_Datos'!$O89,"")</f>
+      </c>
+      <c r="C89" s="204">
+        <f>IF('_Datos'!$C89,'_Datos'!$F89,"")</f>
+      </c>
+      <c r="D89" s="203">
+        <f>IF('_Datos'!$C89,IF('_Datos'!$N89=9999,"(Sin sprint)",'_Datos'!$N89),"")</f>
+      </c>
+      <c r="E89" s="203">
+        <f>IF('_Datos'!$C89,'_Datos'!$AE89,"")</f>
+      </c>
+      <c r="F89" s="203"/>
+      <c r="G89" s="204"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="203">
+        <f>IF('_Datos'!$C90,'_Datos'!$O90,"")</f>
+      </c>
+      <c r="C90" s="204">
+        <f>IF('_Datos'!$C90,'_Datos'!$F90,"")</f>
+      </c>
+      <c r="D90" s="203">
+        <f>IF('_Datos'!$C90,IF('_Datos'!$N90=9999,"(Sin sprint)",'_Datos'!$N90),"")</f>
+      </c>
+      <c r="E90" s="203">
+        <f>IF('_Datos'!$C90,'_Datos'!$AE90,"")</f>
+      </c>
+      <c r="F90" s="203"/>
+      <c r="G90" s="204"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="203">
+        <f>IF('_Datos'!$C91,'_Datos'!$O91,"")</f>
+      </c>
+      <c r="C91" s="204">
+        <f>IF('_Datos'!$C91,'_Datos'!$F91,"")</f>
+      </c>
+      <c r="D91" s="203">
+        <f>IF('_Datos'!$C91,IF('_Datos'!$N91=9999,"(Sin sprint)",'_Datos'!$N91),"")</f>
+      </c>
+      <c r="E91" s="203">
+        <f>IF('_Datos'!$C91,'_Datos'!$AE91,"")</f>
+      </c>
+      <c r="F91" s="203"/>
+      <c r="G91" s="204"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="203">
+        <f>IF('_Datos'!$C92,'_Datos'!$O92,"")</f>
+      </c>
+      <c r="C92" s="204">
+        <f>IF('_Datos'!$C92,'_Datos'!$F92,"")</f>
+      </c>
+      <c r="D92" s="203">
+        <f>IF('_Datos'!$C92,IF('_Datos'!$N92=9999,"(Sin sprint)",'_Datos'!$N92),"")</f>
+      </c>
+      <c r="E92" s="203">
+        <f>IF('_Datos'!$C92,'_Datos'!$AE92,"")</f>
+      </c>
+      <c r="F92" s="203"/>
+      <c r="G92" s="204"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="203">
+        <f>IF('_Datos'!$C93,'_Datos'!$O93,"")</f>
+      </c>
+      <c r="C93" s="204">
+        <f>IF('_Datos'!$C93,'_Datos'!$F93,"")</f>
+      </c>
+      <c r="D93" s="203">
+        <f>IF('_Datos'!$C93,IF('_Datos'!$N93=9999,"(Sin sprint)",'_Datos'!$N93),"")</f>
+      </c>
+      <c r="E93" s="203">
+        <f>IF('_Datos'!$C93,'_Datos'!$AE93,"")</f>
+      </c>
+      <c r="F93" s="203"/>
+      <c r="G93" s="204"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="203">
+        <f>IF('_Datos'!$C94,'_Datos'!$O94,"")</f>
+      </c>
+      <c r="C94" s="204">
+        <f>IF('_Datos'!$C94,'_Datos'!$F94,"")</f>
+      </c>
+      <c r="D94" s="203">
+        <f>IF('_Datos'!$C94,IF('_Datos'!$N94=9999,"(Sin sprint)",'_Datos'!$N94),"")</f>
+      </c>
+      <c r="E94" s="203">
+        <f>IF('_Datos'!$C94,'_Datos'!$AE94,"")</f>
+      </c>
+      <c r="F94" s="203"/>
+      <c r="G94" s="204"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="203">
+        <f>IF('_Datos'!$C95,'_Datos'!$O95,"")</f>
+      </c>
+      <c r="C95" s="204">
+        <f>IF('_Datos'!$C95,'_Datos'!$F95,"")</f>
+      </c>
+      <c r="D95" s="203">
+        <f>IF('_Datos'!$C95,IF('_Datos'!$N95=9999,"(Sin sprint)",'_Datos'!$N95),"")</f>
+      </c>
+      <c r="E95" s="203">
+        <f>IF('_Datos'!$C95,'_Datos'!$AE95,"")</f>
+      </c>
+      <c r="F95" s="203"/>
+      <c r="G95" s="204"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="203">
+        <f>IF('_Datos'!$C96,'_Datos'!$O96,"")</f>
+      </c>
+      <c r="C96" s="204">
+        <f>IF('_Datos'!$C96,'_Datos'!$F96,"")</f>
+      </c>
+      <c r="D96" s="203">
+        <f>IF('_Datos'!$C96,IF('_Datos'!$N96=9999,"(Sin sprint)",'_Datos'!$N96),"")</f>
+      </c>
+      <c r="E96" s="203">
+        <f>IF('_Datos'!$C96,'_Datos'!$AE96,"")</f>
+      </c>
+      <c r="F96" s="203"/>
+      <c r="G96" s="204"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="203">
+        <f>IF('_Datos'!$C97,'_Datos'!$O97,"")</f>
+      </c>
+      <c r="C97" s="204">
+        <f>IF('_Datos'!$C97,'_Datos'!$F97,"")</f>
+      </c>
+      <c r="D97" s="203">
+        <f>IF('_Datos'!$C97,IF('_Datos'!$N97=9999,"(Sin sprint)",'_Datos'!$N97),"")</f>
+      </c>
+      <c r="E97" s="203">
+        <f>IF('_Datos'!$C97,'_Datos'!$AE97,"")</f>
+      </c>
+      <c r="F97" s="203"/>
+      <c r="G97" s="204"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="203">
+        <f>IF('_Datos'!$C98,'_Datos'!$O98,"")</f>
+      </c>
+      <c r="C98" s="204">
+        <f>IF('_Datos'!$C98,'_Datos'!$F98,"")</f>
+      </c>
+      <c r="D98" s="203">
+        <f>IF('_Datos'!$C98,IF('_Datos'!$N98=9999,"(Sin sprint)",'_Datos'!$N98),"")</f>
+      </c>
+      <c r="E98" s="203">
+        <f>IF('_Datos'!$C98,'_Datos'!$AE98,"")</f>
+      </c>
+      <c r="F98" s="203"/>
+      <c r="G98" s="204"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="203">
+        <f>IF('_Datos'!$C99,'_Datos'!$O99,"")</f>
+      </c>
+      <c r="C99" s="204">
+        <f>IF('_Datos'!$C99,'_Datos'!$F99,"")</f>
+      </c>
+      <c r="D99" s="203">
+        <f>IF('_Datos'!$C99,IF('_Datos'!$N99=9999,"(Sin sprint)",'_Datos'!$N99),"")</f>
+      </c>
+      <c r="E99" s="203">
+        <f>IF('_Datos'!$C99,'_Datos'!$AE99,"")</f>
+      </c>
+      <c r="F99" s="203"/>
+      <c r="G99" s="204"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="203">
+        <f>IF('_Datos'!$C100,'_Datos'!$O100,"")</f>
+      </c>
+      <c r="C100" s="204">
+        <f>IF('_Datos'!$C100,'_Datos'!$F100,"")</f>
+      </c>
+      <c r="D100" s="203">
+        <f>IF('_Datos'!$C100,IF('_Datos'!$N100=9999,"(Sin sprint)",'_Datos'!$N100),"")</f>
+      </c>
+      <c r="E100" s="203">
+        <f>IF('_Datos'!$C100,'_Datos'!$AE100,"")</f>
+      </c>
+      <c r="F100" s="203"/>
+      <c r="G100" s="204"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="203">
+        <f>IF('_Datos'!$C101,'_Datos'!$O101,"")</f>
+      </c>
+      <c r="C101" s="204">
+        <f>IF('_Datos'!$C101,'_Datos'!$F101,"")</f>
+      </c>
+      <c r="D101" s="203">
+        <f>IF('_Datos'!$C101,IF('_Datos'!$N101=9999,"(Sin sprint)",'_Datos'!$N101),"")</f>
+      </c>
+      <c r="E101" s="203">
+        <f>IF('_Datos'!$C101,'_Datos'!$AE101,"")</f>
+      </c>
+      <c r="F101" s="203"/>
+      <c r="G101" s="204"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="203">
+        <f>IF('_Datos'!$C102,'_Datos'!$O102,"")</f>
+      </c>
+      <c r="C102" s="204">
+        <f>IF('_Datos'!$C102,'_Datos'!$F102,"")</f>
+      </c>
+      <c r="D102" s="203">
+        <f>IF('_Datos'!$C102,IF('_Datos'!$N102=9999,"(Sin sprint)",'_Datos'!$N102),"")</f>
+      </c>
+      <c r="E102" s="203">
+        <f>IF('_Datos'!$C102,'_Datos'!$AE102,"")</f>
+      </c>
+      <c r="F102" s="203"/>
+      <c r="G102" s="204"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="203">
+        <f>IF('_Datos'!$C103,'_Datos'!$O103,"")</f>
+      </c>
+      <c r="C103" s="204">
+        <f>IF('_Datos'!$C103,'_Datos'!$F103,"")</f>
+      </c>
+      <c r="D103" s="203">
+        <f>IF('_Datos'!$C103,IF('_Datos'!$N103=9999,"(Sin sprint)",'_Datos'!$N103),"")</f>
+      </c>
+      <c r="E103" s="203">
+        <f>IF('_Datos'!$C103,'_Datos'!$AE103,"")</f>
+      </c>
+      <c r="F103" s="203"/>
+      <c r="G103" s="204"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="203">
+        <f>IF('_Datos'!$C104,'_Datos'!$O104,"")</f>
+      </c>
+      <c r="C104" s="204">
+        <f>IF('_Datos'!$C104,'_Datos'!$F104,"")</f>
+      </c>
+      <c r="D104" s="203">
+        <f>IF('_Datos'!$C104,IF('_Datos'!$N104=9999,"(Sin sprint)",'_Datos'!$N104),"")</f>
+      </c>
+      <c r="E104" s="203">
+        <f>IF('_Datos'!$C104,'_Datos'!$AE104,"")</f>
+      </c>
+      <c r="F104" s="203"/>
+      <c r="G104" s="204"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="203">
+        <f>IF('_Datos'!$C105,'_Datos'!$O105,"")</f>
+      </c>
+      <c r="C105" s="204">
+        <f>IF('_Datos'!$C105,'_Datos'!$F105,"")</f>
+      </c>
+      <c r="D105" s="203">
+        <f>IF('_Datos'!$C105,IF('_Datos'!$N105=9999,"(Sin sprint)",'_Datos'!$N105),"")</f>
+      </c>
+      <c r="E105" s="203">
+        <f>IF('_Datos'!$C105,'_Datos'!$AE105,"")</f>
+      </c>
+      <c r="F105" s="203"/>
+      <c r="G105" s="204"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="203">
+        <f>IF('_Datos'!$C106,'_Datos'!$O106,"")</f>
+      </c>
+      <c r="C106" s="204">
+        <f>IF('_Datos'!$C106,'_Datos'!$F106,"")</f>
+      </c>
+      <c r="D106" s="203">
+        <f>IF('_Datos'!$C106,IF('_Datos'!$N106=9999,"(Sin sprint)",'_Datos'!$N106),"")</f>
+      </c>
+      <c r="E106" s="203">
+        <f>IF('_Datos'!$C106,'_Datos'!$AE106,"")</f>
+      </c>
+      <c r="F106" s="203"/>
+      <c r="G106" s="204"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="203">
+        <f>IF('_Datos'!$C107,'_Datos'!$O107,"")</f>
+      </c>
+      <c r="C107" s="204">
+        <f>IF('_Datos'!$C107,'_Datos'!$F107,"")</f>
+      </c>
+      <c r="D107" s="203">
+        <f>IF('_Datos'!$C107,IF('_Datos'!$N107=9999,"(Sin sprint)",'_Datos'!$N107),"")</f>
+      </c>
+      <c r="E107" s="203">
+        <f>IF('_Datos'!$C107,'_Datos'!$AE107,"")</f>
+      </c>
+      <c r="F107" s="203"/>
+      <c r="G107" s="204"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="203">
+        <f>IF('_Datos'!$C108,'_Datos'!$O108,"")</f>
+      </c>
+      <c r="C108" s="204">
+        <f>IF('_Datos'!$C108,'_Datos'!$F108,"")</f>
+      </c>
+      <c r="D108" s="203">
+        <f>IF('_Datos'!$C108,IF('_Datos'!$N108=9999,"(Sin sprint)",'_Datos'!$N108),"")</f>
+      </c>
+      <c r="E108" s="203">
+        <f>IF('_Datos'!$C108,'_Datos'!$AE108,"")</f>
+      </c>
+      <c r="F108" s="203"/>
+      <c r="G108" s="204"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="203">
+        <f>IF('_Datos'!$C109,'_Datos'!$O109,"")</f>
+      </c>
+      <c r="C109" s="204">
+        <f>IF('_Datos'!$C109,'_Datos'!$F109,"")</f>
+      </c>
+      <c r="D109" s="203">
+        <f>IF('_Datos'!$C109,IF('_Datos'!$N109=9999,"(Sin sprint)",'_Datos'!$N109),"")</f>
+      </c>
+      <c r="E109" s="203">
+        <f>IF('_Datos'!$C109,'_Datos'!$AE109,"")</f>
+      </c>
+      <c r="F109" s="203"/>
+      <c r="G109" s="204"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="203">
+        <f>IF('_Datos'!$C110,'_Datos'!$O110,"")</f>
+      </c>
+      <c r="C110" s="204">
+        <f>IF('_Datos'!$C110,'_Datos'!$F110,"")</f>
+      </c>
+      <c r="D110" s="203">
+        <f>IF('_Datos'!$C110,IF('_Datos'!$N110=9999,"(Sin sprint)",'_Datos'!$N110),"")</f>
+      </c>
+      <c r="E110" s="203">
+        <f>IF('_Datos'!$C110,'_Datos'!$AE110,"")</f>
+      </c>
+      <c r="F110" s="203"/>
+      <c r="G110" s="204"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="203">
+        <f>IF('_Datos'!$C111,'_Datos'!$O111,"")</f>
+      </c>
+      <c r="C111" s="204">
+        <f>IF('_Datos'!$C111,'_Datos'!$F111,"")</f>
+      </c>
+      <c r="D111" s="203">
+        <f>IF('_Datos'!$C111,IF('_Datos'!$N111=9999,"(Sin sprint)",'_Datos'!$N111),"")</f>
+      </c>
+      <c r="E111" s="203">
+        <f>IF('_Datos'!$C111,'_Datos'!$AE111,"")</f>
+      </c>
+      <c r="F111" s="203"/>
+      <c r="G111" s="204"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="203">
+        <f>IF('_Datos'!$C112,'_Datos'!$O112,"")</f>
+      </c>
+      <c r="C112" s="204">
+        <f>IF('_Datos'!$C112,'_Datos'!$F112,"")</f>
+      </c>
+      <c r="D112" s="203">
+        <f>IF('_Datos'!$C112,IF('_Datos'!$N112=9999,"(Sin sprint)",'_Datos'!$N112),"")</f>
+      </c>
+      <c r="E112" s="203">
+        <f>IF('_Datos'!$C112,'_Datos'!$AE112,"")</f>
+      </c>
+      <c r="F112" s="203"/>
+      <c r="G112" s="204"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="203">
+        <f>IF('_Datos'!$C113,'_Datos'!$O113,"")</f>
+      </c>
+      <c r="C113" s="204">
+        <f>IF('_Datos'!$C113,'_Datos'!$F113,"")</f>
+      </c>
+      <c r="D113" s="203">
+        <f>IF('_Datos'!$C113,IF('_Datos'!$N113=9999,"(Sin sprint)",'_Datos'!$N113),"")</f>
+      </c>
+      <c r="E113" s="203">
+        <f>IF('_Datos'!$C113,'_Datos'!$AE113,"")</f>
+      </c>
+      <c r="F113" s="203"/>
+      <c r="G113" s="204"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="203">
+        <f>IF('_Datos'!$C114,'_Datos'!$O114,"")</f>
+      </c>
+      <c r="C114" s="204">
+        <f>IF('_Datos'!$C114,'_Datos'!$F114,"")</f>
+      </c>
+      <c r="D114" s="203">
+        <f>IF('_Datos'!$C114,IF('_Datos'!$N114=9999,"(Sin sprint)",'_Datos'!$N114),"")</f>
+      </c>
+      <c r="E114" s="203">
+        <f>IF('_Datos'!$C114,'_Datos'!$AE114,"")</f>
+      </c>
+      <c r="F114" s="203"/>
+      <c r="G114" s="204"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="203">
+        <f>IF('_Datos'!$C115,'_Datos'!$O115,"")</f>
+      </c>
+      <c r="C115" s="204">
+        <f>IF('_Datos'!$C115,'_Datos'!$F115,"")</f>
+      </c>
+      <c r="D115" s="203">
+        <f>IF('_Datos'!$C115,IF('_Datos'!$N115=9999,"(Sin sprint)",'_Datos'!$N115),"")</f>
+      </c>
+      <c r="E115" s="203">
+        <f>IF('_Datos'!$C115,'_Datos'!$AE115,"")</f>
+      </c>
+      <c r="F115" s="203"/>
+      <c r="G115" s="204"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="203">
+        <f>IF('_Datos'!$C116,'_Datos'!$O116,"")</f>
+      </c>
+      <c r="C116" s="204">
+        <f>IF('_Datos'!$C116,'_Datos'!$F116,"")</f>
+      </c>
+      <c r="D116" s="203">
+        <f>IF('_Datos'!$C116,IF('_Datos'!$N116=9999,"(Sin sprint)",'_Datos'!$N116),"")</f>
+      </c>
+      <c r="E116" s="203">
+        <f>IF('_Datos'!$C116,'_Datos'!$AE116,"")</f>
+      </c>
+      <c r="F116" s="203"/>
+      <c r="G116" s="204"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="203">
+        <f>IF('_Datos'!$C117,'_Datos'!$O117,"")</f>
+      </c>
+      <c r="C117" s="204">
+        <f>IF('_Datos'!$C117,'_Datos'!$F117,"")</f>
+      </c>
+      <c r="D117" s="203">
+        <f>IF('_Datos'!$C117,IF('_Datos'!$N117=9999,"(Sin sprint)",'_Datos'!$N117),"")</f>
+      </c>
+      <c r="E117" s="203">
+        <f>IF('_Datos'!$C117,'_Datos'!$AE117,"")</f>
+      </c>
+      <c r="F117" s="203"/>
+      <c r="G117" s="204"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="203">
+        <f>IF('_Datos'!$C118,'_Datos'!$O118,"")</f>
+      </c>
+      <c r="C118" s="204">
+        <f>IF('_Datos'!$C118,'_Datos'!$F118,"")</f>
+      </c>
+      <c r="D118" s="203">
+        <f>IF('_Datos'!$C118,IF('_Datos'!$N118=9999,"(Sin sprint)",'_Datos'!$N118),"")</f>
+      </c>
+      <c r="E118" s="203">
+        <f>IF('_Datos'!$C118,'_Datos'!$AE118,"")</f>
+      </c>
+      <c r="F118" s="203"/>
+      <c r="G118" s="204"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="203">
+        <f>IF('_Datos'!$C119,'_Datos'!$O119,"")</f>
+      </c>
+      <c r="C119" s="204">
+        <f>IF('_Datos'!$C119,'_Datos'!$F119,"")</f>
+      </c>
+      <c r="D119" s="203">
+        <f>IF('_Datos'!$C119,IF('_Datos'!$N119=9999,"(Sin sprint)",'_Datos'!$N119),"")</f>
+      </c>
+      <c r="E119" s="203">
+        <f>IF('_Datos'!$C119,'_Datos'!$AE119,"")</f>
+      </c>
+      <c r="F119" s="203"/>
+      <c r="G119" s="204"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="203">
+        <f>IF('_Datos'!$C120,'_Datos'!$O120,"")</f>
+      </c>
+      <c r="C120" s="204">
+        <f>IF('_Datos'!$C120,'_Datos'!$F120,"")</f>
+      </c>
+      <c r="D120" s="203">
+        <f>IF('_Datos'!$C120,IF('_Datos'!$N120=9999,"(Sin sprint)",'_Datos'!$N120),"")</f>
+      </c>
+      <c r="E120" s="203">
+        <f>IF('_Datos'!$C120,'_Datos'!$AE120,"")</f>
+      </c>
+      <c r="F120" s="203"/>
+      <c r="G120" s="204"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="203">
+        <f>IF('_Datos'!$C121,'_Datos'!$O121,"")</f>
+      </c>
+      <c r="C121" s="204">
+        <f>IF('_Datos'!$C121,'_Datos'!$F121,"")</f>
+      </c>
+      <c r="D121" s="203">
+        <f>IF('_Datos'!$C121,IF('_Datos'!$N121=9999,"(Sin sprint)",'_Datos'!$N121),"")</f>
+      </c>
+      <c r="E121" s="203">
+        <f>IF('_Datos'!$C121,'_Datos'!$AE121,"")</f>
+      </c>
+      <c r="F121" s="203"/>
+      <c r="G121" s="204"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="203">
+        <f>IF('_Datos'!$C122,'_Datos'!$O122,"")</f>
+      </c>
+      <c r="C122" s="204">
+        <f>IF('_Datos'!$C122,'_Datos'!$F122,"")</f>
+      </c>
+      <c r="D122" s="203">
+        <f>IF('_Datos'!$C122,IF('_Datos'!$N122=9999,"(Sin sprint)",'_Datos'!$N122),"")</f>
+      </c>
+      <c r="E122" s="203">
+        <f>IF('_Datos'!$C122,'_Datos'!$AE122,"")</f>
+      </c>
+      <c r="F122" s="203"/>
+      <c r="G122" s="204"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="203">
+        <f>IF('_Datos'!$C123,'_Datos'!$O123,"")</f>
+      </c>
+      <c r="C123" s="204">
+        <f>IF('_Datos'!$C123,'_Datos'!$F123,"")</f>
+      </c>
+      <c r="D123" s="203">
+        <f>IF('_Datos'!$C123,IF('_Datos'!$N123=9999,"(Sin sprint)",'_Datos'!$N123),"")</f>
+      </c>
+      <c r="E123" s="203">
+        <f>IF('_Datos'!$C123,'_Datos'!$AE123,"")</f>
+      </c>
+      <c r="F123" s="203"/>
+      <c r="G123" s="204"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="203">
+        <f>IF('_Datos'!$C124,'_Datos'!$O124,"")</f>
+      </c>
+      <c r="C124" s="204">
+        <f>IF('_Datos'!$C124,'_Datos'!$F124,"")</f>
+      </c>
+      <c r="D124" s="203">
+        <f>IF('_Datos'!$C124,IF('_Datos'!$N124=9999,"(Sin sprint)",'_Datos'!$N124),"")</f>
+      </c>
+      <c r="E124" s="203">
+        <f>IF('_Datos'!$C124,'_Datos'!$AE124,"")</f>
+      </c>
+      <c r="F124" s="203"/>
+      <c r="G124" s="204"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="203">
+        <f>IF('_Datos'!$C125,'_Datos'!$O125,"")</f>
+      </c>
+      <c r="C125" s="204">
+        <f>IF('_Datos'!$C125,'_Datos'!$F125,"")</f>
+      </c>
+      <c r="D125" s="203">
+        <f>IF('_Datos'!$C125,IF('_Datos'!$N125=9999,"(Sin sprint)",'_Datos'!$N125),"")</f>
+      </c>
+      <c r="E125" s="203">
+        <f>IF('_Datos'!$C125,'_Datos'!$AE125,"")</f>
+      </c>
+      <c r="F125" s="203"/>
+      <c r="G125" s="204"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="203">
+        <f>IF('_Datos'!$C126,'_Datos'!$O126,"")</f>
+      </c>
+      <c r="C126" s="204">
+        <f>IF('_Datos'!$C126,'_Datos'!$F126,"")</f>
+      </c>
+      <c r="D126" s="203">
+        <f>IF('_Datos'!$C126,IF('_Datos'!$N126=9999,"(Sin sprint)",'_Datos'!$N126),"")</f>
+      </c>
+      <c r="E126" s="203">
+        <f>IF('_Datos'!$C126,'_Datos'!$AE126,"")</f>
+      </c>
+      <c r="F126" s="203"/>
+      <c r="G126" s="204"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="203">
+        <f>IF('_Datos'!$C127,'_Datos'!$O127,"")</f>
+      </c>
+      <c r="C127" s="204">
+        <f>IF('_Datos'!$C127,'_Datos'!$F127,"")</f>
+      </c>
+      <c r="D127" s="203">
+        <f>IF('_Datos'!$C127,IF('_Datos'!$N127=9999,"(Sin sprint)",'_Datos'!$N127),"")</f>
+      </c>
+      <c r="E127" s="203">
+        <f>IF('_Datos'!$C127,'_Datos'!$AE127,"")</f>
+      </c>
+      <c r="F127" s="203"/>
+      <c r="G127" s="204"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="203">
+        <f>IF('_Datos'!$C128,'_Datos'!$O128,"")</f>
+      </c>
+      <c r="C128" s="204">
+        <f>IF('_Datos'!$C128,'_Datos'!$F128,"")</f>
+      </c>
+      <c r="D128" s="203">
+        <f>IF('_Datos'!$C128,IF('_Datos'!$N128=9999,"(Sin sprint)",'_Datos'!$N128),"")</f>
+      </c>
+      <c r="E128" s="203">
+        <f>IF('_Datos'!$C128,'_Datos'!$AE128,"")</f>
+      </c>
+      <c r="F128" s="203"/>
+      <c r="G128" s="204"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="203">
+        <f>IF('_Datos'!$C129,'_Datos'!$O129,"")</f>
+      </c>
+      <c r="C129" s="204">
+        <f>IF('_Datos'!$C129,'_Datos'!$F129,"")</f>
+      </c>
+      <c r="D129" s="203">
+        <f>IF('_Datos'!$C129,IF('_Datos'!$N129=9999,"(Sin sprint)",'_Datos'!$N129),"")</f>
+      </c>
+      <c r="E129" s="203">
+        <f>IF('_Datos'!$C129,'_Datos'!$AE129,"")</f>
+      </c>
+      <c r="F129" s="203"/>
+      <c r="G129" s="204"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="203">
+        <f>IF('_Datos'!$C130,'_Datos'!$O130,"")</f>
+      </c>
+      <c r="C130" s="204">
+        <f>IF('_Datos'!$C130,'_Datos'!$F130,"")</f>
+      </c>
+      <c r="D130" s="203">
+        <f>IF('_Datos'!$C130,IF('_Datos'!$N130=9999,"(Sin sprint)",'_Datos'!$N130),"")</f>
+      </c>
+      <c r="E130" s="203">
+        <f>IF('_Datos'!$C130,'_Datos'!$AE130,"")</f>
+      </c>
+      <c r="F130" s="203"/>
+      <c r="G130" s="204"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="203">
+        <f>IF('_Datos'!$C131,'_Datos'!$O131,"")</f>
+      </c>
+      <c r="C131" s="204">
+        <f>IF('_Datos'!$C131,'_Datos'!$F131,"")</f>
+      </c>
+      <c r="D131" s="203">
+        <f>IF('_Datos'!$C131,IF('_Datos'!$N131=9999,"(Sin sprint)",'_Datos'!$N131),"")</f>
+      </c>
+      <c r="E131" s="203">
+        <f>IF('_Datos'!$C131,'_Datos'!$AE131,"")</f>
+      </c>
+      <c r="F131" s="203"/>
+      <c r="G131" s="204"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="203">
+        <f>IF('_Datos'!$C132,'_Datos'!$O132,"")</f>
+      </c>
+      <c r="C132" s="204">
+        <f>IF('_Datos'!$C132,'_Datos'!$F132,"")</f>
+      </c>
+      <c r="D132" s="203">
+        <f>IF('_Datos'!$C132,IF('_Datos'!$N132=9999,"(Sin sprint)",'_Datos'!$N132),"")</f>
+      </c>
+      <c r="E132" s="203">
+        <f>IF('_Datos'!$C132,'_Datos'!$AE132,"")</f>
+      </c>
+      <c r="F132" s="203"/>
+      <c r="G132" s="204"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="203">
+        <f>IF('_Datos'!$C133,'_Datos'!$O133,"")</f>
+      </c>
+      <c r="C133" s="204">
+        <f>IF('_Datos'!$C133,'_Datos'!$F133,"")</f>
+      </c>
+      <c r="D133" s="203">
+        <f>IF('_Datos'!$C133,IF('_Datos'!$N133=9999,"(Sin sprint)",'_Datos'!$N133),"")</f>
+      </c>
+      <c r="E133" s="203">
+        <f>IF('_Datos'!$C133,'_Datos'!$AE133,"")</f>
+      </c>
+      <c r="F133" s="203"/>
+      <c r="G133" s="204"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="203">
+        <f>IF('_Datos'!$C134,'_Datos'!$O134,"")</f>
+      </c>
+      <c r="C134" s="204">
+        <f>IF('_Datos'!$C134,'_Datos'!$F134,"")</f>
+      </c>
+      <c r="D134" s="203">
+        <f>IF('_Datos'!$C134,IF('_Datos'!$N134=9999,"(Sin sprint)",'_Datos'!$N134),"")</f>
+      </c>
+      <c r="E134" s="203">
+        <f>IF('_Datos'!$C134,'_Datos'!$AE134,"")</f>
+      </c>
+      <c r="F134" s="203"/>
+      <c r="G134" s="204"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="203">
+        <f>IF('_Datos'!$C135,'_Datos'!$O135,"")</f>
+      </c>
+      <c r="C135" s="204">
+        <f>IF('_Datos'!$C135,'_Datos'!$F135,"")</f>
+      </c>
+      <c r="D135" s="203">
+        <f>IF('_Datos'!$C135,IF('_Datos'!$N135=9999,"(Sin sprint)",'_Datos'!$N135),"")</f>
+      </c>
+      <c r="E135" s="203">
+        <f>IF('_Datos'!$C135,'_Datos'!$AE135,"")</f>
+      </c>
+      <c r="F135" s="203"/>
+      <c r="G135" s="204"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="203">
+        <f>IF('_Datos'!$C136,'_Datos'!$O136,"")</f>
+      </c>
+      <c r="C136" s="204">
+        <f>IF('_Datos'!$C136,'_Datos'!$F136,"")</f>
+      </c>
+      <c r="D136" s="203">
+        <f>IF('_Datos'!$C136,IF('_Datos'!$N136=9999,"(Sin sprint)",'_Datos'!$N136),"")</f>
+      </c>
+      <c r="E136" s="203">
+        <f>IF('_Datos'!$C136,'_Datos'!$AE136,"")</f>
+      </c>
+      <c r="F136" s="203"/>
+      <c r="G136" s="204"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="203">
+        <f>IF('_Datos'!$C137,'_Datos'!$O137,"")</f>
+      </c>
+      <c r="C137" s="204">
+        <f>IF('_Datos'!$C137,'_Datos'!$F137,"")</f>
+      </c>
+      <c r="D137" s="203">
+        <f>IF('_Datos'!$C137,IF('_Datos'!$N137=9999,"(Sin sprint)",'_Datos'!$N137),"")</f>
+      </c>
+      <c r="E137" s="203">
+        <f>IF('_Datos'!$C137,'_Datos'!$AE137,"")</f>
+      </c>
+      <c r="F137" s="203"/>
+      <c r="G137" s="204"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="203">
+        <f>IF('_Datos'!$C138,'_Datos'!$O138,"")</f>
+      </c>
+      <c r="C138" s="204">
+        <f>IF('_Datos'!$C138,'_Datos'!$F138,"")</f>
+      </c>
+      <c r="D138" s="203">
+        <f>IF('_Datos'!$C138,IF('_Datos'!$N138=9999,"(Sin sprint)",'_Datos'!$N138),"")</f>
+      </c>
+      <c r="E138" s="203">
+        <f>IF('_Datos'!$C138,'_Datos'!$AE138,"")</f>
+      </c>
+      <c r="F138" s="203"/>
+      <c r="G138" s="204"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="203">
+        <f>IF('_Datos'!$C139,'_Datos'!$O139,"")</f>
+      </c>
+      <c r="C139" s="204">
+        <f>IF('_Datos'!$C139,'_Datos'!$F139,"")</f>
+      </c>
+      <c r="D139" s="203">
+        <f>IF('_Datos'!$C139,IF('_Datos'!$N139=9999,"(Sin sprint)",'_Datos'!$N139),"")</f>
+      </c>
+      <c r="E139" s="203">
+        <f>IF('_Datos'!$C139,'_Datos'!$AE139,"")</f>
+      </c>
+      <c r="F139" s="203"/>
+      <c r="G139" s="204"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="203">
+        <f>IF('_Datos'!$C140,'_Datos'!$O140,"")</f>
+      </c>
+      <c r="C140" s="204">
+        <f>IF('_Datos'!$C140,'_Datos'!$F140,"")</f>
+      </c>
+      <c r="D140" s="203">
+        <f>IF('_Datos'!$C140,IF('_Datos'!$N140=9999,"(Sin sprint)",'_Datos'!$N140),"")</f>
+      </c>
+      <c r="E140" s="203">
+        <f>IF('_Datos'!$C140,'_Datos'!$AE140,"")</f>
+      </c>
+      <c r="F140" s="203"/>
+      <c r="G140" s="204"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="203">
+        <f>IF('_Datos'!$C141,'_Datos'!$O141,"")</f>
+      </c>
+      <c r="C141" s="204">
+        <f>IF('_Datos'!$C141,'_Datos'!$F141,"")</f>
+      </c>
+      <c r="D141" s="203">
+        <f>IF('_Datos'!$C141,IF('_Datos'!$N141=9999,"(Sin sprint)",'_Datos'!$N141),"")</f>
+      </c>
+      <c r="E141" s="203">
+        <f>IF('_Datos'!$C141,'_Datos'!$AE141,"")</f>
+      </c>
+      <c r="F141" s="203"/>
+      <c r="G141" s="204"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="203">
+        <f>IF('_Datos'!$C142,'_Datos'!$O142,"")</f>
+      </c>
+      <c r="C142" s="204">
+        <f>IF('_Datos'!$C142,'_Datos'!$F142,"")</f>
+      </c>
+      <c r="D142" s="203">
+        <f>IF('_Datos'!$C142,IF('_Datos'!$N142=9999,"(Sin sprint)",'_Datos'!$N142),"")</f>
+      </c>
+      <c r="E142" s="203">
+        <f>IF('_Datos'!$C142,'_Datos'!$AE142,"")</f>
+      </c>
+      <c r="F142" s="203"/>
+      <c r="G142" s="204"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="203">
+        <f>IF('_Datos'!$C143,'_Datos'!$O143,"")</f>
+      </c>
+      <c r="C143" s="204">
+        <f>IF('_Datos'!$C143,'_Datos'!$F143,"")</f>
+      </c>
+      <c r="D143" s="203">
+        <f>IF('_Datos'!$C143,IF('_Datos'!$N143=9999,"(Sin sprint)",'_Datos'!$N143),"")</f>
+      </c>
+      <c r="E143" s="203">
+        <f>IF('_Datos'!$C143,'_Datos'!$AE143,"")</f>
+      </c>
+      <c r="F143" s="203"/>
+      <c r="G143" s="204"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="203">
+        <f>IF('_Datos'!$C144,'_Datos'!$O144,"")</f>
+      </c>
+      <c r="C144" s="204">
+        <f>IF('_Datos'!$C144,'_Datos'!$F144,"")</f>
+      </c>
+      <c r="D144" s="203">
+        <f>IF('_Datos'!$C144,IF('_Datos'!$N144=9999,"(Sin sprint)",'_Datos'!$N144),"")</f>
+      </c>
+      <c r="E144" s="203">
+        <f>IF('_Datos'!$C144,'_Datos'!$AE144,"")</f>
+      </c>
+      <c r="F144" s="203"/>
+      <c r="G144" s="204"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="203">
+        <f>IF('_Datos'!$C145,'_Datos'!$O145,"")</f>
+      </c>
+      <c r="C145" s="204">
+        <f>IF('_Datos'!$C145,'_Datos'!$F145,"")</f>
+      </c>
+      <c r="D145" s="203">
+        <f>IF('_Datos'!$C145,IF('_Datos'!$N145=9999,"(Sin sprint)",'_Datos'!$N145),"")</f>
+      </c>
+      <c r="E145" s="203">
+        <f>IF('_Datos'!$C145,'_Datos'!$AE145,"")</f>
+      </c>
+      <c r="F145" s="203"/>
+      <c r="G145" s="204"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="203">
+        <f>IF('_Datos'!$C146,'_Datos'!$O146,"")</f>
+      </c>
+      <c r="C146" s="204">
+        <f>IF('_Datos'!$C146,'_Datos'!$F146,"")</f>
+      </c>
+      <c r="D146" s="203">
+        <f>IF('_Datos'!$C146,IF('_Datos'!$N146=9999,"(Sin sprint)",'_Datos'!$N146),"")</f>
+      </c>
+      <c r="E146" s="203">
+        <f>IF('_Datos'!$C146,'_Datos'!$AE146,"")</f>
+      </c>
+      <c r="F146" s="203"/>
+      <c r="G146" s="204"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="203">
+        <f>IF('_Datos'!$C147,'_Datos'!$O147,"")</f>
+      </c>
+      <c r="C147" s="204">
+        <f>IF('_Datos'!$C147,'_Datos'!$F147,"")</f>
+      </c>
+      <c r="D147" s="203">
+        <f>IF('_Datos'!$C147,IF('_Datos'!$N147=9999,"(Sin sprint)",'_Datos'!$N147),"")</f>
+      </c>
+      <c r="E147" s="203">
+        <f>IF('_Datos'!$C147,'_Datos'!$AE147,"")</f>
+      </c>
+      <c r="F147" s="203"/>
+      <c r="G147" s="204"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="203">
+        <f>IF('_Datos'!$C148,'_Datos'!$O148,"")</f>
+      </c>
+      <c r="C148" s="204">
+        <f>IF('_Datos'!$C148,'_Datos'!$F148,"")</f>
+      </c>
+      <c r="D148" s="203">
+        <f>IF('_Datos'!$C148,IF('_Datos'!$N148=9999,"(Sin sprint)",'_Datos'!$N148),"")</f>
+      </c>
+      <c r="E148" s="203">
+        <f>IF('_Datos'!$C148,'_Datos'!$AE148,"")</f>
+      </c>
+      <c r="F148" s="203"/>
+      <c r="G148" s="204"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="203">
+        <f>IF('_Datos'!$C149,'_Datos'!$O149,"")</f>
+      </c>
+      <c r="C149" s="204">
+        <f>IF('_Datos'!$C149,'_Datos'!$F149,"")</f>
+      </c>
+      <c r="D149" s="203">
+        <f>IF('_Datos'!$C149,IF('_Datos'!$N149=9999,"(Sin sprint)",'_Datos'!$N149),"")</f>
+      </c>
+      <c r="E149" s="203">
+        <f>IF('_Datos'!$C149,'_Datos'!$AE149,"")</f>
+      </c>
+      <c r="F149" s="203"/>
+      <c r="G149" s="204"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="203">
+        <f>IF('_Datos'!$C150,'_Datos'!$O150,"")</f>
+      </c>
+      <c r="C150" s="204">
+        <f>IF('_Datos'!$C150,'_Datos'!$F150,"")</f>
+      </c>
+      <c r="D150" s="203">
+        <f>IF('_Datos'!$C150,IF('_Datos'!$N150=9999,"(Sin sprint)",'_Datos'!$N150),"")</f>
+      </c>
+      <c r="E150" s="203">
+        <f>IF('_Datos'!$C150,'_Datos'!$AE150,"")</f>
+      </c>
+      <c r="F150" s="203"/>
+      <c r="G150" s="204"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="203">
+        <f>IF('_Datos'!$C151,'_Datos'!$O151,"")</f>
+      </c>
+      <c r="C151" s="204">
+        <f>IF('_Datos'!$C151,'_Datos'!$F151,"")</f>
+      </c>
+      <c r="D151" s="203">
+        <f>IF('_Datos'!$C151,IF('_Datos'!$N151=9999,"(Sin sprint)",'_Datos'!$N151),"")</f>
+      </c>
+      <c r="E151" s="203">
+        <f>IF('_Datos'!$C151,'_Datos'!$AE151,"")</f>
+      </c>
+      <c r="F151" s="203"/>
+      <c r="G151" s="204"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="203">
+        <f>IF('_Datos'!$C152,'_Datos'!$O152,"")</f>
+      </c>
+      <c r="C152" s="204">
+        <f>IF('_Datos'!$C152,'_Datos'!$F152,"")</f>
+      </c>
+      <c r="D152" s="203">
+        <f>IF('_Datos'!$C152,IF('_Datos'!$N152=9999,"(Sin sprint)",'_Datos'!$N152),"")</f>
+      </c>
+      <c r="E152" s="203">
+        <f>IF('_Datos'!$C152,'_Datos'!$AE152,"")</f>
+      </c>
+      <c r="F152" s="203"/>
+      <c r="G152" s="204"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="203">
+        <f>IF('_Datos'!$C153,'_Datos'!$O153,"")</f>
+      </c>
+      <c r="C153" s="204">
+        <f>IF('_Datos'!$C153,'_Datos'!$F153,"")</f>
+      </c>
+      <c r="D153" s="203">
+        <f>IF('_Datos'!$C153,IF('_Datos'!$N153=9999,"(Sin sprint)",'_Datos'!$N153),"")</f>
+      </c>
+      <c r="E153" s="203">
+        <f>IF('_Datos'!$C153,'_Datos'!$AE153,"")</f>
+      </c>
+      <c r="F153" s="203"/>
+      <c r="G153" s="204"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="203">
+        <f>IF('_Datos'!$C154,'_Datos'!$O154,"")</f>
+      </c>
+      <c r="C154" s="204">
+        <f>IF('_Datos'!$C154,'_Datos'!$F154,"")</f>
+      </c>
+      <c r="D154" s="203">
+        <f>IF('_Datos'!$C154,IF('_Datos'!$N154=9999,"(Sin sprint)",'_Datos'!$N154),"")</f>
+      </c>
+      <c r="E154" s="203">
+        <f>IF('_Datos'!$C154,'_Datos'!$AE154,"")</f>
+      </c>
+      <c r="F154" s="203"/>
+      <c r="G154" s="204"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="203">
+        <f>IF('_Datos'!$C155,'_Datos'!$O155,"")</f>
+      </c>
+      <c r="C155" s="204">
+        <f>IF('_Datos'!$C155,'_Datos'!$F155,"")</f>
+      </c>
+      <c r="D155" s="203">
+        <f>IF('_Datos'!$C155,IF('_Datos'!$N155=9999,"(Sin sprint)",'_Datos'!$N155),"")</f>
+      </c>
+      <c r="E155" s="203">
+        <f>IF('_Datos'!$C155,'_Datos'!$AE155,"")</f>
+      </c>
+      <c r="F155" s="203"/>
+      <c r="G155" s="204"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="203">
+        <f>IF('_Datos'!$C156,'_Datos'!$O156,"")</f>
+      </c>
+      <c r="C156" s="204">
+        <f>IF('_Datos'!$C156,'_Datos'!$F156,"")</f>
+      </c>
+      <c r="D156" s="203">
+        <f>IF('_Datos'!$C156,IF('_Datos'!$N156=9999,"(Sin sprint)",'_Datos'!$N156),"")</f>
+      </c>
+      <c r="E156" s="203">
+        <f>IF('_Datos'!$C156,'_Datos'!$AE156,"")</f>
+      </c>
+      <c r="F156" s="203"/>
+      <c r="G156" s="204"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="203">
+        <f>IF('_Datos'!$C157,'_Datos'!$O157,"")</f>
+      </c>
+      <c r="C157" s="204">
+        <f>IF('_Datos'!$C157,'_Datos'!$F157,"")</f>
+      </c>
+      <c r="D157" s="203">
+        <f>IF('_Datos'!$C157,IF('_Datos'!$N157=9999,"(Sin sprint)",'_Datos'!$N157),"")</f>
+      </c>
+      <c r="E157" s="203">
+        <f>IF('_Datos'!$C157,'_Datos'!$AE157,"")</f>
+      </c>
+      <c r="F157" s="203"/>
+      <c r="G157" s="204"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="203">
+        <f>IF('_Datos'!$C158,'_Datos'!$O158,"")</f>
+      </c>
+      <c r="C158" s="204">
+        <f>IF('_Datos'!$C158,'_Datos'!$F158,"")</f>
+      </c>
+      <c r="D158" s="203">
+        <f>IF('_Datos'!$C158,IF('_Datos'!$N158=9999,"(Sin sprint)",'_Datos'!$N158),"")</f>
+      </c>
+      <c r="E158" s="203">
+        <f>IF('_Datos'!$C158,'_Datos'!$AE158,"")</f>
+      </c>
+      <c r="F158" s="203"/>
+      <c r="G158" s="204"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="203">
+        <f>IF('_Datos'!$C159,'_Datos'!$O159,"")</f>
+      </c>
+      <c r="C159" s="204">
+        <f>IF('_Datos'!$C159,'_Datos'!$F159,"")</f>
+      </c>
+      <c r="D159" s="203">
+        <f>IF('_Datos'!$C159,IF('_Datos'!$N159=9999,"(Sin sprint)",'_Datos'!$N159),"")</f>
+      </c>
+      <c r="E159" s="203">
+        <f>IF('_Datos'!$C159,'_Datos'!$AE159,"")</f>
+      </c>
+      <c r="F159" s="203"/>
+      <c r="G159" s="204"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="203">
+        <f>IF('_Datos'!$C160,'_Datos'!$O160,"")</f>
+      </c>
+      <c r="C160" s="204">
+        <f>IF('_Datos'!$C160,'_Datos'!$F160,"")</f>
+      </c>
+      <c r="D160" s="203">
+        <f>IF('_Datos'!$C160,IF('_Datos'!$N160=9999,"(Sin sprint)",'_Datos'!$N160),"")</f>
+      </c>
+      <c r="E160" s="203">
+        <f>IF('_Datos'!$C160,'_Datos'!$AE160,"")</f>
+      </c>
+      <c r="F160" s="203"/>
+      <c r="G160" s="204"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="203">
+        <f>IF('_Datos'!$C161,'_Datos'!$O161,"")</f>
+      </c>
+      <c r="C161" s="204">
+        <f>IF('_Datos'!$C161,'_Datos'!$F161,"")</f>
+      </c>
+      <c r="D161" s="203">
+        <f>IF('_Datos'!$C161,IF('_Datos'!$N161=9999,"(Sin sprint)",'_Datos'!$N161),"")</f>
+      </c>
+      <c r="E161" s="203">
+        <f>IF('_Datos'!$C161,'_Datos'!$AE161,"")</f>
+      </c>
+      <c r="F161" s="203"/>
+      <c r="G161" s="204"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="203">
+        <f>IF('_Datos'!$C162,'_Datos'!$O162,"")</f>
+      </c>
+      <c r="C162" s="204">
+        <f>IF('_Datos'!$C162,'_Datos'!$F162,"")</f>
+      </c>
+      <c r="D162" s="203">
+        <f>IF('_Datos'!$C162,IF('_Datos'!$N162=9999,"(Sin sprint)",'_Datos'!$N162),"")</f>
+      </c>
+      <c r="E162" s="203">
+        <f>IF('_Datos'!$C162,'_Datos'!$AE162,"")</f>
+      </c>
+      <c r="F162" s="203"/>
+      <c r="G162" s="204"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="203">
+        <f>IF('_Datos'!$C163,'_Datos'!$O163,"")</f>
+      </c>
+      <c r="C163" s="204">
+        <f>IF('_Datos'!$C163,'_Datos'!$F163,"")</f>
+      </c>
+      <c r="D163" s="203">
+        <f>IF('_Datos'!$C163,IF('_Datos'!$N163=9999,"(Sin sprint)",'_Datos'!$N163),"")</f>
+      </c>
+      <c r="E163" s="203">
+        <f>IF('_Datos'!$C163,'_Datos'!$AE163,"")</f>
+      </c>
+      <c r="F163" s="203"/>
+      <c r="G163" s="204"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="203">
+        <f>IF('_Datos'!$C164,'_Datos'!$O164,"")</f>
+      </c>
+      <c r="C164" s="204">
+        <f>IF('_Datos'!$C164,'_Datos'!$F164,"")</f>
+      </c>
+      <c r="D164" s="203">
+        <f>IF('_Datos'!$C164,IF('_Datos'!$N164=9999,"(Sin sprint)",'_Datos'!$N164),"")</f>
+      </c>
+      <c r="E164" s="203">
+        <f>IF('_Datos'!$C164,'_Datos'!$AE164,"")</f>
+      </c>
+      <c r="F164" s="203"/>
+      <c r="G164" s="204"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="203">
+        <f>IF('_Datos'!$C165,'_Datos'!$O165,"")</f>
+      </c>
+      <c r="C165" s="204">
+        <f>IF('_Datos'!$C165,'_Datos'!$F165,"")</f>
+      </c>
+      <c r="D165" s="203">
+        <f>IF('_Datos'!$C165,IF('_Datos'!$N165=9999,"(Sin sprint)",'_Datos'!$N165),"")</f>
+      </c>
+      <c r="E165" s="203">
+        <f>IF('_Datos'!$C165,'_Datos'!$AE165,"")</f>
+      </c>
+      <c r="F165" s="203"/>
+      <c r="G165" s="204"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="203">
+        <f>IF('_Datos'!$C166,'_Datos'!$O166,"")</f>
+      </c>
+      <c r="C166" s="204">
+        <f>IF('_Datos'!$C166,'_Datos'!$F166,"")</f>
+      </c>
+      <c r="D166" s="203">
+        <f>IF('_Datos'!$C166,IF('_Datos'!$N166=9999,"(Sin sprint)",'_Datos'!$N166),"")</f>
+      </c>
+      <c r="E166" s="203">
+        <f>IF('_Datos'!$C166,'_Datos'!$AE166,"")</f>
+      </c>
+      <c r="F166" s="203"/>
+      <c r="G166" s="204"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="203">
+        <f>IF('_Datos'!$C167,'_Datos'!$O167,"")</f>
+      </c>
+      <c r="C167" s="204">
+        <f>IF('_Datos'!$C167,'_Datos'!$F167,"")</f>
+      </c>
+      <c r="D167" s="203">
+        <f>IF('_Datos'!$C167,IF('_Datos'!$N167=9999,"(Sin sprint)",'_Datos'!$N167),"")</f>
+      </c>
+      <c r="E167" s="203">
+        <f>IF('_Datos'!$C167,'_Datos'!$AE167,"")</f>
+      </c>
+      <c r="F167" s="203"/>
+      <c r="G167" s="204"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="203">
+        <f>IF('_Datos'!$C168,'_Datos'!$O168,"")</f>
+      </c>
+      <c r="C168" s="204">
+        <f>IF('_Datos'!$C168,'_Datos'!$F168,"")</f>
+      </c>
+      <c r="D168" s="203">
+        <f>IF('_Datos'!$C168,IF('_Datos'!$N168=9999,"(Sin sprint)",'_Datos'!$N168),"")</f>
+      </c>
+      <c r="E168" s="203">
+        <f>IF('_Datos'!$C168,'_Datos'!$AE168,"")</f>
+      </c>
+      <c r="F168" s="203"/>
+      <c r="G168" s="204"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="203">
+        <f>IF('_Datos'!$C169,'_Datos'!$O169,"")</f>
+      </c>
+      <c r="C169" s="204">
+        <f>IF('_Datos'!$C169,'_Datos'!$F169,"")</f>
+      </c>
+      <c r="D169" s="203">
+        <f>IF('_Datos'!$C169,IF('_Datos'!$N169=9999,"(Sin sprint)",'_Datos'!$N169),"")</f>
+      </c>
+      <c r="E169" s="203">
+        <f>IF('_Datos'!$C169,'_Datos'!$AE169,"")</f>
+      </c>
+      <c r="F169" s="203"/>
+      <c r="G169" s="204"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="203">
+        <f>IF('_Datos'!$C170,'_Datos'!$O170,"")</f>
+      </c>
+      <c r="C170" s="204">
+        <f>IF('_Datos'!$C170,'_Datos'!$F170,"")</f>
+      </c>
+      <c r="D170" s="203">
+        <f>IF('_Datos'!$C170,IF('_Datos'!$N170=9999,"(Sin sprint)",'_Datos'!$N170),"")</f>
+      </c>
+      <c r="E170" s="203">
+        <f>IF('_Datos'!$C170,'_Datos'!$AE170,"")</f>
+      </c>
+      <c r="F170" s="203"/>
+      <c r="G170" s="204"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="203">
+        <f>IF('_Datos'!$C171,'_Datos'!$O171,"")</f>
+      </c>
+      <c r="C171" s="204">
+        <f>IF('_Datos'!$C171,'_Datos'!$F171,"")</f>
+      </c>
+      <c r="D171" s="203">
+        <f>IF('_Datos'!$C171,IF('_Datos'!$N171=9999,"(Sin sprint)",'_Datos'!$N171),"")</f>
+      </c>
+      <c r="E171" s="203">
+        <f>IF('_Datos'!$C171,'_Datos'!$AE171,"")</f>
+      </c>
+      <c r="F171" s="203"/>
+      <c r="G171" s="204"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="203">
+        <f>IF('_Datos'!$C172,'_Datos'!$O172,"")</f>
+      </c>
+      <c r="C172" s="204">
+        <f>IF('_Datos'!$C172,'_Datos'!$F172,"")</f>
+      </c>
+      <c r="D172" s="203">
+        <f>IF('_Datos'!$C172,IF('_Datos'!$N172=9999,"(Sin sprint)",'_Datos'!$N172),"")</f>
+      </c>
+      <c r="E172" s="203">
+        <f>IF('_Datos'!$C172,'_Datos'!$AE172,"")</f>
+      </c>
+      <c r="F172" s="203"/>
+      <c r="G172" s="204"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="203">
+        <f>IF('_Datos'!$C173,'_Datos'!$O173,"")</f>
+      </c>
+      <c r="C173" s="204">
+        <f>IF('_Datos'!$C173,'_Datos'!$F173,"")</f>
+      </c>
+      <c r="D173" s="203">
+        <f>IF('_Datos'!$C173,IF('_Datos'!$N173=9999,"(Sin sprint)",'_Datos'!$N173),"")</f>
+      </c>
+      <c r="E173" s="203">
+        <f>IF('_Datos'!$C173,'_Datos'!$AE173,"")</f>
+      </c>
+      <c r="F173" s="203"/>
+      <c r="G173" s="204"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="203">
+        <f>IF('_Datos'!$C174,'_Datos'!$O174,"")</f>
+      </c>
+      <c r="C174" s="204">
+        <f>IF('_Datos'!$C174,'_Datos'!$F174,"")</f>
+      </c>
+      <c r="D174" s="203">
+        <f>IF('_Datos'!$C174,IF('_Datos'!$N174=9999,"(Sin sprint)",'_Datos'!$N174),"")</f>
+      </c>
+      <c r="E174" s="203">
+        <f>IF('_Datos'!$C174,'_Datos'!$AE174,"")</f>
+      </c>
+      <c r="F174" s="203"/>
+      <c r="G174" s="204"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="203">
+        <f>IF('_Datos'!$C175,'_Datos'!$O175,"")</f>
+      </c>
+      <c r="C175" s="204">
+        <f>IF('_Datos'!$C175,'_Datos'!$F175,"")</f>
+      </c>
+      <c r="D175" s="203">
+        <f>IF('_Datos'!$C175,IF('_Datos'!$N175=9999,"(Sin sprint)",'_Datos'!$N175),"")</f>
+      </c>
+      <c r="E175" s="203">
+        <f>IF('_Datos'!$C175,'_Datos'!$AE175,"")</f>
+      </c>
+      <c r="F175" s="203"/>
+      <c r="G175" s="204"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="203">
+        <f>IF('_Datos'!$C176,'_Datos'!$O176,"")</f>
+      </c>
+      <c r="C176" s="204">
+        <f>IF('_Datos'!$C176,'_Datos'!$F176,"")</f>
+      </c>
+      <c r="D176" s="203">
+        <f>IF('_Datos'!$C176,IF('_Datos'!$N176=9999,"(Sin sprint)",'_Datos'!$N176),"")</f>
+      </c>
+      <c r="E176" s="203">
+        <f>IF('_Datos'!$C176,'_Datos'!$AE176,"")</f>
+      </c>
+      <c r="F176" s="203"/>
+      <c r="G176" s="204"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="203">
+        <f>IF('_Datos'!$C177,'_Datos'!$O177,"")</f>
+      </c>
+      <c r="C177" s="204">
+        <f>IF('_Datos'!$C177,'_Datos'!$F177,"")</f>
+      </c>
+      <c r="D177" s="203">
+        <f>IF('_Datos'!$C177,IF('_Datos'!$N177=9999,"(Sin sprint)",'_Datos'!$N177),"")</f>
+      </c>
+      <c r="E177" s="203">
+        <f>IF('_Datos'!$C177,'_Datos'!$AE177,"")</f>
+      </c>
+      <c r="F177" s="203"/>
+      <c r="G177" s="204"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="203">
+        <f>IF('_Datos'!$C178,'_Datos'!$O178,"")</f>
+      </c>
+      <c r="C178" s="204">
+        <f>IF('_Datos'!$C178,'_Datos'!$F178,"")</f>
+      </c>
+      <c r="D178" s="203">
+        <f>IF('_Datos'!$C178,IF('_Datos'!$N178=9999,"(Sin sprint)",'_Datos'!$N178),"")</f>
+      </c>
+      <c r="E178" s="203">
+        <f>IF('_Datos'!$C178,'_Datos'!$AE178,"")</f>
+      </c>
+      <c r="F178" s="203"/>
+      <c r="G178" s="204"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="203">
+        <f>IF('_Datos'!$C179,'_Datos'!$O179,"")</f>
+      </c>
+      <c r="C179" s="204">
+        <f>IF('_Datos'!$C179,'_Datos'!$F179,"")</f>
+      </c>
+      <c r="D179" s="203">
+        <f>IF('_Datos'!$C179,IF('_Datos'!$N179=9999,"(Sin sprint)",'_Datos'!$N179),"")</f>
+      </c>
+      <c r="E179" s="203">
+        <f>IF('_Datos'!$C179,'_Datos'!$AE179,"")</f>
+      </c>
+      <c r="F179" s="203"/>
+      <c r="G179" s="204"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="203">
+        <f>IF('_Datos'!$C180,'_Datos'!$O180,"")</f>
+      </c>
+      <c r="C180" s="204">
+        <f>IF('_Datos'!$C180,'_Datos'!$F180,"")</f>
+      </c>
+      <c r="D180" s="203">
+        <f>IF('_Datos'!$C180,IF('_Datos'!$N180=9999,"(Sin sprint)",'_Datos'!$N180),"")</f>
+      </c>
+      <c r="E180" s="203">
+        <f>IF('_Datos'!$C180,'_Datos'!$AE180,"")</f>
+      </c>
+      <c r="F180" s="203"/>
+      <c r="G180" s="204"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="203">
+        <f>IF('_Datos'!$C181,'_Datos'!$O181,"")</f>
+      </c>
+      <c r="C181" s="204">
+        <f>IF('_Datos'!$C181,'_Datos'!$F181,"")</f>
+      </c>
+      <c r="D181" s="203">
+        <f>IF('_Datos'!$C181,IF('_Datos'!$N181=9999,"(Sin sprint)",'_Datos'!$N181),"")</f>
+      </c>
+      <c r="E181" s="203">
+        <f>IF('_Datos'!$C181,'_Datos'!$AE181,"")</f>
+      </c>
+      <c r="F181" s="203"/>
+      <c r="G181" s="204"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="203">
+        <f>IF('_Datos'!$C182,'_Datos'!$O182,"")</f>
+      </c>
+      <c r="C182" s="204">
+        <f>IF('_Datos'!$C182,'_Datos'!$F182,"")</f>
+      </c>
+      <c r="D182" s="203">
+        <f>IF('_Datos'!$C182,IF('_Datos'!$N182=9999,"(Sin sprint)",'_Datos'!$N182),"")</f>
+      </c>
+      <c r="E182" s="203">
+        <f>IF('_Datos'!$C182,'_Datos'!$AE182,"")</f>
+      </c>
+      <c r="F182" s="203"/>
+      <c r="G182" s="204"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="203">
+        <f>IF('_Datos'!$C183,'_Datos'!$O183,"")</f>
+      </c>
+      <c r="C183" s="204">
+        <f>IF('_Datos'!$C183,'_Datos'!$F183,"")</f>
+      </c>
+      <c r="D183" s="203">
+        <f>IF('_Datos'!$C183,IF('_Datos'!$N183=9999,"(Sin sprint)",'_Datos'!$N183),"")</f>
+      </c>
+      <c r="E183" s="203">
+        <f>IF('_Datos'!$C183,'_Datos'!$AE183,"")</f>
+      </c>
+      <c r="F183" s="203"/>
+      <c r="G183" s="204"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="203">
+        <f>IF('_Datos'!$C184,'_Datos'!$O184,"")</f>
+      </c>
+      <c r="C184" s="204">
+        <f>IF('_Datos'!$C184,'_Datos'!$F184,"")</f>
+      </c>
+      <c r="D184" s="203">
+        <f>IF('_Datos'!$C184,IF('_Datos'!$N184=9999,"(Sin sprint)",'_Datos'!$N184),"")</f>
+      </c>
+      <c r="E184" s="203">
+        <f>IF('_Datos'!$C184,'_Datos'!$AE184,"")</f>
+      </c>
+      <c r="F184" s="203"/>
+      <c r="G184" s="204"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="203">
+        <f>IF('_Datos'!$C185,'_Datos'!$O185,"")</f>
+      </c>
+      <c r="C185" s="204">
+        <f>IF('_Datos'!$C185,'_Datos'!$F185,"")</f>
+      </c>
+      <c r="D185" s="203">
+        <f>IF('_Datos'!$C185,IF('_Datos'!$N185=9999,"(Sin sprint)",'_Datos'!$N185),"")</f>
+      </c>
+      <c r="E185" s="203">
+        <f>IF('_Datos'!$C185,'_Datos'!$AE185,"")</f>
+      </c>
+      <c r="F185" s="203"/>
+      <c r="G185" s="204"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="203">
+        <f>IF('_Datos'!$C186,'_Datos'!$O186,"")</f>
+      </c>
+      <c r="C186" s="204">
+        <f>IF('_Datos'!$C186,'_Datos'!$F186,"")</f>
+      </c>
+      <c r="D186" s="203">
+        <f>IF('_Datos'!$C186,IF('_Datos'!$N186=9999,"(Sin sprint)",'_Datos'!$N186),"")</f>
+      </c>
+      <c r="E186" s="203">
+        <f>IF('_Datos'!$C186,'_Datos'!$AE186,"")</f>
+      </c>
+      <c r="F186" s="203"/>
+      <c r="G186" s="204"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="203">
+        <f>IF('_Datos'!$C187,'_Datos'!$O187,"")</f>
+      </c>
+      <c r="C187" s="204">
+        <f>IF('_Datos'!$C187,'_Datos'!$F187,"")</f>
+      </c>
+      <c r="D187" s="203">
+        <f>IF('_Datos'!$C187,IF('_Datos'!$N187=9999,"(Sin sprint)",'_Datos'!$N187),"")</f>
+      </c>
+      <c r="E187" s="203">
+        <f>IF('_Datos'!$C187,'_Datos'!$AE187,"")</f>
+      </c>
+      <c r="F187" s="203"/>
+      <c r="G187" s="204"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="203">
+        <f>IF('_Datos'!$C188,'_Datos'!$O188,"")</f>
+      </c>
+      <c r="C188" s="204">
+        <f>IF('_Datos'!$C188,'_Datos'!$F188,"")</f>
+      </c>
+      <c r="D188" s="203">
+        <f>IF('_Datos'!$C188,IF('_Datos'!$N188=9999,"(Sin sprint)",'_Datos'!$N188),"")</f>
+      </c>
+      <c r="E188" s="203">
+        <f>IF('_Datos'!$C188,'_Datos'!$AE188,"")</f>
+      </c>
+      <c r="F188" s="203"/>
+      <c r="G188" s="204"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="203">
+        <f>IF('_Datos'!$C189,'_Datos'!$O189,"")</f>
+      </c>
+      <c r="C189" s="204">
+        <f>IF('_Datos'!$C189,'_Datos'!$F189,"")</f>
+      </c>
+      <c r="D189" s="203">
+        <f>IF('_Datos'!$C189,IF('_Datos'!$N189=9999,"(Sin sprint)",'_Datos'!$N189),"")</f>
+      </c>
+      <c r="E189" s="203">
+        <f>IF('_Datos'!$C189,'_Datos'!$AE189,"")</f>
+      </c>
+      <c r="F189" s="203"/>
+      <c r="G189" s="204"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="203">
+        <f>IF('_Datos'!$C190,'_Datos'!$O190,"")</f>
+      </c>
+      <c r="C190" s="204">
+        <f>IF('_Datos'!$C190,'_Datos'!$F190,"")</f>
+      </c>
+      <c r="D190" s="203">
+        <f>IF('_Datos'!$C190,IF('_Datos'!$N190=9999,"(Sin sprint)",'_Datos'!$N190),"")</f>
+      </c>
+      <c r="E190" s="203">
+        <f>IF('_Datos'!$C190,'_Datos'!$AE190,"")</f>
+      </c>
+      <c r="F190" s="203"/>
+      <c r="G190" s="204"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="203">
+        <f>IF('_Datos'!$C191,'_Datos'!$O191,"")</f>
+      </c>
+      <c r="C191" s="204">
+        <f>IF('_Datos'!$C191,'_Datos'!$F191,"")</f>
+      </c>
+      <c r="D191" s="203">
+        <f>IF('_Datos'!$C191,IF('_Datos'!$N191=9999,"(Sin sprint)",'_Datos'!$N191),"")</f>
+      </c>
+      <c r="E191" s="203">
+        <f>IF('_Datos'!$C191,'_Datos'!$AE191,"")</f>
+      </c>
+      <c r="F191" s="203"/>
+      <c r="G191" s="204"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="203">
+        <f>IF('_Datos'!$C192,'_Datos'!$O192,"")</f>
+      </c>
+      <c r="C192" s="204">
+        <f>IF('_Datos'!$C192,'_Datos'!$F192,"")</f>
+      </c>
+      <c r="D192" s="203">
+        <f>IF('_Datos'!$C192,IF('_Datos'!$N192=9999,"(Sin sprint)",'_Datos'!$N192),"")</f>
+      </c>
+      <c r="E192" s="203">
+        <f>IF('_Datos'!$C192,'_Datos'!$AE192,"")</f>
+      </c>
+      <c r="F192" s="203"/>
+      <c r="G192" s="204"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="203">
+        <f>IF('_Datos'!$C193,'_Datos'!$O193,"")</f>
+      </c>
+      <c r="C193" s="204">
+        <f>IF('_Datos'!$C193,'_Datos'!$F193,"")</f>
+      </c>
+      <c r="D193" s="203">
+        <f>IF('_Datos'!$C193,IF('_Datos'!$N193=9999,"(Sin sprint)",'_Datos'!$N193),"")</f>
+      </c>
+      <c r="E193" s="203">
+        <f>IF('_Datos'!$C193,'_Datos'!$AE193,"")</f>
+      </c>
+      <c r="F193" s="203"/>
+      <c r="G193" s="204"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="203">
+        <f>IF('_Datos'!$C194,'_Datos'!$O194,"")</f>
+      </c>
+      <c r="C194" s="204">
+        <f>IF('_Datos'!$C194,'_Datos'!$F194,"")</f>
+      </c>
+      <c r="D194" s="203">
+        <f>IF('_Datos'!$C194,IF('_Datos'!$N194=9999,"(Sin sprint)",'_Datos'!$N194),"")</f>
+      </c>
+      <c r="E194" s="203">
+        <f>IF('_Datos'!$C194,'_Datos'!$AE194,"")</f>
+      </c>
+      <c r="F194" s="203"/>
+      <c r="G194" s="204"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="203">
+        <f>IF('_Datos'!$C195,'_Datos'!$O195,"")</f>
+      </c>
+      <c r="C195" s="204">
+        <f>IF('_Datos'!$C195,'_Datos'!$F195,"")</f>
+      </c>
+      <c r="D195" s="203">
+        <f>IF('_Datos'!$C195,IF('_Datos'!$N195=9999,"(Sin sprint)",'_Datos'!$N195),"")</f>
+      </c>
+      <c r="E195" s="203">
+        <f>IF('_Datos'!$C195,'_Datos'!$AE195,"")</f>
+      </c>
+      <c r="F195" s="203"/>
+      <c r="G195" s="204"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="203">
+        <f>IF('_Datos'!$C196,'_Datos'!$O196,"")</f>
+      </c>
+      <c r="C196" s="204">
+        <f>IF('_Datos'!$C196,'_Datos'!$F196,"")</f>
+      </c>
+      <c r="D196" s="203">
+        <f>IF('_Datos'!$C196,IF('_Datos'!$N196=9999,"(Sin sprint)",'_Datos'!$N196),"")</f>
+      </c>
+      <c r="E196" s="203">
+        <f>IF('_Datos'!$C196,'_Datos'!$AE196,"")</f>
+      </c>
+      <c r="F196" s="203"/>
+      <c r="G196" s="204"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="203">
+        <f>IF('_Datos'!$C197,'_Datos'!$O197,"")</f>
+      </c>
+      <c r="C197" s="204">
+        <f>IF('_Datos'!$C197,'_Datos'!$F197,"")</f>
+      </c>
+      <c r="D197" s="203">
+        <f>IF('_Datos'!$C197,IF('_Datos'!$N197=9999,"(Sin sprint)",'_Datos'!$N197),"")</f>
+      </c>
+      <c r="E197" s="203">
+        <f>IF('_Datos'!$C197,'_Datos'!$AE197,"")</f>
+      </c>
+      <c r="F197" s="203"/>
+      <c r="G197" s="204"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="203">
+        <f>IF('_Datos'!$C198,'_Datos'!$O198,"")</f>
+      </c>
+      <c r="C198" s="204">
+        <f>IF('_Datos'!$C198,'_Datos'!$F198,"")</f>
+      </c>
+      <c r="D198" s="203">
+        <f>IF('_Datos'!$C198,IF('_Datos'!$N198=9999,"(Sin sprint)",'_Datos'!$N198),"")</f>
+      </c>
+      <c r="E198" s="203">
+        <f>IF('_Datos'!$C198,'_Datos'!$AE198,"")</f>
+      </c>
+      <c r="F198" s="203"/>
+      <c r="G198" s="204"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="203">
+        <f>IF('_Datos'!$C199,'_Datos'!$O199,"")</f>
+      </c>
+      <c r="C199" s="204">
+        <f>IF('_Datos'!$C199,'_Datos'!$F199,"")</f>
+      </c>
+      <c r="D199" s="203">
+        <f>IF('_Datos'!$C199,IF('_Datos'!$N199=9999,"(Sin sprint)",'_Datos'!$N199),"")</f>
+      </c>
+      <c r="E199" s="203">
+        <f>IF('_Datos'!$C199,'_Datos'!$AE199,"")</f>
+      </c>
+      <c r="F199" s="203"/>
+      <c r="G199" s="204"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="203">
+        <f>IF('_Datos'!$C200,'_Datos'!$O200,"")</f>
+      </c>
+      <c r="C200" s="204">
+        <f>IF('_Datos'!$C200,'_Datos'!$F200,"")</f>
+      </c>
+      <c r="D200" s="203">
+        <f>IF('_Datos'!$C200,IF('_Datos'!$N200=9999,"(Sin sprint)",'_Datos'!$N200),"")</f>
+      </c>
+      <c r="E200" s="203">
+        <f>IF('_Datos'!$C200,'_Datos'!$AE200,"")</f>
+      </c>
+      <c r="F200" s="203"/>
+      <c r="G200" s="204"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F7:G200">
+    <cfRule type="expression" dxfId="27" priority="9">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:G200">
+    <cfRule type="expression" dxfId="21" priority="10">
+      <formula>$B7&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F7:F200">
+      <formula1>"0,1,2,3"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G7:G200">
+      <formula1>$I$5:$I$12</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
